--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -784,20 +784,44 @@
       <c r="M2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr"/>
-      <c r="Y2" s="4" t="inlineStr"/>
+      <c r="P2" s="4" t="n">
+        <v>2452.2</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>2427.68</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>2476.72</v>
+      </c>
+      <c r="S2" s="4" t="n">
+        <v>2329.59</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>2648.38</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>2820.03</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" s="4" t="inlineStr"/>
       <c r="AA2" s="4" t="inlineStr"/>
       <c r="AB2" s="4" t="inlineStr">
@@ -815,7 +839,9 @@
       <c r="AF2" s="4" t="inlineStr"/>
       <c r="AG2" s="4" t="inlineStr"/>
       <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ2" s="4" t="inlineStr"/>
       <c r="AK2" s="4" t="inlineStr"/>
       <c r="AL2" s="4" t="inlineStr"/>
@@ -824,7 +850,7 @@
       <c r="AO2" s="4" t="inlineStr"/>
       <c r="AP2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -882,20 +908,44 @@
       <c r="M3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="inlineStr"/>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="n">
+        <v>5196.6</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>5144.63</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>5248.57</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>4936.77</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>5612.33</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>5976.09</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" s="4" t="inlineStr"/>
       <c r="AA3" s="4" t="inlineStr"/>
       <c r="AB3" s="4" t="inlineStr">
@@ -913,7 +963,9 @@
       <c r="AF3" s="4" t="inlineStr"/>
       <c r="AG3" s="4" t="inlineStr"/>
       <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ3" s="4" t="inlineStr"/>
       <c r="AK3" s="4" t="inlineStr"/>
       <c r="AL3" s="4" t="inlineStr"/>
@@ -922,7 +974,7 @@
       <c r="AO3" s="4" t="inlineStr"/>
       <c r="AP3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -976,20 +1028,44 @@
       <c r="M4" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr"/>
-      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="n">
+        <v>133.14</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>131.81</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>134.47</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>143.79</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>153.11</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" s="4" t="inlineStr"/>
       <c r="AA4" s="4" t="inlineStr"/>
       <c r="AB4" s="4" t="inlineStr">
@@ -1007,7 +1083,9 @@
       <c r="AF4" s="4" t="inlineStr"/>
       <c r="AG4" s="4" t="inlineStr"/>
       <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ4" s="4" t="inlineStr"/>
       <c r="AK4" s="4" t="inlineStr"/>
       <c r="AL4" s="4" t="inlineStr"/>
@@ -1016,7 +1094,7 @@
       <c r="AO4" s="4" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1070,20 +1148,44 @@
       <c r="M5" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="n">
+        <v>5524</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>5468.76</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>5579.24</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>5247.8</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>5965.92</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>6352.6</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="4" t="inlineStr"/>
       <c r="AA5" s="4" t="inlineStr"/>
       <c r="AB5" s="4" t="inlineStr">
@@ -1101,7 +1203,9 @@
       <c r="AF5" s="4" t="inlineStr"/>
       <c r="AG5" s="4" t="inlineStr"/>
       <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ5" s="4" t="inlineStr"/>
       <c r="AK5" s="4" t="inlineStr"/>
       <c r="AL5" s="4" t="inlineStr"/>
@@ -1110,7 +1214,7 @@
       <c r="AO5" s="4" t="inlineStr"/>
       <c r="AP5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1168,20 +1272,44 @@
       <c r="M6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="n">
+        <v>1346.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1333.13</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>1360.07</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>1279.27</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>1454.33</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>1548.59</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z6" s="4" t="inlineStr"/>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr">
@@ -1199,7 +1327,9 @@
       <c r="AF6" s="4" t="inlineStr"/>
       <c r="AG6" s="4" t="inlineStr"/>
       <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ6" s="4" t="inlineStr"/>
       <c r="AK6" s="4" t="inlineStr"/>
       <c r="AL6" s="4" t="inlineStr"/>
@@ -1208,7 +1338,7 @@
       <c r="AO6" s="4" t="inlineStr"/>
       <c r="AP6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1262,20 +1392,44 @@
       <c r="M7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="n">
+        <v>11602</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>11485.98</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>11718.02</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>11021.9</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>12530.16</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>13342.3</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z7" s="4" t="inlineStr"/>
       <c r="AA7" s="4" t="inlineStr"/>
       <c r="AB7" s="4" t="inlineStr">
@@ -1293,7 +1447,9 @@
       <c r="AF7" s="4" t="inlineStr"/>
       <c r="AG7" s="4" t="inlineStr"/>
       <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ7" s="4" t="inlineStr"/>
       <c r="AK7" s="4" t="inlineStr"/>
       <c r="AL7" s="4" t="inlineStr"/>
@@ -1302,7 +1458,7 @@
       <c r="AO7" s="4" t="inlineStr"/>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1356,20 +1512,44 @@
       <c r="M8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="inlineStr"/>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1146.42</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>1169.58</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1250.64</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>1331.7</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z8" s="4" t="inlineStr"/>
       <c r="AA8" s="4" t="inlineStr"/>
       <c r="AB8" s="4" t="inlineStr">
@@ -1387,7 +1567,9 @@
       <c r="AF8" s="4" t="inlineStr"/>
       <c r="AG8" s="4" t="inlineStr"/>
       <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ8" s="4" t="inlineStr"/>
       <c r="AK8" s="4" t="inlineStr"/>
       <c r="AL8" s="4" t="inlineStr"/>
@@ -1396,7 +1578,7 @@
       <c r="AO8" s="4" t="inlineStr"/>
       <c r="AP8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1454,20 +1636,44 @@
       <c r="M9" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr"/>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>444.86</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>453.84</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>426.88</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="4" t="inlineStr"/>
       <c r="AA9" s="4" t="inlineStr"/>
       <c r="AB9" s="4" t="inlineStr">
@@ -1485,7 +1691,9 @@
       <c r="AF9" s="4" t="inlineStr"/>
       <c r="AG9" s="4" t="inlineStr"/>
       <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ9" s="4" t="inlineStr"/>
       <c r="AK9" s="4" t="inlineStr"/>
       <c r="AL9" s="4" t="inlineStr"/>
@@ -1494,7 +1702,7 @@
       <c r="AO9" s="4" t="inlineStr"/>
       <c r="AP9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1552,20 +1760,44 @@
       <c r="M10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>284.33</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr">
@@ -1583,7 +1815,9 @@
       <c r="AF10" s="4" t="inlineStr"/>
       <c r="AG10" s="4" t="inlineStr"/>
       <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ10" s="4" t="inlineStr"/>
       <c r="AK10" s="4" t="inlineStr"/>
       <c r="AL10" s="4" t="inlineStr"/>
@@ -1592,7 +1826,7 @@
       <c r="AO10" s="4" t="inlineStr"/>
       <c r="AP10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1646,20 +1880,44 @@
       <c r="M11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="inlineStr"/>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="n">
+        <v>10880</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>10771.2</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>10988.8</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>10336</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>11750.4</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>12512</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr">
@@ -1677,7 +1935,9 @@
       <c r="AF11" s="4" t="inlineStr"/>
       <c r="AG11" s="4" t="inlineStr"/>
       <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ11" s="4" t="inlineStr"/>
       <c r="AK11" s="4" t="inlineStr"/>
       <c r="AL11" s="4" t="inlineStr"/>
@@ -1686,7 +1946,7 @@
       <c r="AO11" s="4" t="inlineStr"/>
       <c r="AP11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1744,20 +2004,44 @@
       <c r="M12" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>943.02</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>962.08</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>904.92</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1028.75</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>1095.43</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr">
@@ -1775,7 +2059,9 @@
       <c r="AF12" s="4" t="inlineStr"/>
       <c r="AG12" s="4" t="inlineStr"/>
       <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ12" s="4" t="inlineStr"/>
       <c r="AK12" s="4" t="inlineStr"/>
       <c r="AL12" s="4" t="inlineStr"/>
@@ -1784,7 +2070,7 @@
       <c r="AO12" s="4" t="inlineStr"/>
       <c r="AP12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1842,20 +2128,44 @@
       <c r="M13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="inlineStr"/>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="n">
+        <v>431.4</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>427.09</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>435.71</v>
+      </c>
+      <c r="S13" s="4" t="n">
+        <v>409.83</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>465.91</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>496.11</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr">
@@ -1873,7 +2183,9 @@
       <c r="AF13" s="4" t="inlineStr"/>
       <c r="AG13" s="4" t="inlineStr"/>
       <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ13" s="4" t="inlineStr"/>
       <c r="AK13" s="4" t="inlineStr"/>
       <c r="AL13" s="4" t="inlineStr"/>
@@ -1882,7 +2194,7 @@
       <c r="AO13" s="4" t="inlineStr"/>
       <c r="AP13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -1936,20 +2248,44 @@
       <c r="M14" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="inlineStr"/>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="n">
+        <v>2157.8</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>2136.22</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>2179.38</v>
+      </c>
+      <c r="S14" s="4" t="n">
+        <v>2049.91</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>2330.42</v>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>2481.47</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr">
@@ -1967,7 +2303,9 @@
       <c r="AF14" s="4" t="inlineStr"/>
       <c r="AG14" s="4" t="inlineStr"/>
       <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ14" s="4" t="inlineStr"/>
       <c r="AK14" s="4" t="inlineStr"/>
       <c r="AL14" s="4" t="inlineStr"/>
@@ -1976,7 +2314,7 @@
       <c r="AO14" s="4" t="inlineStr"/>
       <c r="AP14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2034,20 +2372,44 @@
       <c r="M15" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="inlineStr"/>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>541.9299999999999</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>552.87</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>591.1900000000001</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>629.51</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr">
@@ -2065,7 +2427,9 @@
       <c r="AF15" s="4" t="inlineStr"/>
       <c r="AG15" s="4" t="inlineStr"/>
       <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ15" s="4" t="inlineStr"/>
       <c r="AK15" s="4" t="inlineStr"/>
       <c r="AL15" s="4" t="inlineStr"/>
@@ -2074,7 +2438,7 @@
       <c r="AO15" s="4" t="inlineStr"/>
       <c r="AP15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2128,20 +2492,44 @@
       <c r="M16" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="inlineStr"/>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="n">
+        <v>1363</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1349.37</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>1376.63</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>1294.85</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>1472.04</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>1567.45</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
       <c r="AB16" s="4" t="inlineStr">
@@ -2159,7 +2547,9 @@
       <c r="AF16" s="4" t="inlineStr"/>
       <c r="AG16" s="4" t="inlineStr"/>
       <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="AJ16" s="4" t="inlineStr"/>
       <c r="AK16" s="4" t="inlineStr"/>
       <c r="AL16" s="4" t="inlineStr"/>
@@ -2168,7 +2558,7 @@
       <c r="AO16" s="4" t="inlineStr"/>
       <c r="AP16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2222,13 +2612,23 @@
       <c r="M17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1424.12</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>1452.88</v>
+      </c>
       <c r="S17" s="4" t="n">
         <v>1366.575</v>
       </c>
@@ -2247,7 +2647,9 @@
       <c r="X17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
       <c r="AB17" s="4" t="inlineStr">
@@ -2276,7 +2678,7 @@
       <c r="AO17" s="4" t="inlineStr"/>
       <c r="AP17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2330,13 +2732,23 @@
       <c r="M18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
+      <c r="P18" s="4" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1994.65</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>2034.95</v>
+      </c>
       <c r="S18" s="4" t="n">
         <v>1914.06</v>
       </c>
@@ -2355,7 +2767,9 @@
       <c r="X18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
       <c r="AB18" s="4" t="inlineStr">
@@ -2384,7 +2798,7 @@
       <c r="AO18" s="4" t="inlineStr"/>
       <c r="AP18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2438,13 +2852,23 @@
       <c r="M19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="n">
+        <v>2417</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>2441.17</v>
+      </c>
       <c r="S19" s="4" t="n">
         <v>2296.15</v>
       </c>
@@ -2463,7 +2887,9 @@
       <c r="X19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
       <c r="AB19" s="4" t="inlineStr">
@@ -2492,7 +2918,7 @@
       <c r="AO19" s="4" t="inlineStr"/>
       <c r="AP19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2546,13 +2972,23 @@
       <c r="M20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="P20" s="4" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1609.24</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>1641.76</v>
+      </c>
       <c r="S20" s="4" t="n">
         <v>1544.225</v>
       </c>
@@ -2571,7 +3007,9 @@
       <c r="X20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
       <c r="AB20" s="4" t="inlineStr">
@@ -2600,7 +3038,7 @@
       <c r="AO20" s="4" t="inlineStr"/>
       <c r="AP20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2654,13 +3092,23 @@
       <c r="M21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>349.26</v>
+      </c>
       <c r="S21" s="4" t="n">
         <v>328.51</v>
       </c>
@@ -2679,7 +3127,9 @@
       <c r="X21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
       <c r="AB21" s="4" t="inlineStr">
@@ -2708,7 +3158,7 @@
       <c r="AO21" s="4" t="inlineStr"/>
       <c r="AP21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2762,13 +3212,23 @@
       <c r="M22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>393.19</v>
+      </c>
       <c r="S22" s="4" t="n">
         <v>369.835</v>
       </c>
@@ -2787,7 +3247,9 @@
       <c r="X22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr">
@@ -2816,7 +3278,7 @@
       <c r="AO22" s="4" t="inlineStr"/>
       <c r="AP22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2870,13 +3332,23 @@
       <c r="M23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>288.76</v>
+      </c>
       <c r="S23" s="4" t="n">
         <v>271.605</v>
       </c>
@@ -2895,7 +3367,9 @@
       <c r="X23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y23" s="4" t="inlineStr"/>
+      <c r="Y23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr">
@@ -2924,7 +3398,7 @@
       <c r="AO23" s="4" t="inlineStr"/>
       <c r="AP23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -2978,13 +3452,23 @@
       <c r="M24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>489.46</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>499.34</v>
+      </c>
       <c r="S24" s="4" t="n">
         <v>469.6799999999999</v>
       </c>
@@ -3003,7 +3487,9 @@
       <c r="X24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y24" s="4" t="inlineStr"/>
+      <c r="Y24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr">
@@ -3032,7 +3518,7 @@
       <c r="AO24" s="4" t="inlineStr"/>
       <c r="AP24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3086,13 +3572,23 @@
       <c r="M25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>392.59</v>
+      </c>
       <c r="S25" s="4" t="n">
         <v>369.265</v>
       </c>
@@ -3111,7 +3607,9 @@
       <c r="X25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" s="4" t="inlineStr"/>
+      <c r="Y25" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr">
@@ -3140,7 +3638,7 @@
       <c r="AO25" s="4" t="inlineStr"/>
       <c r="AP25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3194,13 +3692,23 @@
       <c r="M26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>415.41</v>
+      </c>
       <c r="S26" s="4" t="n">
         <v>390.735</v>
       </c>
@@ -3219,7 +3727,9 @@
       <c r="X26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y26" s="4" t="inlineStr"/>
+      <c r="Y26" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr">
@@ -3248,7 +3758,7 @@
       <c r="AO26" s="4" t="inlineStr"/>
       <c r="AP26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3298,13 +3808,23 @@
       <c r="M27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
       <c r="O27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr"/>
-      <c r="R27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="n">
+        <v>5406</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>5460.06</v>
+      </c>
       <c r="S27" s="4" t="n">
         <v>5135.7</v>
       </c>
@@ -3323,7 +3843,9 @@
       <c r="X27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr">
@@ -3352,7 +3874,7 @@
       <c r="AO27" s="4" t="inlineStr"/>
       <c r="AP27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3482,7 +4004,7 @@
       <c r="AO28" s="4" t="inlineStr"/>
       <c r="AP28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3551,14 +4073,30 @@
       <c r="P29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="Q29" s="4" t="inlineStr"/>
-      <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="inlineStr"/>
-      <c r="W29" s="4" t="inlineStr"/>
-      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="S29" s="4" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>412.34</v>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y29" s="4" t="n">
         <v>0</v>
       </c>
@@ -3594,7 +4132,7 @@
       <c r="AO29" s="4" t="inlineStr"/>
       <c r="AP29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3663,14 +4201,30 @@
       <c r="P30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="Q30" s="4" t="inlineStr"/>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="inlineStr"/>
-      <c r="W30" s="4" t="inlineStr"/>
-      <c r="X30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="n">
+        <v>200.78</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>204.84</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>192.67</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>219.03</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>233.23</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y30" s="4" t="n">
         <v>0</v>
       </c>
@@ -3706,7 +4260,7 @@
       <c r="AO30" s="4" t="inlineStr"/>
       <c r="AP30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3775,14 +4329,30 @@
       <c r="P31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="Q31" s="4" t="inlineStr"/>
-      <c r="R31" s="4" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="inlineStr"/>
-      <c r="W31" s="4" t="inlineStr"/>
-      <c r="X31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="n">
+        <v>337.69</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y31" s="4" t="n">
         <v>0</v>
       </c>
@@ -3818,7 +4388,7 @@
       <c r="AO31" s="4" t="inlineStr"/>
       <c r="AP31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3887,14 +4457,30 @@
       <c r="P32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="inlineStr"/>
-      <c r="W32" s="4" t="inlineStr"/>
-      <c r="X32" s="4" t="inlineStr"/>
+      <c r="Q32" s="4" t="n">
+        <v>222.77</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>243.02</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>258.77</v>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y32" s="4" t="n">
         <v>0</v>
       </c>
@@ -3930,7 +4516,7 @@
       <c r="AO32" s="4" t="inlineStr"/>
       <c r="AP32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -3999,14 +4585,30 @@
       <c r="P33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="Q33" s="4" t="inlineStr"/>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="inlineStr"/>
-      <c r="W33" s="4" t="inlineStr"/>
-      <c r="X33" s="4" t="inlineStr"/>
+      <c r="Q33" s="4" t="n">
+        <v>1054.57</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>1075.87</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>1011.96</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>1150.44</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>1225</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y33" s="4" t="n">
         <v>0</v>
       </c>
@@ -4042,7 +4644,7 @@
       <c r="AO33" s="4" t="inlineStr"/>
       <c r="AP33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4111,14 +4713,30 @@
       <c r="P34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="Q34" s="4" t="inlineStr"/>
-      <c r="R34" s="4" t="inlineStr"/>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="inlineStr"/>
-      <c r="W34" s="4" t="inlineStr"/>
-      <c r="X34" s="4" t="inlineStr"/>
+      <c r="Q34" s="4" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>337.08</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>317.05</v>
+      </c>
+      <c r="T34" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" s="4" t="n">
+        <v>383.8</v>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y34" s="4" t="n">
         <v>0</v>
       </c>
@@ -4154,7 +4772,7 @@
       <c r="AO34" s="4" t="inlineStr"/>
       <c r="AP34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4223,14 +4841,30 @@
       <c r="P35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="Q35" s="4" t="inlineStr"/>
-      <c r="R35" s="4" t="inlineStr"/>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="inlineStr"/>
-      <c r="W35" s="4" t="inlineStr"/>
-      <c r="X35" s="4" t="inlineStr"/>
+      <c r="Q35" s="4" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>397.76</v>
+      </c>
+      <c r="S35" s="4" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="T35" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>425.33</v>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W35" s="4" t="n">
+        <v>452.89</v>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y35" s="4" t="n">
         <v>0</v>
       </c>
@@ -4266,7 +4900,7 @@
       <c r="AO35" s="4" t="inlineStr"/>
       <c r="AP35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4335,14 +4969,30 @@
       <c r="P36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="Q36" s="4" t="inlineStr"/>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr"/>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="inlineStr"/>
-      <c r="W36" s="4" t="inlineStr"/>
-      <c r="X36" s="4" t="inlineStr"/>
+      <c r="Q36" s="4" t="n">
+        <v>80.73999999999999</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="S36" s="4" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>93.79000000000001</v>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y36" s="4" t="n">
         <v>0</v>
       </c>
@@ -4378,7 +5028,7 @@
       <c r="AO36" s="4" t="inlineStr"/>
       <c r="AP36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4447,14 +5097,30 @@
       <c r="P37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="Q37" s="4" t="inlineStr"/>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="inlineStr"/>
-      <c r="W37" s="4" t="inlineStr"/>
-      <c r="X37" s="4" t="inlineStr"/>
+      <c r="Q37" s="4" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>161.44</v>
+      </c>
+      <c r="S37" s="4" t="n">
+        <v>151.85</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U37" s="4" t="n">
+        <v>172.63</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" s="4" t="n">
+        <v>183.82</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y37" s="4" t="n">
         <v>0</v>
       </c>
@@ -4490,7 +5156,7 @@
       <c r="AO37" s="4" t="inlineStr"/>
       <c r="AP37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4559,14 +5225,30 @@
       <c r="P38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="Q38" s="4" t="inlineStr"/>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr"/>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="inlineStr"/>
-      <c r="W38" s="4" t="inlineStr"/>
-      <c r="X38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="n">
+        <v>94.09</v>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="S38" s="4" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="T38" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>102.64</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y38" s="4" t="n">
         <v>0</v>
       </c>
@@ -4602,7 +5284,7 @@
       <c r="AO38" s="4" t="inlineStr"/>
       <c r="AP38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4671,14 +5353,30 @@
       <c r="P39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="Q39" s="4" t="inlineStr"/>
-      <c r="R39" s="4" t="inlineStr"/>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="inlineStr"/>
-      <c r="W39" s="4" t="inlineStr"/>
-      <c r="X39" s="4" t="inlineStr"/>
+      <c r="Q39" s="4" t="n">
+        <v>211.89</v>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>216.17</v>
+      </c>
+      <c r="S39" s="4" t="n">
+        <v>203.33</v>
+      </c>
+      <c r="T39" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U39" s="4" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W39" s="4" t="n">
+        <v>246.13</v>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y39" s="4" t="n">
         <v>0</v>
       </c>
@@ -4714,7 +5412,7 @@
       <c r="AO39" s="4" t="inlineStr"/>
       <c r="AP39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4783,14 +5481,30 @@
       <c r="P40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="Q40" s="4" t="inlineStr"/>
-      <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="inlineStr"/>
-      <c r="W40" s="4" t="inlineStr"/>
-      <c r="X40" s="4" t="inlineStr"/>
+      <c r="Q40" s="4" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="S40" s="4" t="n">
+        <v>321.93</v>
+      </c>
+      <c r="T40" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U40" s="4" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" s="4" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y40" s="4" t="n">
         <v>0</v>
       </c>
@@ -4826,7 +5540,7 @@
       <c r="AO40" s="4" t="inlineStr"/>
       <c r="AP40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -4895,14 +5609,30 @@
       <c r="P41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q41" s="4" t="inlineStr"/>
-      <c r="R41" s="4" t="inlineStr"/>
-      <c r="S41" s="4" t="inlineStr"/>
-      <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="inlineStr"/>
-      <c r="W41" s="4" t="inlineStr"/>
-      <c r="X41" s="4" t="inlineStr"/>
+      <c r="Q41" s="4" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="S41" s="4" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="T41" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W41" s="4" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y41" s="4" t="n">
         <v>0</v>
       </c>
@@ -4938,7 +5668,7 @@
       <c r="AO41" s="4" t="inlineStr"/>
       <c r="AP41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>
@@ -5007,14 +5737,30 @@
       <c r="P42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="inlineStr"/>
-      <c r="W42" s="4" t="inlineStr"/>
-      <c r="X42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="n">
+        <v>265.03</v>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>270.39</v>
+      </c>
+      <c r="S42" s="4" t="n">
+        <v>254.32</v>
+      </c>
+      <c r="T42" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>289.13</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="Y42" s="4" t="n">
         <v>0</v>
       </c>
@@ -5050,7 +5796,7 @@
       <c r="AO42" s="4" t="inlineStr"/>
       <c r="AP42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 14:05</t>
+          <t>2026-08-01 14:08</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AP$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AG$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP42"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -502,20 +502,11 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="32" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="17" customWidth="1" min="33" max="33"/>
-    <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="17" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="21" customWidth="1" min="37" max="37"/>
-    <col width="12" customWidth="1" min="38" max="38"/>
-    <col width="15" customWidth="1" min="39" max="39"/>
-    <col width="17" customWidth="1" min="40" max="40"/>
-    <col width="18" customWidth="1" min="41" max="41"/>
-    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="32" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -661,70 +652,25 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Exit Triggers Hit</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Risk Flags</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Sector Exposure %</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Portfolio Weight %</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Band Low %</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence Band High %</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Correlation</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Win Rate %</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Median Ret %</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Hist Avg Hold (d)</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -829,28 +775,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD2" s="4" t="inlineStr"/>
       <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr"/>
-      <c r="AP2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -953,28 +890,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD3" s="4" t="inlineStr"/>
       <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1073,28 +1001,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AD4" s="4" t="inlineStr"/>
       <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1193,28 +1112,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
+      <c r="AD5" s="4" t="inlineStr"/>
       <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1317,28 +1227,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
+      <c r="AD6" s="4" t="inlineStr"/>
       <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1437,28 +1338,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
+      <c r="AD7" s="4" t="inlineStr"/>
       <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1557,28 +1449,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
+      <c r="AD8" s="4" t="inlineStr"/>
       <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1681,28 +1564,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
+      <c r="AD9" s="4" t="inlineStr"/>
       <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="inlineStr"/>
-      <c r="AG9" s="4" t="inlineStr"/>
-      <c r="AH9" s="4" t="inlineStr"/>
-      <c r="AI9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
-      <c r="AK9" s="4" t="inlineStr"/>
-      <c r="AL9" s="4" t="inlineStr"/>
-      <c r="AM9" s="4" t="inlineStr"/>
-      <c r="AN9" s="4" t="inlineStr"/>
-      <c r="AO9" s="4" t="inlineStr"/>
-      <c r="AP9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1805,28 +1679,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
+      <c r="AD10" s="4" t="inlineStr"/>
       <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -1925,28 +1790,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
+      <c r="AD11" s="4" t="inlineStr"/>
       <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2049,28 +1905,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD12" s="4" t="inlineStr"/>
       <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2173,28 +2020,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AC13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD13" s="4" t="inlineStr"/>
       <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2293,28 +2131,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AC14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD14" s="4" t="inlineStr"/>
       <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
-      <c r="AP14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2417,28 +2246,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AC15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD15" s="4" t="inlineStr"/>
       <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2537,28 +2357,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD16" s="4" t="inlineStr"/>
       <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2658,27 +2469,18 @@
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr"/>
-      <c r="AD17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="n">
+      <c r="AF17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2778,27 +2580,18 @@
         </is>
       </c>
       <c r="AC18" s="4" t="inlineStr"/>
-      <c r="AD18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="n">
+      <c r="AF18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -2898,27 +2691,18 @@
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
       <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3018,27 +2802,18 @@
         </is>
       </c>
       <c r="AC20" s="4" t="inlineStr"/>
-      <c r="AD20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
       <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>Chemicals</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="inlineStr"/>
-      <c r="AH20" s="4" t="inlineStr"/>
-      <c r="AI20" s="4" t="n">
+      <c r="AF20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
-      <c r="AK20" s="4" t="inlineStr"/>
-      <c r="AL20" s="4" t="inlineStr"/>
-      <c r="AM20" s="4" t="inlineStr"/>
-      <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
-      <c r="AP20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3138,27 +2913,18 @@
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr"/>
-      <c r="AD21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
       <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3258,27 +3024,18 @@
         </is>
       </c>
       <c r="AC22" s="4" t="inlineStr"/>
-      <c r="AD22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
-      <c r="AP22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3378,27 +3135,18 @@
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr"/>
-      <c r="AD23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
       <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="AG23" s="4" t="inlineStr"/>
-      <c r="AH23" s="4" t="inlineStr"/>
-      <c r="AI23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
-      <c r="AK23" s="4" t="inlineStr"/>
-      <c r="AL23" s="4" t="inlineStr"/>
-      <c r="AM23" s="4" t="inlineStr"/>
-      <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="inlineStr"/>
-      <c r="AP23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3498,27 +3246,18 @@
         </is>
       </c>
       <c r="AC24" s="4" t="inlineStr"/>
-      <c r="AD24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
       <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr"/>
-      <c r="AI24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3618,27 +3357,18 @@
         </is>
       </c>
       <c r="AC25" s="4" t="inlineStr"/>
-      <c r="AD25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr"/>
-      <c r="AI25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3738,27 +3468,18 @@
         </is>
       </c>
       <c r="AC26" s="4" t="inlineStr"/>
-      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr"/>
-      <c r="AH26" s="4" t="inlineStr"/>
-      <c r="AI26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="inlineStr"/>
-      <c r="AM26" s="4" t="inlineStr"/>
-      <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="inlineStr"/>
-      <c r="AP26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3854,27 +3575,18 @@
         </is>
       </c>
       <c r="AC27" s="4" t="inlineStr"/>
-      <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AG27" s="4" t="inlineStr"/>
-      <c r="AH27" s="4" t="inlineStr"/>
-      <c r="AI27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
-      <c r="AK27" s="4" t="inlineStr"/>
-      <c r="AL27" s="4" t="inlineStr"/>
-      <c r="AM27" s="4" t="inlineStr"/>
-      <c r="AN27" s="4" t="inlineStr"/>
-      <c r="AO27" s="4" t="inlineStr"/>
-      <c r="AP27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -3981,30 +3693,21 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AC28" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr"/>
-      <c r="AG28" s="4" t="inlineStr"/>
-      <c r="AH28" s="4" t="n">
+      <c r="AD28" s="4" t="inlineStr"/>
+      <c r="AE28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AI28" s="4" t="n">
+      <c r="AF28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
-      <c r="AK28" s="4" t="inlineStr"/>
-      <c r="AL28" s="4" t="inlineStr"/>
-      <c r="AM28" s="4" t="inlineStr"/>
-      <c r="AN28" s="4" t="inlineStr"/>
-      <c r="AO28" s="4" t="inlineStr"/>
-      <c r="AP28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4111,28 +3814,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AC29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
+      <c r="AD29" s="4" t="inlineStr"/>
       <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="inlineStr"/>
-      <c r="AG29" s="4" t="inlineStr"/>
-      <c r="AH29" s="4" t="inlineStr"/>
-      <c r="AI29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
-      <c r="AK29" s="4" t="inlineStr"/>
-      <c r="AL29" s="4" t="inlineStr"/>
-      <c r="AM29" s="4" t="inlineStr"/>
-      <c r="AN29" s="4" t="inlineStr"/>
-      <c r="AO29" s="4" t="inlineStr"/>
-      <c r="AP29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AF29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4239,28 +3933,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AC30" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
+      <c r="AD30" s="4" t="inlineStr"/>
       <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" s="4" t="inlineStr"/>
-      <c r="AG30" s="4" t="inlineStr"/>
-      <c r="AH30" s="4" t="inlineStr"/>
-      <c r="AI30" s="4" t="n">
+      <c r="AF30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
-      <c r="AK30" s="4" t="inlineStr"/>
-      <c r="AL30" s="4" t="inlineStr"/>
-      <c r="AM30" s="4" t="inlineStr"/>
-      <c r="AN30" s="4" t="inlineStr"/>
-      <c r="AO30" s="4" t="inlineStr"/>
-      <c r="AP30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4367,28 +4052,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC31" s="4" t="inlineStr"/>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AC31" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
+      <c r="AD31" s="4" t="inlineStr"/>
       <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="4" t="inlineStr"/>
-      <c r="AG31" s="4" t="inlineStr"/>
-      <c r="AH31" s="4" t="inlineStr"/>
-      <c r="AI31" s="4" t="n">
+      <c r="AF31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
-      <c r="AK31" s="4" t="inlineStr"/>
-      <c r="AL31" s="4" t="inlineStr"/>
-      <c r="AM31" s="4" t="inlineStr"/>
-      <c r="AN31" s="4" t="inlineStr"/>
-      <c r="AO31" s="4" t="inlineStr"/>
-      <c r="AP31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4495,28 +4171,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AC32" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
+      <c r="AD32" s="4" t="inlineStr"/>
       <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="inlineStr"/>
-      <c r="AI32" s="4" t="n">
+      <c r="AF32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
-      <c r="AK32" s="4" t="inlineStr"/>
-      <c r="AL32" s="4" t="inlineStr"/>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr"/>
-      <c r="AP32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4623,28 +4290,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AC33" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
+      <c r="AD33" s="4" t="inlineStr"/>
       <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="inlineStr"/>
-      <c r="AG33" s="4" t="inlineStr"/>
-      <c r="AH33" s="4" t="inlineStr"/>
-      <c r="AI33" s="4" t="n">
+      <c r="AF33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
-      <c r="AK33" s="4" t="inlineStr"/>
-      <c r="AL33" s="4" t="inlineStr"/>
-      <c r="AM33" s="4" t="inlineStr"/>
-      <c r="AN33" s="4" t="inlineStr"/>
-      <c r="AO33" s="4" t="inlineStr"/>
-      <c r="AP33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4751,28 +4409,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AC34" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
+      <c r="AD34" s="4" t="inlineStr"/>
       <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="inlineStr"/>
-      <c r="AG34" s="4" t="inlineStr"/>
-      <c r="AH34" s="4" t="inlineStr"/>
-      <c r="AI34" s="4" t="n">
+      <c r="AF34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
-      <c r="AK34" s="4" t="inlineStr"/>
-      <c r="AL34" s="4" t="inlineStr"/>
-      <c r="AM34" s="4" t="inlineStr"/>
-      <c r="AN34" s="4" t="inlineStr"/>
-      <c r="AO34" s="4" t="inlineStr"/>
-      <c r="AP34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -4879,28 +4528,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AC35" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
+      <c r="AD35" s="4" t="inlineStr"/>
       <c r="AE35" s="4" t="inlineStr"/>
-      <c r="AF35" s="4" t="inlineStr"/>
-      <c r="AG35" s="4" t="inlineStr"/>
-      <c r="AH35" s="4" t="inlineStr"/>
-      <c r="AI35" s="4" t="n">
+      <c r="AF35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AJ35" s="4" t="inlineStr"/>
-      <c r="AK35" s="4" t="inlineStr"/>
-      <c r="AL35" s="4" t="inlineStr"/>
-      <c r="AM35" s="4" t="inlineStr"/>
-      <c r="AN35" s="4" t="inlineStr"/>
-      <c r="AO35" s="4" t="inlineStr"/>
-      <c r="AP35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5007,28 +4647,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
-      <c r="AD36" s="4" t="inlineStr">
+      <c r="AC36" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
+      <c r="AD36" s="4" t="inlineStr"/>
       <c r="AE36" s="4" t="inlineStr"/>
-      <c r="AF36" s="4" t="inlineStr"/>
-      <c r="AG36" s="4" t="inlineStr"/>
-      <c r="AH36" s="4" t="inlineStr"/>
-      <c r="AI36" s="4" t="n">
+      <c r="AF36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AJ36" s="4" t="inlineStr"/>
-      <c r="AK36" s="4" t="inlineStr"/>
-      <c r="AL36" s="4" t="inlineStr"/>
-      <c r="AM36" s="4" t="inlineStr"/>
-      <c r="AN36" s="4" t="inlineStr"/>
-      <c r="AO36" s="4" t="inlineStr"/>
-      <c r="AP36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5135,28 +4766,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AC37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
+      <c r="AD37" s="4" t="inlineStr"/>
       <c r="AE37" s="4" t="inlineStr"/>
-      <c r="AF37" s="4" t="inlineStr"/>
-      <c r="AG37" s="4" t="inlineStr"/>
-      <c r="AH37" s="4" t="inlineStr"/>
-      <c r="AI37" s="4" t="n">
+      <c r="AF37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
-      <c r="AK37" s="4" t="inlineStr"/>
-      <c r="AL37" s="4" t="inlineStr"/>
-      <c r="AM37" s="4" t="inlineStr"/>
-      <c r="AN37" s="4" t="inlineStr"/>
-      <c r="AO37" s="4" t="inlineStr"/>
-      <c r="AP37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5263,28 +4885,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
-      <c r="AD38" s="4" t="inlineStr">
+      <c r="AC38" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD38" s="4" t="inlineStr"/>
       <c r="AE38" s="4" t="inlineStr"/>
-      <c r="AF38" s="4" t="inlineStr"/>
-      <c r="AG38" s="4" t="inlineStr"/>
-      <c r="AH38" s="4" t="inlineStr"/>
-      <c r="AI38" s="4" t="n">
+      <c r="AF38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AJ38" s="4" t="inlineStr"/>
-      <c r="AK38" s="4" t="inlineStr"/>
-      <c r="AL38" s="4" t="inlineStr"/>
-      <c r="AM38" s="4" t="inlineStr"/>
-      <c r="AN38" s="4" t="inlineStr"/>
-      <c r="AO38" s="4" t="inlineStr"/>
-      <c r="AP38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5391,28 +5004,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
-      <c r="AD39" s="4" t="inlineStr">
+      <c r="AC39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
+      <c r="AD39" s="4" t="inlineStr"/>
       <c r="AE39" s="4" t="inlineStr"/>
-      <c r="AF39" s="4" t="inlineStr"/>
-      <c r="AG39" s="4" t="inlineStr"/>
-      <c r="AH39" s="4" t="inlineStr"/>
-      <c r="AI39" s="4" t="n">
+      <c r="AF39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
-      <c r="AK39" s="4" t="inlineStr"/>
-      <c r="AL39" s="4" t="inlineStr"/>
-      <c r="AM39" s="4" t="inlineStr"/>
-      <c r="AN39" s="4" t="inlineStr"/>
-      <c r="AO39" s="4" t="inlineStr"/>
-      <c r="AP39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5519,28 +5123,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC40" s="4" t="inlineStr"/>
-      <c r="AD40" s="4" t="inlineStr">
+      <c r="AC40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD40" s="4" t="inlineStr"/>
       <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="inlineStr"/>
-      <c r="AG40" s="4" t="inlineStr"/>
-      <c r="AH40" s="4" t="inlineStr"/>
-      <c r="AI40" s="4" t="n">
+      <c r="AF40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AJ40" s="4" t="inlineStr"/>
-      <c r="AK40" s="4" t="inlineStr"/>
-      <c r="AL40" s="4" t="inlineStr"/>
-      <c r="AM40" s="4" t="inlineStr"/>
-      <c r="AN40" s="4" t="inlineStr"/>
-      <c r="AO40" s="4" t="inlineStr"/>
-      <c r="AP40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5647,28 +5242,19 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="inlineStr"/>
-      <c r="AD41" s="4" t="inlineStr">
+      <c r="AC41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD41" s="4" t="inlineStr"/>
       <c r="AE41" s="4" t="inlineStr"/>
-      <c r="AF41" s="4" t="inlineStr"/>
-      <c r="AG41" s="4" t="inlineStr"/>
-      <c r="AH41" s="4" t="inlineStr"/>
-      <c r="AI41" s="4" t="n">
+      <c r="AF41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AJ41" s="4" t="inlineStr"/>
-      <c r="AK41" s="4" t="inlineStr"/>
-      <c r="AL41" s="4" t="inlineStr"/>
-      <c r="AM41" s="4" t="inlineStr"/>
-      <c r="AN41" s="4" t="inlineStr"/>
-      <c r="AO41" s="4" t="inlineStr"/>
-      <c r="AP41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
@@ -5775,33 +5361,24 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="inlineStr"/>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AC42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
+      <c r="AD42" s="4" t="inlineStr"/>
       <c r="AE42" s="4" t="inlineStr"/>
-      <c r="AF42" s="4" t="inlineStr"/>
-      <c r="AG42" s="4" t="inlineStr"/>
-      <c r="AH42" s="4" t="inlineStr"/>
-      <c r="AI42" s="4" t="n">
+      <c r="AF42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AJ42" s="4" t="inlineStr"/>
-      <c r="AK42" s="4" t="inlineStr"/>
-      <c r="AL42" s="4" t="inlineStr"/>
-      <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="inlineStr"/>
-      <c r="AO42" s="4" t="inlineStr"/>
-      <c r="AP42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:08</t>
+      <c r="AG42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP42"/>
+  <autoFilter ref="A1:AG42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AG$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AJ$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,8 +66,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
-        <bgColor rgb="00FFD966"/>
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -480,33 +480,36 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="32" customWidth="1" min="29" max="29"/>
-    <col width="20" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="17" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="17" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -542,135 +545,150 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Exit P&amp;L %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Today Move %</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Lifecycle State</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -707,87 +725,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>2452.2</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>2427.68</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>2476.72</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>2329.59</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="W2" s="4" t="n">
         <v>2648.38</v>
       </c>
-      <c r="V2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W2" s="4" t="n">
+      <c r="X2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y2" s="4" t="n">
         <v>2820.03</v>
       </c>
-      <c r="X2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="4" t="inlineStr"/>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="AB2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="inlineStr"/>
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr"/>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG2" s="4" t="inlineStr"/>
+      <c r="AH2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -822,87 +845,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>40.6</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>5196.6</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>5144.63</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>5248.57</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>4936.77</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="W3" s="4" t="n">
         <v>5612.33</v>
       </c>
-      <c r="V3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" s="4" t="n">
         <v>5976.09</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4" t="inlineStr"/>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="inlineStr"/>
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr"/>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG3" s="4" t="inlineStr"/>
+      <c r="AH3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -933,87 +961,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>39.3</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>24.3</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>133.14</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>131.81</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>134.47</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>126.48</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="W4" s="4" t="n">
         <v>143.79</v>
       </c>
-      <c r="V4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W4" s="4" t="n">
+      <c r="X4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y4" s="4" t="n">
         <v>153.11</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="4" t="inlineStr"/>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="inlineStr"/>
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>Quality · Momentum · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr"/>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG4" s="4" t="inlineStr"/>
+      <c r="AH4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1044,87 +1077,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>5524</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>5468.76</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="T5" s="4" t="n">
         <v>5579.24</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>5247.8</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="W5" s="4" t="n">
         <v>5965.92</v>
       </c>
-      <c r="V5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W5" s="4" t="n">
+      <c r="X5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="4" t="n">
         <v>6352.6</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="4" t="inlineStr"/>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="inlineStr"/>
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>Trend · Growth · Value</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr"/>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1159,87 +1197,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>43.1</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="O6" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>1346.6</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>1333.13</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="T6" s="4" t="n">
         <v>1360.07</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>1279.27</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="V6" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="W6" s="4" t="n">
         <v>1454.33</v>
       </c>
-      <c r="V6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" s="4" t="n">
+      <c r="X6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" s="4" t="n">
         <v>1548.59</v>
       </c>
-      <c r="X6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="4" t="inlineStr"/>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="AB6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="inlineStr"/>
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr"/>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1270,87 +1313,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>46.4</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>11602</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>11485.98</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>11718.02</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>11021.9</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="W7" s="4" t="n">
         <v>12530.16</v>
       </c>
-      <c r="V7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W7" s="4" t="n">
+      <c r="X7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" s="4" t="n">
         <v>13342.3</v>
       </c>
-      <c r="X7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="inlineStr"/>
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr"/>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1381,87 +1429,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>40.7</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>1158</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>1146.42</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>1169.58</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>1100.1</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="W8" s="4" t="n">
         <v>1250.64</v>
       </c>
-      <c r="V8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W8" s="4" t="n">
+      <c r="X8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="4" t="n">
         <v>1331.7</v>
       </c>
-      <c r="X8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="4" t="inlineStr"/>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="inlineStr"/>
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr"/>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1496,87 +1549,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>449.35</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>444.86</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>453.84</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>426.88</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="W9" s="4" t="n">
         <v>485.3</v>
       </c>
-      <c r="V9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W9" s="4" t="n">
+      <c r="X9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y9" s="4" t="n">
         <v>516.75</v>
       </c>
-      <c r="X9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="AB9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="inlineStr"/>
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>Value · Mean Reversion · Growth</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr"/>
-      <c r="AE9" s="4" t="inlineStr"/>
-      <c r="AF9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1611,87 +1669,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>21.6</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>287.2</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>284.33</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>290.07</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>272.84</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="W10" s="4" t="n">
         <v>310.18</v>
       </c>
-      <c r="V10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W10" s="4" t="n">
+      <c r="X10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="4" t="n">
         <v>330.28</v>
       </c>
-      <c r="X10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr">
+      <c r="AA10" s="4" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="inlineStr"/>
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Value</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr"/>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG10" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG10" s="4" t="inlineStr"/>
+      <c r="AH10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1722,87 +1785,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>10771.2</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>10988.8</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>10336</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="W11" s="4" t="n">
         <v>11750.4</v>
       </c>
-      <c r="V11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" s="4" t="n">
+      <c r="X11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="4" t="n">
         <v>12512</v>
       </c>
-      <c r="X11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="4" t="inlineStr"/>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="inlineStr"/>
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>Value · Quality · Trend</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1837,87 +1905,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>-26.6</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>952.55</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>943.02</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>962.08</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>904.92</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="W12" s="4" t="n">
         <v>1028.75</v>
       </c>
-      <c r="V12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" s="4" t="n">
+      <c r="X12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="4" t="n">
         <v>1095.43</v>
       </c>
-      <c r="X12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="4" t="inlineStr"/>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AB12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="inlineStr"/>
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr"/>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -1952,87 +2025,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>-28.1</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="O13" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>431.4</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>427.09</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>435.71</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>409.83</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="W13" s="4" t="n">
         <v>465.91</v>
       </c>
-      <c r="V13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W13" s="4" t="n">
+      <c r="X13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="4" t="n">
         <v>496.11</v>
       </c>
-      <c r="X13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="4" t="inlineStr"/>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AB13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="inlineStr"/>
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr"/>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG13" s="4" t="inlineStr"/>
+      <c r="AH13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2063,87 +2141,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="L14" s="4" t="n">
         <v>-28.4</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="O14" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>2157.8</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>2136.22</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>2179.38</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>2049.91</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="W14" s="4" t="n">
         <v>2330.42</v>
       </c>
-      <c r="V14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" s="4" t="n">
+      <c r="X14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="4" t="n">
         <v>2481.47</v>
       </c>
-      <c r="X14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="4" t="inlineStr"/>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr">
+      <c r="AA14" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AB14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="inlineStr"/>
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2178,87 +2261,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="L15" s="4" t="n">
         <v>-29.9</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="O15" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>547.4</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>541.9299999999999</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>552.87</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>520.03</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="W15" s="4" t="n">
         <v>591.1900000000001</v>
       </c>
-      <c r="V15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" s="4" t="n">
+      <c r="X15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="4" t="n">
         <v>629.51</v>
       </c>
-      <c r="X15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr">
+      <c r="AA15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="inlineStr"/>
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr"/>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2289,87 +2377,92 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>28.4</v>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="L16" s="4" t="n">
         <v>-31.5</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="O16" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>1363</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="S16" s="4" t="n">
         <v>1349.37</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>1376.63</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="U16" s="4" t="n">
         <v>1294.85</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="V16" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="W16" s="4" t="n">
         <v>1472.04</v>
       </c>
-      <c r="V16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" s="4" t="n">
+      <c r="X16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y16" s="4" t="n">
         <v>1567.45</v>
       </c>
-      <c r="X16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr">
+      <c r="AA16" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="inlineStr"/>
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr"/>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG16" s="4" t="inlineStr"/>
+      <c r="AH16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2405,82 +2498,87 @@
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="L17" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="n">
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="O17" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="n">
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>1438.5</v>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="S17" s="4" t="n">
         <v>1424.12</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>1452.88</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>1366.575</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="V17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="W17" s="4" t="n">
         <v>1515</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="X17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="Y17" s="4" t="n">
         <v>1654.275</v>
       </c>
-      <c r="X17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr">
+      <c r="AA17" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="inlineStr"/>
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="n">
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="n">
         <v>5.32</v>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2516,82 +2614,87 @@
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="L18" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="O18" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="n">
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>2014.8</v>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>1994.65</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>2034.95</v>
       </c>
-      <c r="S18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>1914.06</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="V18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="W18" s="4" t="n">
         <v>2107</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="Y18" s="4" t="n">
         <v>2317.02</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr">
+      <c r="AA18" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="inlineStr"/>
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr"/>
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="n">
+      <c r="AH18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="n">
         <v>4.58</v>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2627,82 +2730,87 @@
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="L19" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="O19" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="n">
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>2417</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>2392.83</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="T19" s="4" t="n">
         <v>2441.17</v>
       </c>
-      <c r="S19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>2296.15</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="V19" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>2610.36</v>
       </c>
-      <c r="V19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" s="4" t="n">
+      <c r="X19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" s="4" t="n">
         <v>2779.55</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr">
+      <c r="AA19" s="4" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="inlineStr"/>
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr"/>
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2738,82 +2846,87 @@
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="L20" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="O20" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>1625.5</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="S20" s="4" t="n">
         <v>1609.24</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="T20" s="4" t="n">
         <v>1641.76</v>
       </c>
-      <c r="S20" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>1544.225</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="V20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="W20" s="4" t="n">
         <v>1648</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="Y20" s="4" t="n">
         <v>1869.325</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr">
+      <c r="AA20" s="4" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AB20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="inlineStr"/>
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr"/>
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="n">
+      <c r="AH20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2849,82 +2962,87 @@
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="L21" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="n">
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="O21" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="n">
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>345.8</v>
       </c>
-      <c r="Q21" s="4" t="n">
+      <c r="S21" s="4" t="n">
         <v>342.34</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="T21" s="4" t="n">
         <v>349.26</v>
       </c>
-      <c r="S21" s="4" t="n">
+      <c r="U21" s="4" t="n">
         <v>328.51</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="V21" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="W21" s="4" t="n">
         <v>373.4640000000001</v>
       </c>
-      <c r="V21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W21" s="4" t="n">
+      <c r="X21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="4" t="n">
         <v>397.67</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr">
+      <c r="AA21" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="inlineStr"/>
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr"/>
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -2960,82 +3078,87 @@
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="L22" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="O22" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="n">
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>389.3</v>
       </c>
-      <c r="Q22" s="4" t="n">
+      <c r="S22" s="4" t="n">
         <v>385.41</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="T22" s="4" t="n">
         <v>393.19</v>
       </c>
-      <c r="S22" s="4" t="n">
+      <c r="U22" s="4" t="n">
         <v>369.835</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="V22" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="W22" s="4" t="n">
         <v>420.444</v>
       </c>
-      <c r="V22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W22" s="4" t="n">
+      <c r="X22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="4" t="n">
         <v>447.695</v>
       </c>
-      <c r="X22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="4" t="inlineStr"/>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="inlineStr">
+      <c r="AA22" s="4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AB22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="inlineStr"/>
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr"/>
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3071,82 +3194,87 @@
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="L23" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="n">
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="O23" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="n">
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="R23" s="4" t="n">
         <v>285.9</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="S23" s="4" t="n">
         <v>283.04</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="T23" s="4" t="n">
         <v>288.76</v>
       </c>
-      <c r="S23" s="4" t="n">
+      <c r="U23" s="4" t="n">
         <v>271.605</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="V23" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="W23" s="4" t="n">
         <v>308.772</v>
       </c>
-      <c r="V23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" s="4" t="n">
+      <c r="X23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y23" s="4" t="n">
         <v>328.785</v>
       </c>
-      <c r="X23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="4" t="inlineStr"/>
-      <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="inlineStr">
+      <c r="AA23" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="inlineStr"/>
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG23" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3182,82 +3310,87 @@
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="L24" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="O24" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="n">
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>494.4</v>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="S24" s="4" t="n">
         <v>489.46</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="T24" s="4" t="n">
         <v>499.34</v>
       </c>
-      <c r="S24" s="4" t="n">
+      <c r="U24" s="4" t="n">
         <v>469.6799999999999</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="V24" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="W24" s="4" t="n">
         <v>533.952</v>
       </c>
-      <c r="V24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W24" s="4" t="n">
+      <c r="X24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="4" t="n">
         <v>568.5599999999999</v>
       </c>
-      <c r="X24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="4" t="inlineStr"/>
-      <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="inlineStr"/>
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr"/>
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG24" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3293,82 +3426,87 @@
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="L25" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="n">
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="O25" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>388.7</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="S25" s="4" t="n">
         <v>384.81</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="T25" s="4" t="n">
         <v>392.59</v>
       </c>
-      <c r="S25" s="4" t="n">
+      <c r="U25" s="4" t="n">
         <v>369.265</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="V25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="W25" s="4" t="n">
         <v>419.796</v>
       </c>
-      <c r="V25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W25" s="4" t="n">
+      <c r="X25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y25" s="4" t="n">
         <v>447.0049999999999</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="4" t="inlineStr"/>
-      <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="inlineStr">
+      <c r="AA25" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="inlineStr"/>
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr"/>
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG25" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3404,82 +3542,87 @@
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="L26" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="n">
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="O26" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>411.3</v>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>407.19</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="T26" s="4" t="n">
         <v>415.41</v>
       </c>
-      <c r="S26" s="4" t="n">
+      <c r="U26" s="4" t="n">
         <v>390.735</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="V26" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>444.2040000000001</v>
       </c>
-      <c r="V26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W26" s="4" t="n">
+      <c r="X26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y26" s="4" t="n">
         <v>472.995</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="4" t="inlineStr"/>
-      <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="inlineStr">
+      <c r="AA26" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="inlineStr"/>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr"/>
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3511,82 +3654,87 @@
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="L27" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="O27" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="n">
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>5406</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="S27" s="4" t="n">
         <v>5351.94</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="T27" s="4" t="n">
         <v>5460.06</v>
       </c>
-      <c r="S27" s="4" t="n">
+      <c r="U27" s="4" t="n">
         <v>5135.7</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="V27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="W27" s="4" t="n">
         <v>5838.48</v>
       </c>
-      <c r="V27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" s="4" t="n">
+      <c r="X27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y27" s="4" t="n">
         <v>6216.9</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="4" t="inlineStr"/>
-      <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="inlineStr">
+      <c r="AA27" s="4" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="AB27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr"/>
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr"/>
-      <c r="AF27" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG27" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AH27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3621,93 +3769,96 @@
           <t>NEW BUY</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>56.8</v>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="L28" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="O28" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="Q28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>368.98</v>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>365.29</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="T28" s="4" t="n">
         <v>372.67</v>
       </c>
-      <c r="S28" s="4" t="n">
+      <c r="U28" s="4" t="n">
         <v>346.84</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="V28" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="W28" s="4" t="n">
         <v>413.26</v>
       </c>
-      <c r="V28" s="4" t="n">
+      <c r="X28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="Y28" s="4" t="n">
         <v>457.54</v>
       </c>
-      <c r="X28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="Y28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="4" t="n">
+      <c r="AA28" s="4" t="inlineStr"/>
+      <c r="AB28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="AA28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="4" t="inlineStr">
+      <c r="AD28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr"/>
-      <c r="AE28" s="4" t="n">
+      <c r="AG28" s="4" t="inlineStr"/>
+      <c r="AH28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AF28" s="4" t="n">
+      <c r="AI28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3742,91 +3893,94 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="J29" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="K29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="O29" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="Q29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>358.56</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="S29" s="4" t="n">
         <v>354.97</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>362.15</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="U29" s="4" t="n">
         <v>340.63</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U29" s="4" t="n">
+      <c r="W29" s="4" t="n">
         <v>387.24</v>
       </c>
-      <c r="V29" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W29" s="4" t="n">
+      <c r="X29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="4" t="n">
         <v>412.34</v>
       </c>
-      <c r="X29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="4" t="n">
+      <c r="AA29" s="4" t="inlineStr"/>
+      <c r="AB29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="4" t="n">
         <v>2.11</v>
       </c>
-      <c r="AA29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="4" t="inlineStr">
+      <c r="AD29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr"/>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AG29" s="4" t="inlineStr"/>
+      <c r="AH29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3858,94 +4012,103 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+12.2pp)</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="J30" s="4" t="n">
         <v>47.3</v>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="L30" s="4" t="n">
         <v>17.1</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="O30" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="Q30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>202.81</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="S30" s="4" t="n">
         <v>200.78</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="T30" s="4" t="n">
         <v>204.84</v>
       </c>
-      <c r="S30" s="4" t="n">
+      <c r="U30" s="4" t="n">
         <v>192.67</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="V30" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U30" s="4" t="n">
+      <c r="W30" s="4" t="n">
         <v>219.03</v>
       </c>
-      <c r="V30" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W30" s="4" t="n">
+      <c r="X30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y30" s="4" t="n">
         <v>233.23</v>
       </c>
-      <c r="X30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AA30" s="4" t="inlineStr"/>
+      <c r="AB30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="AB30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr"/>
-      <c r="AE30" s="4" t="inlineStr"/>
-      <c r="AF30" s="4" t="n">
+      <c r="AG30" s="4" t="inlineStr"/>
+      <c r="AH30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="n">
         <v>12.15</v>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -3977,94 +4140,103 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+13.0pp)</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="J31" s="4" t="n">
         <v>49.7</v>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>16.3</v>
       </c>
-      <c r="K31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="O31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="Q31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>341.1</v>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="S31" s="4" t="n">
         <v>337.69</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>344.51</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="U31" s="4" t="n">
         <v>324.05</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="V31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="W31" s="4" t="n">
         <v>368.39</v>
       </c>
-      <c r="V31" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W31" s="4" t="n">
+      <c r="X31" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y31" s="4" t="n">
         <v>392.26</v>
       </c>
-      <c r="X31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="4" t="n">
+      <c r="AA31" s="4" t="inlineStr"/>
+      <c r="AB31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="4" t="n">
         <v>3.13</v>
       </c>
-      <c r="AA31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="4" t="inlineStr">
+      <c r="AD31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr"/>
-      <c r="AE31" s="4" t="inlineStr"/>
-      <c r="AF31" s="4" t="n">
+      <c r="AG31" s="4" t="inlineStr"/>
+      <c r="AH31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="n">
         <v>12.97</v>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ31" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4096,94 +4268,103 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.4pp)</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="J32" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="L32" s="4" t="n">
         <v>14.8</v>
       </c>
-      <c r="K32" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="O32" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="Q32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>225.02</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="S32" s="4" t="n">
         <v>222.77</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="T32" s="4" t="n">
         <v>227.27</v>
       </c>
-      <c r="S32" s="4" t="n">
+      <c r="U32" s="4" t="n">
         <v>213.77</v>
       </c>
-      <c r="T32" s="4" t="n">
+      <c r="V32" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U32" s="4" t="n">
+      <c r="W32" s="4" t="n">
         <v>243.02</v>
       </c>
-      <c r="V32" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W32" s="4" t="n">
+      <c r="X32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y32" s="4" t="n">
         <v>258.77</v>
       </c>
-      <c r="X32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="4" t="n">
+      <c r="AA32" s="4" t="inlineStr"/>
+      <c r="AB32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="AA32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
+      <c r="AD32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr"/>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="n">
+      <c r="AG32" s="4" t="inlineStr"/>
+      <c r="AH32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="n">
         <v>14.45</v>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4215,94 +4396,103 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.8pp)</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="J33" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="L33" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="K33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="O33" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="Q33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>1065.22</v>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="S33" s="4" t="n">
         <v>1054.57</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="T33" s="4" t="n">
         <v>1075.87</v>
       </c>
-      <c r="S33" s="4" t="n">
+      <c r="U33" s="4" t="n">
         <v>1011.96</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U33" s="4" t="n">
+      <c r="W33" s="4" t="n">
         <v>1150.44</v>
       </c>
-      <c r="V33" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W33" s="4" t="n">
+      <c r="X33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="4" t="n">
         <v>1225</v>
       </c>
-      <c r="X33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AA33" s="4" t="inlineStr"/>
+      <c r="AB33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="AB33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr"/>
-      <c r="AE33" s="4" t="inlineStr"/>
-      <c r="AF33" s="4" t="n">
+      <c r="AG33" s="4" t="inlineStr"/>
+      <c r="AH33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="n">
         <v>14.77</v>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4334,94 +4524,103 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+14.9pp)</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="L34" s="4" t="n">
         <v>14.4</v>
       </c>
-      <c r="K34" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="N34" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="O34" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="Q34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="R34" s="4" t="n">
         <v>333.74</v>
       </c>
-      <c r="Q34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>330.4</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="T34" s="4" t="n">
         <v>337.08</v>
       </c>
-      <c r="S34" s="4" t="n">
+      <c r="U34" s="4" t="n">
         <v>317.05</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="V34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U34" s="4" t="n">
+      <c r="W34" s="4" t="n">
         <v>360.44</v>
       </c>
-      <c r="V34" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W34" s="4" t="n">
+      <c r="X34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y34" s="4" t="n">
         <v>383.8</v>
       </c>
-      <c r="X34" s="4" t="n">
+      <c r="Z34" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="4" t="n">
+      <c r="AA34" s="4" t="inlineStr"/>
+      <c r="AB34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="4" t="n">
         <v>-7.44</v>
       </c>
-      <c r="AB34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr"/>
-      <c r="AE34" s="4" t="inlineStr"/>
-      <c r="AF34" s="4" t="n">
+      <c r="AG34" s="4" t="inlineStr"/>
+      <c r="AH34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="n">
         <v>14.87</v>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ34" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4453,94 +4652,103 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>8</v>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.2pp)</t>
+        </is>
       </c>
       <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="L35" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="K35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="O35" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="Q35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="R35" s="4" t="n">
         <v>393.82</v>
       </c>
-      <c r="Q35" s="4" t="n">
+      <c r="S35" s="4" t="n">
         <v>389.88</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="T35" s="4" t="n">
         <v>397.76</v>
       </c>
-      <c r="S35" s="4" t="n">
+      <c r="U35" s="4" t="n">
         <v>374.13</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="V35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U35" s="4" t="n">
+      <c r="W35" s="4" t="n">
         <v>425.33</v>
       </c>
-      <c r="V35" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W35" s="4" t="n">
+      <c r="X35" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y35" s="4" t="n">
         <v>452.89</v>
       </c>
-      <c r="X35" s="4" t="n">
+      <c r="Z35" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="4" t="n">
+      <c r="AA35" s="4" t="inlineStr"/>
+      <c r="AB35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="AA35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="4" t="inlineStr">
+      <c r="AD35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AD35" s="4" t="inlineStr"/>
-      <c r="AE35" s="4" t="inlineStr"/>
-      <c r="AF35" s="4" t="n">
+      <c r="AG35" s="4" t="inlineStr"/>
+      <c r="AH35" s="4" t="inlineStr"/>
+      <c r="AI35" s="4" t="n">
         <v>15.21</v>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4572,94 +4780,103 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+15.5pp)</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="J36" s="4" t="n">
         <v>50.5</v>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="L36" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="K36" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="O36" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="Q36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="R36" s="4" t="n">
         <v>81.56</v>
       </c>
-      <c r="Q36" s="4" t="n">
+      <c r="S36" s="4" t="n">
         <v>80.73999999999999</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="T36" s="4" t="n">
         <v>82.38</v>
       </c>
-      <c r="S36" s="4" t="n">
+      <c r="U36" s="4" t="n">
         <v>77.48</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="V36" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U36" s="4" t="n">
+      <c r="W36" s="4" t="n">
         <v>88.08</v>
       </c>
-      <c r="V36" s="4" t="n">
+      <c r="X36" s="4" t="n">
         <v>7.99</v>
       </c>
-      <c r="W36" s="4" t="n">
+      <c r="Y36" s="4" t="n">
         <v>93.79000000000001</v>
       </c>
-      <c r="X36" s="4" t="n">
+      <c r="Z36" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="4" t="n">
+      <c r="AA36" s="4" t="inlineStr"/>
+      <c r="AB36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="4" t="n">
         <v>7.39</v>
       </c>
-      <c r="AA36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="4" t="inlineStr">
+      <c r="AD36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AD36" s="4" t="inlineStr"/>
-      <c r="AE36" s="4" t="inlineStr"/>
-      <c r="AF36" s="4" t="n">
+      <c r="AG36" s="4" t="inlineStr"/>
+      <c r="AH36" s="4" t="inlineStr"/>
+      <c r="AI36" s="4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ36" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4691,94 +4908,103 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+16.4pp)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="J37" s="4" t="n">
         <v>53.6</v>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="L37" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="O37" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="Q37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="R37" s="4" t="n">
         <v>159.84</v>
       </c>
-      <c r="Q37" s="4" t="n">
+      <c r="S37" s="4" t="n">
         <v>158.24</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="T37" s="4" t="n">
         <v>161.44</v>
       </c>
-      <c r="S37" s="4" t="n">
+      <c r="U37" s="4" t="n">
         <v>151.85</v>
       </c>
-      <c r="T37" s="4" t="n">
+      <c r="V37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U37" s="4" t="n">
+      <c r="W37" s="4" t="n">
         <v>172.63</v>
       </c>
-      <c r="V37" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W37" s="4" t="n">
+      <c r="X37" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y37" s="4" t="n">
         <v>183.82</v>
       </c>
-      <c r="X37" s="4" t="n">
+      <c r="Z37" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="4" t="n">
+      <c r="AA37" s="4" t="inlineStr"/>
+      <c r="AB37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="AA37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="4" t="inlineStr">
+      <c r="AD37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AD37" s="4" t="inlineStr"/>
-      <c r="AE37" s="4" t="inlineStr"/>
-      <c r="AF37" s="4" t="n">
+      <c r="AG37" s="4" t="inlineStr"/>
+      <c r="AH37" s="4" t="inlineStr"/>
+      <c r="AI37" s="4" t="n">
         <v>16.4</v>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4810,94 +5036,103 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.2pp)</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="L38" s="4" t="n">
         <v>-7.9</v>
       </c>
-      <c r="K38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="N38" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="O38" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="Q38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="R38" s="4" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="Q38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>94.09</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="T38" s="4" t="n">
         <v>95.98999999999999</v>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="U38" s="4" t="n">
         <v>90.29000000000001</v>
       </c>
-      <c r="T38" s="4" t="n">
+      <c r="V38" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U38" s="4" t="n">
+      <c r="W38" s="4" t="n">
         <v>102.64</v>
       </c>
-      <c r="V38" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W38" s="4" t="n">
+      <c r="X38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y38" s="4" t="n">
         <v>109.3</v>
       </c>
-      <c r="X38" s="4" t="n">
+      <c r="Z38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="4" t="n">
+      <c r="AA38" s="4" t="inlineStr"/>
+      <c r="AB38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="4" t="n">
         <v>-5.09</v>
       </c>
-      <c r="AB38" s="4" t="inlineStr">
+      <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD38" s="4" t="inlineStr"/>
-      <c r="AE38" s="4" t="inlineStr"/>
-      <c r="AF38" s="4" t="n">
+      <c r="AG38" s="4" t="inlineStr"/>
+      <c r="AH38" s="4" t="inlineStr"/>
+      <c r="AI38" s="4" t="n">
         <v>37.17</v>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -4929,94 +5164,103 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+37.8pp)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>30.8</v>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="L39" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="K39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="O39" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="Q39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="R39" s="4" t="n">
         <v>214.03</v>
       </c>
-      <c r="Q39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>211.89</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="T39" s="4" t="n">
         <v>216.17</v>
       </c>
-      <c r="S39" s="4" t="n">
+      <c r="U39" s="4" t="n">
         <v>203.33</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="V39" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U39" s="4" t="n">
+      <c r="W39" s="4" t="n">
         <v>231.15</v>
       </c>
-      <c r="V39" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W39" s="4" t="n">
+      <c r="X39" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y39" s="4" t="n">
         <v>246.13</v>
       </c>
-      <c r="X39" s="4" t="n">
+      <c r="Z39" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="4" t="n">
+      <c r="AA39" s="4" t="inlineStr"/>
+      <c r="AB39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="AA39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="4" t="inlineStr">
+      <c r="AD39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AD39" s="4" t="inlineStr"/>
-      <c r="AE39" s="4" t="inlineStr"/>
-      <c r="AF39" s="4" t="n">
+      <c r="AG39" s="4" t="inlineStr"/>
+      <c r="AH39" s="4" t="inlineStr"/>
+      <c r="AI39" s="4" t="n">
         <v>37.79</v>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ39" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5048,94 +5292,103 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+43.9pp)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="J40" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="L40" s="4" t="n">
         <v>-14.6</v>
       </c>
-      <c r="K40" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="N40" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M40" s="4" t="n">
+      <c r="O40" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="Q40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="R40" s="4" t="n">
         <v>338.87</v>
       </c>
-      <c r="Q40" s="4" t="n">
+      <c r="S40" s="4" t="n">
         <v>335.48</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="T40" s="4" t="n">
         <v>342.26</v>
       </c>
-      <c r="S40" s="4" t="n">
+      <c r="U40" s="4" t="n">
         <v>321.93</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="V40" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U40" s="4" t="n">
+      <c r="W40" s="4" t="n">
         <v>365.98</v>
       </c>
-      <c r="V40" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" s="4" t="n">
+      <c r="X40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y40" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="X40" s="4" t="n">
+      <c r="Z40" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="4" t="n">
+      <c r="AA40" s="4" t="inlineStr"/>
+      <c r="AB40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="AB40" s="4" t="inlineStr">
+      <c r="AE40" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD40" s="4" t="inlineStr"/>
-      <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="n">
+      <c r="AG40" s="4" t="inlineStr"/>
+      <c r="AH40" s="4" t="inlineStr"/>
+      <c r="AI40" s="4" t="n">
         <v>43.85</v>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ40" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5167,94 +5420,103 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.6pp)</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="J41" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="L41" s="4" t="n">
         <v>-16.4</v>
       </c>
-      <c r="K41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="O41" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="Q41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="R41" s="4" t="n">
         <v>97.67</v>
       </c>
-      <c r="Q41" s="4" t="n">
+      <c r="S41" s="4" t="n">
         <v>96.69</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="T41" s="4" t="n">
         <v>98.65000000000001</v>
       </c>
-      <c r="S41" s="4" t="n">
+      <c r="U41" s="4" t="n">
         <v>92.79000000000001</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="V41" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U41" s="4" t="n">
+      <c r="W41" s="4" t="n">
         <v>105.48</v>
       </c>
-      <c r="V41" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W41" s="4" t="n">
+      <c r="X41" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y41" s="4" t="n">
         <v>112.32</v>
       </c>
-      <c r="X41" s="4" t="n">
+      <c r="Z41" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="4" t="n">
+      <c r="AA41" s="4" t="inlineStr"/>
+      <c r="AB41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="AB41" s="4" t="inlineStr">
+      <c r="AE41" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD41" s="4" t="inlineStr"/>
-      <c r="AE41" s="4" t="inlineStr"/>
-      <c r="AF41" s="4" t="n">
+      <c r="AG41" s="4" t="inlineStr"/>
+      <c r="AH41" s="4" t="inlineStr"/>
+      <c r="AI41" s="4" t="n">
         <v>45.62</v>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
@@ -5286,99 +5548,108 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>ROTATE OUT</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n">
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TRV (+45.9pp)</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="L42" s="4" t="n">
         <v>-16.7</v>
       </c>
-      <c r="K42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="N42" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="Q42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="R42" s="4" t="n">
         <v>267.71</v>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>265.03</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>270.39</v>
       </c>
-      <c r="S42" s="4" t="n">
+      <c r="U42" s="4" t="n">
         <v>254.32</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="V42" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="U42" s="4" t="n">
+      <c r="W42" s="4" t="n">
         <v>289.13</v>
       </c>
-      <c r="V42" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="W42" s="4" t="n">
+      <c r="X42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y42" s="4" t="n">
         <v>307.87</v>
       </c>
-      <c r="X42" s="4" t="n">
+      <c r="Z42" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="Y42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
+      <c r="AA42" s="4" t="inlineStr"/>
+      <c r="AB42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="AA42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="4" t="inlineStr">
+      <c r="AD42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr"/>
-      <c r="AE42" s="4" t="inlineStr"/>
-      <c r="AF42" s="4" t="n">
+      <c r="AG42" s="4" t="inlineStr"/>
+      <c r="AH42" s="4" t="inlineStr"/>
+      <c r="AI42" s="4" t="n">
         <v>45.94</v>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-01 14:12</t>
+      <c r="AJ42" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG42"/>
+  <autoFilter ref="A1:AJ42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AM$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AM$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM81"/>
+  <dimension ref="A1:AM108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10633,8 +10633,3411 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K82" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R82" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="S82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T82" s="4" t="n">
+        <v>2460</v>
+      </c>
+      <c r="U82" s="4" t="n">
+        <v>2460</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>2435.4</v>
+      </c>
+      <c r="W82" s="4" t="n">
+        <v>2484.6</v>
+      </c>
+      <c r="X82" s="4" t="n">
+        <v>2312.4</v>
+      </c>
+      <c r="Y82" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z82" s="4" t="n">
+        <v>2755.2</v>
+      </c>
+      <c r="AA82" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB82" s="4" t="n">
+        <v>3050.4</v>
+      </c>
+      <c r="AC82" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD82" s="4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="4" t="inlineStr"/>
+      <c r="AG82" s="4" t="inlineStr"/>
+      <c r="AH82" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI82" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AJ82" s="4" t="inlineStr"/>
+      <c r="AK82" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>HCL Tech</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K83" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R83" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T83" s="4" t="n">
+        <v>1369.9</v>
+      </c>
+      <c r="U83" s="4" t="n">
+        <v>1369.9</v>
+      </c>
+      <c r="V83" s="4" t="n">
+        <v>1356.2</v>
+      </c>
+      <c r="W83" s="4" t="n">
+        <v>1383.6</v>
+      </c>
+      <c r="X83" s="4" t="n">
+        <v>1287.71</v>
+      </c>
+      <c r="Y83" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z83" s="4" t="n">
+        <v>1534.29</v>
+      </c>
+      <c r="AA83" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB83" s="4" t="n">
+        <v>1698.68</v>
+      </c>
+      <c r="AC83" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD83" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="4" t="inlineStr"/>
+      <c r="AG83" s="4" t="inlineStr"/>
+      <c r="AH83" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI83" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Quality · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AJ83" s="4" t="inlineStr"/>
+      <c r="AK83" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L84" s="4" t="inlineStr"/>
+      <c r="M84" s="4" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R84" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T84" s="4" t="n">
+        <v>11600</v>
+      </c>
+      <c r="U84" s="4" t="n">
+        <v>11600</v>
+      </c>
+      <c r="V84" s="4" t="n">
+        <v>11484</v>
+      </c>
+      <c r="W84" s="4" t="n">
+        <v>11716</v>
+      </c>
+      <c r="X84" s="4" t="n">
+        <v>10904</v>
+      </c>
+      <c r="Y84" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z84" s="4" t="n">
+        <v>12992</v>
+      </c>
+      <c r="AA84" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB84" s="4" t="n">
+        <v>14384</v>
+      </c>
+      <c r="AC84" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD84" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AE84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="4" t="inlineStr"/>
+      <c r="AG84" s="4" t="inlineStr"/>
+      <c r="AH84" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI84" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Growth · News</t>
+        </is>
+      </c>
+      <c r="AJ84" s="4" t="inlineStr"/>
+      <c r="AK84" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>ATUL</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+5.4pp)</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr"/>
+      <c r="L85" s="4" t="inlineStr"/>
+      <c r="M85" s="4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R85" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T85" s="4" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="U85" s="4" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="V85" s="4" t="n">
+        <v>6725.56</v>
+      </c>
+      <c r="W85" s="4" t="n">
+        <v>6861.44</v>
+      </c>
+      <c r="X85" s="4" t="n">
+        <v>6453.82</v>
+      </c>
+      <c r="Y85" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z85" s="4" t="n">
+        <v>7336.98</v>
+      </c>
+      <c r="AA85" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB85" s="4" t="n">
+        <v>7812.52</v>
+      </c>
+      <c r="AC85" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD85" s="4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AE85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="4" t="inlineStr"/>
+      <c r="AG85" s="4" t="inlineStr"/>
+      <c r="AH85" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI85" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AJ85" s="4" t="inlineStr"/>
+      <c r="AK85" s="4" t="inlineStr"/>
+      <c r="AL85" s="4" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AM85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+5.4pp)</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
+      <c r="L86" s="4" t="inlineStr"/>
+      <c r="M86" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q86" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R86" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T86" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="U86" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>836.55</v>
+      </c>
+      <c r="W86" s="4" t="n">
+        <v>853.45</v>
+      </c>
+      <c r="X86" s="4" t="n">
+        <v>802.75</v>
+      </c>
+      <c r="Y86" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z86" s="4" t="n">
+        <v>912.6</v>
+      </c>
+      <c r="AA86" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB86" s="4" t="n">
+        <v>971.75</v>
+      </c>
+      <c r="AC86" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD86" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="4" t="inlineStr"/>
+      <c r="AG86" s="4" t="inlineStr"/>
+      <c r="AH86" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI86" s="4" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Quality</t>
+        </is>
+      </c>
+      <c r="AJ86" s="4" t="inlineStr"/>
+      <c r="AK86" s="4" t="inlineStr"/>
+      <c r="AL86" s="4" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="AM86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+8.0pp)</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr"/>
+      <c r="M87" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q87" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R87" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T87" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="U87" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="V87" s="4" t="n">
+        <v>5492.52</v>
+      </c>
+      <c r="W87" s="4" t="n">
+        <v>5603.48</v>
+      </c>
+      <c r="X87" s="4" t="n">
+        <v>5270.6</v>
+      </c>
+      <c r="Y87" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z87" s="4" t="n">
+        <v>5991.84</v>
+      </c>
+      <c r="AA87" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB87" s="4" t="n">
+        <v>6380.2</v>
+      </c>
+      <c r="AC87" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD87" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="4" t="inlineStr"/>
+      <c r="AG87" s="4" t="inlineStr"/>
+      <c r="AH87" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI87" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Quality · Growth</t>
+        </is>
+      </c>
+      <c r="AJ87" s="4" t="inlineStr"/>
+      <c r="AK87" s="4" t="inlineStr"/>
+      <c r="AL87" s="4" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="AM87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+8.3pp)</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr"/>
+      <c r="L88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R88" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T88" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="U88" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="V88" s="4" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="W88" s="4" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="X88" s="4" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="Y88" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z88" s="4" t="n">
+        <v>407.16</v>
+      </c>
+      <c r="AA88" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB88" s="4" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="AC88" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD88" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="4" t="inlineStr"/>
+      <c r="AG88" s="4" t="inlineStr"/>
+      <c r="AH88" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI88" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Quality · Value</t>
+        </is>
+      </c>
+      <c r="AJ88" s="4" t="inlineStr"/>
+      <c r="AK88" s="4" t="inlineStr"/>
+      <c r="AL88" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AM88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+8.4pp)</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
+      <c r="L89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R89" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T89" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="U89" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="W89" s="4" t="n">
+        <v>454.5</v>
+      </c>
+      <c r="X89" s="4" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="Y89" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z89" s="4" t="n">
+        <v>486</v>
+      </c>
+      <c r="AA89" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB89" s="4" t="n">
+        <v>517.5</v>
+      </c>
+      <c r="AC89" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD89" s="4" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AE89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="4" t="inlineStr"/>
+      <c r="AG89" s="4" t="inlineStr"/>
+      <c r="AH89" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI89" s="4" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AJ89" s="4" t="inlineStr"/>
+      <c r="AK89" s="4" t="inlineStr"/>
+      <c r="AL89" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AM89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+9.0pp)</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
+      <c r="L90" s="4" t="inlineStr"/>
+      <c r="M90" s="4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q90" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R90" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T90" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="U90" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="V90" s="4" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="W90" s="4" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="X90" s="4" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="Y90" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z90" s="4" t="n">
+        <v>422.6</v>
+      </c>
+      <c r="AA90" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB90" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="AC90" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD90" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="4" t="inlineStr"/>
+      <c r="AG90" s="4" t="inlineStr"/>
+      <c r="AH90" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI90" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Momentum</t>
+        </is>
+      </c>
+      <c r="AJ90" s="4" t="inlineStr"/>
+      <c r="AK90" s="4" t="inlineStr"/>
+      <c r="AL90" s="4" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AM90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+9.7pp)</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="P91" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R91" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T91" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="U91" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="V91" s="4" t="n">
+        <v>11360.25</v>
+      </c>
+      <c r="W91" s="4" t="n">
+        <v>11589.75</v>
+      </c>
+      <c r="X91" s="4" t="n">
+        <v>10901.25</v>
+      </c>
+      <c r="Y91" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z91" s="4" t="n">
+        <v>12393</v>
+      </c>
+      <c r="AA91" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="4" t="n">
+        <v>13196.25</v>
+      </c>
+      <c r="AC91" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD91" s="4" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AE91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="4" t="inlineStr"/>
+      <c r="AG91" s="4" t="inlineStr"/>
+      <c r="AH91" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI91" s="4" t="inlineStr">
+        <is>
+          <t>Value · Quality · Growth</t>
+        </is>
+      </c>
+      <c r="AJ91" s="4" t="inlineStr"/>
+      <c r="AK91" s="4" t="inlineStr"/>
+      <c r="AL91" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AM91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+55.0pp)</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q92" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R92" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T92" s="4" t="n">
+        <v>1327.7</v>
+      </c>
+      <c r="U92" s="4" t="n">
+        <v>1327.7</v>
+      </c>
+      <c r="V92" s="4" t="n">
+        <v>1314.42</v>
+      </c>
+      <c r="W92" s="4" t="n">
+        <v>1340.98</v>
+      </c>
+      <c r="X92" s="4" t="n">
+        <v>1261.32</v>
+      </c>
+      <c r="Y92" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z92" s="4" t="n">
+        <v>1433.92</v>
+      </c>
+      <c r="AA92" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB92" s="4" t="n">
+        <v>1526.86</v>
+      </c>
+      <c r="AC92" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD92" s="4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AE92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="4" t="inlineStr"/>
+      <c r="AG92" s="4" t="inlineStr"/>
+      <c r="AH92" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI92" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AJ92" s="4" t="inlineStr"/>
+      <c r="AK92" s="4" t="inlineStr"/>
+      <c r="AL92" s="4" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="AM92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+55.5pp)</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="P93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R93" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T93" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="U93" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="V93" s="4" t="n">
+        <v>2716.86</v>
+      </c>
+      <c r="W93" s="4" t="n">
+        <v>2771.74</v>
+      </c>
+      <c r="X93" s="4" t="n">
+        <v>2607.09</v>
+      </c>
+      <c r="Y93" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z93" s="4" t="n">
+        <v>2963.84</v>
+      </c>
+      <c r="AA93" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB93" s="4" t="n">
+        <v>3155.95</v>
+      </c>
+      <c r="AC93" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD93" s="4" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="AE93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="4" t="inlineStr"/>
+      <c r="AG93" s="4" t="inlineStr"/>
+      <c r="AH93" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI93" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AJ93" s="4" t="inlineStr"/>
+      <c r="AK93" s="4" t="inlineStr"/>
+      <c r="AL93" s="4" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="AM93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+57.8pp)</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="P94" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q94" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R94" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="S94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T94" s="4" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="U94" s="4" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="V94" s="4" t="n">
+        <v>923.47</v>
+      </c>
+      <c r="W94" s="4" t="n">
+        <v>942.13</v>
+      </c>
+      <c r="X94" s="4" t="n">
+        <v>886.16</v>
+      </c>
+      <c r="Y94" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z94" s="4" t="n">
+        <v>1007.42</v>
+      </c>
+      <c r="AA94" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="4" t="n">
+        <v>1072.72</v>
+      </c>
+      <c r="AC94" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD94" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AE94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="4" t="inlineStr"/>
+      <c r="AG94" s="4" t="inlineStr"/>
+      <c r="AH94" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI94" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AJ94" s="4" t="inlineStr"/>
+      <c r="AK94" s="4" t="inlineStr"/>
+      <c r="AL94" s="4" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="AM94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+59.8pp)</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="n">
+        <v>-30.1</v>
+      </c>
+      <c r="P95" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R95" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="S95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T95" s="4" t="n">
+        <v>1595</v>
+      </c>
+      <c r="U95" s="4" t="n">
+        <v>1595</v>
+      </c>
+      <c r="V95" s="4" t="n">
+        <v>1579.05</v>
+      </c>
+      <c r="W95" s="4" t="n">
+        <v>1610.95</v>
+      </c>
+      <c r="X95" s="4" t="n">
+        <v>1515.25</v>
+      </c>
+      <c r="Y95" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z95" s="4" t="n">
+        <v>1722.6</v>
+      </c>
+      <c r="AA95" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB95" s="4" t="n">
+        <v>1834.25</v>
+      </c>
+      <c r="AC95" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD95" s="4" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="AE95" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="4" t="inlineStr"/>
+      <c r="AG95" s="4" t="inlineStr"/>
+      <c r="AH95" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI95" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AJ95" s="4" t="inlineStr"/>
+      <c r="AK95" s="4" t="inlineStr"/>
+      <c r="AL95" s="4" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="AM95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Rotation → TCS.NS (+63.9pp)</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="n">
+        <v>-34.3</v>
+      </c>
+      <c r="P96" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q96" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R96" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="S96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T96" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="U96" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="V96" s="4" t="n">
+        <v>417.78</v>
+      </c>
+      <c r="W96" s="4" t="n">
+        <v>426.22</v>
+      </c>
+      <c r="X96" s="4" t="n">
+        <v>400.9</v>
+      </c>
+      <c r="Y96" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z96" s="4" t="n">
+        <v>455.76</v>
+      </c>
+      <c r="AA96" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB96" s="4" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="AC96" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD96" s="4" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="AE96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="4" t="inlineStr"/>
+      <c r="AG96" s="4" t="inlineStr"/>
+      <c r="AH96" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI96" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AJ96" s="4" t="inlineStr"/>
+      <c r="AK96" s="4" t="inlineStr"/>
+      <c r="AL96" s="4" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="AM96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="P97" s="4" t="inlineStr"/>
+      <c r="Q97" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R97" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T97" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="U97" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="V97" s="4" t="n">
+        <v>1440.05</v>
+      </c>
+      <c r="W97" s="4" t="n">
+        <v>1469.15</v>
+      </c>
+      <c r="X97" s="4" t="n">
+        <v>1381.87</v>
+      </c>
+      <c r="Y97" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z97" s="4" t="n">
+        <v>1532</v>
+      </c>
+      <c r="AA97" s="4" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AB97" s="4" t="n">
+        <v>1672.79</v>
+      </c>
+      <c r="AC97" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD97" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="4" t="inlineStr"/>
+      <c r="AG97" s="4" t="inlineStr"/>
+      <c r="AH97" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI97" s="4" t="inlineStr"/>
+      <c r="AJ97" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AK97" s="4" t="inlineStr"/>
+      <c r="AL97" s="4" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AM97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="P98" s="4" t="inlineStr"/>
+      <c r="Q98" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R98" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="U98" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="V98" s="4" t="n">
+        <v>1944.36</v>
+      </c>
+      <c r="W98" s="4" t="n">
+        <v>1983.64</v>
+      </c>
+      <c r="X98" s="4" t="n">
+        <v>1865.8</v>
+      </c>
+      <c r="Y98" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z98" s="4" t="n">
+        <v>2054</v>
+      </c>
+      <c r="AA98" s="4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AB98" s="4" t="n">
+        <v>2258.6</v>
+      </c>
+      <c r="AC98" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD98" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AE98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="4" t="inlineStr"/>
+      <c r="AG98" s="4" t="inlineStr"/>
+      <c r="AH98" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI98" s="4" t="inlineStr"/>
+      <c r="AJ98" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AK98" s="4" t="inlineStr"/>
+      <c r="AL98" s="4" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AM98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="P99" s="4" t="inlineStr"/>
+      <c r="Q99" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R99" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T99" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="U99" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="V99" s="4" t="n">
+        <v>1603.8</v>
+      </c>
+      <c r="W99" s="4" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="X99" s="4" t="n">
+        <v>1539</v>
+      </c>
+      <c r="Y99" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z99" s="4" t="n">
+        <v>1642</v>
+      </c>
+      <c r="AA99" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB99" s="4" t="n">
+        <v>1863</v>
+      </c>
+      <c r="AC99" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD99" s="4" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="AE99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="4" t="inlineStr"/>
+      <c r="AG99" s="4" t="inlineStr"/>
+      <c r="AH99" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI99" s="4" t="inlineStr"/>
+      <c r="AJ99" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="AK99" s="4" t="inlineStr"/>
+      <c r="AL99" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="P100" s="4" t="inlineStr"/>
+      <c r="Q100" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R100" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T100" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="U100" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="V100" s="4" t="n">
+        <v>2385.9</v>
+      </c>
+      <c r="W100" s="4" t="n">
+        <v>2434.1</v>
+      </c>
+      <c r="X100" s="4" t="n">
+        <v>2289.5</v>
+      </c>
+      <c r="Y100" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z100" s="4" t="n">
+        <v>2602.8</v>
+      </c>
+      <c r="AA100" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB100" s="4" t="n">
+        <v>2771.5</v>
+      </c>
+      <c r="AC100" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD100" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="4" t="inlineStr"/>
+      <c r="AG100" s="4" t="inlineStr"/>
+      <c r="AH100" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI100" s="4" t="inlineStr"/>
+      <c r="AJ100" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AK100" s="4" t="inlineStr"/>
+      <c r="AL100" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="P101" s="4" t="inlineStr"/>
+      <c r="Q101" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R101" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T101" s="4" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="U101" s="4" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="V101" s="4" t="n">
+        <v>340.16</v>
+      </c>
+      <c r="W101" s="4" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="X101" s="4" t="n">
+        <v>326.42</v>
+      </c>
+      <c r="Y101" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z101" s="4" t="n">
+        <v>371.088</v>
+      </c>
+      <c r="AA101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB101" s="4" t="n">
+        <v>395.14</v>
+      </c>
+      <c r="AC101" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD101" s="4" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AE101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="4" t="inlineStr"/>
+      <c r="AG101" s="4" t="inlineStr"/>
+      <c r="AH101" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI101" s="4" t="inlineStr"/>
+      <c r="AJ101" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AK101" s="4" t="inlineStr"/>
+      <c r="AL101" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="inlineStr"/>
+      <c r="I102" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="P102" s="4" t="inlineStr"/>
+      <c r="Q102" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R102" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T102" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="U102" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="V102" s="4" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="W102" s="4" t="n">
+        <v>401.98</v>
+      </c>
+      <c r="X102" s="4" t="n">
+        <v>378.1</v>
+      </c>
+      <c r="Y102" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z102" s="4" t="n">
+        <v>429.84</v>
+      </c>
+      <c r="AA102" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="4" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="AC102" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD102" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="4" t="inlineStr"/>
+      <c r="AG102" s="4" t="inlineStr"/>
+      <c r="AH102" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI102" s="4" t="inlineStr"/>
+      <c r="AJ102" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AK102" s="4" t="inlineStr"/>
+      <c r="AL102" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J103" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr"/>
+      <c r="M103" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="P103" s="4" t="inlineStr"/>
+      <c r="Q103" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R103" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T103" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="U103" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="V103" s="4" t="n">
+        <v>280.57</v>
+      </c>
+      <c r="W103" s="4" t="n">
+        <v>286.23</v>
+      </c>
+      <c r="X103" s="4" t="n">
+        <v>269.23</v>
+      </c>
+      <c r="Y103" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z103" s="4" t="n">
+        <v>306.072</v>
+      </c>
+      <c r="AA103" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB103" s="4" t="n">
+        <v>325.91</v>
+      </c>
+      <c r="AC103" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD103" s="4" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="AE103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="4" t="inlineStr"/>
+      <c r="AG103" s="4" t="inlineStr"/>
+      <c r="AH103" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI103" s="4" t="inlineStr"/>
+      <c r="AJ103" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AK103" s="4" t="inlineStr"/>
+      <c r="AL103" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
+      <c r="L104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="P104" s="4" t="inlineStr"/>
+      <c r="Q104" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R104" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T104" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="U104" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="V104" s="4" t="n">
+        <v>286.11</v>
+      </c>
+      <c r="W104" s="4" t="n">
+        <v>291.89</v>
+      </c>
+      <c r="X104" s="4" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="Y104" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z104" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="AA104" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB104" s="4" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="AC104" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD104" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="4" t="inlineStr"/>
+      <c r="AG104" s="4" t="inlineStr"/>
+      <c r="AH104" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI104" s="4" t="inlineStr"/>
+      <c r="AJ104" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AK104" s="4" t="inlineStr"/>
+      <c r="AL104" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AM104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K105" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="P105" s="4" t="inlineStr"/>
+      <c r="Q105" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R105" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T105" s="4" t="n">
+        <v>510.2</v>
+      </c>
+      <c r="U105" s="4" t="n">
+        <v>510.2</v>
+      </c>
+      <c r="V105" s="4" t="n">
+        <v>505.1</v>
+      </c>
+      <c r="W105" s="4" t="n">
+        <v>515.3</v>
+      </c>
+      <c r="X105" s="4" t="n">
+        <v>484.6899999999999</v>
+      </c>
+      <c r="Y105" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z105" s="4" t="n">
+        <v>551.0160000000001</v>
+      </c>
+      <c r="AA105" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB105" s="4" t="n">
+        <v>586.7299999999999</v>
+      </c>
+      <c r="AC105" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD105" s="4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="4" t="inlineStr"/>
+      <c r="AG105" s="4" t="inlineStr"/>
+      <c r="AH105" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI105" s="4" t="inlineStr"/>
+      <c r="AJ105" s="4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AK105" s="4" t="inlineStr"/>
+      <c r="AL105" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr"/>
+      <c r="I106" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K106" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R106" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T106" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="U106" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="V106" s="4" t="n">
+        <v>387.58</v>
+      </c>
+      <c r="W106" s="4" t="n">
+        <v>395.42</v>
+      </c>
+      <c r="X106" s="4" t="n">
+        <v>371.925</v>
+      </c>
+      <c r="Y106" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z106" s="4" t="n">
+        <v>422.8200000000001</v>
+      </c>
+      <c r="AA106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB106" s="4" t="n">
+        <v>450.225</v>
+      </c>
+      <c r="AC106" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD106" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="4" t="inlineStr"/>
+      <c r="AG106" s="4" t="inlineStr"/>
+      <c r="AH106" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI106" s="4" t="inlineStr"/>
+      <c r="AJ106" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AK106" s="4" t="inlineStr"/>
+      <c r="AL106" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J107" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K107" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="P107" s="4" t="inlineStr"/>
+      <c r="Q107" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R107" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T107" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="U107" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="V107" s="4" t="n">
+        <v>5423.22</v>
+      </c>
+      <c r="W107" s="4" t="n">
+        <v>5532.78</v>
+      </c>
+      <c r="X107" s="4" t="n">
+        <v>5204.099999999999</v>
+      </c>
+      <c r="Y107" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z107" s="4" t="n">
+        <v>5916.240000000001</v>
+      </c>
+      <c r="AA107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB107" s="4" t="n">
+        <v>6299.7</v>
+      </c>
+      <c r="AC107" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD107" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AE107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="4" t="inlineStr"/>
+      <c r="AG107" s="4" t="inlineStr"/>
+      <c r="AH107" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI107" s="4" t="inlineStr"/>
+      <c r="AJ107" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AK107" s="4" t="inlineStr"/>
+      <c r="AL107" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K108" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P108" s="4" t="inlineStr"/>
+      <c r="Q108" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="R108" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="S108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="T108" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="U108" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="V108" s="4" t="n">
+        <v>413.42</v>
+      </c>
+      <c r="W108" s="4" t="n">
+        <v>421.78</v>
+      </c>
+      <c r="X108" s="4" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="Y108" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Z108" s="4" t="n">
+        <v>451.008</v>
+      </c>
+      <c r="AA108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB108" s="4" t="n">
+        <v>480.24</v>
+      </c>
+      <c r="AC108" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD108" s="4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AE108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="4" t="inlineStr"/>
+      <c r="AG108" s="4" t="inlineStr"/>
+      <c r="AH108" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AI108" s="4" t="inlineStr"/>
+      <c r="AJ108" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="AK108" s="4" t="inlineStr"/>
+      <c r="AL108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM81"/>
+  <autoFilter ref="A1:AM108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AS82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="AS83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -10993,7 +10993,7 @@
       </c>
       <c r="AS84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AS85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="AS86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AS87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="AS88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AS89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AS90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="AS91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="AS92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="AS93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="AS94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="AS95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="AS96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12944,7 @@
       </c>
       <c r="AS97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="AS98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="AS99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AS100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="AS101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13619,7 @@
       </c>
       <c r="AS102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AS103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="AS104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="AS105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AS106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="AS107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AS108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14576,7 @@
       </c>
       <c r="AS109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="AS110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="AS111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="AS112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AS113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="AS114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="AS115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="AS116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="AS117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="AS118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="AS119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="AS120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="AS121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16539,14 +16539,14 @@
         </is>
       </c>
       <c r="N122" s="4" t="n">
-        <v>34</v>
+        <v>30.5</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>-0.8</v>
+        <v>-4.2</v>
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>DIS Earnings in 0d (impact=medium) → -3.5pts</t>
         </is>
       </c>
       <c r="Q122" s="4" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="AS122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="AS123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:27</t>
+          <t>2026-08-05 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AS$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AS$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS123"/>
+  <dimension ref="A1:AS131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10568,9 +10568,9 @@
           <t>TCS</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -10585,11 +10585,11 @@
         <v>-8</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>77.5</v>
+        <v>73.7</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="N82" s="4" t="n">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band HOLD · 59d left · → STRONG BUY</t>
+          <t>Rank ↑ 9→1 · Conf 39% · band HOLD→WATCH · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R82" s="4" t="inlineStr"/>
@@ -10618,16 +10618,16 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>29.6</v>
+        <v>26.3</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W82" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X82" s="4" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
@@ -10635,34 +10635,34 @@
         </is>
       </c>
       <c r="Z82" s="4" t="n">
-        <v>2460</v>
+        <v>2452.2</v>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>2460</v>
+        <v>2452.2</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>2435.4</v>
+        <v>2427.68</v>
       </c>
       <c r="AC82" s="4" t="n">
-        <v>2484.6</v>
+        <v>2476.72</v>
       </c>
       <c r="AD82" s="4" t="n">
-        <v>2312.4</v>
+        <v>2329.59</v>
       </c>
       <c r="AE82" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF82" s="4" t="n">
-        <v>2755.2</v>
+        <v>2648.38</v>
       </c>
       <c r="AG82" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH82" s="4" t="n">
-        <v>3050.4</v>
+        <v>2820.03</v>
       </c>
       <c r="AI82" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ82" s="4" t="n">
         <v>0.84</v>
@@ -10679,19 +10679,17 @@
       </c>
       <c r="AO82" s="4" t="inlineStr">
         <is>
-          <t>Quality · Mean Reversion · Trend</t>
+          <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
       <c r="AP82" s="4" t="inlineStr"/>
-      <c r="AQ82" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AQ82" s="4" t="inlineStr"/>
       <c r="AR82" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -10721,24 +10719,24 @@
           <t>HCL Tech</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>81.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
@@ -10758,7 +10756,7 @@
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 8→2 · Conf 43% · band HOLD · 16d left · → STRONG BUY</t>
+          <t>Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R83" s="4" t="inlineStr"/>
@@ -10771,16 +10769,16 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
       <c r="V83" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W83" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X83" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y83" s="4" t="inlineStr">
         <is>
@@ -10788,34 +10786,34 @@
         </is>
       </c>
       <c r="Z83" s="4" t="n">
-        <v>1369.9</v>
+        <v>1346.6</v>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>1369.9</v>
+        <v>1346.6</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>1356.2</v>
+        <v>1333.13</v>
       </c>
       <c r="AC83" s="4" t="n">
-        <v>1383.6</v>
+        <v>1360.07</v>
       </c>
       <c r="AD83" s="4" t="n">
-        <v>1287.71</v>
+        <v>1279.27</v>
       </c>
       <c r="AE83" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF83" s="4" t="n">
-        <v>1534.29</v>
+        <v>1454.33</v>
       </c>
       <c r="AG83" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH83" s="4" t="n">
-        <v>1698.68</v>
+        <v>1548.59</v>
       </c>
       <c r="AI83" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ83" s="4" t="n">
         <v>0.46</v>
@@ -10832,19 +10830,17 @@
       </c>
       <c r="AO83" s="4" t="inlineStr">
         <is>
-          <t>Trend · Quality · Mean Reversion</t>
+          <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
       <c r="AP83" s="4" t="inlineStr"/>
-      <c r="AQ83" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="AQ83" s="4" t="inlineStr"/>
       <c r="AR83" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -10870,28 +10866,28 @@
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>69.5</v>
+        <v>78.8</v>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="N84" s="4" t="n">
@@ -10907,7 +10903,7 @@
       </c>
       <c r="Q84" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 6→3 · Conf 46% · band WATCH · 59d left · → BUY</t>
+          <t>Rank → 6→6 · Conf 46% · band WATCH→HOLD · 11d left · → HOLD</t>
         </is>
       </c>
       <c r="R84" s="4" t="inlineStr"/>
@@ -10920,16 +10916,16 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W84" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X84" s="4" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="Y84" s="4" t="inlineStr">
         <is>
@@ -10937,34 +10933,34 @@
         </is>
       </c>
       <c r="Z84" s="4" t="n">
-        <v>11600</v>
+        <v>11602</v>
       </c>
       <c r="AA84" s="4" t="n">
-        <v>11600</v>
+        <v>11602</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>11484</v>
+        <v>11485.98</v>
       </c>
       <c r="AC84" s="4" t="n">
-        <v>11716</v>
+        <v>11718.02</v>
       </c>
       <c r="AD84" s="4" t="n">
-        <v>10904</v>
+        <v>11021.9</v>
       </c>
       <c r="AE84" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="AF84" s="4" t="n">
-        <v>12992</v>
+        <v>12530.16</v>
       </c>
       <c r="AG84" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH84" s="4" t="n">
-        <v>14384</v>
+        <v>13342.3</v>
       </c>
       <c r="AI84" s="4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AJ84" s="4" t="n">
         <v>0.99</v>
@@ -10981,19 +10977,17 @@
       </c>
       <c r="AO84" s="4" t="inlineStr">
         <is>
-          <t>Quality · Growth · News</t>
+          <t>Quality · Growth · Momentum</t>
         </is>
       </c>
       <c r="AP84" s="4" t="inlineStr"/>
-      <c r="AQ84" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="AQ84" s="4" t="inlineStr"/>
       <c r="AR84" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11136,7 @@
       </c>
       <c r="AS85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11285,7 @@
       </c>
       <c r="AS86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -11321,30 +11315,24 @@
           <t>Hero MotoCorp</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+8.0pp)</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
       <c r="I87" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>79.8</v>
+        <v>75.7</v>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
@@ -11352,7 +11340,7 @@
         </is>
       </c>
       <c r="N87" s="4" t="n">
-        <v>37.6</v>
+        <v>39.8</v>
       </c>
       <c r="O87" s="4" t="n">
         <v>-0.8</v>
@@ -11364,12 +11352,12 @@
       </c>
       <c r="Q87" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 2→6 · Conf 38% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R87" s="4" t="inlineStr"/>
       <c r="S87" s="4" t="n">
-        <v>38.3</v>
+        <v>40.6</v>
       </c>
       <c r="T87" s="4" t="inlineStr">
         <is>
@@ -11377,16 +11365,16 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>21.6</v>
+        <v>26.2</v>
       </c>
       <c r="V87" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W87" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X87" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y87" s="4" t="inlineStr">
         <is>
@@ -11394,31 +11382,31 @@
         </is>
       </c>
       <c r="Z87" s="4" t="n">
-        <v>5548</v>
+        <v>5196.6</v>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>5548</v>
+        <v>5196.6</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>5492.52</v>
+        <v>5144.63</v>
       </c>
       <c r="AC87" s="4" t="n">
-        <v>5603.48</v>
+        <v>5248.57</v>
       </c>
       <c r="AD87" s="4" t="n">
-        <v>5270.6</v>
+        <v>4936.77</v>
       </c>
       <c r="AE87" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF87" s="4" t="n">
-        <v>5991.84</v>
+        <v>5612.33</v>
       </c>
       <c r="AG87" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH87" s="4" t="n">
-        <v>6380.2</v>
+        <v>5976.09</v>
       </c>
       <c r="AI87" s="4" t="n">
         <v>15</v>
@@ -11438,17 +11426,17 @@
       </c>
       <c r="AO87" s="4" t="inlineStr">
         <is>
-          <t>Trend · Quality · Growth</t>
+          <t>Quality · Growth · Ai Hybrid</t>
         </is>
       </c>
       <c r="AP87" s="4" t="inlineStr"/>
       <c r="AQ87" s="4" t="inlineStr"/>
       <c r="AR87" s="4" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11585,7 @@
       </c>
       <c r="AS88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11734,7 @@
       </c>
       <c r="AS89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11883,7 @@
       </c>
       <c r="AS90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -11921,19 +11909,13 @@
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+9.7pp)</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="inlineStr"/>
       <c r="I91" s="4" t="n">
         <v>10</v>
       </c>
@@ -11944,7 +11926,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="4" t="n">
-        <v>82</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
@@ -11952,7 +11934,7 @@
         </is>
       </c>
       <c r="N91" s="4" t="n">
-        <v>35.3</v>
+        <v>37.6</v>
       </c>
       <c r="O91" s="4" t="n">
         <v>-0.8</v>
@@ -11964,12 +11946,12 @@
       </c>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 36% · band HOLD · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank → 10→10 · Conf 38% · band HOLD · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R91" s="4" t="inlineStr"/>
       <c r="S91" s="4" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="T91" s="4" t="inlineStr">
         <is>
@@ -11977,16 +11959,16 @@
         </is>
       </c>
       <c r="U91" s="4" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="V91" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W91" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X91" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y91" s="4" t="inlineStr">
         <is>
@@ -11994,31 +11976,31 @@
         </is>
       </c>
       <c r="Z91" s="4" t="n">
-        <v>11475</v>
+        <v>10880</v>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>11475</v>
+        <v>10880</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>11360.25</v>
+        <v>10771.2</v>
       </c>
       <c r="AC91" s="4" t="n">
-        <v>11589.75</v>
+        <v>10988.8</v>
       </c>
       <c r="AD91" s="4" t="n">
-        <v>10901.25</v>
+        <v>10336</v>
       </c>
       <c r="AE91" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF91" s="4" t="n">
-        <v>12393</v>
+        <v>11750.4</v>
       </c>
       <c r="AG91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH91" s="4" t="n">
-        <v>13196.25</v>
+        <v>12512</v>
       </c>
       <c r="AI91" s="4" t="n">
         <v>15</v>
@@ -12038,17 +12020,17 @@
       </c>
       <c r="AO91" s="4" t="inlineStr">
         <is>
-          <t>Value · Quality · Growth</t>
+          <t>Value · Quality · Trend</t>
         </is>
       </c>
       <c r="AP91" s="4" t="inlineStr"/>
       <c r="AQ91" s="4" t="inlineStr"/>
       <c r="AR91" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12179,7 @@
       </c>
       <c r="AS92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -12346,7 +12328,7 @@
       </c>
       <c r="AS93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -12376,27 +12358,21 @@
           <t>Fortis Healthcare</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+57.8pp)</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="4" t="n">
         <v>52.2</v>
@@ -12419,7 +12395,7 @@
       </c>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 12→13 · Conf 25% · band REVIEW · 59d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↑ 12→11 · Conf 25% · band REVIEW · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R94" s="4" t="inlineStr"/>
@@ -12432,16 +12408,16 @@
         </is>
       </c>
       <c r="U94" s="4" t="n">
-        <v>-28.2</v>
+        <v>-26.6</v>
       </c>
       <c r="V94" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W94" s="4" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="X94" s="4" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="Y94" s="4" t="inlineStr">
         <is>
@@ -12449,31 +12425,31 @@
         </is>
       </c>
       <c r="Z94" s="4" t="n">
-        <v>932.8</v>
+        <v>952.55</v>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>932.8</v>
+        <v>952.55</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>923.47</v>
+        <v>943.02</v>
       </c>
       <c r="AC94" s="4" t="n">
-        <v>942.13</v>
+        <v>962.08</v>
       </c>
       <c r="AD94" s="4" t="n">
-        <v>886.16</v>
+        <v>904.92</v>
       </c>
       <c r="AE94" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF94" s="4" t="n">
-        <v>1007.42</v>
+        <v>1028.75</v>
       </c>
       <c r="AG94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH94" s="4" t="n">
-        <v>1072.72</v>
+        <v>1095.43</v>
       </c>
       <c r="AI94" s="4" t="n">
         <v>15</v>
@@ -12493,17 +12469,17 @@
       </c>
       <c r="AO94" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
       <c r="AP94" s="4" t="inlineStr"/>
       <c r="AQ94" s="4" t="inlineStr"/>
       <c r="AR94" s="4" t="n">
-        <v>57.8</v>
+        <v>8</v>
       </c>
       <c r="AS94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12628,7 @@
       </c>
       <c r="AS95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -12682,27 +12658,21 @@
           <t>Biocon</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Rotation → TCS.NS (+63.9pp)</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="inlineStr"/>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="n">
         <v>52.5</v>
@@ -12725,7 +12695,7 @@
       </c>
       <c r="Q96" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 11→15 · Conf 30% · band REVIEW · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>Rank ↓ 11→12 · Conf 30% · band REVIEW · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R96" s="4" t="inlineStr"/>
@@ -12738,16 +12708,16 @@
         </is>
       </c>
       <c r="U96" s="4" t="n">
-        <v>-34.3</v>
+        <v>-28.1</v>
       </c>
       <c r="V96" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W96" s="4" t="n">
         <v>17</v>
       </c>
       <c r="X96" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y96" s="4" t="inlineStr">
         <is>
@@ -12755,31 +12725,31 @@
         </is>
       </c>
       <c r="Z96" s="4" t="n">
-        <v>422</v>
+        <v>431.4</v>
       </c>
       <c r="AA96" s="4" t="n">
-        <v>422</v>
+        <v>431.4</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>417.78</v>
+        <v>427.09</v>
       </c>
       <c r="AC96" s="4" t="n">
-        <v>426.22</v>
+        <v>435.71</v>
       </c>
       <c r="AD96" s="4" t="n">
-        <v>400.9</v>
+        <v>409.83</v>
       </c>
       <c r="AE96" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AF96" s="4" t="n">
-        <v>455.76</v>
+        <v>465.91</v>
       </c>
       <c r="AG96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AH96" s="4" t="n">
-        <v>485.3</v>
+        <v>496.11</v>
       </c>
       <c r="AI96" s="4" t="n">
         <v>15</v>
@@ -12799,17 +12769,17 @@
       </c>
       <c r="AO96" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
       <c r="AP96" s="4" t="inlineStr"/>
       <c r="AQ96" s="4" t="inlineStr"/>
       <c r="AR96" s="4" t="n">
-        <v>63.94</v>
+        <v>8</v>
       </c>
       <c r="AS96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -12944,7 +12914,7 @@
       </c>
       <c r="AS97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13049,7 @@
       </c>
       <c r="AS98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13184,7 @@
       </c>
       <c r="AS99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13319,7 @@
       </c>
       <c r="AS100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13454,7 @@
       </c>
       <c r="AS101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13589,7 @@
       </c>
       <c r="AS102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13724,7 @@
       </c>
       <c r="AS103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13855,7 @@
       </c>
       <c r="AS104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 15:55</t>
         </is>
       </c>
     </row>
@@ -13923,13 +13893,13 @@
       <c r="G105" s="4" t="inlineStr"/>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="4" t="inlineStr"/>
       <c r="M105" s="4" t="inlineStr"/>
@@ -13938,7 +13908,7 @@
       <c r="P105" s="4" t="inlineStr"/>
       <c r="Q105" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 7→9 · Conf 67% · 61d left · → HOLD</t>
+          <t>Rank ↓ 7→8 · Conf 67% · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="R105" s="4" t="inlineStr"/>
@@ -14020,7 +13990,7 @@
       </c>
       <c r="AS105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14058,13 +14028,13 @@
       <c r="G106" s="4" t="inlineStr"/>
       <c r="H106" s="4" t="inlineStr"/>
       <c r="I106" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" s="4" t="inlineStr"/>
       <c r="M106" s="4" t="inlineStr"/>
@@ -14073,7 +14043,7 @@
       <c r="P106" s="4" t="inlineStr"/>
       <c r="Q106" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 8→10 · Conf 64% · 61d left · → BUY</t>
+          <t>Rank ↓ 8→9 · Conf 64% · 61d left · → BUY</t>
         </is>
       </c>
       <c r="R106" s="4" t="inlineStr"/>
@@ -14155,7 +14125,7 @@
       </c>
       <c r="AS106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14189,13 +14159,13 @@
       <c r="G107" s="4" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr"/>
       <c r="I107" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L107" s="4" t="inlineStr"/>
       <c r="M107" s="4" t="inlineStr"/>
@@ -14204,7 +14174,7 @@
       <c r="P107" s="4" t="inlineStr"/>
       <c r="Q107" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 9→11 · Conf 66% · 61d left · → HOLD</t>
+          <t>Rank ↓ 9→10 · Conf 66% · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="R107" s="4" t="inlineStr"/>
@@ -14286,7 +14256,7 @@
       </c>
       <c r="AS107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14324,13 +14294,13 @@
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr"/>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L108" s="4" t="inlineStr"/>
       <c r="M108" s="4" t="inlineStr"/>
@@ -14339,7 +14309,7 @@
       <c r="P108" s="4" t="inlineStr"/>
       <c r="Q108" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 10→12 · Conf 66% · 61d left · → BUY</t>
+          <t>Rank ↓ 10→11 · Conf 66% · 61d left · → BUY</t>
         </is>
       </c>
       <c r="R108" s="4" t="inlineStr"/>
@@ -14421,7 +14391,7 @@
       </c>
       <c r="AS108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14576,7 +14546,7 @@
       </c>
       <c r="AS109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14729,7 +14699,7 @@
       </c>
       <c r="AS110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14858,7 @@
       </c>
       <c r="AS111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15017,7 @@
       </c>
       <c r="AS112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15176,7 @@
       </c>
       <c r="AS113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15335,7 @@
       </c>
       <c r="AS114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15494,7 @@
       </c>
       <c r="AS115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15653,7 @@
       </c>
       <c r="AS116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -15842,7 +15812,7 @@
       </c>
       <c r="AS117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16001,7 +15971,7 @@
       </c>
       <c r="AS118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16160,7 +16130,7 @@
       </c>
       <c r="AS119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16289,7 @@
       </c>
       <c r="AS120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16448,7 @@
       </c>
       <c r="AS121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16607,7 @@
       </c>
       <c r="AS122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
@@ -16796,12 +16766,1200 @@
       </c>
       <c r="AS123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 15:46</t>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="O124" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P124" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 39% · band WATCH · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R124" s="4" t="inlineStr"/>
+      <c r="S124" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="T124" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U124" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="V124" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W124" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X124" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z124" s="4" t="n">
+        <v>133.14</v>
+      </c>
+      <c r="AA124" s="4" t="n">
+        <v>133.14</v>
+      </c>
+      <c r="AB124" s="4" t="n">
+        <v>131.81</v>
+      </c>
+      <c r="AC124" s="4" t="n">
+        <v>134.47</v>
+      </c>
+      <c r="AD124" s="4" t="n">
+        <v>126.48</v>
+      </c>
+      <c r="AE124" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF124" s="4" t="n">
+        <v>143.79</v>
+      </c>
+      <c r="AG124" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH124" s="4" t="n">
+        <v>153.11</v>
+      </c>
+      <c r="AI124" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ124" s="4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL124" s="4" t="inlineStr"/>
+      <c r="AM124" s="4" t="inlineStr"/>
+      <c r="AN124" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO124" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Momentum · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AP124" s="4" t="inlineStr"/>
+      <c r="AQ124" s="4" t="inlineStr"/>
+      <c r="AR124" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="M125" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N125" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O125" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P125" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 4→4 · Conf 41% · band HOLD · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R125" s="4" t="inlineStr"/>
+      <c r="S125" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="T125" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U125" s="4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V125" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W125" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X125" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z125" s="4" t="n">
+        <v>5524</v>
+      </c>
+      <c r="AA125" s="4" t="n">
+        <v>5524</v>
+      </c>
+      <c r="AB125" s="4" t="n">
+        <v>5468.76</v>
+      </c>
+      <c r="AC125" s="4" t="n">
+        <v>5579.24</v>
+      </c>
+      <c r="AD125" s="4" t="n">
+        <v>5247.8</v>
+      </c>
+      <c r="AE125" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF125" s="4" t="n">
+        <v>5965.92</v>
+      </c>
+      <c r="AG125" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH125" s="4" t="n">
+        <v>6352.6</v>
+      </c>
+      <c r="AI125" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ125" s="4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AK125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" s="4" t="inlineStr"/>
+      <c r="AM125" s="4" t="inlineStr"/>
+      <c r="AN125" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO125" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AP125" s="4" t="inlineStr"/>
+      <c r="AQ125" s="4" t="inlineStr"/>
+      <c r="AR125" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J126" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O126" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P126" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 41% · band HOLD · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R126" s="4" t="inlineStr"/>
+      <c r="S126" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="T126" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U126" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="V126" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W126" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X126" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z126" s="4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="AA126" s="4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="AB126" s="4" t="n">
+        <v>1146.42</v>
+      </c>
+      <c r="AC126" s="4" t="n">
+        <v>1169.58</v>
+      </c>
+      <c r="AD126" s="4" t="n">
+        <v>1100.1</v>
+      </c>
+      <c r="AE126" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF126" s="4" t="n">
+        <v>1250.64</v>
+      </c>
+      <c r="AG126" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH126" s="4" t="n">
+        <v>1331.7</v>
+      </c>
+      <c r="AI126" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ126" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AK126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="4" t="inlineStr"/>
+      <c r="AM126" s="4" t="inlineStr"/>
+      <c r="AN126" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO126" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Quality · Momentum</t>
+        </is>
+      </c>
+      <c r="AP126" s="4" t="inlineStr"/>
+      <c r="AQ126" s="4" t="inlineStr"/>
+      <c r="AR126" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J127" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="M127" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="O127" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P127" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 3→8 · Conf 38% · band WATCH · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R127" s="4" t="inlineStr"/>
+      <c r="S127" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="T127" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U127" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W127" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X127" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z127" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="AA127" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="AB127" s="4" t="n">
+        <v>444.86</v>
+      </c>
+      <c r="AC127" s="4" t="n">
+        <v>453.84</v>
+      </c>
+      <c r="AD127" s="4" t="n">
+        <v>426.88</v>
+      </c>
+      <c r="AE127" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF127" s="4" t="n">
+        <v>485.3</v>
+      </c>
+      <c r="AG127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH127" s="4" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="AI127" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ127" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL127" s="4" t="inlineStr"/>
+      <c r="AM127" s="4" t="inlineStr"/>
+      <c r="AN127" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO127" s="4" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Growth</t>
+        </is>
+      </c>
+      <c r="AP127" s="4" t="inlineStr"/>
+      <c r="AQ127" s="4" t="inlineStr"/>
+      <c r="AR127" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J128" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="O128" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P128" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 7→9 · Conf 38% · band WATCH · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R128" s="4" t="inlineStr"/>
+      <c r="S128" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="T128" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U128" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="V128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W128" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X128" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z128" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AA128" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AB128" s="4" t="n">
+        <v>284.33</v>
+      </c>
+      <c r="AC128" s="4" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="AD128" s="4" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="AE128" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF128" s="4" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="AG128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH128" s="4" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="AI128" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ128" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" s="4" t="inlineStr"/>
+      <c r="AM128" s="4" t="inlineStr"/>
+      <c r="AN128" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO128" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Value</t>
+        </is>
+      </c>
+      <c r="AP128" s="4" t="inlineStr"/>
+      <c r="AQ128" s="4" t="inlineStr"/>
+      <c r="AR128" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M129" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N129" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="O129" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P129" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 30% · band REVIEW · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R129" s="4" t="inlineStr"/>
+      <c r="S129" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="T129" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U129" s="4" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="V129" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W129" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X129" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z129" s="4" t="n">
+        <v>2157.8</v>
+      </c>
+      <c r="AA129" s="4" t="n">
+        <v>2157.8</v>
+      </c>
+      <c r="AB129" s="4" t="n">
+        <v>2136.22</v>
+      </c>
+      <c r="AC129" s="4" t="n">
+        <v>2179.38</v>
+      </c>
+      <c r="AD129" s="4" t="n">
+        <v>2049.91</v>
+      </c>
+      <c r="AE129" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF129" s="4" t="n">
+        <v>2330.42</v>
+      </c>
+      <c r="AG129" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH129" s="4" t="n">
+        <v>2481.47</v>
+      </c>
+      <c r="AI129" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ129" s="4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AK129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" s="4" t="inlineStr"/>
+      <c r="AM129" s="4" t="inlineStr"/>
+      <c r="AN129" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO129" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AP129" s="4" t="inlineStr"/>
+      <c r="AQ129" s="4" t="inlineStr"/>
+      <c r="AR129" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>JSW Energy</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J130" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K130" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="M130" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="O130" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P130" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↓ 13→14 · Conf 25% · band REVIEW · 53d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R130" s="4" t="inlineStr"/>
+      <c r="S130" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="T130" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U130" s="4" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="V130" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W130" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X130" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z130" s="4" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="AA130" s="4" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="AB130" s="4" t="n">
+        <v>541.9299999999999</v>
+      </c>
+      <c r="AC130" s="4" t="n">
+        <v>552.87</v>
+      </c>
+      <c r="AD130" s="4" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="AE130" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF130" s="4" t="n">
+        <v>591.1900000000001</v>
+      </c>
+      <c r="AG130" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH130" s="4" t="n">
+        <v>629.51</v>
+      </c>
+      <c r="AI130" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ130" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL130" s="4" t="inlineStr"/>
+      <c r="AM130" s="4" t="inlineStr"/>
+      <c r="AN130" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO130" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AP130" s="4" t="inlineStr"/>
+      <c r="AQ130" s="4" t="inlineStr"/>
+      <c r="AR130" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="inlineStr"/>
+      <c r="I131" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J131" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K131" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O131" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P131" s="4" t="inlineStr">
+        <is>
+          <t>no material context signals</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · band REVIEW · 54d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="R131" s="4" t="inlineStr"/>
+      <c r="S131" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="T131" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="U131" s="4" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="V131" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W131" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="X131" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y131" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z131" s="4" t="n">
+        <v>1363</v>
+      </c>
+      <c r="AA131" s="4" t="n">
+        <v>1363</v>
+      </c>
+      <c r="AB131" s="4" t="n">
+        <v>1349.37</v>
+      </c>
+      <c r="AC131" s="4" t="n">
+        <v>1376.63</v>
+      </c>
+      <c r="AD131" s="4" t="n">
+        <v>1294.85</v>
+      </c>
+      <c r="AE131" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF131" s="4" t="n">
+        <v>1472.04</v>
+      </c>
+      <c r="AG131" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH131" s="4" t="n">
+        <v>1567.45</v>
+      </c>
+      <c r="AI131" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ131" s="4" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AK131" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL131" s="4" t="inlineStr"/>
+      <c r="AM131" s="4" t="inlineStr"/>
+      <c r="AN131" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AO131" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AP131" s="4" t="inlineStr"/>
+      <c r="AQ131" s="4" t="inlineStr"/>
+      <c r="AR131" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS131" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS123"/>
+  <autoFilter ref="A1:AS131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10593,19 +10593,19 @@
         </is>
       </c>
       <c r="N82" s="4" t="n">
-        <v>38.6</v>
+        <v>36.6</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 9→1 · Conf 39% · band HOLD→WATCH · 10d left · → HOLD</t>
+          <t>Rank ↑ 9→1 · Conf 39% · band WATCH · 10d left · → HOLD</t>
         </is>
       </c>
       <c r="R82" s="4" t="inlineStr"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="AS82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -10744,14 +10744,14 @@
         </is>
       </c>
       <c r="N83" s="4" t="n">
-        <v>42.4</v>
+        <v>40.4</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="AS83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -10891,19 +10891,19 @@
         </is>
       </c>
       <c r="N84" s="4" t="n">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q84" s="4" t="inlineStr">
         <is>
-          <t>Rank → 6→6 · Conf 46% · band WATCH→HOLD · 11d left · → HOLD</t>
+          <t>Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
         </is>
       </c>
       <c r="R84" s="4" t="inlineStr"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="AS84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -11340,14 +11340,14 @@
         </is>
       </c>
       <c r="N87" s="4" t="n">
-        <v>39.8</v>
+        <v>37.8</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q87" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="AS87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -11934,14 +11934,14 @@
         </is>
       </c>
       <c r="N91" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q91" s="4" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="AS91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -12383,14 +12383,14 @@
         </is>
       </c>
       <c r="N94" s="4" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q94" s="4" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="AS94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -12683,14 +12683,14 @@
         </is>
       </c>
       <c r="N96" s="4" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q96" s="4" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="AS96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AS97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="AS98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AS99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="AS100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="AS101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13589,7 +13589,7 @@
       </c>
       <c r="AS102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="AS103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="AS105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="AS106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14256,7 +14256,7 @@
       </c>
       <c r="AS107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="AS108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="AS109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="AS110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="AS111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15017,7 +15017,7 @@
       </c>
       <c r="AS112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="AS113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="AS114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="AS115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="AS116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="AS117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15971,7 @@
       </c>
       <c r="AS118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="AS119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AS120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AS121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AS122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="AS123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16817,14 +16817,14 @@
         </is>
       </c>
       <c r="N124" s="4" t="n">
-        <v>38.6</v>
+        <v>36.6</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q124" s="4" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="AS124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -16964,14 +16964,14 @@
         </is>
       </c>
       <c r="N125" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O125" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q125" s="4" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="AS125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17111,14 +17111,14 @@
         </is>
       </c>
       <c r="N126" s="4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q126" s="4" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="AS126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17262,14 +17262,14 @@
         </is>
       </c>
       <c r="N127" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q127" s="4" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="AS127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17413,14 +17413,14 @@
         </is>
       </c>
       <c r="N128" s="4" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q128" s="4" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="AS128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17560,14 +17560,14 @@
         </is>
       </c>
       <c r="N129" s="4" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="O129" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q129" s="4" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AS129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17711,14 +17711,14 @@
         </is>
       </c>
       <c r="N130" s="4" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q130" s="4" t="inlineStr">
@@ -17807,7 +17807,7 @@
       </c>
       <c r="AS130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>
@@ -17858,14 +17858,14 @@
         </is>
       </c>
       <c r="N131" s="4" t="n">
-        <v>27.6</v>
+        <v>25.6</v>
       </c>
       <c r="O131" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.8</v>
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>no material context signals</t>
+          <t>overall breadth 23.3% → -2.0pts</t>
         </is>
       </c>
       <c r="Q131" s="4" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AS131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:00</t>
+          <t>2026-08-05 16:18</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AV132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AV133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AV134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AV135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="AV136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18636,7 +18636,7 @@
       </c>
       <c r="AV137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="AV138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="AV139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="AV140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="AV141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="AV142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="AV143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="AV144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AV145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="AV146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20062,7 +20062,7 @@
       <c r="S147" s="4" t="inlineStr"/>
       <c r="T147" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 2→1 · Conf 83% · 61d left · → STRONG BUY</t>
+          <t>Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U147" s="4" t="inlineStr"/>
@@ -20071,7 +20071,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X147" s="4" t="n">
@@ -20096,10 +20096,10 @@
         <v>1454.6</v>
       </c>
       <c r="AE147" s="4" t="n">
-        <v>1440.05</v>
+        <v>1415</v>
       </c>
       <c r="AF147" s="4" t="n">
-        <v>1469.15</v>
+        <v>1495</v>
       </c>
       <c r="AG147" s="4" t="n">
         <v>1381.87</v>
@@ -20114,10 +20114,10 @@
         <v>5.32</v>
       </c>
       <c r="AK147" s="4" t="n">
-        <v>1672.79</v>
+        <v>1639.24</v>
       </c>
       <c r="AL147" s="4" t="n">
-        <v>15</v>
+        <v>12.69</v>
       </c>
       <c r="AM147" s="4" t="n">
         <v>0.35</v>
@@ -20138,13 +20138,15 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT147" s="4" t="inlineStr"/>
+      <c r="AT147" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU147" s="4" t="n">
         <v>5.32</v>
       </c>
       <c r="AV147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20202,7 @@
       <c r="S148" s="4" t="inlineStr"/>
       <c r="T148" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 1→2 · Conf 88% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U148" s="4" t="inlineStr"/>
@@ -20209,7 +20211,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X148" s="4" t="n">
@@ -20234,10 +20236,10 @@
         <v>1964</v>
       </c>
       <c r="AE148" s="4" t="n">
-        <v>1944.36</v>
+        <v>1911</v>
       </c>
       <c r="AF148" s="4" t="n">
-        <v>1983.64</v>
+        <v>2017</v>
       </c>
       <c r="AG148" s="4" t="n">
         <v>1865.8</v>
@@ -20252,10 +20254,10 @@
         <v>4.58</v>
       </c>
       <c r="AK148" s="4" t="n">
-        <v>2258.6</v>
+        <v>2197.78</v>
       </c>
       <c r="AL148" s="4" t="n">
-        <v>15</v>
+        <v>11.9</v>
       </c>
       <c r="AM148" s="4" t="n">
         <v>0.44</v>
@@ -20276,13 +20278,15 @@
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT148" s="4" t="inlineStr"/>
+      <c r="AT148" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU148" s="4" t="n">
         <v>4.58</v>
       </c>
       <c r="AV148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20342,7 @@
       <c r="S149" s="4" t="inlineStr"/>
       <c r="T149" s="4" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 86% · 61d left · → STRONG BUY</t>
+          <t>Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U149" s="4" t="inlineStr"/>
@@ -20347,7 +20351,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X149" s="4" t="n">
@@ -20372,10 +20376,10 @@
         <v>1620</v>
       </c>
       <c r="AE149" s="4" t="n">
-        <v>1603.8</v>
+        <v>1569</v>
       </c>
       <c r="AF149" s="4" t="n">
-        <v>1636.2</v>
+        <v>1671</v>
       </c>
       <c r="AG149" s="4" t="n">
         <v>1539</v>
@@ -20390,10 +20394,10 @@
         <v>1.36</v>
       </c>
       <c r="AK149" s="4" t="n">
-        <v>1863</v>
+        <v>1756.94</v>
       </c>
       <c r="AL149" s="4" t="n">
-        <v>15</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AM149" s="4" t="n">
         <v>-1.37</v>
@@ -20414,13 +20418,15 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="AT149" s="4" t="inlineStr"/>
+      <c r="AT149" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU149" s="4" t="n">
         <v>1.36</v>
       </c>
       <c r="AV149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20476,7 +20482,7 @@
       <c r="S150" s="4" t="inlineStr"/>
       <c r="T150" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 3→4 · Conf 71% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U150" s="4" t="inlineStr"/>
@@ -20485,7 +20491,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X150" s="4" t="n">
@@ -20510,10 +20516,10 @@
         <v>2410</v>
       </c>
       <c r="AE150" s="4" t="n">
-        <v>2385.9</v>
+        <v>2349</v>
       </c>
       <c r="AF150" s="4" t="n">
-        <v>2434.1</v>
+        <v>2471</v>
       </c>
       <c r="AG150" s="4" t="n">
         <v>2289.5</v>
@@ -20528,10 +20534,10 @@
         <v>8</v>
       </c>
       <c r="AK150" s="4" t="n">
-        <v>2771.5</v>
+        <v>2784.996000000001</v>
       </c>
       <c r="AL150" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM150" s="4" t="n">
         <v>1.09</v>
@@ -20552,13 +20558,15 @@
           <t>Pharma</t>
         </is>
       </c>
-      <c r="AT150" s="4" t="inlineStr"/>
+      <c r="AT150" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20622,7 @@
       <c r="S151" s="4" t="inlineStr"/>
       <c r="T151" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 4→5 · Conf 72% · 61d left · → STRONG BUY</t>
+          <t>Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="U151" s="4" t="inlineStr"/>
@@ -20623,7 +20631,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X151" s="4" t="n">
@@ -20648,10 +20656,10 @@
         <v>343.6</v>
       </c>
       <c r="AE151" s="4" t="n">
-        <v>340.16</v>
+        <v>335</v>
       </c>
       <c r="AF151" s="4" t="n">
-        <v>347.04</v>
+        <v>353</v>
       </c>
       <c r="AG151" s="4" t="n">
         <v>326.42</v>
@@ -20666,10 +20674,10 @@
         <v>8</v>
       </c>
       <c r="AK151" s="4" t="n">
-        <v>395.14</v>
+        <v>397.0641600000001</v>
       </c>
       <c r="AL151" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM151" s="4" t="n">
         <v>-1.04</v>
@@ -20690,13 +20698,15 @@
           <t>Power</t>
         </is>
       </c>
-      <c r="AT151" s="4" t="inlineStr"/>
+      <c r="AT151" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU151" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20752,7 +20762,7 @@
       <c r="S152" s="4" t="inlineStr"/>
       <c r="T152" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 5→6 · Conf 72% · 61d left · → BUY</t>
+          <t>Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U152" s="4" t="inlineStr"/>
@@ -20761,7 +20771,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X152" s="4" t="n">
@@ -20786,10 +20796,10 @@
         <v>398</v>
       </c>
       <c r="AE152" s="4" t="n">
-        <v>394.02</v>
+        <v>386</v>
       </c>
       <c r="AF152" s="4" t="n">
-        <v>401.98</v>
+        <v>410</v>
       </c>
       <c r="AG152" s="4" t="n">
         <v>378.1</v>
@@ -20804,10 +20814,10 @@
         <v>8</v>
       </c>
       <c r="AK152" s="4" t="n">
-        <v>457.7</v>
+        <v>459.9288000000001</v>
       </c>
       <c r="AL152" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM152" s="4" t="n">
         <v>0.25</v>
@@ -20828,13 +20838,15 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="AT152" s="4" t="inlineStr"/>
+      <c r="AT152" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU152" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -20890,7 +20902,7 @@
       <c r="S153" s="4" t="inlineStr"/>
       <c r="T153" s="4" t="inlineStr">
         <is>
-          <t>Rank → 7→7 · Conf 69% · 61d left · → BUY</t>
+          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U153" s="4" t="inlineStr"/>
@@ -20899,7 +20911,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X153" s="4" t="n">
@@ -20924,10 +20936,10 @@
         <v>283.4</v>
       </c>
       <c r="AE153" s="4" t="n">
-        <v>280.57</v>
+        <v>276</v>
       </c>
       <c r="AF153" s="4" t="n">
-        <v>286.23</v>
+        <v>290</v>
       </c>
       <c r="AG153" s="4" t="n">
         <v>269.23</v>
@@ -20942,10 +20954,10 @@
         <v>8</v>
       </c>
       <c r="AK153" s="4" t="n">
-        <v>325.91</v>
+        <v>327.49704</v>
       </c>
       <c r="AL153" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM153" s="4" t="n">
         <v>-0.86</v>
@@ -20966,13 +20978,15 @@
           <t>Power</t>
         </is>
       </c>
-      <c r="AT153" s="4" t="inlineStr"/>
+      <c r="AT153" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21028,7 +21042,7 @@
       <c r="S154" s="4" t="inlineStr"/>
       <c r="T154" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 7→8 · Conf 67% · 61d left · → HOLD</t>
+          <t>Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U154" s="4" t="inlineStr"/>
@@ -21037,7 +21051,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X154" s="4" t="n">
@@ -21062,10 +21076,10 @@
         <v>510.2</v>
       </c>
       <c r="AE154" s="4" t="n">
-        <v>505.1</v>
+        <v>495</v>
       </c>
       <c r="AF154" s="4" t="n">
-        <v>515.3</v>
+        <v>526</v>
       </c>
       <c r="AG154" s="4" t="n">
         <v>484.6899999999999</v>
@@ -21080,10 +21094,10 @@
         <v>8</v>
       </c>
       <c r="AK154" s="4" t="n">
-        <v>586.7299999999999</v>
+        <v>589.5871200000001</v>
       </c>
       <c r="AL154" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM154" s="4" t="n">
         <v>0.46</v>
@@ -21104,13 +21118,15 @@
           <t>Transport</t>
         </is>
       </c>
-      <c r="AT154" s="4" t="inlineStr"/>
+      <c r="AT154" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU154" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21182,7 @@
       <c r="S155" s="4" t="inlineStr"/>
       <c r="T155" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 8→9 · Conf 64% · 61d left · → BUY</t>
+          <t>Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U155" s="4" t="inlineStr"/>
@@ -21175,7 +21191,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X155" s="4" t="n">
@@ -21200,10 +21216,10 @@
         <v>391.5</v>
       </c>
       <c r="AE155" s="4" t="n">
-        <v>387.58</v>
+        <v>379</v>
       </c>
       <c r="AF155" s="4" t="n">
-        <v>395.42</v>
+        <v>404</v>
       </c>
       <c r="AG155" s="4" t="n">
         <v>371.925</v>
@@ -21218,10 +21234,10 @@
         <v>8</v>
       </c>
       <c r="AK155" s="4" t="n">
-        <v>450.225</v>
+        <v>452.4174000000001</v>
       </c>
       <c r="AL155" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM155" s="4" t="n">
         <v>0.42</v>
@@ -21242,13 +21258,15 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="AT155" s="4" t="inlineStr"/>
+      <c r="AT155" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU155" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21300,7 +21318,7 @@
       <c r="S156" s="4" t="inlineStr"/>
       <c r="T156" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 9→10 · Conf 66% · 61d left · → HOLD</t>
+          <t>Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U156" s="4" t="inlineStr"/>
@@ -21309,7 +21327,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X156" s="4" t="n">
@@ -21334,10 +21352,10 @@
         <v>5478</v>
       </c>
       <c r="AE156" s="4" t="n">
-        <v>5423.22</v>
+        <v>5335</v>
       </c>
       <c r="AF156" s="4" t="n">
-        <v>5532.78</v>
+        <v>5621</v>
       </c>
       <c r="AG156" s="4" t="n">
         <v>5204.099999999999</v>
@@ -21352,10 +21370,10 @@
         <v>8</v>
       </c>
       <c r="AK156" s="4" t="n">
-        <v>6299.7</v>
+        <v>6330.376800000001</v>
       </c>
       <c r="AL156" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM156" s="4" t="n">
         <v>0.43</v>
@@ -21376,13 +21394,15 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="AT156" s="4" t="inlineStr"/>
+      <c r="AT156" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU156" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21438,7 +21458,7 @@
       <c r="S157" s="4" t="inlineStr"/>
       <c r="T157" s="4" t="inlineStr">
         <is>
-          <t>Rank ↓ 10→11 · Conf 66% · 61d left · → BUY</t>
+          <t>Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="U157" s="4" t="inlineStr"/>
@@ -21447,7 +21467,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Calibrated</t>
         </is>
       </c>
       <c r="X157" s="4" t="n">
@@ -21472,10 +21492,10 @@
         <v>417.6</v>
       </c>
       <c r="AE157" s="4" t="n">
-        <v>413.42</v>
+        <v>405</v>
       </c>
       <c r="AF157" s="4" t="n">
-        <v>421.78</v>
+        <v>430</v>
       </c>
       <c r="AG157" s="4" t="n">
         <v>396.72</v>
@@ -21490,10 +21510,10 @@
         <v>8</v>
       </c>
       <c r="AK157" s="4" t="n">
-        <v>480.24</v>
+        <v>482.5785600000001</v>
       </c>
       <c r="AL157" s="4" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM157" s="4" t="n">
         <v>0.59</v>
@@ -21514,13 +21534,15 @@
           <t>Metal</t>
         </is>
       </c>
-      <c r="AT157" s="4" t="inlineStr"/>
+      <c r="AT157" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AU157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AV157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21680,7 +21702,7 @@
       </c>
       <c r="AV158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21862,7 @@
       </c>
       <c r="AV159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22026,7 @@
       </c>
       <c r="AV160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22190,7 @@
       </c>
       <c r="AV161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22356,7 @@
       </c>
       <c r="AV162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22498,7 +22520,7 @@
       </c>
       <c r="AV163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22664,7 +22686,7 @@
       </c>
       <c r="AV164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22732,11 +22754,11 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 32 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R165" s="4" t="n">
         <v>0.15</v>
@@ -22830,7 +22852,7 @@
       </c>
       <c r="AV165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -22996,7 +23018,7 @@
       </c>
       <c r="AV166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23160,7 +23182,7 @@
       </c>
       <c r="AV167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23346,7 @@
       </c>
       <c r="AV168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23490,7 +23512,7 @@
       </c>
       <c r="AV169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23656,7 +23678,7 @@
       </c>
       <c r="AV170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23844,7 @@
       </c>
       <c r="AV171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>
@@ -23988,7 +24010,7 @@
       </c>
       <c r="AV172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 00:43</t>
+          <t>2026-08-06 02:17</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV172"/>
+  <dimension ref="A1:AV182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AV132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AV133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="AV134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AV135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="AV136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18636,7 +18636,7 @@
       </c>
       <c r="AV137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18786,7 +18786,7 @@
       </c>
       <c r="AV138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="AV139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="AV140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="AV141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="AV142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="AV143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19702,7 @@
       </c>
       <c r="AV144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19856,7 @@
       </c>
       <c r="AV145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="AV146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20146,7 +20146,7 @@
       </c>
       <c r="AV147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20286,7 @@
       </c>
       <c r="AV148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="AV149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="AV150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="AV151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="AV152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="AV153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="AV154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="AV155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="AV156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="AV157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21702,7 +21702,7 @@
       </c>
       <c r="AV158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -21862,7 +21862,7 @@
       </c>
       <c r="AV159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="AV160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="AV161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="AV162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="AV163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22686,7 +22686,7 @@
       </c>
       <c r="AV164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="AV165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="AV166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23182,7 +23182,7 @@
       </c>
       <c r="AV167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="AV168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23512,7 +23512,7 @@
       </c>
       <c r="AV169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="AV170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="AV171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
@@ -24010,12 +24010,1562 @@
       </c>
       <c r="AV172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:17</t>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr"/>
+      <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr"/>
+      <c r="L173" s="4" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M173" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O173" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P173" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q173" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" s="4" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="S173" s="4" t="inlineStr"/>
+      <c r="T173" s="4" t="inlineStr">
+        <is>
+          <t>Rank #1 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U173" s="4" t="inlineStr"/>
+      <c r="V173" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W173" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X173" s="4" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="Y173" s="4" t="inlineStr"/>
+      <c r="Z173" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA173" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB173" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC173" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AD173" s="4" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AE173" s="4" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AF173" s="4" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AG173" s="4" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AH173" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI173" s="4" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AJ173" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK173" s="4" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AL173" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM173" s="4" t="inlineStr"/>
+      <c r="AN173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO173" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ173" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR173" s="4" t="inlineStr"/>
+      <c r="AS173" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT173" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU173" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV173" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr"/>
+      <c r="H174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr"/>
+      <c r="L174" s="4" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="M174" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="O174" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P174" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R174" s="4" t="inlineStr"/>
+      <c r="S174" s="4" t="inlineStr"/>
+      <c r="T174" s="4" t="inlineStr">
+        <is>
+          <t>Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U174" s="4" t="inlineStr"/>
+      <c r="V174" s="4" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="W174" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X174" s="4" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="Y174" s="4" t="inlineStr"/>
+      <c r="Z174" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA174" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB174" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC174" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AD174" s="4" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AE174" s="4" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AF174" s="4" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AG174" s="4" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AH174" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI174" s="4" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AJ174" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK174" s="4" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AL174" s="4" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AM174" s="4" t="inlineStr"/>
+      <c r="AN174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO174" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ174" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR174" s="4" t="inlineStr"/>
+      <c r="AS174" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT174" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU174" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV174" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr"/>
+      <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="M175" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="O175" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P175" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q175" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="R175" s="4" t="inlineStr"/>
+      <c r="S175" s="4" t="inlineStr"/>
+      <c r="T175" s="4" t="inlineStr">
+        <is>
+          <t>Rank #3 · Conf 47% · momentum → · band WATCH · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U175" s="4" t="inlineStr"/>
+      <c r="V175" s="4" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W175" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X175" s="4" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Y175" s="4" t="inlineStr"/>
+      <c r="Z175" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA175" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB175" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC175" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AD175" s="4" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AE175" s="4" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AF175" s="4" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AG175" s="4" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AH175" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI175" s="4" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AJ175" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK175" s="4" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AL175" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM175" s="4" t="inlineStr"/>
+      <c r="AN175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP175" s="4" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AQ175" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR175" s="4" t="inlineStr"/>
+      <c r="AS175" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT175" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU175" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV175" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr"/>
+      <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="M176" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O176" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P176" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="R176" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S176" s="4" t="inlineStr"/>
+      <c r="T176" s="4" t="inlineStr">
+        <is>
+          <t>Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U176" s="4" t="inlineStr"/>
+      <c r="V176" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W176" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X176" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y176" s="4" t="inlineStr"/>
+      <c r="Z176" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA176" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB176" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC176" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AD176" s="4" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AE176" s="4" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AF176" s="4" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AG176" s="4" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AH176" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI176" s="4" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AJ176" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK176" s="4" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AL176" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM176" s="4" t="inlineStr"/>
+      <c r="AN176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO176" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ176" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR176" s="4" t="inlineStr"/>
+      <c r="AS176" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT176" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU176" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV176" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="M177" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N177" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O177" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P177" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q177" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="R177" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="S177" s="4" t="inlineStr"/>
+      <c r="T177" s="4" t="inlineStr">
+        <is>
+          <t>Rank #5 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U177" s="4" t="inlineStr"/>
+      <c r="V177" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W177" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X177" s="4" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="Y177" s="4" t="inlineStr"/>
+      <c r="Z177" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA177" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB177" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC177" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AD177" s="4" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AE177" s="4" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AF177" s="4" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AG177" s="4" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AH177" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI177" s="4" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AJ177" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK177" s="4" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AL177" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM177" s="4" t="inlineStr"/>
+      <c r="AN177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO177" s="4" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AP177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ177" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR177" s="4" t="inlineStr"/>
+      <c r="AS177" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT177" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU177" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV177" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr"/>
+      <c r="H178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr"/>
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="M178" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O178" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P178" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="R178" s="4" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="S178" s="4" t="inlineStr"/>
+      <c r="T178" s="4" t="inlineStr">
+        <is>
+          <t>Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U178" s="4" t="inlineStr"/>
+      <c r="V178" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W178" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X178" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="Y178" s="4" t="inlineStr"/>
+      <c r="Z178" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA178" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB178" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC178" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AD178" s="4" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AE178" s="4" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AF178" s="4" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AG178" s="4" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AH178" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI178" s="4" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AJ178" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK178" s="4" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AL178" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM178" s="4" t="inlineStr"/>
+      <c r="AN178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO178" s="4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AP178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ178" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR178" s="4" t="inlineStr"/>
+      <c r="AS178" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT178" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU178" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV178" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr"/>
+      <c r="H179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr"/>
+      <c r="K179" s="4" t="inlineStr"/>
+      <c r="L179" s="4" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="M179" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="O179" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P179" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q179" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R179" s="4" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="S179" s="4" t="inlineStr"/>
+      <c r="T179" s="4" t="inlineStr">
+        <is>
+          <t>Rank #7 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U179" s="4" t="inlineStr"/>
+      <c r="V179" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W179" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X179" s="4" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="Y179" s="4" t="inlineStr"/>
+      <c r="Z179" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA179" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB179" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC179" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AD179" s="4" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AE179" s="4" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AF179" s="4" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AG179" s="4" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AH179" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI179" s="4" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AJ179" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK179" s="4" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AL179" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM179" s="4" t="inlineStr"/>
+      <c r="AN179" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP179" s="4" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="AQ179" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR179" s="4" t="inlineStr"/>
+      <c r="AS179" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT179" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU179" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV179" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr"/>
+      <c r="H180" s="4" t="inlineStr"/>
+      <c r="I180" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr"/>
+      <c r="K180" s="4" t="inlineStr"/>
+      <c r="L180" s="4" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="O180" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P180" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R180" s="4" t="inlineStr"/>
+      <c r="S180" s="4" t="inlineStr"/>
+      <c r="T180" s="4" t="inlineStr">
+        <is>
+          <t>Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U180" s="4" t="inlineStr"/>
+      <c r="V180" s="4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W180" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X180" s="4" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="Y180" s="4" t="inlineStr"/>
+      <c r="Z180" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA180" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB180" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC180" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AD180" s="4" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AE180" s="4" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AF180" s="4" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AG180" s="4" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AH180" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI180" s="4" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AJ180" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK180" s="4" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AL180" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM180" s="4" t="inlineStr"/>
+      <c r="AN180" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AP180" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ180" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR180" s="4" t="inlineStr"/>
+      <c r="AS180" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT180" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU180" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV180" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J181" s="4" t="inlineStr"/>
+      <c r="K181" s="4" t="inlineStr"/>
+      <c r="L181" s="4" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="M181" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="N181" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="O181" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P181" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q181" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R181" s="4" t="inlineStr"/>
+      <c r="S181" s="4" t="inlineStr"/>
+      <c r="T181" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 51% · momentum → · band WATCH · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U181" s="4" t="inlineStr"/>
+      <c r="V181" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="W181" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X181" s="4" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Y181" s="4" t="inlineStr"/>
+      <c r="Z181" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA181" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB181" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AC181" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AD181" s="4" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AE181" s="4" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AF181" s="4" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AG181" s="4" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AH181" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI181" s="4" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AJ181" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK181" s="4" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AL181" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM181" s="4" t="inlineStr"/>
+      <c r="AN181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP181" s="4" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AQ181" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR181" s="4" t="inlineStr"/>
+      <c r="AS181" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT181" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU181" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV181" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr"/>
+      <c r="H182" s="4" t="inlineStr"/>
+      <c r="I182" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J182" s="4" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr"/>
+      <c r="L182" s="4" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O182" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P182" s="4" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="R182" s="4" t="inlineStr"/>
+      <c r="S182" s="4" t="inlineStr"/>
+      <c r="T182" s="4" t="inlineStr">
+        <is>
+          <t>Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U182" s="4" t="inlineStr"/>
+      <c r="V182" s="4" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W182" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X182" s="4" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Y182" s="4" t="inlineStr"/>
+      <c r="Z182" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA182" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB182" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AC182" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AD182" s="4" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AE182" s="4" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AF182" s="4" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AG182" s="4" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AH182" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI182" s="4" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AJ182" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK182" s="4" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AL182" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AM182" s="4" t="inlineStr"/>
+      <c r="AN182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO182" s="4" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AP182" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ182" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AR182" s="4" t="inlineStr"/>
+      <c r="AS182" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT182" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU182" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV182" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 02:20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV172"/>
+  <autoFilter ref="A1:AV182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fresh Buys" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AW$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AEGIS Daily'!$A$1:$AW$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -105,6 +106,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,6 +475,756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Zone Δ %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Base Conf %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Adj Conf %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Why Fresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>11602</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1346.6</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>5524</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>5196.6</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>2452.2</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>133.14</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>institutional flow ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AW182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17518,7 +18272,7 @@
       </c>
       <c r="AW132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -17679,7 +18433,7 @@
       </c>
       <c r="AW133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -17836,7 +18590,7 @@
       </c>
       <c r="AW134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -17993,7 +18747,7 @@
       </c>
       <c r="AW135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18908,7 @@
       </c>
       <c r="AW136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18311,7 +19065,7 @@
       </c>
       <c r="AW137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18468,7 +19222,7 @@
       </c>
       <c r="AW138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18629,7 +19383,7 @@
       </c>
       <c r="AW139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18786,7 +19540,7 @@
       </c>
       <c r="AW140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -18939,7 +19693,7 @@
       </c>
       <c r="AW141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19850,7 @@
       </c>
       <c r="AW142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19253,7 +20007,7 @@
       </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19406,7 +20160,7 @@
       </c>
       <c r="AW144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19563,7 +20317,7 @@
       </c>
       <c r="AW145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19716,7 +20470,7 @@
       </c>
       <c r="AW146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19857,7 +20611,7 @@
       </c>
       <c r="AW147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -19998,7 +20752,7 @@
       </c>
       <c r="AW148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20893,7 @@
       </c>
       <c r="AW149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20280,7 +21034,7 @@
       </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20421,7 +21175,7 @@
       </c>
       <c r="AW151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20562,7 +21316,7 @@
       </c>
       <c r="AW152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20703,7 +21457,7 @@
       </c>
       <c r="AW153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20844,7 +21598,7 @@
       </c>
       <c r="AW154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -20985,7 +21739,7 @@
       </c>
       <c r="AW155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21122,7 +21876,7 @@
       </c>
       <c r="AW156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21263,7 +22017,7 @@
       </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21430,7 +22184,7 @@
       </c>
       <c r="AW158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21597,7 +22351,7 @@
       </c>
       <c r="AW159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21768,7 +22522,7 @@
       </c>
       <c r="AW160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -21939,7 +22693,7 @@
       </c>
       <c r="AW161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22866,7 @@
       </c>
       <c r="AW162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22283,7 +23037,7 @@
       </c>
       <c r="AW163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22456,7 +23210,7 @@
       </c>
       <c r="AW164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22629,7 +23383,7 @@
       </c>
       <c r="AW165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22798,7 +23552,7 @@
       </c>
       <c r="AW166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -22965,7 +23719,7 @@
       </c>
       <c r="AW167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23132,7 +23886,7 @@
       </c>
       <c r="AW168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23301,7 +24055,7 @@
       </c>
       <c r="AW169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23470,7 +24224,7 @@
       </c>
       <c r="AW170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23639,7 +24393,7 @@
       </c>
       <c r="AW171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23808,7 +24562,7 @@
       </c>
       <c r="AW172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -23971,7 +24725,7 @@
       </c>
       <c r="AW173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24132,7 +24886,7 @@
       </c>
       <c r="AW174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24293,7 +25047,7 @@
       </c>
       <c r="AW175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24456,7 +25210,7 @@
       </c>
       <c r="AW176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24615,7 +25369,7 @@
       </c>
       <c r="AW177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24778,7 +25532,7 @@
       </c>
       <c r="AW178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -24941,7 +25695,7 @@
       </c>
       <c r="AW179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -25102,7 +25856,7 @@
       </c>
       <c r="AW180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -25263,7 +26017,7 @@
       </c>
       <c r="AW181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>
@@ -25420,7 +26174,7 @@
       </c>
       <c r="AW182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:32</t>
+          <t>2026-08-06 03:38</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fresh Buys" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fresh Buys" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AEGIS Daily" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AEGIS Daily'!$A$1:$AW$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'AEGIS Daily'!$A$1:$AW$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>11602</v>
+        <v>11727</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>-1.96</v>
+        <v>-0.99</v>
       </c>
       <c r="G2" s="8" t="n">
         <v>46.4</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>1346.6</v>
+        <v>1351.3</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>-1.96</v>
@@ -617,7 +617,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>5524</v>
+        <v>443.9</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>-1.96</v>
@@ -659,7 +659,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>STRONG</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -675,11 +675,11 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1158</v>
+        <v>2421.9</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-1.96</v>
+        <v>-0.99</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>40.7</v>
+        <v>39.3</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>38</v>
+        <v>36.6</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -717,11 +717,11 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>5196.6</v>
+        <v>553.3</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>-1.96</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -772,20 +772,20 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2452.2</v>
+        <v>5651.5</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>-1.96</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>39.3</v>
+        <v>38.3</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>36.6</v>
+        <v>35.6</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -801,11 +801,11 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>133.14</v>
+        <v>6834</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>-1.96</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>39.3</v>
+        <v>35.2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>36.6</v>
+        <v>32.5</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>449.35</v>
+        <v>853.4</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1.96</v>
+        <v>-0.99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>38.3</v>
+        <v>35</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>35.6</v>
+        <v>32.2</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW182"/>
+  <dimension ref="A1:AW193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18141,9 +18141,9 @@
           <t>TCS</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
@@ -18188,7 +18188,7 @@
       <c r="T132" s="4" t="inlineStr"/>
       <c r="U132" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 10d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V132" s="4" t="inlineStr"/>
@@ -18201,16 +18201,16 @@
         </is>
       </c>
       <c r="Y132" s="4" t="n">
-        <v>26.3</v>
+        <v>28.4</v>
       </c>
       <c r="Z132" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA132" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
@@ -18218,37 +18218,37 @@
         </is>
       </c>
       <c r="AD132" s="4" t="n">
-        <v>2452.2</v>
+        <v>2421.9</v>
       </c>
       <c r="AE132" s="4" t="n">
-        <v>2452.2</v>
+        <v>2421.9</v>
       </c>
       <c r="AF132" s="4" t="n">
-        <v>2427.68</v>
+        <v>2397.68</v>
       </c>
       <c r="AG132" s="4" t="n">
-        <v>2476.72</v>
+        <v>2446.12</v>
       </c>
       <c r="AH132" s="4" t="n">
-        <v>2329.59</v>
+        <v>2276.59</v>
       </c>
       <c r="AI132" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AJ132" s="4" t="n">
-        <v>2648.38</v>
+        <v>2712.53</v>
       </c>
       <c r="AK132" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL132" s="4" t="n">
-        <v>2820.03</v>
+        <v>3003.16</v>
       </c>
       <c r="AM132" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN132" s="4" t="n">
-        <v>0.84</v>
+        <v>-1.55</v>
       </c>
       <c r="AO132" s="4" t="n">
         <v>0</v>
@@ -18266,13 +18266,15 @@
         </is>
       </c>
       <c r="AT132" s="4" t="inlineStr"/>
-      <c r="AU132" s="4" t="inlineStr"/>
+      <c r="AU132" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV132" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -18302,25 +18304,31 @@
           <t>Hero MotoCorp</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr"/>
-      <c r="H133" s="4" t="inlineStr"/>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +6.4pp alpha</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I133" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -18334,7 +18342,7 @@
         </is>
       </c>
       <c r="O133" s="4" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="P133" s="4" t="n">
         <v>-2.8</v>
@@ -18349,12 +18357,12 @@
       <c r="T133" s="4" t="inlineStr"/>
       <c r="U133" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 41% · band HOLD · 10d left · → HOLD</t>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band HOLD→STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
       <c r="V133" s="4" t="inlineStr"/>
       <c r="W133" s="4" t="n">
-        <v>40.6</v>
+        <v>38.3</v>
       </c>
       <c r="X133" s="4" t="inlineStr">
         <is>
@@ -18362,16 +18370,16 @@
         </is>
       </c>
       <c r="Y133" s="4" t="n">
-        <v>26.2</v>
+        <v>22</v>
       </c>
       <c r="Z133" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC133" s="4" t="inlineStr">
         <is>
@@ -18379,37 +18387,37 @@
         </is>
       </c>
       <c r="AD133" s="4" t="n">
-        <v>5196.6</v>
+        <v>5651.5</v>
       </c>
       <c r="AE133" s="4" t="n">
-        <v>5196.6</v>
+        <v>5651.5</v>
       </c>
       <c r="AF133" s="4" t="n">
-        <v>5144.63</v>
+        <v>5594.98</v>
       </c>
       <c r="AG133" s="4" t="n">
-        <v>5248.57</v>
+        <v>5708.02</v>
       </c>
       <c r="AH133" s="4" t="n">
-        <v>4936.77</v>
+        <v>5368.93</v>
       </c>
       <c r="AI133" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ133" s="4" t="n">
-        <v>5612.33</v>
+        <v>6103.62</v>
       </c>
       <c r="AK133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL133" s="4" t="n">
-        <v>5976.09</v>
+        <v>6499.22</v>
       </c>
       <c r="AM133" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AN133" s="4" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AO133" s="4" t="n">
         <v>0</v>
@@ -18423,17 +18431,17 @@
       </c>
       <c r="AS133" s="4" t="inlineStr">
         <is>
-          <t>Quality · Growth · Ai Hybrid</t>
+          <t>Trend · Quality · Growth</t>
         </is>
       </c>
       <c r="AT133" s="4" t="inlineStr"/>
       <c r="AU133" s="4" t="inlineStr"/>
       <c r="AV133" s="4" t="n">
-        <v>8</v>
+        <v>6.42</v>
       </c>
       <c r="AW133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -18795,7 +18803,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>STRONG</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -18824,7 +18832,7 @@
       <c r="T136" s="4" t="inlineStr"/>
       <c r="U136" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band HOLD · 10d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band HOLD→STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="V136" s="4" t="inlineStr"/>
@@ -18837,16 +18845,16 @@
         </is>
       </c>
       <c r="Y136" s="4" t="n">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
       <c r="Z136" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA136" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
@@ -18854,37 +18862,37 @@
         </is>
       </c>
       <c r="AD136" s="4" t="n">
-        <v>1346.6</v>
+        <v>1351.3</v>
       </c>
       <c r="AE136" s="4" t="n">
-        <v>1346.6</v>
+        <v>1351.3</v>
       </c>
       <c r="AF136" s="4" t="n">
-        <v>1333.13</v>
+        <v>1337.79</v>
       </c>
       <c r="AG136" s="4" t="n">
-        <v>1360.07</v>
+        <v>1364.81</v>
       </c>
       <c r="AH136" s="4" t="n">
-        <v>1279.27</v>
+        <v>1283.73</v>
       </c>
       <c r="AI136" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ136" s="4" t="n">
-        <v>1454.33</v>
+        <v>1459.4</v>
       </c>
       <c r="AK136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL136" s="4" t="n">
-        <v>1548.59</v>
+        <v>1553.99</v>
       </c>
       <c r="AM136" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AN136" s="4" t="n">
-        <v>0.46</v>
+        <v>-1.36</v>
       </c>
       <c r="AO136" s="4" t="n">
         <v>0</v>
@@ -18898,17 +18906,17 @@
       </c>
       <c r="AS136" s="4" t="inlineStr">
         <is>
-          <t>Quality · Mean Reversion · Momentum</t>
+          <t>Trend · Quality · Mean Reversion</t>
         </is>
       </c>
       <c r="AT136" s="4" t="inlineStr"/>
       <c r="AU136" s="4" t="inlineStr"/>
       <c r="AV136" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -18934,21 +18942,21 @@
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr"/>
       <c r="I137" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -18981,7 +18989,7 @@
       <c r="T137" s="4" t="inlineStr"/>
       <c r="U137" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 46% · band HOLD · 11d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→2 · Conf 46% · band HOLD · 16d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V137" s="4" t="inlineStr"/>
@@ -18994,16 +19002,16 @@
         </is>
       </c>
       <c r="Y137" s="4" t="n">
-        <v>23.8</v>
+        <v>27.2</v>
       </c>
       <c r="Z137" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AA137" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AB137" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AC137" s="4" t="inlineStr">
         <is>
@@ -19011,37 +19019,37 @@
         </is>
       </c>
       <c r="AD137" s="4" t="n">
-        <v>11602</v>
+        <v>11727</v>
       </c>
       <c r="AE137" s="4" t="n">
-        <v>11602</v>
+        <v>11727</v>
       </c>
       <c r="AF137" s="4" t="n">
-        <v>11485.98</v>
+        <v>11609.73</v>
       </c>
       <c r="AG137" s="4" t="n">
-        <v>11718.02</v>
+        <v>11844.27</v>
       </c>
       <c r="AH137" s="4" t="n">
-        <v>11021.9</v>
+        <v>11023.38</v>
       </c>
       <c r="AI137" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AJ137" s="4" t="n">
-        <v>12530.16</v>
+        <v>13134.24</v>
       </c>
       <c r="AK137" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL137" s="4" t="n">
-        <v>13342.3</v>
+        <v>14541.48</v>
       </c>
       <c r="AM137" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AN137" s="4" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AO137" s="4" t="n">
         <v>0</v>
@@ -19059,13 +19067,15 @@
         </is>
       </c>
       <c r="AT137" s="4" t="inlineStr"/>
-      <c r="AU137" s="4" t="inlineStr"/>
+      <c r="AU137" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AV137" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -19880,13 +19890,19 @@
           <t>Biocon</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="G143" s="4" t="inlineStr"/>
-      <c r="H143" s="4" t="inlineStr"/>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +55.4pp alpha</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I143" s="4" t="n">
         <v>12</v>
       </c>
@@ -19923,7 +19939,7 @@
       <c r="T143" s="4" t="inlineStr"/>
       <c r="U143" s="4" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 10d left · → HOLD</t>
+          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
       <c r="V143" s="4" t="inlineStr"/>
@@ -19936,16 +19952,16 @@
         </is>
       </c>
       <c r="Y143" s="4" t="n">
-        <v>-28.1</v>
+        <v>-27.1</v>
       </c>
       <c r="Z143" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA143" s="4" t="n">
         <v>17</v>
       </c>
       <c r="AB143" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AC143" s="4" t="inlineStr">
         <is>
@@ -19953,37 +19969,37 @@
         </is>
       </c>
       <c r="AD143" s="4" t="n">
-        <v>431.4</v>
+        <v>428.2</v>
       </c>
       <c r="AE143" s="4" t="n">
-        <v>431.4</v>
+        <v>428.2</v>
       </c>
       <c r="AF143" s="4" t="n">
-        <v>427.09</v>
+        <v>423.92</v>
       </c>
       <c r="AG143" s="4" t="n">
-        <v>435.71</v>
+        <v>432.48</v>
       </c>
       <c r="AH143" s="4" t="n">
-        <v>409.83</v>
+        <v>406.79</v>
       </c>
       <c r="AI143" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ143" s="4" t="n">
-        <v>465.91</v>
+        <v>462.46</v>
       </c>
       <c r="AK143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL143" s="4" t="n">
-        <v>496.11</v>
+        <v>492.43</v>
       </c>
       <c r="AM143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="AN143" s="4" t="n">
-        <v>-0.72</v>
+        <v>1.47</v>
       </c>
       <c r="AO143" s="4" t="n">
         <v>0</v>
@@ -19997,17 +20013,17 @@
       </c>
       <c r="AS143" s="4" t="inlineStr">
         <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
       <c r="AT143" s="4" t="inlineStr"/>
       <c r="AU143" s="4" t="inlineStr"/>
       <c r="AV143" s="4" t="n">
-        <v>8</v>
+        <v>55.43</v>
       </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -20523,11 +20539,13 @@
       <c r="P147" s="4" t="inlineStr"/>
       <c r="Q147" s="4" t="inlineStr"/>
       <c r="R147" s="4" t="inlineStr"/>
-      <c r="S147" s="4" t="inlineStr"/>
+      <c r="S147" s="4" t="n">
+        <v>0.106</v>
+      </c>
       <c r="T147" s="4" t="inlineStr"/>
       <c r="U147" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V147" s="4" t="inlineStr"/>
@@ -20555,37 +20573,37 @@
         </is>
       </c>
       <c r="AD147" s="4" t="n">
-        <v>1454.6</v>
+        <v>1449.6</v>
       </c>
       <c r="AE147" s="4" t="n">
-        <v>1454.6</v>
+        <v>1449.6</v>
       </c>
       <c r="AF147" s="4" t="n">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="AG147" s="4" t="n">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="AH147" s="4" t="n">
-        <v>1381.87</v>
+        <v>1377.12</v>
       </c>
       <c r="AI147" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ147" s="4" t="n">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="AK147" s="4" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="AL147" s="4" t="n">
-        <v>1639.24</v>
+        <v>1633.89</v>
       </c>
       <c r="AM147" s="4" t="n">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="AN147" s="4" t="n">
-        <v>0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="AO147" s="4" t="n">
         <v>0</v>
@@ -20607,11 +20625,11 @@
         <v>5</v>
       </c>
       <c r="AV147" s="4" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="AW147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -20696,37 +20714,37 @@
         </is>
       </c>
       <c r="AD148" s="4" t="n">
-        <v>1964</v>
+        <v>1949</v>
       </c>
       <c r="AE148" s="4" t="n">
-        <v>1964</v>
+        <v>1949</v>
       </c>
       <c r="AF148" s="4" t="n">
-        <v>1911</v>
+        <v>1897</v>
       </c>
       <c r="AG148" s="4" t="n">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="AH148" s="4" t="n">
-        <v>1865.8</v>
+        <v>1851.55</v>
       </c>
       <c r="AI148" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ148" s="4" t="n">
-        <v>2054</v>
+        <v>2038</v>
       </c>
       <c r="AK148" s="4" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="AL148" s="4" t="n">
-        <v>2197.78</v>
+        <v>2180.66</v>
       </c>
       <c r="AM148" s="4" t="n">
-        <v>11.9</v>
+        <v>11.89</v>
       </c>
       <c r="AN148" s="4" t="n">
-        <v>0.44</v>
+        <v>-0.76</v>
       </c>
       <c r="AO148" s="4" t="n">
         <v>0</v>
@@ -20748,11 +20766,11 @@
         <v>5</v>
       </c>
       <c r="AV148" s="4" t="n">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="AW148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -20790,13 +20808,13 @@
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr"/>
       <c r="I149" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149" s="4" t="inlineStr"/>
       <c r="M149" s="4" t="inlineStr"/>
@@ -20805,11 +20823,13 @@
       <c r="P149" s="4" t="inlineStr"/>
       <c r="Q149" s="4" t="inlineStr"/>
       <c r="R149" s="4" t="inlineStr"/>
-      <c r="S149" s="4" t="inlineStr"/>
+      <c r="S149" s="4" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T149" s="4" t="inlineStr"/>
       <c r="U149" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-3.1%) · Rank ↓ 3→4 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V149" s="4" t="inlineStr"/>
@@ -20837,37 +20857,37 @@
         </is>
       </c>
       <c r="AD149" s="4" t="n">
-        <v>1620</v>
+        <v>1657</v>
       </c>
       <c r="AE149" s="4" t="n">
-        <v>1620</v>
+        <v>1657</v>
       </c>
       <c r="AF149" s="4" t="n">
-        <v>1569</v>
+        <v>1604</v>
       </c>
       <c r="AG149" s="4" t="n">
-        <v>1671</v>
+        <v>1710</v>
       </c>
       <c r="AH149" s="4" t="n">
-        <v>1539</v>
+        <v>1574.15</v>
       </c>
       <c r="AI149" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ149" s="4" t="n">
-        <v>1642</v>
+        <v>1680</v>
       </c>
       <c r="AK149" s="4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL149" s="4" t="n">
-        <v>1756.94</v>
+        <v>1797.6</v>
       </c>
       <c r="AM149" s="4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="AN149" s="4" t="n">
-        <v>-1.37</v>
+        <v>2.28</v>
       </c>
       <c r="AO149" s="4" t="n">
         <v>0</v>
@@ -20889,11 +20909,11 @@
         <v>5</v>
       </c>
       <c r="AV149" s="4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AW149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -20931,13 +20951,13 @@
       <c r="G150" s="4" t="inlineStr"/>
       <c r="H150" s="4" t="inlineStr"/>
       <c r="I150" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" s="4" t="inlineStr"/>
       <c r="M150" s="4" t="inlineStr"/>
@@ -20950,12 +20970,12 @@
       <c r="T150" s="4" t="inlineStr"/>
       <c r="U150" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V150" s="4" t="inlineStr"/>
       <c r="W150" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X150" s="4" t="inlineStr">
         <is>
@@ -20963,7 +20983,7 @@
         </is>
       </c>
       <c r="Y150" s="4" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Z150" s="4" t="inlineStr"/>
       <c r="AA150" s="4" t="n">
@@ -20978,37 +20998,37 @@
         </is>
       </c>
       <c r="AD150" s="4" t="n">
-        <v>2410</v>
+        <v>2390.4</v>
       </c>
       <c r="AE150" s="4" t="n">
-        <v>2410</v>
+        <v>2390.4</v>
       </c>
       <c r="AF150" s="4" t="n">
-        <v>2349</v>
+        <v>2329</v>
       </c>
       <c r="AG150" s="4" t="n">
-        <v>2471</v>
+        <v>2451</v>
       </c>
       <c r="AH150" s="4" t="n">
-        <v>2289.5</v>
+        <v>2270.88</v>
       </c>
       <c r="AI150" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ150" s="4" t="n">
-        <v>2602.8</v>
+        <v>2581.632</v>
       </c>
       <c r="AK150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL150" s="4" t="n">
-        <v>2784.996000000001</v>
+        <v>2762.34624</v>
       </c>
       <c r="AM150" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN150" s="4" t="n">
-        <v>1.09</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AO150" s="4" t="n">
         <v>0</v>
@@ -21034,7 +21054,7 @@
       </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21064,21 +21084,21 @@
           <t>NTPC</t>
         </is>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
       <c r="H151" s="4" t="inlineStr"/>
       <c r="I151" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L151" s="4" t="inlineStr"/>
       <c r="M151" s="4" t="inlineStr"/>
@@ -21091,7 +21111,7 @@
       <c r="T151" s="4" t="inlineStr"/>
       <c r="U151" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 4→6 · Conf 72% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="V151" s="4" t="inlineStr"/>
@@ -21104,7 +21124,7 @@
         </is>
       </c>
       <c r="Y151" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Z151" s="4" t="inlineStr"/>
       <c r="AA151" s="4" t="n">
@@ -21119,37 +21139,37 @@
         </is>
       </c>
       <c r="AD151" s="4" t="n">
-        <v>343.6</v>
+        <v>346.9</v>
       </c>
       <c r="AE151" s="4" t="n">
-        <v>343.6</v>
+        <v>346.9</v>
       </c>
       <c r="AF151" s="4" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG151" s="4" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AH151" s="4" t="n">
-        <v>326.42</v>
+        <v>329.5549999999999</v>
       </c>
       <c r="AI151" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ151" s="4" t="n">
-        <v>371.088</v>
+        <v>374.652</v>
       </c>
       <c r="AK151" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL151" s="4" t="n">
-        <v>397.0641600000001</v>
+        <v>400.87764</v>
       </c>
       <c r="AM151" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN151" s="4" t="n">
-        <v>-1.04</v>
+        <v>0.95</v>
       </c>
       <c r="AO151" s="4" t="n">
         <v>0</v>
@@ -21175,7 +21195,7 @@
       </c>
       <c r="AW151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21205,21 +21225,21 @@
           <t>Kotak Bank</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
       <c r="H152" s="4" t="inlineStr"/>
       <c r="I152" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="4" t="inlineStr"/>
       <c r="M152" s="4" t="inlineStr"/>
@@ -21232,12 +21252,12 @@
       <c r="T152" s="4" t="inlineStr"/>
       <c r="U152" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 5→6 · Conf 72% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank → 5→5 · Conf 73% · momentum → · 61d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="V152" s="4" t="inlineStr"/>
       <c r="W152" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X152" s="4" t="inlineStr">
         <is>
@@ -21245,7 +21265,7 @@
         </is>
       </c>
       <c r="Y152" s="4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Z152" s="4" t="inlineStr"/>
       <c r="AA152" s="4" t="n">
@@ -21260,37 +21280,37 @@
         </is>
       </c>
       <c r="AD152" s="4" t="n">
-        <v>398</v>
+        <v>397.2</v>
       </c>
       <c r="AE152" s="4" t="n">
-        <v>398</v>
+        <v>397.2</v>
       </c>
       <c r="AF152" s="4" t="n">
         <v>386</v>
       </c>
       <c r="AG152" s="4" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AH152" s="4" t="n">
-        <v>378.1</v>
+        <v>377.34</v>
       </c>
       <c r="AI152" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ152" s="4" t="n">
-        <v>429.84</v>
+        <v>428.976</v>
       </c>
       <c r="AK152" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL152" s="4" t="n">
-        <v>459.9288000000001</v>
+        <v>459.00432</v>
       </c>
       <c r="AM152" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN152" s="4" t="n">
-        <v>0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AO152" s="4" t="n">
         <v>0</v>
@@ -21316,7 +21336,7 @@
       </c>
       <c r="AW152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21373,12 +21393,12 @@
       <c r="T153" s="4" t="inlineStr"/>
       <c r="U153" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.3%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 68% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="V153" s="4" t="inlineStr"/>
       <c r="W153" s="4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X153" s="4" t="inlineStr">
         <is>
@@ -21386,7 +21406,7 @@
         </is>
       </c>
       <c r="Y153" s="4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z153" s="4" t="inlineStr"/>
       <c r="AA153" s="4" t="n">
@@ -21401,37 +21421,37 @@
         </is>
       </c>
       <c r="AD153" s="4" t="n">
-        <v>283.4</v>
+        <v>276.8</v>
       </c>
       <c r="AE153" s="4" t="n">
-        <v>283.4</v>
+        <v>276.8</v>
       </c>
       <c r="AF153" s="4" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG153" s="4" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="AH153" s="4" t="n">
-        <v>269.23</v>
+        <v>262.96</v>
       </c>
       <c r="AI153" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ153" s="4" t="n">
-        <v>306.072</v>
+        <v>298.944</v>
       </c>
       <c r="AK153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL153" s="4" t="n">
-        <v>327.49704</v>
+        <v>319.87008</v>
       </c>
       <c r="AM153" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN153" s="4" t="n">
-        <v>-0.86</v>
+        <v>-2.33</v>
       </c>
       <c r="AO153" s="4" t="n">
         <v>0</v>
@@ -21457,7 +21477,7 @@
       </c>
       <c r="AW153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21495,13 +21515,13 @@
       <c r="G154" s="4" t="inlineStr"/>
       <c r="H154" s="4" t="inlineStr"/>
       <c r="I154" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="4" t="inlineStr"/>
       <c r="M154" s="4" t="inlineStr"/>
@@ -21514,7 +21534,7 @@
       <c r="T154" s="4" t="inlineStr"/>
       <c r="U154" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="V154" s="4" t="inlineStr"/>
@@ -21542,10 +21562,10 @@
         </is>
       </c>
       <c r="AD154" s="4" t="n">
-        <v>510.2</v>
+        <v>510.9</v>
       </c>
       <c r="AE154" s="4" t="n">
-        <v>510.2</v>
+        <v>510.9</v>
       </c>
       <c r="AF154" s="4" t="n">
         <v>495</v>
@@ -21554,25 +21574,25 @@
         <v>526</v>
       </c>
       <c r="AH154" s="4" t="n">
-        <v>484.6899999999999</v>
+        <v>485.355</v>
       </c>
       <c r="AI154" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ154" s="4" t="n">
-        <v>551.0160000000001</v>
+        <v>551.772</v>
       </c>
       <c r="AK154" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL154" s="4" t="n">
-        <v>589.5871200000001</v>
+        <v>590.3960400000001</v>
       </c>
       <c r="AM154" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN154" s="4" t="n">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
       <c r="AO154" s="4" t="n">
         <v>0</v>
@@ -21598,7 +21618,7 @@
       </c>
       <c r="AW154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21636,13 +21656,13 @@
       <c r="G155" s="4" t="inlineStr"/>
       <c r="H155" s="4" t="inlineStr"/>
       <c r="I155" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="4" t="inlineStr"/>
       <c r="M155" s="4" t="inlineStr"/>
@@ -21655,12 +21675,12 @@
       <c r="T155" s="4" t="inlineStr"/>
       <c r="U155" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank ↓ 8→9 · Conf 64% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 8→10 · Conf 63% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="V155" s="4" t="inlineStr"/>
       <c r="W155" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X155" s="4" t="inlineStr">
         <is>
@@ -21668,7 +21688,7 @@
         </is>
       </c>
       <c r="Y155" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z155" s="4" t="inlineStr"/>
       <c r="AA155" s="4" t="n">
@@ -21683,37 +21703,37 @@
         </is>
       </c>
       <c r="AD155" s="4" t="n">
-        <v>391.5</v>
+        <v>390</v>
       </c>
       <c r="AE155" s="4" t="n">
-        <v>391.5</v>
+        <v>390</v>
       </c>
       <c r="AF155" s="4" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG155" s="4" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AH155" s="4" t="n">
-        <v>371.925</v>
+        <v>370.5</v>
       </c>
       <c r="AI155" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ155" s="4" t="n">
-        <v>422.8200000000001</v>
+        <v>421.2</v>
       </c>
       <c r="AK155" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL155" s="4" t="n">
-        <v>452.4174000000001</v>
+        <v>450.6840000000001</v>
       </c>
       <c r="AM155" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN155" s="4" t="n">
-        <v>0.42</v>
+        <v>-0.37</v>
       </c>
       <c r="AO155" s="4" t="n">
         <v>0</v>
@@ -21739,7 +21759,7 @@
       </c>
       <c r="AW155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21773,13 +21793,13 @@
       <c r="G156" s="4" t="inlineStr"/>
       <c r="H156" s="4" t="inlineStr"/>
       <c r="I156" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L156" s="4" t="inlineStr"/>
       <c r="M156" s="4" t="inlineStr"/>
@@ -21788,11 +21808,13 @@
       <c r="P156" s="4" t="inlineStr"/>
       <c r="Q156" s="4" t="inlineStr"/>
       <c r="R156" s="4" t="inlineStr"/>
-      <c r="S156" s="4" t="inlineStr"/>
+      <c r="S156" s="4" t="n">
+        <v>0.114</v>
+      </c>
       <c r="T156" s="4" t="inlineStr"/>
       <c r="U156" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→12 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="V156" s="4" t="inlineStr"/>
@@ -21805,7 +21827,7 @@
         </is>
       </c>
       <c r="Y156" s="4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Z156" s="4" t="inlineStr"/>
       <c r="AA156" s="4" t="n">
@@ -21820,37 +21842,37 @@
         </is>
       </c>
       <c r="AD156" s="4" t="n">
-        <v>5478</v>
+        <v>5429</v>
       </c>
       <c r="AE156" s="4" t="n">
-        <v>5478</v>
+        <v>5429</v>
       </c>
       <c r="AF156" s="4" t="n">
-        <v>5335</v>
+        <v>5287</v>
       </c>
       <c r="AG156" s="4" t="n">
-        <v>5621</v>
+        <v>5571</v>
       </c>
       <c r="AH156" s="4" t="n">
-        <v>5204.099999999999</v>
+        <v>5157.55</v>
       </c>
       <c r="AI156" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ156" s="4" t="n">
-        <v>5916.240000000001</v>
+        <v>5863.320000000001</v>
       </c>
       <c r="AK156" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL156" s="4" t="n">
-        <v>6330.376800000001</v>
+        <v>6273.752400000001</v>
       </c>
       <c r="AM156" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN156" s="4" t="n">
-        <v>0.43</v>
+        <v>-0.89</v>
       </c>
       <c r="AO156" s="4" t="n">
         <v>0</v>
@@ -21876,7 +21898,7 @@
       </c>
       <c r="AW156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -21933,7 +21955,7 @@
       <c r="T157" s="4" t="inlineStr"/>
       <c r="U157" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="V157" s="4" t="inlineStr"/>
@@ -21946,7 +21968,7 @@
         </is>
       </c>
       <c r="Y157" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z157" s="4" t="inlineStr"/>
       <c r="AA157" s="4" t="n">
@@ -21961,37 +21983,37 @@
         </is>
       </c>
       <c r="AD157" s="4" t="n">
-        <v>417.6</v>
+        <v>414</v>
       </c>
       <c r="AE157" s="4" t="n">
-        <v>417.6</v>
+        <v>414</v>
       </c>
       <c r="AF157" s="4" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG157" s="4" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AH157" s="4" t="n">
-        <v>396.72</v>
+        <v>393.3</v>
       </c>
       <c r="AI157" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AJ157" s="4" t="n">
-        <v>451.008</v>
+        <v>447.12</v>
       </c>
       <c r="AK157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AL157" s="4" t="n">
-        <v>482.5785600000001</v>
+        <v>478.4184</v>
       </c>
       <c r="AM157" s="4" t="n">
         <v>15.56</v>
       </c>
       <c r="AN157" s="4" t="n">
-        <v>0.59</v>
+        <v>-0.85</v>
       </c>
       <c r="AO157" s="4" t="n">
         <v>0</v>
@@ -22017,7 +22039,7 @@
       </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 03:38</t>
+          <t>2026-08-06 03:53</t>
         </is>
       </c>
     </row>
@@ -26178,8 +26200,1711 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr"/>
+      <c r="H183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J183" s="4" t="inlineStr"/>
+      <c r="K183" s="4" t="inlineStr"/>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M183" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O183" s="4" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="P183" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q183" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R183" s="4" t="inlineStr"/>
+      <c r="S183" s="4" t="inlineStr"/>
+      <c r="T183" s="4" t="inlineStr"/>
+      <c r="U183" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 35% · band HOLD · 17d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V183" s="4" t="inlineStr"/>
+      <c r="W183" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="X183" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y183" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="Z183" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA183" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB183" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC183" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD183" s="4" t="n">
+        <v>853.4</v>
+      </c>
+      <c r="AE183" s="4" t="n">
+        <v>853.4</v>
+      </c>
+      <c r="AF183" s="4" t="n">
+        <v>844.87</v>
+      </c>
+      <c r="AG183" s="4" t="n">
+        <v>861.9299999999999</v>
+      </c>
+      <c r="AH183" s="4" t="n">
+        <v>802.2</v>
+      </c>
+      <c r="AI183" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ183" s="4" t="n">
+        <v>955.8099999999999</v>
+      </c>
+      <c r="AK183" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL183" s="4" t="n">
+        <v>1058.22</v>
+      </c>
+      <c r="AM183" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN183" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AO183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP183" s="4" t="inlineStr"/>
+      <c r="AQ183" s="4" t="inlineStr"/>
+      <c r="AR183" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS183" s="4" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT183" s="4" t="inlineStr"/>
+      <c r="AU183" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV183" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>ATUL</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr"/>
+      <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J184" s="4" t="inlineStr"/>
+      <c r="K184" s="4" t="inlineStr"/>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O184" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="P184" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q184" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R184" s="4" t="inlineStr"/>
+      <c r="S184" s="4" t="inlineStr"/>
+      <c r="T184" s="4" t="inlineStr"/>
+      <c r="U184" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 35% · band HOLD · 17d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V184" s="4" t="inlineStr"/>
+      <c r="W184" s="4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="X184" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y184" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z184" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA184" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB184" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD184" s="4" t="n">
+        <v>6834</v>
+      </c>
+      <c r="AE184" s="4" t="n">
+        <v>6834</v>
+      </c>
+      <c r="AF184" s="4" t="n">
+        <v>6765.66</v>
+      </c>
+      <c r="AG184" s="4" t="n">
+        <v>6902.34</v>
+      </c>
+      <c r="AH184" s="4" t="n">
+        <v>6492.3</v>
+      </c>
+      <c r="AI184" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ184" s="4" t="n">
+        <v>7380.72</v>
+      </c>
+      <c r="AK184" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL184" s="4" t="n">
+        <v>7859.1</v>
+      </c>
+      <c r="AM184" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN184" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AO184" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP184" s="4" t="inlineStr"/>
+      <c r="AQ184" s="4" t="inlineStr"/>
+      <c r="AR184" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS184" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AT184" s="4" t="inlineStr"/>
+      <c r="AU184" s="4" t="inlineStr"/>
+      <c r="AV184" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr"/>
+      <c r="H185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J185" s="4" t="inlineStr"/>
+      <c r="K185" s="4" t="inlineStr"/>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M185" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O185" s="4" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="P185" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q185" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R185" s="4" t="inlineStr"/>
+      <c r="S185" s="4" t="inlineStr"/>
+      <c r="T185" s="4" t="inlineStr"/>
+      <c r="U185" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 39% · band HOLD · 60d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="V185" s="4" t="inlineStr"/>
+      <c r="W185" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="X185" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y185" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Z185" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA185" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB185" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC185" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD185" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AE185" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AF185" s="4" t="n">
+        <v>547.77</v>
+      </c>
+      <c r="AG185" s="4" t="n">
+        <v>558.83</v>
+      </c>
+      <c r="AH185" s="4" t="n">
+        <v>525.63</v>
+      </c>
+      <c r="AI185" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ185" s="4" t="n">
+        <v>597.5599999999999</v>
+      </c>
+      <c r="AK185" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL185" s="4" t="n">
+        <v>636.29</v>
+      </c>
+      <c r="AM185" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN185" s="4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AO185" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP185" s="4" t="inlineStr"/>
+      <c r="AQ185" s="4" t="inlineStr"/>
+      <c r="AR185" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS185" s="4" t="inlineStr">
+        <is>
+          <t>Value · Momentum · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT185" s="4" t="inlineStr"/>
+      <c r="AU185" s="4" t="inlineStr"/>
+      <c r="AV185" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +5.5pp alpha</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J186" s="4" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr"/>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NEW</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O186" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="P186" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q186" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R186" s="4" t="inlineStr"/>
+      <c r="S186" s="4" t="inlineStr"/>
+      <c r="T186" s="4" t="inlineStr"/>
+      <c r="U186" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #7 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V186" s="4" t="inlineStr"/>
+      <c r="W186" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="X186" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y186" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Z186" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA186" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB186" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD186" s="4" t="n">
+        <v>443.9</v>
+      </c>
+      <c r="AE186" s="4" t="n">
+        <v>443.9</v>
+      </c>
+      <c r="AF186" s="4" t="n">
+        <v>439.46</v>
+      </c>
+      <c r="AG186" s="4" t="n">
+        <v>448.34</v>
+      </c>
+      <c r="AH186" s="4" t="n">
+        <v>421.7</v>
+      </c>
+      <c r="AI186" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ186" s="4" t="n">
+        <v>479.41</v>
+      </c>
+      <c r="AK186" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL186" s="4" t="n">
+        <v>510.48</v>
+      </c>
+      <c r="AM186" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN186" s="4" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AO186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP186" s="4" t="inlineStr"/>
+      <c r="AQ186" s="4" t="inlineStr"/>
+      <c r="AR186" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS186" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT186" s="4" t="inlineStr"/>
+      <c r="AU186" s="4" t="inlineStr"/>
+      <c r="AV186" s="4" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AW186" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Vedanta</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +7.1pp alpha</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J187" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K187" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M187" s="4" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O187" s="4" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="P187" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q187" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R187" s="4" t="inlineStr"/>
+      <c r="S187" s="4" t="inlineStr"/>
+      <c r="T187" s="4" t="inlineStr"/>
+      <c r="U187" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 6→9 · Conf 33% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V187" s="4" t="inlineStr"/>
+      <c r="W187" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="X187" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y187" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Z187" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA187" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB187" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC187" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD187" s="4" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="AE187" s="4" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="AF187" s="4" t="n">
+        <v>276.01</v>
+      </c>
+      <c r="AG187" s="4" t="n">
+        <v>281.59</v>
+      </c>
+      <c r="AH187" s="4" t="n">
+        <v>264.86</v>
+      </c>
+      <c r="AI187" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ187" s="4" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="AK187" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL187" s="4" t="n">
+        <v>320.62</v>
+      </c>
+      <c r="AM187" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN187" s="4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AO187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP187" s="4" t="inlineStr"/>
+      <c r="AQ187" s="4" t="inlineStr"/>
+      <c r="AR187" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS187" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Growth</t>
+        </is>
+      </c>
+      <c r="AT187" s="4" t="inlineStr"/>
+      <c r="AU187" s="4" t="inlineStr"/>
+      <c r="AV187" s="4" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AW187" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +7.3pp alpha</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J188" s="4" t="inlineStr"/>
+      <c r="K188" s="4" t="inlineStr"/>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="M188" s="4" t="inlineStr"/>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P188" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q188" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R188" s="4" t="inlineStr"/>
+      <c r="S188" s="4" t="inlineStr"/>
+      <c r="T188" s="4" t="inlineStr"/>
+      <c r="U188" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #10 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V188" s="4" t="inlineStr"/>
+      <c r="W188" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="X188" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y188" s="4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Z188" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA188" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB188" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC188" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD188" s="4" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="AE188" s="4" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="AF188" s="4" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="AG188" s="4" t="n">
+        <v>384.15</v>
+      </c>
+      <c r="AH188" s="4" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="AI188" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ188" s="4" t="n">
+        <v>410.78</v>
+      </c>
+      <c r="AK188" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL188" s="4" t="n">
+        <v>437.4</v>
+      </c>
+      <c r="AM188" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN188" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP188" s="4" t="inlineStr"/>
+      <c r="AQ188" s="4" t="inlineStr"/>
+      <c r="AR188" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS188" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Quality · Value</t>
+        </is>
+      </c>
+      <c r="AT188" s="4" t="inlineStr"/>
+      <c r="AU188" s="4" t="inlineStr"/>
+      <c r="AV188" s="4" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AW188" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Amber Ent.</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +55.4pp alpha</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J189" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K189" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M189" s="4" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O189" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="P189" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q189" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R189" s="4" t="inlineStr"/>
+      <c r="S189" s="4" t="inlineStr"/>
+      <c r="T189" s="4" t="inlineStr"/>
+      <c r="U189" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↑ 14→11 · Conf 24% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V189" s="4" t="inlineStr"/>
+      <c r="W189" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="X189" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y189" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="Z189" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA189" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB189" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC189" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD189" s="4" t="n">
+        <v>7531.5</v>
+      </c>
+      <c r="AE189" s="4" t="n">
+        <v>7531.5</v>
+      </c>
+      <c r="AF189" s="4" t="n">
+        <v>7456.18</v>
+      </c>
+      <c r="AG189" s="4" t="n">
+        <v>7606.82</v>
+      </c>
+      <c r="AH189" s="4" t="n">
+        <v>7154.92</v>
+      </c>
+      <c r="AI189" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ189" s="4" t="n">
+        <v>8134.02</v>
+      </c>
+      <c r="AK189" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL189" s="4" t="n">
+        <v>8661.219999999999</v>
+      </c>
+      <c r="AM189" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN189" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP189" s="4" t="inlineStr"/>
+      <c r="AQ189" s="4" t="inlineStr"/>
+      <c r="AR189" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS189" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Fund Debt To Equity</t>
+        </is>
+      </c>
+      <c r="AT189" s="4" t="inlineStr"/>
+      <c r="AU189" s="4" t="inlineStr"/>
+      <c r="AV189" s="4" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="AW189" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +56.3pp alpha</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J190" s="4" t="inlineStr"/>
+      <c r="K190" s="4" t="inlineStr"/>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M190" s="4" t="inlineStr"/>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O190" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="P190" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q190" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R190" s="4" t="inlineStr"/>
+      <c r="S190" s="4" t="inlineStr"/>
+      <c r="T190" s="4" t="inlineStr"/>
+      <c r="U190" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #13 · Conf 25% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V190" s="4" t="inlineStr"/>
+      <c r="W190" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X190" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y190" s="4" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Z190" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA190" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB190" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD190" s="4" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="AE190" s="4" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="AF190" s="4" t="n">
+        <v>466.49</v>
+      </c>
+      <c r="AG190" s="4" t="n">
+        <v>475.91</v>
+      </c>
+      <c r="AH190" s="4" t="n">
+        <v>447.64</v>
+      </c>
+      <c r="AI190" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ190" s="4" t="n">
+        <v>508.9</v>
+      </c>
+      <c r="AK190" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL190" s="4" t="n">
+        <v>541.88</v>
+      </c>
+      <c r="AM190" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN190" s="4" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="AO190" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP190" s="4" t="inlineStr"/>
+      <c r="AQ190" s="4" t="inlineStr"/>
+      <c r="AR190" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS190" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AT190" s="4" t="inlineStr"/>
+      <c r="AU190" s="4" t="inlineStr"/>
+      <c r="AV190" s="4" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="AW190" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +58.3pp alpha</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J191" s="4" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr"/>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M191" s="4" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O191" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="P191" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q191" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R191" s="4" t="inlineStr"/>
+      <c r="S191" s="4" t="inlineStr"/>
+      <c r="T191" s="4" t="inlineStr"/>
+      <c r="U191" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #14 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V191" s="4" t="inlineStr"/>
+      <c r="W191" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X191" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y191" s="4" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="Z191" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA191" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB191" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC191" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD191" s="4" t="n">
+        <v>1594.5</v>
+      </c>
+      <c r="AE191" s="4" t="n">
+        <v>1594.5</v>
+      </c>
+      <c r="AF191" s="4" t="n">
+        <v>1578.56</v>
+      </c>
+      <c r="AG191" s="4" t="n">
+        <v>1610.44</v>
+      </c>
+      <c r="AH191" s="4" t="n">
+        <v>1514.77</v>
+      </c>
+      <c r="AI191" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ191" s="4" t="n">
+        <v>1722.06</v>
+      </c>
+      <c r="AK191" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL191" s="4" t="n">
+        <v>1833.67</v>
+      </c>
+      <c r="AM191" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN191" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AO191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP191" s="4" t="inlineStr"/>
+      <c r="AQ191" s="4" t="inlineStr"/>
+      <c r="AR191" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS191" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AT191" s="4" t="inlineStr"/>
+      <c r="AU191" s="4" t="inlineStr"/>
+      <c r="AV191" s="4" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="AW191" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +60.5pp alpha</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J192" s="4" t="inlineStr"/>
+      <c r="K192" s="4" t="inlineStr"/>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="M192" s="4" t="inlineStr"/>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O192" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="P192" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Q192" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R192" s="4" t="inlineStr"/>
+      <c r="S192" s="4" t="inlineStr"/>
+      <c r="T192" s="4" t="inlineStr"/>
+      <c r="U192" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #15 · Conf 24% · band EXIT · 17d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="V192" s="4" t="inlineStr"/>
+      <c r="W192" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="X192" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y192" s="4" t="n">
+        <v>-32.1</v>
+      </c>
+      <c r="Z192" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA192" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB192" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC192" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD192" s="4" t="n">
+        <v>1296.8</v>
+      </c>
+      <c r="AE192" s="4" t="n">
+        <v>1296.8</v>
+      </c>
+      <c r="AF192" s="4" t="n">
+        <v>1283.83</v>
+      </c>
+      <c r="AG192" s="4" t="n">
+        <v>1309.77</v>
+      </c>
+      <c r="AH192" s="4" t="n">
+        <v>1231.96</v>
+      </c>
+      <c r="AI192" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ192" s="4" t="n">
+        <v>1400.54</v>
+      </c>
+      <c r="AK192" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL192" s="4" t="n">
+        <v>1491.32</v>
+      </c>
+      <c r="AM192" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN192" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AO192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP192" s="4" t="inlineStr"/>
+      <c r="AQ192" s="4" t="inlineStr"/>
+      <c r="AR192" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS192" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AT192" s="4" t="inlineStr"/>
+      <c r="AU192" s="4" t="inlineStr"/>
+      <c r="AV192" s="4" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="AW192" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" s="4" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr"/>
+      <c r="L193" s="4" t="inlineStr"/>
+      <c r="M193" s="4" t="inlineStr"/>
+      <c r="N193" s="4" t="inlineStr"/>
+      <c r="O193" s="4" t="inlineStr"/>
+      <c r="P193" s="4" t="inlineStr"/>
+      <c r="Q193" s="4" t="inlineStr"/>
+      <c r="R193" s="4" t="inlineStr"/>
+      <c r="S193" s="4" t="inlineStr"/>
+      <c r="T193" s="4" t="inlineStr"/>
+      <c r="U193" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank #8 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="V193" s="4" t="inlineStr"/>
+      <c r="W193" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="X193" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="Y193" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Z193" s="4" t="inlineStr"/>
+      <c r="AA193" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB193" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD193" s="4" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="AE193" s="4" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="AF193" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="AG193" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="AH193" s="4" t="n">
+        <v>271.51</v>
+      </c>
+      <c r="AI193" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ193" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="AK193" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AL193" s="4" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="AM193" s="4" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="AN193" s="4" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AO193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP193" s="4" t="inlineStr"/>
+      <c r="AQ193" s="4" t="inlineStr"/>
+      <c r="AR193" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AS193" s="4" t="inlineStr"/>
+      <c r="AT193" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AU193" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV193" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AW193" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AW182"/>
+  <autoFilter ref="A1:AW193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$BB$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$BB$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB206"/>
+  <dimension ref="A1:BB225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
       <c r="W133" s="4" t="inlineStr"/>
       <c r="X133" s="4" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band HOLD→STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band STRONG · 16d left · → EXIT (rotate to TCS.NS)</t>
         </is>
       </c>
       <c r="Y133" s="4" t="inlineStr"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18808,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band HOLD→STRONG · 16d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y136" s="4" t="inlineStr"/>
@@ -18898,7 +18898,7 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21094,7 +21094,7 @@
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22210,7 +22210,7 @@
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22390,7 @@
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22570,7 +22570,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23124,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -23680,7 +23680,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -23866,7 +23866,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24050,7 +24050,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24606,7 +24606,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -24978,7 +24978,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -26683,7 +26683,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -26851,7 +26851,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -27167,7 +27167,7 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -27349,7 +27349,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -27523,7 +27523,7 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -28029,7 +28029,7 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -28496,7 +28496,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -28670,7 +28670,7 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29004,7 +29004,7 @@
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29356,7 +29356,7 @@
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29534,7 +29534,7 @@
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -29890,7 +29890,7 @@
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -30068,7 +30068,7 @@
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -30244,7 +30244,7 @@
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
@@ -30596,12 +30596,2336 @@
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 10:36</t>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr"/>
+      <c r="J207" s="4" t="inlineStr"/>
+      <c r="K207" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L207" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M207" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N207" s="4" t="inlineStr"/>
+      <c r="O207" s="4" t="inlineStr"/>
+      <c r="P207" s="4" t="inlineStr"/>
+      <c r="Q207" s="4" t="inlineStr"/>
+      <c r="R207" s="4" t="inlineStr"/>
+      <c r="S207" s="4" t="inlineStr"/>
+      <c r="T207" s="4" t="inlineStr"/>
+      <c r="U207" s="4" t="inlineStr"/>
+      <c r="V207" s="4" t="inlineStr"/>
+      <c r="W207" s="4" t="inlineStr"/>
+      <c r="X207" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y207" s="4" t="inlineStr"/>
+      <c r="Z207" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AA207" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB207" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC207" s="4" t="inlineStr"/>
+      <c r="AD207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF207" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG207" s="4" t="inlineStr"/>
+      <c r="AH207" s="4" t="inlineStr"/>
+      <c r="AI207" s="4" t="inlineStr"/>
+      <c r="AJ207" s="4" t="inlineStr"/>
+      <c r="AK207" s="4" t="inlineStr"/>
+      <c r="AL207" s="4" t="inlineStr"/>
+      <c r="AM207" s="4" t="inlineStr"/>
+      <c r="AN207" s="4" t="inlineStr"/>
+      <c r="AO207" s="4" t="inlineStr"/>
+      <c r="AP207" s="4" t="inlineStr"/>
+      <c r="AQ207" s="4" t="inlineStr"/>
+      <c r="AR207" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AS207" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AT207" s="4" t="inlineStr"/>
+      <c r="AU207" s="4" t="inlineStr"/>
+      <c r="AV207" s="4" t="inlineStr"/>
+      <c r="AW207" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX207" s="4" t="inlineStr"/>
+      <c r="AY207" s="4" t="inlineStr"/>
+      <c r="AZ207" s="4" t="inlineStr"/>
+      <c r="BA207" s="4" t="inlineStr"/>
+      <c r="BB207" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>PNB_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Punjab Natl. Bank</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr"/>
+      <c r="J208" s="4" t="inlineStr"/>
+      <c r="K208" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr"/>
+      <c r="P208" s="4" t="inlineStr"/>
+      <c r="Q208" s="4" t="inlineStr"/>
+      <c r="R208" s="4" t="inlineStr"/>
+      <c r="S208" s="4" t="inlineStr"/>
+      <c r="T208" s="4" t="inlineStr"/>
+      <c r="U208" s="4" t="inlineStr"/>
+      <c r="V208" s="4" t="inlineStr"/>
+      <c r="W208" s="4" t="inlineStr"/>
+      <c r="X208" s="4" t="inlineStr">
+        <is>
+          <t>Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y208" s="4" t="inlineStr"/>
+      <c r="Z208" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="AA208" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB208" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AC208" s="4" t="inlineStr"/>
+      <c r="AD208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE208" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF208" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG208" s="4" t="inlineStr"/>
+      <c r="AH208" s="4" t="inlineStr"/>
+      <c r="AI208" s="4" t="inlineStr"/>
+      <c r="AJ208" s="4" t="inlineStr"/>
+      <c r="AK208" s="4" t="inlineStr"/>
+      <c r="AL208" s="4" t="inlineStr"/>
+      <c r="AM208" s="4" t="inlineStr"/>
+      <c r="AN208" s="4" t="inlineStr"/>
+      <c r="AO208" s="4" t="inlineStr"/>
+      <c r="AP208" s="4" t="inlineStr"/>
+      <c r="AQ208" s="4" t="inlineStr"/>
+      <c r="AR208" s="4" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="AS208" s="4" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AT208" s="4" t="inlineStr"/>
+      <c r="AU208" s="4" t="inlineStr"/>
+      <c r="AV208" s="4" t="inlineStr"/>
+      <c r="AW208" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX208" s="4" t="inlineStr"/>
+      <c r="AY208" s="4" t="inlineStr"/>
+      <c r="AZ208" s="4" t="inlineStr"/>
+      <c r="BA208" s="4" t="inlineStr"/>
+      <c r="BB208" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr"/>
+      <c r="J209" s="4" t="inlineStr"/>
+      <c r="K209" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L209" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M209" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N209" s="4" t="inlineStr"/>
+      <c r="O209" s="4" t="inlineStr"/>
+      <c r="P209" s="4" t="inlineStr"/>
+      <c r="Q209" s="4" t="inlineStr"/>
+      <c r="R209" s="4" t="inlineStr"/>
+      <c r="S209" s="4" t="inlineStr"/>
+      <c r="T209" s="4" t="inlineStr"/>
+      <c r="U209" s="4" t="inlineStr"/>
+      <c r="V209" s="4" t="inlineStr"/>
+      <c r="W209" s="4" t="inlineStr"/>
+      <c r="X209" s="4" t="inlineStr">
+        <is>
+          <t>Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y209" s="4" t="inlineStr"/>
+      <c r="Z209" s="4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="AA209" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB209" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AC209" s="4" t="inlineStr"/>
+      <c r="AD209" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE209" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF209" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG209" s="4" t="inlineStr"/>
+      <c r="AH209" s="4" t="inlineStr"/>
+      <c r="AI209" s="4" t="inlineStr"/>
+      <c r="AJ209" s="4" t="inlineStr"/>
+      <c r="AK209" s="4" t="inlineStr"/>
+      <c r="AL209" s="4" t="inlineStr"/>
+      <c r="AM209" s="4" t="inlineStr"/>
+      <c r="AN209" s="4" t="inlineStr"/>
+      <c r="AO209" s="4" t="inlineStr"/>
+      <c r="AP209" s="4" t="inlineStr"/>
+      <c r="AQ209" s="4" t="inlineStr"/>
+      <c r="AR209" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AS209" s="4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AT209" s="4" t="inlineStr"/>
+      <c r="AU209" s="4" t="inlineStr"/>
+      <c r="AV209" s="4" t="inlineStr"/>
+      <c r="AW209" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX209" s="4" t="inlineStr"/>
+      <c r="AY209" s="4" t="inlineStr"/>
+      <c r="AZ209" s="4" t="inlineStr"/>
+      <c r="BA209" s="4" t="inlineStr"/>
+      <c r="BB209" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr"/>
+      <c r="K210" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="inlineStr"/>
+      <c r="N210" s="4" t="inlineStr"/>
+      <c r="O210" s="4" t="inlineStr"/>
+      <c r="P210" s="4" t="inlineStr"/>
+      <c r="Q210" s="4" t="inlineStr"/>
+      <c r="R210" s="4" t="inlineStr"/>
+      <c r="S210" s="4" t="inlineStr"/>
+      <c r="T210" s="4" t="inlineStr"/>
+      <c r="U210" s="4" t="inlineStr"/>
+      <c r="V210" s="4" t="inlineStr"/>
+      <c r="W210" s="4" t="inlineStr"/>
+      <c r="X210" s="4" t="inlineStr">
+        <is>
+          <t>Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y210" s="4" t="inlineStr"/>
+      <c r="Z210" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="AA210" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB210" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AC210" s="4" t="inlineStr"/>
+      <c r="AD210" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF210" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG210" s="4" t="inlineStr"/>
+      <c r="AH210" s="4" t="inlineStr"/>
+      <c r="AI210" s="4" t="inlineStr"/>
+      <c r="AJ210" s="4" t="inlineStr"/>
+      <c r="AK210" s="4" t="inlineStr"/>
+      <c r="AL210" s="4" t="inlineStr"/>
+      <c r="AM210" s="4" t="inlineStr"/>
+      <c r="AN210" s="4" t="inlineStr"/>
+      <c r="AO210" s="4" t="inlineStr"/>
+      <c r="AP210" s="4" t="inlineStr"/>
+      <c r="AQ210" s="4" t="inlineStr"/>
+      <c r="AR210" s="4" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="AS210" s="4" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="AT210" s="4" t="inlineStr"/>
+      <c r="AU210" s="4" t="inlineStr"/>
+      <c r="AV210" s="4" t="inlineStr"/>
+      <c r="AW210" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX210" s="4" t="inlineStr"/>
+      <c r="AY210" s="4" t="inlineStr"/>
+      <c r="AZ210" s="4" t="inlineStr"/>
+      <c r="BA210" s="4" t="inlineStr"/>
+      <c r="BB210" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>BATAINDIA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr"/>
+      <c r="J211" s="4" t="inlineStr"/>
+      <c r="K211" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L211" s="4" t="inlineStr"/>
+      <c r="M211" s="4" t="inlineStr"/>
+      <c r="N211" s="4" t="inlineStr"/>
+      <c r="O211" s="4" t="inlineStr"/>
+      <c r="P211" s="4" t="inlineStr"/>
+      <c r="Q211" s="4" t="inlineStr"/>
+      <c r="R211" s="4" t="inlineStr"/>
+      <c r="S211" s="4" t="inlineStr"/>
+      <c r="T211" s="4" t="inlineStr"/>
+      <c r="U211" s="4" t="inlineStr"/>
+      <c r="V211" s="4" t="inlineStr"/>
+      <c r="W211" s="4" t="inlineStr"/>
+      <c r="X211" s="4" t="inlineStr">
+        <is>
+          <t>Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y211" s="4" t="inlineStr"/>
+      <c r="Z211" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA211" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB211" s="4" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="AC211" s="4" t="inlineStr"/>
+      <c r="AD211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF211" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG211" s="4" t="inlineStr"/>
+      <c r="AH211" s="4" t="inlineStr"/>
+      <c r="AI211" s="4" t="inlineStr"/>
+      <c r="AJ211" s="4" t="inlineStr"/>
+      <c r="AK211" s="4" t="inlineStr"/>
+      <c r="AL211" s="4" t="inlineStr"/>
+      <c r="AM211" s="4" t="inlineStr"/>
+      <c r="AN211" s="4" t="inlineStr"/>
+      <c r="AO211" s="4" t="inlineStr"/>
+      <c r="AP211" s="4" t="inlineStr"/>
+      <c r="AQ211" s="4" t="inlineStr"/>
+      <c r="AR211" s="4" t="n">
+        <v>709.55</v>
+      </c>
+      <c r="AS211" s="4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT211" s="4" t="inlineStr"/>
+      <c r="AU211" s="4" t="inlineStr"/>
+      <c r="AV211" s="4" t="inlineStr"/>
+      <c r="AW211" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX211" s="4" t="inlineStr"/>
+      <c r="AY211" s="4" t="inlineStr"/>
+      <c r="AZ211" s="4" t="inlineStr"/>
+      <c r="BA211" s="4" t="inlineStr"/>
+      <c r="BB211" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>LICI_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr"/>
+      <c r="J212" s="4" t="inlineStr"/>
+      <c r="K212" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr"/>
+      <c r="N212" s="4" t="inlineStr"/>
+      <c r="O212" s="4" t="inlineStr"/>
+      <c r="P212" s="4" t="inlineStr"/>
+      <c r="Q212" s="4" t="inlineStr"/>
+      <c r="R212" s="4" t="inlineStr"/>
+      <c r="S212" s="4" t="inlineStr"/>
+      <c r="T212" s="4" t="inlineStr"/>
+      <c r="U212" s="4" t="inlineStr"/>
+      <c r="V212" s="4" t="inlineStr"/>
+      <c r="W212" s="4" t="inlineStr"/>
+      <c r="X212" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y212" s="4" t="inlineStr"/>
+      <c r="Z212" s="4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AA212" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB212" s="4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AC212" s="4" t="inlineStr"/>
+      <c r="AD212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE212" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF212" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG212" s="4" t="inlineStr"/>
+      <c r="AH212" s="4" t="inlineStr"/>
+      <c r="AI212" s="4" t="inlineStr"/>
+      <c r="AJ212" s="4" t="inlineStr"/>
+      <c r="AK212" s="4" t="inlineStr"/>
+      <c r="AL212" s="4" t="inlineStr"/>
+      <c r="AM212" s="4" t="inlineStr"/>
+      <c r="AN212" s="4" t="inlineStr"/>
+      <c r="AO212" s="4" t="inlineStr"/>
+      <c r="AP212" s="4" t="inlineStr"/>
+      <c r="AQ212" s="4" t="inlineStr"/>
+      <c r="AR212" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AS212" s="4" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AT212" s="4" t="inlineStr"/>
+      <c r="AU212" s="4" t="inlineStr"/>
+      <c r="AV212" s="4" t="inlineStr"/>
+      <c r="AW212" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX212" s="4" t="inlineStr"/>
+      <c r="AY212" s="4" t="inlineStr"/>
+      <c r="AZ212" s="4" t="inlineStr"/>
+      <c r="BA212" s="4" t="inlineStr"/>
+      <c r="BB212" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr"/>
+      <c r="K213" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr"/>
+      <c r="O213" s="4" t="inlineStr"/>
+      <c r="P213" s="4" t="inlineStr"/>
+      <c r="Q213" s="4" t="inlineStr"/>
+      <c r="R213" s="4" t="inlineStr"/>
+      <c r="S213" s="4" t="inlineStr"/>
+      <c r="T213" s="4" t="inlineStr"/>
+      <c r="U213" s="4" t="inlineStr"/>
+      <c r="V213" s="4" t="inlineStr"/>
+      <c r="W213" s="4" t="inlineStr"/>
+      <c r="X213" s="4" t="inlineStr">
+        <is>
+          <t>Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y213" s="4" t="inlineStr"/>
+      <c r="Z213" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AA213" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB213" s="4" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="AC213" s="4" t="inlineStr"/>
+      <c r="AD213" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE213" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF213" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG213" s="4" t="inlineStr"/>
+      <c r="AH213" s="4" t="inlineStr"/>
+      <c r="AI213" s="4" t="inlineStr"/>
+      <c r="AJ213" s="4" t="inlineStr"/>
+      <c r="AK213" s="4" t="inlineStr"/>
+      <c r="AL213" s="4" t="inlineStr"/>
+      <c r="AM213" s="4" t="inlineStr"/>
+      <c r="AN213" s="4" t="inlineStr"/>
+      <c r="AO213" s="4" t="inlineStr"/>
+      <c r="AP213" s="4" t="inlineStr"/>
+      <c r="AQ213" s="4" t="inlineStr"/>
+      <c r="AR213" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AS213" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AT213" s="4" t="inlineStr"/>
+      <c r="AU213" s="4" t="inlineStr"/>
+      <c r="AV213" s="4" t="inlineStr"/>
+      <c r="AW213" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX213" s="4" t="inlineStr"/>
+      <c r="AY213" s="4" t="inlineStr"/>
+      <c r="AZ213" s="4" t="inlineStr"/>
+      <c r="BA213" s="4" t="inlineStr"/>
+      <c r="BB213" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr"/>
+      <c r="J214" s="4" t="inlineStr"/>
+      <c r="K214" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" s="4" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr"/>
+      <c r="P214" s="4" t="inlineStr"/>
+      <c r="Q214" s="4" t="inlineStr"/>
+      <c r="R214" s="4" t="inlineStr"/>
+      <c r="S214" s="4" t="inlineStr"/>
+      <c r="T214" s="4" t="inlineStr"/>
+      <c r="U214" s="4" t="inlineStr"/>
+      <c r="V214" s="4" t="inlineStr"/>
+      <c r="W214" s="4" t="inlineStr"/>
+      <c r="X214" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y214" s="4" t="inlineStr"/>
+      <c r="Z214" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="AA214" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB214" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AC214" s="4" t="inlineStr"/>
+      <c r="AD214" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF214" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG214" s="4" t="inlineStr"/>
+      <c r="AH214" s="4" t="inlineStr"/>
+      <c r="AI214" s="4" t="inlineStr"/>
+      <c r="AJ214" s="4" t="inlineStr"/>
+      <c r="AK214" s="4" t="inlineStr"/>
+      <c r="AL214" s="4" t="inlineStr"/>
+      <c r="AM214" s="4" t="inlineStr"/>
+      <c r="AN214" s="4" t="inlineStr"/>
+      <c r="AO214" s="4" t="inlineStr"/>
+      <c r="AP214" s="4" t="inlineStr"/>
+      <c r="AQ214" s="4" t="inlineStr"/>
+      <c r="AR214" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="AS214" s="4" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AT214" s="4" t="inlineStr"/>
+      <c r="AU214" s="4" t="inlineStr"/>
+      <c r="AV214" s="4" t="inlineStr"/>
+      <c r="AW214" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX214" s="4" t="inlineStr"/>
+      <c r="AY214" s="4" t="inlineStr"/>
+      <c r="AZ214" s="4" t="inlineStr"/>
+      <c r="BA214" s="4" t="inlineStr"/>
+      <c r="BB214" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr"/>
+      <c r="K215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" s="4" t="inlineStr"/>
+      <c r="O215" s="4" t="inlineStr"/>
+      <c r="P215" s="4" t="inlineStr"/>
+      <c r="Q215" s="4" t="inlineStr"/>
+      <c r="R215" s="4" t="inlineStr"/>
+      <c r="S215" s="4" t="inlineStr"/>
+      <c r="T215" s="4" t="inlineStr"/>
+      <c r="U215" s="4" t="inlineStr"/>
+      <c r="V215" s="4" t="inlineStr"/>
+      <c r="W215" s="4" t="inlineStr"/>
+      <c r="X215" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y215" s="4" t="inlineStr"/>
+      <c r="Z215" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA215" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB215" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AC215" s="4" t="inlineStr"/>
+      <c r="AD215" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE215" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF215" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG215" s="4" t="inlineStr"/>
+      <c r="AH215" s="4" t="inlineStr"/>
+      <c r="AI215" s="4" t="inlineStr"/>
+      <c r="AJ215" s="4" t="inlineStr"/>
+      <c r="AK215" s="4" t="inlineStr"/>
+      <c r="AL215" s="4" t="inlineStr"/>
+      <c r="AM215" s="4" t="inlineStr"/>
+      <c r="AN215" s="4" t="inlineStr"/>
+      <c r="AO215" s="4" t="inlineStr"/>
+      <c r="AP215" s="4" t="inlineStr"/>
+      <c r="AQ215" s="4" t="inlineStr"/>
+      <c r="AR215" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="AS215" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AT215" s="4" t="inlineStr"/>
+      <c r="AU215" s="4" t="inlineStr"/>
+      <c r="AV215" s="4" t="inlineStr"/>
+      <c r="AW215" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX215" s="4" t="inlineStr"/>
+      <c r="AY215" s="4" t="inlineStr"/>
+      <c r="AZ215" s="4" t="inlineStr"/>
+      <c r="BA215" s="4" t="inlineStr"/>
+      <c r="BB215" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr"/>
+      <c r="J216" s="4" t="inlineStr"/>
+      <c r="K216" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L216" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" s="4" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr"/>
+      <c r="P216" s="4" t="inlineStr"/>
+      <c r="Q216" s="4" t="inlineStr"/>
+      <c r="R216" s="4" t="inlineStr"/>
+      <c r="S216" s="4" t="inlineStr"/>
+      <c r="T216" s="4" t="inlineStr"/>
+      <c r="U216" s="4" t="inlineStr"/>
+      <c r="V216" s="4" t="inlineStr"/>
+      <c r="W216" s="4" t="inlineStr"/>
+      <c r="X216" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y216" s="4" t="inlineStr"/>
+      <c r="Z216" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA216" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB216" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC216" s="4" t="inlineStr"/>
+      <c r="AD216" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE216" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF216" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG216" s="4" t="inlineStr"/>
+      <c r="AH216" s="4" t="inlineStr"/>
+      <c r="AI216" s="4" t="inlineStr"/>
+      <c r="AJ216" s="4" t="inlineStr"/>
+      <c r="AK216" s="4" t="inlineStr"/>
+      <c r="AL216" s="4" t="inlineStr"/>
+      <c r="AM216" s="4" t="inlineStr"/>
+      <c r="AN216" s="4" t="inlineStr"/>
+      <c r="AO216" s="4" t="inlineStr"/>
+      <c r="AP216" s="4" t="inlineStr"/>
+      <c r="AQ216" s="4" t="inlineStr"/>
+      <c r="AR216" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AS216" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AT216" s="4" t="inlineStr"/>
+      <c r="AU216" s="4" t="inlineStr"/>
+      <c r="AV216" s="4" t="inlineStr"/>
+      <c r="AW216" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX216" s="4" t="inlineStr"/>
+      <c r="AY216" s="4" t="inlineStr"/>
+      <c r="AZ216" s="4" t="inlineStr"/>
+      <c r="BA216" s="4" t="inlineStr"/>
+      <c r="BB216" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr"/>
+      <c r="J217" s="4" t="inlineStr"/>
+      <c r="K217" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L217" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" s="4" t="inlineStr"/>
+      <c r="O217" s="4" t="inlineStr"/>
+      <c r="P217" s="4" t="inlineStr"/>
+      <c r="Q217" s="4" t="inlineStr"/>
+      <c r="R217" s="4" t="inlineStr"/>
+      <c r="S217" s="4" t="inlineStr"/>
+      <c r="T217" s="4" t="inlineStr"/>
+      <c r="U217" s="4" t="inlineStr"/>
+      <c r="V217" s="4" t="inlineStr"/>
+      <c r="W217" s="4" t="inlineStr"/>
+      <c r="X217" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y217" s="4" t="inlineStr"/>
+      <c r="Z217" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="AA217" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB217" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC217" s="4" t="inlineStr"/>
+      <c r="AD217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE217" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF217" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG217" s="4" t="inlineStr"/>
+      <c r="AH217" s="4" t="inlineStr"/>
+      <c r="AI217" s="4" t="inlineStr"/>
+      <c r="AJ217" s="4" t="inlineStr"/>
+      <c r="AK217" s="4" t="inlineStr"/>
+      <c r="AL217" s="4" t="inlineStr"/>
+      <c r="AM217" s="4" t="inlineStr"/>
+      <c r="AN217" s="4" t="inlineStr"/>
+      <c r="AO217" s="4" t="inlineStr"/>
+      <c r="AP217" s="4" t="inlineStr"/>
+      <c r="AQ217" s="4" t="inlineStr"/>
+      <c r="AR217" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AS217" s="4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT217" s="4" t="inlineStr"/>
+      <c r="AU217" s="4" t="inlineStr"/>
+      <c r="AV217" s="4" t="inlineStr"/>
+      <c r="AW217" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX217" s="4" t="inlineStr"/>
+      <c r="AY217" s="4" t="inlineStr"/>
+      <c r="AZ217" s="4" t="inlineStr"/>
+      <c r="BA217" s="4" t="inlineStr"/>
+      <c r="BB217" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr"/>
+      <c r="J218" s="4" t="inlineStr"/>
+      <c r="K218" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L218" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" s="4" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr"/>
+      <c r="P218" s="4" t="inlineStr"/>
+      <c r="Q218" s="4" t="inlineStr"/>
+      <c r="R218" s="4" t="inlineStr"/>
+      <c r="S218" s="4" t="inlineStr"/>
+      <c r="T218" s="4" t="inlineStr"/>
+      <c r="U218" s="4" t="inlineStr"/>
+      <c r="V218" s="4" t="inlineStr"/>
+      <c r="W218" s="4" t="inlineStr"/>
+      <c r="X218" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y218" s="4" t="inlineStr"/>
+      <c r="Z218" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="AA218" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB218" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC218" s="4" t="inlineStr"/>
+      <c r="AD218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE218" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF218" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG218" s="4" t="inlineStr"/>
+      <c r="AH218" s="4" t="inlineStr"/>
+      <c r="AI218" s="4" t="inlineStr"/>
+      <c r="AJ218" s="4" t="inlineStr"/>
+      <c r="AK218" s="4" t="inlineStr"/>
+      <c r="AL218" s="4" t="inlineStr"/>
+      <c r="AM218" s="4" t="inlineStr"/>
+      <c r="AN218" s="4" t="inlineStr"/>
+      <c r="AO218" s="4" t="inlineStr"/>
+      <c r="AP218" s="4" t="inlineStr"/>
+      <c r="AQ218" s="4" t="inlineStr"/>
+      <c r="AR218" s="4" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="AS218" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT218" s="4" t="inlineStr"/>
+      <c r="AU218" s="4" t="inlineStr"/>
+      <c r="AV218" s="4" t="inlineStr"/>
+      <c r="AW218" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX218" s="4" t="inlineStr"/>
+      <c r="AY218" s="4" t="inlineStr"/>
+      <c r="AZ218" s="4" t="inlineStr"/>
+      <c r="BA218" s="4" t="inlineStr"/>
+      <c r="BB218" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr"/>
+      <c r="J219" s="4" t="inlineStr"/>
+      <c r="K219" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L219" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" s="4" t="inlineStr"/>
+      <c r="O219" s="4" t="inlineStr"/>
+      <c r="P219" s="4" t="inlineStr"/>
+      <c r="Q219" s="4" t="inlineStr"/>
+      <c r="R219" s="4" t="inlineStr"/>
+      <c r="S219" s="4" t="inlineStr"/>
+      <c r="T219" s="4" t="inlineStr"/>
+      <c r="U219" s="4" t="inlineStr"/>
+      <c r="V219" s="4" t="inlineStr"/>
+      <c r="W219" s="4" t="inlineStr"/>
+      <c r="X219" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y219" s="4" t="inlineStr"/>
+      <c r="Z219" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA219" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB219" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AC219" s="4" t="inlineStr"/>
+      <c r="AD219" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE219" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF219" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG219" s="4" t="inlineStr"/>
+      <c r="AH219" s="4" t="inlineStr"/>
+      <c r="AI219" s="4" t="inlineStr"/>
+      <c r="AJ219" s="4" t="inlineStr"/>
+      <c r="AK219" s="4" t="inlineStr"/>
+      <c r="AL219" s="4" t="inlineStr"/>
+      <c r="AM219" s="4" t="inlineStr"/>
+      <c r="AN219" s="4" t="inlineStr"/>
+      <c r="AO219" s="4" t="inlineStr"/>
+      <c r="AP219" s="4" t="inlineStr"/>
+      <c r="AQ219" s="4" t="inlineStr"/>
+      <c r="AR219" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="AS219" s="4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AT219" s="4" t="inlineStr"/>
+      <c r="AU219" s="4" t="inlineStr"/>
+      <c r="AV219" s="4" t="inlineStr"/>
+      <c r="AW219" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX219" s="4" t="inlineStr"/>
+      <c r="AY219" s="4" t="inlineStr"/>
+      <c r="AZ219" s="4" t="inlineStr"/>
+      <c r="BA219" s="4" t="inlineStr"/>
+      <c r="BB219" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr"/>
+      <c r="J220" s="4" t="inlineStr"/>
+      <c r="K220" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L220" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" s="4" t="inlineStr"/>
+      <c r="O220" s="4" t="inlineStr"/>
+      <c r="P220" s="4" t="inlineStr"/>
+      <c r="Q220" s="4" t="inlineStr"/>
+      <c r="R220" s="4" t="inlineStr"/>
+      <c r="S220" s="4" t="inlineStr"/>
+      <c r="T220" s="4" t="inlineStr"/>
+      <c r="U220" s="4" t="inlineStr"/>
+      <c r="V220" s="4" t="inlineStr"/>
+      <c r="W220" s="4" t="inlineStr"/>
+      <c r="X220" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y220" s="4" t="inlineStr"/>
+      <c r="Z220" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA220" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB220" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC220" s="4" t="inlineStr"/>
+      <c r="AD220" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE220" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF220" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG220" s="4" t="inlineStr"/>
+      <c r="AH220" s="4" t="inlineStr"/>
+      <c r="AI220" s="4" t="inlineStr"/>
+      <c r="AJ220" s="4" t="inlineStr"/>
+      <c r="AK220" s="4" t="inlineStr"/>
+      <c r="AL220" s="4" t="inlineStr"/>
+      <c r="AM220" s="4" t="inlineStr"/>
+      <c r="AN220" s="4" t="inlineStr"/>
+      <c r="AO220" s="4" t="inlineStr"/>
+      <c r="AP220" s="4" t="inlineStr"/>
+      <c r="AQ220" s="4" t="inlineStr"/>
+      <c r="AR220" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="AS220" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AT220" s="4" t="inlineStr"/>
+      <c r="AU220" s="4" t="inlineStr"/>
+      <c r="AV220" s="4" t="inlineStr"/>
+      <c r="AW220" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX220" s="4" t="inlineStr"/>
+      <c r="AY220" s="4" t="inlineStr"/>
+      <c r="AZ220" s="4" t="inlineStr"/>
+      <c r="BA220" s="4" t="inlineStr"/>
+      <c r="BB220" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr"/>
+      <c r="J221" s="4" t="inlineStr"/>
+      <c r="K221" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L221" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" s="4" t="inlineStr"/>
+      <c r="O221" s="4" t="inlineStr"/>
+      <c r="P221" s="4" t="inlineStr"/>
+      <c r="Q221" s="4" t="inlineStr"/>
+      <c r="R221" s="4" t="inlineStr"/>
+      <c r="S221" s="4" t="inlineStr"/>
+      <c r="T221" s="4" t="inlineStr"/>
+      <c r="U221" s="4" t="inlineStr"/>
+      <c r="V221" s="4" t="inlineStr"/>
+      <c r="W221" s="4" t="inlineStr"/>
+      <c r="X221" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y221" s="4" t="inlineStr"/>
+      <c r="Z221" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA221" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB221" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC221" s="4" t="inlineStr"/>
+      <c r="AD221" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE221" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF221" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG221" s="4" t="inlineStr"/>
+      <c r="AH221" s="4" t="inlineStr"/>
+      <c r="AI221" s="4" t="inlineStr"/>
+      <c r="AJ221" s="4" t="inlineStr"/>
+      <c r="AK221" s="4" t="inlineStr"/>
+      <c r="AL221" s="4" t="inlineStr"/>
+      <c r="AM221" s="4" t="inlineStr"/>
+      <c r="AN221" s="4" t="inlineStr"/>
+      <c r="AO221" s="4" t="inlineStr"/>
+      <c r="AP221" s="4" t="inlineStr"/>
+      <c r="AQ221" s="4" t="inlineStr"/>
+      <c r="AR221" s="4" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="AS221" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT221" s="4" t="inlineStr"/>
+      <c r="AU221" s="4" t="inlineStr"/>
+      <c r="AV221" s="4" t="inlineStr"/>
+      <c r="AW221" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX221" s="4" t="inlineStr"/>
+      <c r="AY221" s="4" t="inlineStr"/>
+      <c r="AZ221" s="4" t="inlineStr"/>
+      <c r="BA221" s="4" t="inlineStr"/>
+      <c r="BB221" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr"/>
+      <c r="J222" s="4" t="inlineStr"/>
+      <c r="K222" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L222" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" s="4" t="inlineStr"/>
+      <c r="O222" s="4" t="inlineStr"/>
+      <c r="P222" s="4" t="inlineStr"/>
+      <c r="Q222" s="4" t="inlineStr"/>
+      <c r="R222" s="4" t="inlineStr"/>
+      <c r="S222" s="4" t="inlineStr"/>
+      <c r="T222" s="4" t="inlineStr"/>
+      <c r="U222" s="4" t="inlineStr"/>
+      <c r="V222" s="4" t="inlineStr"/>
+      <c r="W222" s="4" t="inlineStr"/>
+      <c r="X222" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y222" s="4" t="inlineStr"/>
+      <c r="Z222" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA222" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB222" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AC222" s="4" t="inlineStr"/>
+      <c r="AD222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE222" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF222" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG222" s="4" t="inlineStr"/>
+      <c r="AH222" s="4" t="inlineStr"/>
+      <c r="AI222" s="4" t="inlineStr"/>
+      <c r="AJ222" s="4" t="inlineStr"/>
+      <c r="AK222" s="4" t="inlineStr"/>
+      <c r="AL222" s="4" t="inlineStr"/>
+      <c r="AM222" s="4" t="inlineStr"/>
+      <c r="AN222" s="4" t="inlineStr"/>
+      <c r="AO222" s="4" t="inlineStr"/>
+      <c r="AP222" s="4" t="inlineStr"/>
+      <c r="AQ222" s="4" t="inlineStr"/>
+      <c r="AR222" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="AS222" s="4" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AT222" s="4" t="inlineStr"/>
+      <c r="AU222" s="4" t="inlineStr"/>
+      <c r="AV222" s="4" t="inlineStr"/>
+      <c r="AW222" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX222" s="4" t="inlineStr"/>
+      <c r="AY222" s="4" t="inlineStr"/>
+      <c r="AZ222" s="4" t="inlineStr"/>
+      <c r="BA222" s="4" t="inlineStr"/>
+      <c r="BB222" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr"/>
+      <c r="K223" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L223" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" s="4" t="inlineStr"/>
+      <c r="O223" s="4" t="inlineStr"/>
+      <c r="P223" s="4" t="inlineStr"/>
+      <c r="Q223" s="4" t="inlineStr"/>
+      <c r="R223" s="4" t="inlineStr"/>
+      <c r="S223" s="4" t="inlineStr"/>
+      <c r="T223" s="4" t="inlineStr"/>
+      <c r="U223" s="4" t="inlineStr"/>
+      <c r="V223" s="4" t="inlineStr"/>
+      <c r="W223" s="4" t="inlineStr"/>
+      <c r="X223" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y223" s="4" t="inlineStr"/>
+      <c r="Z223" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA223" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB223" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC223" s="4" t="inlineStr"/>
+      <c r="AD223" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE223" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF223" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG223" s="4" t="inlineStr"/>
+      <c r="AH223" s="4" t="inlineStr"/>
+      <c r="AI223" s="4" t="inlineStr"/>
+      <c r="AJ223" s="4" t="inlineStr"/>
+      <c r="AK223" s="4" t="inlineStr"/>
+      <c r="AL223" s="4" t="inlineStr"/>
+      <c r="AM223" s="4" t="inlineStr"/>
+      <c r="AN223" s="4" t="inlineStr"/>
+      <c r="AO223" s="4" t="inlineStr"/>
+      <c r="AP223" s="4" t="inlineStr"/>
+      <c r="AQ223" s="4" t="inlineStr"/>
+      <c r="AR223" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AS223" s="4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AT223" s="4" t="inlineStr"/>
+      <c r="AU223" s="4" t="inlineStr"/>
+      <c r="AV223" s="4" t="inlineStr"/>
+      <c r="AW223" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX223" s="4" t="inlineStr"/>
+      <c r="AY223" s="4" t="inlineStr"/>
+      <c r="AZ223" s="4" t="inlineStr"/>
+      <c r="BA223" s="4" t="inlineStr"/>
+      <c r="BB223" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr"/>
+      <c r="K224" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L224" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" s="4" t="inlineStr"/>
+      <c r="O224" s="4" t="inlineStr"/>
+      <c r="P224" s="4" t="inlineStr"/>
+      <c r="Q224" s="4" t="inlineStr"/>
+      <c r="R224" s="4" t="inlineStr"/>
+      <c r="S224" s="4" t="inlineStr"/>
+      <c r="T224" s="4" t="inlineStr"/>
+      <c r="U224" s="4" t="inlineStr"/>
+      <c r="V224" s="4" t="inlineStr"/>
+      <c r="W224" s="4" t="inlineStr"/>
+      <c r="X224" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y224" s="4" t="inlineStr"/>
+      <c r="Z224" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA224" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB224" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC224" s="4" t="inlineStr"/>
+      <c r="AD224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE224" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF224" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG224" s="4" t="inlineStr"/>
+      <c r="AH224" s="4" t="inlineStr"/>
+      <c r="AI224" s="4" t="inlineStr"/>
+      <c r="AJ224" s="4" t="inlineStr"/>
+      <c r="AK224" s="4" t="inlineStr"/>
+      <c r="AL224" s="4" t="inlineStr"/>
+      <c r="AM224" s="4" t="inlineStr"/>
+      <c r="AN224" s="4" t="inlineStr"/>
+      <c r="AO224" s="4" t="inlineStr"/>
+      <c r="AP224" s="4" t="inlineStr"/>
+      <c r="AQ224" s="4" t="inlineStr"/>
+      <c r="AR224" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="AS224" s="4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AT224" s="4" t="inlineStr"/>
+      <c r="AU224" s="4" t="inlineStr"/>
+      <c r="AV224" s="4" t="inlineStr"/>
+      <c r="AW224" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX224" s="4" t="inlineStr"/>
+      <c r="AY224" s="4" t="inlineStr"/>
+      <c r="AZ224" s="4" t="inlineStr"/>
+      <c r="BA224" s="4" t="inlineStr"/>
+      <c r="BB224" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr"/>
+      <c r="J225" s="4" t="inlineStr"/>
+      <c r="K225" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L225" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" s="4" t="inlineStr"/>
+      <c r="O225" s="4" t="inlineStr"/>
+      <c r="P225" s="4" t="inlineStr"/>
+      <c r="Q225" s="4" t="inlineStr"/>
+      <c r="R225" s="4" t="inlineStr"/>
+      <c r="S225" s="4" t="inlineStr"/>
+      <c r="T225" s="4" t="inlineStr"/>
+      <c r="U225" s="4" t="inlineStr"/>
+      <c r="V225" s="4" t="inlineStr"/>
+      <c r="W225" s="4" t="inlineStr"/>
+      <c r="X225" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="Y225" s="4" t="inlineStr"/>
+      <c r="Z225" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA225" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="AB225" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC225" s="4" t="inlineStr"/>
+      <c r="AD225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE225" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF225" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG225" s="4" t="inlineStr"/>
+      <c r="AH225" s="4" t="inlineStr"/>
+      <c r="AI225" s="4" t="inlineStr"/>
+      <c r="AJ225" s="4" t="inlineStr"/>
+      <c r="AK225" s="4" t="inlineStr"/>
+      <c r="AL225" s="4" t="inlineStr"/>
+      <c r="AM225" s="4" t="inlineStr"/>
+      <c r="AN225" s="4" t="inlineStr"/>
+      <c r="AO225" s="4" t="inlineStr"/>
+      <c r="AP225" s="4" t="inlineStr"/>
+      <c r="AQ225" s="4" t="inlineStr"/>
+      <c r="AR225" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="AS225" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AT225" s="4" t="inlineStr"/>
+      <c r="AU225" s="4" t="inlineStr"/>
+      <c r="AV225" s="4" t="inlineStr"/>
+      <c r="AW225" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AX225" s="4" t="inlineStr"/>
+      <c r="AY225" s="4" t="inlineStr"/>
+      <c r="AZ225" s="4" t="inlineStr"/>
+      <c r="BA225" s="4" t="inlineStr"/>
+      <c r="BB225" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BB206"/>
+  <autoFilter ref="A1:BB225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -868,14 +868,14 @@
       </c>
       <c r="AG2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH2" s="4" t="n">
-        <v>2452.2</v>
+        <v>2351.3</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>2452.2</v>
+        <v>2258.5</v>
       </c>
       <c r="AJ2" s="4" t="n">
         <v>2427.68</v>
@@ -906,7 +906,13 @@
         <v>-3.9</v>
       </c>
       <c r="AT2" s="4" t="n">
-        <v>0</v>
+        <v>4.11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.11</v>
       </c>
       <c r="AW2" s="4" t="inlineStr">
         <is>
@@ -988,14 +994,14 @@
       </c>
       <c r="AG3" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH3" s="4" t="n">
-        <v>5196.6</v>
+        <v>5343.6</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>5196.6</v>
+        <v>5057.4</v>
       </c>
       <c r="AJ3" s="4" t="n">
         <v>5144.63</v>
@@ -1026,7 +1032,13 @@
         <v>3.78</v>
       </c>
       <c r="AT3" s="4" t="n">
-        <v>0</v>
+        <v>5.66</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.81</v>
       </c>
       <c r="AW3" s="4" t="inlineStr">
         <is>
@@ -1104,11 +1116,11 @@
       </c>
       <c r="AG4" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH4" s="4" t="n">
-        <v>133.14</v>
+        <v>133.1</v>
       </c>
       <c r="AI4" s="4" t="n">
         <v>133.14</v>
@@ -1142,7 +1154,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT4" s="4" t="n">
-        <v>0</v>
+        <v>-0.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.03</v>
       </c>
       <c r="AW4" s="4" t="inlineStr">
         <is>
@@ -1220,11 +1238,11 @@
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH5" s="4" t="n">
-        <v>5524</v>
+        <v>5322.4</v>
       </c>
       <c r="AI5" s="4" t="n">
         <v>5524</v>
@@ -1258,7 +1276,13 @@
         <v>-2.93</v>
       </c>
       <c r="AT5" s="4" t="n">
-        <v>0</v>
+        <v>-3.65</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-3.65</v>
       </c>
       <c r="AW5" s="4" t="inlineStr">
         <is>
@@ -1340,14 +1364,14 @@
       </c>
       <c r="AG6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH6" s="4" t="n">
-        <v>1346.6</v>
+        <v>1319.2</v>
       </c>
       <c r="AI6" s="4" t="n">
-        <v>1346.6</v>
+        <v>1263.5</v>
       </c>
       <c r="AJ6" s="4" t="n">
         <v>1333.13</v>
@@ -1378,7 +1402,13 @@
         <v>-1.87</v>
       </c>
       <c r="AT6" s="4" t="n">
-        <v>0</v>
+        <v>4.41</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.41</v>
       </c>
       <c r="AW6" s="4" t="inlineStr">
         <is>
@@ -1456,11 +1486,11 @@
       </c>
       <c r="AG7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH7" s="4" t="n">
-        <v>11602</v>
+        <v>11075</v>
       </c>
       <c r="AI7" s="4" t="n">
         <v>11602</v>
@@ -1494,7 +1524,13 @@
         <v>-3.08</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>0</v>
+        <v>-4.54</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-4.54</v>
       </c>
       <c r="AW7" s="4" t="inlineStr">
         <is>
@@ -1572,11 +1608,11 @@
       </c>
       <c r="AG8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH8" s="4" t="n">
-        <v>1158</v>
+        <v>1115</v>
       </c>
       <c r="AI8" s="4" t="n">
         <v>1158</v>
@@ -1610,7 +1646,13 @@
         <v>-3.51</v>
       </c>
       <c r="AT8" s="4" t="n">
-        <v>0</v>
+        <v>-3.71</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-3.71</v>
       </c>
       <c r="AW8" s="4" t="inlineStr">
         <is>
@@ -1692,14 +1734,14 @@
       </c>
       <c r="AG9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH9" s="4" t="n">
-        <v>449.35</v>
+        <v>443.35</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>449.35</v>
+        <v>430.5</v>
       </c>
       <c r="AJ9" s="4" t="n">
         <v>444.86</v>
@@ -1730,7 +1772,13 @@
         <v>-1.79</v>
       </c>
       <c r="AT9" s="4" t="n">
-        <v>0</v>
+        <v>2.98</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.98</v>
       </c>
       <c r="AW9" s="4" t="inlineStr">
         <is>
@@ -1812,14 +1860,14 @@
       </c>
       <c r="AG10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH10" s="4" t="n">
-        <v>287.2</v>
+        <v>282.9</v>
       </c>
       <c r="AI10" s="4" t="n">
-        <v>287.2</v>
+        <v>280.95</v>
       </c>
       <c r="AJ10" s="4" t="n">
         <v>284.33</v>
@@ -1850,7 +1898,13 @@
         <v>-1.17</v>
       </c>
       <c r="AT10" s="4" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW10" s="4" t="inlineStr">
         <is>
@@ -1928,14 +1982,14 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH11" s="4" t="n">
-        <v>10880</v>
+        <v>11127</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>10880</v>
+        <v>10678</v>
       </c>
       <c r="AJ11" s="4" t="n">
         <v>10771.2</v>
@@ -1966,7 +2020,13 @@
         <v>1.63</v>
       </c>
       <c r="AT11" s="4" t="n">
-        <v>0</v>
+        <v>4.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.89</v>
       </c>
       <c r="AW11" s="4" t="inlineStr">
         <is>
@@ -2048,14 +2108,14 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH12" s="4" t="n">
-        <v>952.55</v>
+        <v>950.2</v>
       </c>
       <c r="AI12" s="4" t="n">
-        <v>952.55</v>
+        <v>943.1</v>
       </c>
       <c r="AJ12" s="4" t="n">
         <v>943.02</v>
@@ -2086,7 +2146,13 @@
         <v>-0.19</v>
       </c>
       <c r="AT12" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.75</v>
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
@@ -2168,14 +2234,14 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH13" s="4" t="n">
-        <v>431.4</v>
+        <v>425.5</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>431.4</v>
+        <v>429.4</v>
       </c>
       <c r="AJ13" s="4" t="n">
         <v>427.09</v>
@@ -2206,7 +2272,13 @@
         <v>-1.3</v>
       </c>
       <c r="AT13" s="4" t="n">
-        <v>0</v>
+        <v>-0.91</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.91</v>
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
@@ -2284,11 +2356,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH14" s="4" t="n">
-        <v>2157.8</v>
+        <v>2187.4</v>
       </c>
       <c r="AI14" s="4" t="n">
         <v>2157.8</v>
@@ -2322,7 +2394,13 @@
         <v>0.73</v>
       </c>
       <c r="AT14" s="4" t="n">
-        <v>0</v>
+        <v>1.37</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.63</v>
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
@@ -2404,14 +2482,14 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH15" s="4" t="n">
-        <v>547.4</v>
+        <v>546</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>547.4</v>
+        <v>550.25</v>
       </c>
       <c r="AJ15" s="4" t="n">
         <v>541.9299999999999</v>
@@ -2442,7 +2520,13 @@
         <v>0.05</v>
       </c>
       <c r="AT15" s="4" t="n">
-        <v>0</v>
+        <v>-0.77</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.83</v>
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
@@ -2520,11 +2604,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH16" s="4" t="n">
-        <v>1363</v>
+        <v>1360.5</v>
       </c>
       <c r="AI16" s="4" t="n">
         <v>1363</v>
@@ -2558,7 +2642,13 @@
         <v>-0.92</v>
       </c>
       <c r="AT16" s="4" t="n">
-        <v>0</v>
+        <v>-0.18</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.18</v>
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
@@ -2871,14 +2961,14 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH19" s="4" t="n">
         <v>2417</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>2417</v>
+        <v>2376.2</v>
       </c>
       <c r="AJ19" s="4" t="n">
         <v>2392.83</v>
@@ -2909,7 +2999,13 @@
         <v>-1.23</v>
       </c>
       <c r="AT19" s="4" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.72</v>
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
@@ -3690,14 +3786,14 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH26" s="4" t="n">
         <v>411.3</v>
       </c>
       <c r="AI26" s="4" t="n">
-        <v>411.3</v>
+        <v>426.65</v>
       </c>
       <c r="AJ26" s="4" t="n">
         <v>407.19</v>
@@ -3728,7 +3824,13 @@
         <v>0.3</v>
       </c>
       <c r="AT26" s="4" t="n">
-        <v>0</v>
+        <v>-3.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-3.89</v>
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
@@ -4084,7 +4186,7 @@
       </c>
       <c r="AR29" s="4" t="inlineStr"/>
       <c r="AT29" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU29" s="4" t="n">
         <v>2.11</v>
@@ -4215,7 +4317,7 @@
       </c>
       <c r="AR30" s="4" t="inlineStr"/>
       <c r="AT30" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU30" s="4" t="n">
         <v>0</v>
@@ -4608,7 +4710,7 @@
       </c>
       <c r="AR33" s="4" t="inlineStr"/>
       <c r="AT33" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU33" s="4" t="n">
         <v>0</v>
@@ -4739,7 +4841,7 @@
       </c>
       <c r="AR34" s="4" t="inlineStr"/>
       <c r="AT34" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU34" s="4" t="n">
         <v>0</v>
@@ -5001,7 +5103,7 @@
       </c>
       <c r="AR36" s="4" t="inlineStr"/>
       <c r="AT36" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU36" s="4" t="n">
         <v>7.39</v>
@@ -5132,7 +5234,7 @@
       </c>
       <c r="AR37" s="4" t="inlineStr"/>
       <c r="AT37" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU37" s="4" t="n">
         <v>10.29</v>
@@ -5394,7 +5496,7 @@
       </c>
       <c r="AR39" s="4" t="inlineStr"/>
       <c r="AT39" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU39" s="4" t="n">
         <v>0.99</v>
@@ -5525,7 +5627,7 @@
       </c>
       <c r="AR40" s="4" t="inlineStr"/>
       <c r="AT40" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU40" s="4" t="n">
         <v>0</v>
@@ -5656,7 +5758,7 @@
       </c>
       <c r="AR41" s="4" t="inlineStr"/>
       <c r="AT41" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU41" s="4" t="n">
         <v>0</v>
@@ -5787,7 +5889,7 @@
       </c>
       <c r="AR42" s="4" t="inlineStr"/>
       <c r="AT42" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU42" s="4" t="n">
         <v>1.09</v>
@@ -5875,11 +5977,11 @@
       </c>
       <c r="AG43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH43" s="4" t="n">
-        <v>2376.2</v>
+        <v>2383.9</v>
       </c>
       <c r="AI43" s="4" t="n">
         <v>2376.2</v>
@@ -5913,7 +6015,13 @@
         <v>-0.59</v>
       </c>
       <c r="AT43" s="4" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0.32</v>
       </c>
       <c r="AW43" s="4" t="inlineStr">
         <is>
@@ -6004,11 +6112,11 @@
       </c>
       <c r="AG44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH44" s="4" t="n">
-        <v>5057.4</v>
+        <v>5470.5</v>
       </c>
       <c r="AI44" s="4" t="n">
         <v>5057.4</v>
@@ -6042,7 +6150,13 @@
         <v>0.6</v>
       </c>
       <c r="AT44" s="4" t="n">
-        <v>0</v>
+        <v>8.17</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1.81</v>
       </c>
       <c r="AW44" s="4" t="inlineStr">
         <is>
@@ -6133,11 +6247,11 @@
       </c>
       <c r="AG45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH45" s="4" t="n">
-        <v>430.5</v>
+        <v>452.35</v>
       </c>
       <c r="AI45" s="4" t="n">
         <v>430.5</v>
@@ -6171,7 +6285,13 @@
         <v>1.7</v>
       </c>
       <c r="AT45" s="4" t="n">
-        <v>0</v>
+        <v>5.08</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.98</v>
       </c>
       <c r="AW45" s="4" t="inlineStr">
         <is>
@@ -6256,11 +6376,11 @@
       </c>
       <c r="AG46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH46" s="4" t="n">
-        <v>109.29</v>
+        <v>113.36</v>
       </c>
       <c r="AI46" s="4" t="n">
         <v>109.29</v>
@@ -6294,7 +6414,13 @@
         <v>0.46</v>
       </c>
       <c r="AT46" s="4" t="n">
-        <v>0</v>
+        <v>3.72</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>1.64</v>
       </c>
       <c r="AW46" s="4" t="inlineStr">
         <is>
@@ -6376,11 +6502,11 @@
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH47" s="4" t="n">
-        <v>426.65</v>
+        <v>415.15</v>
       </c>
       <c r="AI47" s="4" t="n">
         <v>426.65</v>
@@ -6414,7 +6540,13 @@
         <v>0.1</v>
       </c>
       <c r="AT47" s="4" t="n">
-        <v>0</v>
+        <v>-2.7</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>-3.89</v>
       </c>
       <c r="AW47" s="4" t="inlineStr">
         <is>
@@ -6496,11 +6628,11 @@
       </c>
       <c r="AG48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH48" s="4" t="n">
-        <v>261</v>
+        <v>268.5</v>
       </c>
       <c r="AI48" s="4" t="n">
         <v>261</v>
@@ -6534,7 +6666,13 @@
         <v>0.49</v>
       </c>
       <c r="AT48" s="4" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0.96</v>
       </c>
       <c r="AW48" s="4" t="inlineStr">
         <is>
@@ -6622,11 +6760,11 @@
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH49" s="4" t="n">
-        <v>280.95</v>
+        <v>284.85</v>
       </c>
       <c r="AI49" s="4" t="n">
         <v>280.95</v>
@@ -6660,7 +6798,13 @@
         <v>-2.42</v>
       </c>
       <c r="AT49" s="4" t="n">
-        <v>0</v>
+        <v>1.39</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW49" s="4" t="inlineStr">
         <is>
@@ -6748,11 +6892,11 @@
       </c>
       <c r="AG50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH50" s="4" t="n">
-        <v>1263.5</v>
+        <v>1363.6</v>
       </c>
       <c r="AI50" s="4" t="n">
         <v>1263.5</v>
@@ -6786,7 +6930,13 @@
         <v>1.13</v>
       </c>
       <c r="AT50" s="4" t="n">
-        <v>0</v>
+        <v>7.92</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>4.41</v>
       </c>
       <c r="AW50" s="4" t="inlineStr">
         <is>
@@ -6874,11 +7024,11 @@
       </c>
       <c r="AG51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH51" s="4" t="n">
-        <v>2258.5</v>
+        <v>2439.4</v>
       </c>
       <c r="AI51" s="4" t="n">
         <v>2258.5</v>
@@ -6912,7 +7062,13 @@
         <v>1.91</v>
       </c>
       <c r="AT51" s="4" t="n">
-        <v>0</v>
+        <v>8.01</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4.11</v>
       </c>
       <c r="AW51" s="4" t="inlineStr">
         <is>
@@ -6994,11 +7150,11 @@
       </c>
       <c r="AG52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH52" s="4" t="n">
-        <v>526.45</v>
+        <v>552.4</v>
       </c>
       <c r="AI52" s="4" t="n">
         <v>526.45</v>
@@ -7032,7 +7188,13 @@
         <v>1.69</v>
       </c>
       <c r="AT52" s="4" t="n">
-        <v>0</v>
+        <v>4.93</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>1.04</v>
       </c>
       <c r="AW52" s="4" t="inlineStr">
         <is>
@@ -7128,11 +7290,11 @@
       </c>
       <c r="AG53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH53" s="4" t="n">
-        <v>429.4</v>
+        <v>425.05</v>
       </c>
       <c r="AI53" s="4" t="n">
         <v>429.4</v>
@@ -7166,7 +7328,13 @@
         <v>-0.01</v>
       </c>
       <c r="AT53" s="4" t="n">
-        <v>0</v>
+        <v>-1.01</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>-1.01</v>
       </c>
       <c r="AW53" s="4" t="inlineStr">
         <is>
@@ -7262,11 +7430,11 @@
       </c>
       <c r="AG54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH54" s="4" t="n">
-        <v>943.1</v>
+        <v>939.95</v>
       </c>
       <c r="AI54" s="4" t="n">
         <v>943.1</v>
@@ -7300,7 +7468,13 @@
         <v>-2.26</v>
       </c>
       <c r="AT54" s="4" t="n">
-        <v>0</v>
+        <v>-0.33</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>-0.33</v>
       </c>
       <c r="AW54" s="4" t="inlineStr">
         <is>
@@ -7396,11 +7570,11 @@
       </c>
       <c r="AG55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH55" s="4" t="n">
-        <v>550.25</v>
+        <v>567.3</v>
       </c>
       <c r="AI55" s="4" t="n">
         <v>550.25</v>
@@ -7434,7 +7608,13 @@
         <v>0.05</v>
       </c>
       <c r="AT55" s="4" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>-0.83</v>
       </c>
       <c r="AW55" s="4" t="inlineStr">
         <is>
@@ -7524,11 +7704,11 @@
       </c>
       <c r="AG56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH56" s="4" t="n">
-        <v>7338.5</v>
+        <v>7454.5</v>
       </c>
       <c r="AI56" s="4" t="n">
         <v>7338.5</v>
@@ -7562,7 +7742,13 @@
         <v>-0.14</v>
       </c>
       <c r="AT56" s="4" t="n">
-        <v>0</v>
+        <v>1.58</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0.68</v>
       </c>
       <c r="AW56" s="4" t="inlineStr">
         <is>
@@ -7652,11 +7838,11 @@
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH57" s="4" t="n">
-        <v>673.7</v>
+        <v>709</v>
       </c>
       <c r="AI57" s="4" t="n">
         <v>673.7</v>
@@ -7690,7 +7876,13 @@
         <v>1.39</v>
       </c>
       <c r="AT57" s="4" t="n">
-        <v>0</v>
+        <v>5.24</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>2.95</v>
       </c>
       <c r="AW57" s="4" t="inlineStr">
         <is>
@@ -9042,7 +9234,7 @@
       </c>
       <c r="AR68" s="4" t="inlineStr"/>
       <c r="AT68" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU68" s="4" t="n">
         <v>2.11</v>
@@ -9179,7 +9371,7 @@
       </c>
       <c r="AR69" s="4" t="inlineStr"/>
       <c r="AT69" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU69" s="4" t="n">
         <v>0</v>
@@ -9590,7 +9782,7 @@
       </c>
       <c r="AR72" s="4" t="inlineStr"/>
       <c r="AT72" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU72" s="4" t="n">
         <v>0</v>
@@ -9727,7 +9919,7 @@
       </c>
       <c r="AR73" s="4" t="inlineStr"/>
       <c r="AT73" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU73" s="4" t="n">
         <v>0</v>
@@ -10001,7 +10193,7 @@
       </c>
       <c r="AR75" s="4" t="inlineStr"/>
       <c r="AT75" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU75" s="4" t="n">
         <v>7.39</v>
@@ -10138,7 +10330,7 @@
       </c>
       <c r="AR76" s="4" t="inlineStr"/>
       <c r="AT76" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU76" s="4" t="n">
         <v>10.29</v>
@@ -10412,7 +10604,7 @@
       </c>
       <c r="AR78" s="4" t="inlineStr"/>
       <c r="AT78" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU78" s="4" t="n">
         <v>0.99</v>
@@ -10549,7 +10741,7 @@
       </c>
       <c r="AR79" s="4" t="inlineStr"/>
       <c r="AT79" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU79" s="4" t="n">
         <v>0</v>
@@ -10686,7 +10878,7 @@
       </c>
       <c r="AR80" s="4" t="inlineStr"/>
       <c r="AT80" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU80" s="4" t="n">
         <v>0</v>
@@ -10823,7 +11015,7 @@
       </c>
       <c r="AR81" s="4" t="inlineStr"/>
       <c r="AT81" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU81" s="4" t="n">
         <v>1.09</v>
@@ -10938,14 +11130,14 @@
       </c>
       <c r="AG82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH82" s="4" t="n">
-        <v>2452.2</v>
+        <v>2460</v>
       </c>
       <c r="AI82" s="4" t="n">
-        <v>2452.2</v>
+        <v>2258.5</v>
       </c>
       <c r="AJ82" s="4" t="n">
         <v>2427.68</v>
@@ -10976,7 +11168,13 @@
         <v>0.84</v>
       </c>
       <c r="AT82" s="4" t="n">
-        <v>0</v>
+        <v>8.92</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>4.11</v>
       </c>
       <c r="AW82" s="4" t="inlineStr">
         <is>
@@ -11085,14 +11283,14 @@
       </c>
       <c r="AG83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH83" s="4" t="n">
-        <v>1346.6</v>
+        <v>1369.9</v>
       </c>
       <c r="AI83" s="4" t="n">
-        <v>1346.6</v>
+        <v>1263.5</v>
       </c>
       <c r="AJ83" s="4" t="n">
         <v>1333.13</v>
@@ -11123,7 +11321,13 @@
         <v>0.46</v>
       </c>
       <c r="AT83" s="4" t="n">
-        <v>0</v>
+        <v>8.42</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>4.41</v>
       </c>
       <c r="AW83" s="4" t="inlineStr">
         <is>
@@ -11228,11 +11432,11 @@
       </c>
       <c r="AG84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH84" s="4" t="n">
-        <v>11602</v>
+        <v>11600</v>
       </c>
       <c r="AI84" s="4" t="n">
         <v>11602</v>
@@ -11266,7 +11470,13 @@
         <v>0.99</v>
       </c>
       <c r="AT84" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>-4.54</v>
       </c>
       <c r="AW84" s="4" t="inlineStr">
         <is>
@@ -11665,14 +11875,14 @@
       </c>
       <c r="AG87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH87" s="4" t="n">
-        <v>5196.6</v>
+        <v>5548</v>
       </c>
       <c r="AI87" s="4" t="n">
-        <v>5196.6</v>
+        <v>5057.4</v>
       </c>
       <c r="AJ87" s="4" t="n">
         <v>5144.63</v>
@@ -11703,7 +11913,13 @@
         <v>1.42</v>
       </c>
       <c r="AT87" s="4" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>1.81</v>
       </c>
       <c r="AW87" s="4" t="inlineStr">
         <is>
@@ -11955,14 +12171,14 @@
       </c>
       <c r="AG89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH89" s="4" t="n">
         <v>450</v>
       </c>
       <c r="AI89" s="4" t="n">
-        <v>450</v>
+        <v>459.25</v>
       </c>
       <c r="AJ89" s="4" t="n">
         <v>445.5</v>
@@ -11993,7 +12209,13 @@
         <v>-0.12</v>
       </c>
       <c r="AT89" s="4" t="n">
-        <v>0</v>
+        <v>-2.01</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>-3.96</v>
       </c>
       <c r="AW89" s="4" t="inlineStr">
         <is>
@@ -12243,14 +12465,14 @@
       </c>
       <c r="AG91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH91" s="4" t="n">
-        <v>10880</v>
+        <v>11475</v>
       </c>
       <c r="AI91" s="4" t="n">
-        <v>10880</v>
+        <v>10678</v>
       </c>
       <c r="AJ91" s="4" t="n">
         <v>10771.2</v>
@@ -12281,7 +12503,13 @@
         <v>-0.55</v>
       </c>
       <c r="AT91" s="4" t="n">
-        <v>0</v>
+        <v>7.46</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>1.89</v>
       </c>
       <c r="AW91" s="4" t="inlineStr">
         <is>
@@ -12388,14 +12616,14 @@
       </c>
       <c r="AG92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH92" s="4" t="n">
         <v>1327.7</v>
       </c>
       <c r="AI92" s="4" t="n">
-        <v>1327.7</v>
+        <v>1298.9</v>
       </c>
       <c r="AJ92" s="4" t="n">
         <v>1314.42</v>
@@ -12426,7 +12654,13 @@
         <v>-0.4</v>
       </c>
       <c r="AT92" s="4" t="n">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>0.47</v>
       </c>
       <c r="AW92" s="4" t="inlineStr">
         <is>
@@ -12680,14 +12914,14 @@
       </c>
       <c r="AG94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH94" s="4" t="n">
-        <v>952.55</v>
+        <v>932.8</v>
       </c>
       <c r="AI94" s="4" t="n">
-        <v>952.55</v>
+        <v>943.1</v>
       </c>
       <c r="AJ94" s="4" t="n">
         <v>943.02</v>
@@ -12718,7 +12952,13 @@
         <v>-0.76</v>
       </c>
       <c r="AT94" s="4" t="n">
-        <v>0</v>
+        <v>-1.09</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>-1.09</v>
       </c>
       <c r="AW94" s="4" t="inlineStr">
         <is>
@@ -12972,14 +13212,14 @@
       </c>
       <c r="AG96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH96" s="4" t="n">
-        <v>431.4</v>
+        <v>422</v>
       </c>
       <c r="AI96" s="4" t="n">
-        <v>431.4</v>
+        <v>429.4</v>
       </c>
       <c r="AJ96" s="4" t="n">
         <v>427.09</v>
@@ -13010,7 +13250,13 @@
         <v>-0.72</v>
       </c>
       <c r="AT96" s="4" t="n">
-        <v>0</v>
+        <v>-1.72</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>-1.72</v>
       </c>
       <c r="AW96" s="4" t="inlineStr">
         <is>
@@ -13484,14 +13730,14 @@
       </c>
       <c r="AG100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH100" s="4" t="n">
         <v>2410</v>
       </c>
       <c r="AI100" s="4" t="n">
-        <v>2410</v>
+        <v>2376.2</v>
       </c>
       <c r="AJ100" s="4" t="n">
         <v>2385.9</v>
@@ -13522,7 +13768,13 @@
         <v>1.09</v>
       </c>
       <c r="AT100" s="4" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>0.32</v>
       </c>
       <c r="AW100" s="4" t="inlineStr">
         <is>
@@ -13990,14 +14242,14 @@
       </c>
       <c r="AG104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH104" s="4" t="n">
         <v>289</v>
       </c>
       <c r="AI104" s="4" t="n">
-        <v>289</v>
+        <v>280.95</v>
       </c>
       <c r="AJ104" s="4" t="n">
         <v>286.11</v>
@@ -14028,7 +14280,13 @@
         <v>1.46</v>
       </c>
       <c r="AT104" s="4" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW104" s="4" t="inlineStr">
         <is>
@@ -14498,14 +14756,14 @@
       </c>
       <c r="AG108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH108" s="4" t="n">
         <v>417.6</v>
       </c>
       <c r="AI108" s="4" t="n">
-        <v>417.6</v>
+        <v>426.65</v>
       </c>
       <c r="AJ108" s="4" t="n">
         <v>413.42</v>
@@ -14536,7 +14794,13 @@
         <v>0.59</v>
       </c>
       <c r="AT108" s="4" t="n">
-        <v>0</v>
+        <v>-2.12</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>-3.89</v>
       </c>
       <c r="AW108" s="4" t="inlineStr">
         <is>
@@ -14833,7 +15097,7 @@
       </c>
       <c r="AR110" s="4" t="inlineStr"/>
       <c r="AT110" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU110" s="4" t="n">
         <v>2.11</v>
@@ -14991,7 +15255,7 @@
       </c>
       <c r="AR111" s="4" t="inlineStr"/>
       <c r="AT111" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU111" s="4" t="n">
         <v>0</v>
@@ -15465,7 +15729,7 @@
       </c>
       <c r="AR114" s="4" t="inlineStr"/>
       <c r="AT114" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU114" s="4" t="n">
         <v>0</v>
@@ -15623,7 +15887,7 @@
       </c>
       <c r="AR115" s="4" t="inlineStr"/>
       <c r="AT115" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU115" s="4" t="n">
         <v>0</v>
@@ -15939,7 +16203,7 @@
       </c>
       <c r="AR117" s="4" t="inlineStr"/>
       <c r="AT117" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU117" s="4" t="n">
         <v>7.39</v>
@@ -16097,7 +16361,7 @@
       </c>
       <c r="AR118" s="4" t="inlineStr"/>
       <c r="AT118" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU118" s="4" t="n">
         <v>10.29</v>
@@ -16413,7 +16677,7 @@
       </c>
       <c r="AR120" s="4" t="inlineStr"/>
       <c r="AT120" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU120" s="4" t="n">
         <v>0.99</v>
@@ -16571,7 +16835,7 @@
       </c>
       <c r="AR121" s="4" t="inlineStr"/>
       <c r="AT121" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU121" s="4" t="n">
         <v>0</v>
@@ -16729,7 +16993,7 @@
       </c>
       <c r="AR122" s="4" t="inlineStr"/>
       <c r="AT122" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU122" s="4" t="n">
         <v>0</v>
@@ -16887,7 +17151,7 @@
       </c>
       <c r="AR123" s="4" t="inlineStr"/>
       <c r="AT123" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU123" s="4" t="n">
         <v>1.09</v>
@@ -16998,11 +17262,11 @@
       </c>
       <c r="AG124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH124" s="4" t="n">
-        <v>133.14</v>
+        <v>129.2</v>
       </c>
       <c r="AI124" s="4" t="n">
         <v>133.14</v>
@@ -17036,7 +17300,13 @@
         <v>1.33</v>
       </c>
       <c r="AT124" s="4" t="n">
-        <v>0</v>
+        <v>-2.96</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-4.24</v>
       </c>
       <c r="AW124" s="4" t="inlineStr">
         <is>
@@ -17141,11 +17411,11 @@
       </c>
       <c r="AG125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH125" s="4" t="n">
-        <v>5524</v>
+        <v>5499</v>
       </c>
       <c r="AI125" s="4" t="n">
         <v>5524</v>
@@ -17179,7 +17449,13 @@
         <v>0.26</v>
       </c>
       <c r="AT125" s="4" t="n">
-        <v>0</v>
+        <v>-0.45</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-3.65</v>
       </c>
       <c r="AW125" s="4" t="inlineStr">
         <is>
@@ -17284,11 +17560,11 @@
       </c>
       <c r="AG126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH126" s="4" t="n">
-        <v>1158</v>
+        <v>1167.5</v>
       </c>
       <c r="AI126" s="4" t="n">
         <v>1158</v>
@@ -17322,7 +17598,13 @@
         <v>0.21</v>
       </c>
       <c r="AT126" s="4" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-3.71</v>
       </c>
       <c r="AW126" s="4" t="inlineStr">
         <is>
@@ -17431,14 +17713,14 @@
       </c>
       <c r="AG127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH127" s="4" t="n">
-        <v>449.35</v>
+        <v>454.6</v>
       </c>
       <c r="AI127" s="4" t="n">
-        <v>449.35</v>
+        <v>430.5</v>
       </c>
       <c r="AJ127" s="4" t="n">
         <v>444.86</v>
@@ -17469,7 +17751,13 @@
         <v>0.5</v>
       </c>
       <c r="AT127" s="4" t="n">
-        <v>0</v>
+        <v>5.6</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>2.98</v>
       </c>
       <c r="AW127" s="4" t="inlineStr">
         <is>
@@ -17578,14 +17866,14 @@
       </c>
       <c r="AG128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH128" s="4" t="n">
-        <v>287.2</v>
+        <v>289</v>
       </c>
       <c r="AI128" s="4" t="n">
-        <v>287.2</v>
+        <v>280.95</v>
       </c>
       <c r="AJ128" s="4" t="n">
         <v>284.33</v>
@@ -17616,7 +17904,13 @@
         <v>1.46</v>
       </c>
       <c r="AT128" s="4" t="n">
-        <v>0</v>
+        <v>2.87</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW128" s="4" t="inlineStr">
         <is>
@@ -17721,11 +18015,11 @@
       </c>
       <c r="AG129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH129" s="4" t="n">
-        <v>2157.8</v>
+        <v>2195</v>
       </c>
       <c r="AI129" s="4" t="n">
         <v>2157.8</v>
@@ -17759,7 +18053,13 @@
         <v>-0.25</v>
       </c>
       <c r="AT129" s="4" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.63</v>
       </c>
       <c r="AW129" s="4" t="inlineStr">
         <is>
@@ -17868,14 +18168,14 @@
       </c>
       <c r="AG130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH130" s="4" t="n">
-        <v>547.4</v>
+        <v>568</v>
       </c>
       <c r="AI130" s="4" t="n">
-        <v>547.4</v>
+        <v>550.25</v>
       </c>
       <c r="AJ130" s="4" t="n">
         <v>541.9299999999999</v>
@@ -17906,7 +18206,13 @@
         <v>0.12</v>
       </c>
       <c r="AT130" s="4" t="n">
-        <v>0</v>
+        <v>3.23</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.83</v>
       </c>
       <c r="AW130" s="4" t="inlineStr">
         <is>
@@ -18011,11 +18317,11 @@
       </c>
       <c r="AG131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH131" s="4" t="n">
-        <v>1363</v>
+        <v>1384</v>
       </c>
       <c r="AI131" s="4" t="n">
         <v>1363</v>
@@ -18049,7 +18355,13 @@
         <v>-1.52</v>
       </c>
       <c r="AT131" s="4" t="n">
-        <v>0</v>
+        <v>1.54</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>-0.18</v>
       </c>
       <c r="AW131" s="4" t="inlineStr">
         <is>
@@ -18181,14 +18493,14 @@
       </c>
       <c r="AG132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH132" s="4" t="n">
         <v>2421.9</v>
       </c>
       <c r="AI132" s="4" t="n">
-        <v>2421.9</v>
+        <v>2258.5</v>
       </c>
       <c r="AJ132" s="4" t="n">
         <v>2397.68</v>
@@ -18221,10 +18533,14 @@
         <v>-1.55</v>
       </c>
       <c r="AT132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU132" s="4" t="inlineStr"/>
-      <c r="AV132" s="4" t="inlineStr"/>
+        <v>7.23</v>
+      </c>
+      <c r="AU132" s="4" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AV132" s="4" t="n">
+        <v>4.11</v>
+      </c>
       <c r="AW132" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -18244,7 +18560,7 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -18365,14 +18681,14 @@
       </c>
       <c r="AG133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH133" s="4" t="n">
         <v>5651.5</v>
       </c>
       <c r="AI133" s="4" t="n">
-        <v>5651.5</v>
+        <v>5057.4</v>
       </c>
       <c r="AJ133" s="4" t="n">
         <v>5594.98</v>
@@ -18405,10 +18721,14 @@
         <v>1.87</v>
       </c>
       <c r="AT133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" s="4" t="inlineStr"/>
-      <c r="AV133" s="4" t="inlineStr"/>
+        <v>11.75</v>
+      </c>
+      <c r="AU133" s="4" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AV133" s="4" t="n">
+        <v>1.81</v>
+      </c>
       <c r="AW133" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -18426,7 +18746,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -18519,11 +18839,11 @@
       </c>
       <c r="AG134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH134" s="4" t="n">
-        <v>133.14</v>
+        <v>129.61</v>
       </c>
       <c r="AI134" s="4" t="n">
         <v>133.14</v>
@@ -18557,7 +18877,13 @@
         <v>1.33</v>
       </c>
       <c r="AT134" s="4" t="n">
-        <v>0</v>
+        <v>-2.65</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>-4.24</v>
       </c>
       <c r="AW134" s="4" t="inlineStr">
         <is>
@@ -18667,11 +18993,11 @@
       </c>
       <c r="AG135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH135" s="4" t="n">
-        <v>5524</v>
+        <v>5532.5</v>
       </c>
       <c r="AI135" s="4" t="n">
         <v>5524</v>
@@ -18705,7 +19031,13 @@
         <v>0.26</v>
       </c>
       <c r="AT135" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-3.65</v>
       </c>
       <c r="AW135" s="4" t="inlineStr">
         <is>
@@ -18837,14 +19169,14 @@
       </c>
       <c r="AG136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH136" s="4" t="n">
         <v>1351.3</v>
       </c>
       <c r="AI136" s="4" t="n">
-        <v>1351.3</v>
+        <v>1263.5</v>
       </c>
       <c r="AJ136" s="4" t="n">
         <v>1337.79</v>
@@ -18877,10 +19209,14 @@
         <v>-1.36</v>
       </c>
       <c r="AT136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU136" s="4" t="inlineStr"/>
-      <c r="AV136" s="4" t="inlineStr"/>
+        <v>6.95</v>
+      </c>
+      <c r="AU136" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AV136" s="4" t="n">
+        <v>4.41</v>
+      </c>
       <c r="AW136" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -18898,7 +19234,7 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -19009,14 +19345,14 @@
       </c>
       <c r="AG137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH137" s="4" t="n">
         <v>11727</v>
       </c>
       <c r="AI137" s="4" t="n">
-        <v>11727</v>
+        <v>11602</v>
       </c>
       <c r="AJ137" s="4" t="n">
         <v>11609.73</v>
@@ -19049,10 +19385,14 @@
         <v>1.09</v>
       </c>
       <c r="AT137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU137" s="4" t="inlineStr"/>
-      <c r="AV137" s="4" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="AU137" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AV137" s="4" t="n">
+        <v>-4.54</v>
+      </c>
       <c r="AW137" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -19072,7 +19412,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -19165,11 +19505,11 @@
       </c>
       <c r="AG138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH138" s="4" t="n">
-        <v>1158</v>
+        <v>1177</v>
       </c>
       <c r="AI138" s="4" t="n">
         <v>1158</v>
@@ -19203,7 +19543,13 @@
         <v>0.21</v>
       </c>
       <c r="AT138" s="4" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>-3.71</v>
       </c>
       <c r="AW138" s="4" t="inlineStr">
         <is>
@@ -19317,14 +19663,14 @@
       </c>
       <c r="AG139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH139" s="4" t="n">
-        <v>449.35</v>
+        <v>459.55</v>
       </c>
       <c r="AI139" s="4" t="n">
-        <v>449.35</v>
+        <v>430.5</v>
       </c>
       <c r="AJ139" s="4" t="n">
         <v>444.86</v>
@@ -19355,7 +19701,13 @@
         <v>0.5</v>
       </c>
       <c r="AT139" s="4" t="n">
-        <v>0</v>
+        <v>6.75</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>2.98</v>
       </c>
       <c r="AW139" s="4" t="inlineStr">
         <is>
@@ -19469,14 +19821,14 @@
       </c>
       <c r="AG140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH140" s="4" t="n">
-        <v>287.2</v>
+        <v>285.8</v>
       </c>
       <c r="AI140" s="4" t="n">
-        <v>287.2</v>
+        <v>280.95</v>
       </c>
       <c r="AJ140" s="4" t="n">
         <v>284.33</v>
@@ -19507,7 +19859,13 @@
         <v>1.46</v>
       </c>
       <c r="AT140" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW140" s="4" t="inlineStr">
         <is>
@@ -19617,14 +19975,14 @@
       </c>
       <c r="AG141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH141" s="4" t="n">
-        <v>10880</v>
+        <v>11456</v>
       </c>
       <c r="AI141" s="4" t="n">
-        <v>10880</v>
+        <v>10678</v>
       </c>
       <c r="AJ141" s="4" t="n">
         <v>10771.2</v>
@@ -19655,7 +20013,13 @@
         <v>-0.55</v>
       </c>
       <c r="AT141" s="4" t="n">
-        <v>0</v>
+        <v>7.29</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.89</v>
       </c>
       <c r="AW141" s="4" t="inlineStr">
         <is>
@@ -19769,14 +20133,14 @@
       </c>
       <c r="AG142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH142" s="4" t="n">
-        <v>952.55</v>
+        <v>920.65</v>
       </c>
       <c r="AI142" s="4" t="n">
-        <v>952.55</v>
+        <v>943.1</v>
       </c>
       <c r="AJ142" s="4" t="n">
         <v>943.02</v>
@@ -19807,7 +20171,13 @@
         <v>-0.76</v>
       </c>
       <c r="AT142" s="4" t="n">
-        <v>0</v>
+        <v>-2.38</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-2.38</v>
       </c>
       <c r="AW142" s="4" t="inlineStr">
         <is>
@@ -19945,14 +20315,14 @@
       </c>
       <c r="AG143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH143" s="4" t="n">
         <v>428.2</v>
       </c>
       <c r="AI143" s="4" t="n">
-        <v>428.2</v>
+        <v>429.4</v>
       </c>
       <c r="AJ143" s="4" t="n">
         <v>423.92</v>
@@ -19985,10 +20355,14 @@
         <v>1.47</v>
       </c>
       <c r="AT143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU143" s="4" t="inlineStr"/>
-      <c r="AV143" s="4" t="inlineStr"/>
+        <v>-0.28</v>
+      </c>
+      <c r="AU143" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AV143" s="4" t="n">
+        <v>-1.72</v>
+      </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -20006,7 +20380,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -20099,11 +20473,11 @@
       </c>
       <c r="AG144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH144" s="4" t="n">
-        <v>2157.8</v>
+        <v>2182</v>
       </c>
       <c r="AI144" s="4" t="n">
         <v>2157.8</v>
@@ -20137,7 +20511,13 @@
         <v>-0.25</v>
       </c>
       <c r="AT144" s="4" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0.63</v>
       </c>
       <c r="AW144" s="4" t="inlineStr">
         <is>
@@ -20251,14 +20631,14 @@
       </c>
       <c r="AG145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH145" s="4" t="n">
-        <v>547.4</v>
+        <v>567.8</v>
       </c>
       <c r="AI145" s="4" t="n">
-        <v>547.4</v>
+        <v>550.25</v>
       </c>
       <c r="AJ145" s="4" t="n">
         <v>541.9299999999999</v>
@@ -20289,7 +20669,13 @@
         <v>0.12</v>
       </c>
       <c r="AT145" s="4" t="n">
-        <v>0</v>
+        <v>3.19</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>-0.83</v>
       </c>
       <c r="AW145" s="4" t="inlineStr">
         <is>
@@ -20399,11 +20785,11 @@
       </c>
       <c r="AG146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AH146" s="4" t="n">
-        <v>1363</v>
+        <v>1378.5</v>
       </c>
       <c r="AI146" s="4" t="n">
         <v>1363</v>
@@ -20437,7 +20823,13 @@
         <v>-1.52</v>
       </c>
       <c r="AT146" s="4" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>-0.18</v>
       </c>
       <c r="AW146" s="4" t="inlineStr">
         <is>
@@ -20614,7 +21006,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -20774,7 +21166,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -20934,7 +21326,7 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21031,14 +21423,14 @@
       </c>
       <c r="AG150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH150" s="4" t="n">
         <v>2390.4</v>
       </c>
       <c r="AI150" s="4" t="n">
-        <v>2390.4</v>
+        <v>2376.2</v>
       </c>
       <c r="AJ150" s="4" t="n">
         <v>2329</v>
@@ -21071,10 +21463,14 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" s="4" t="inlineStr"/>
-      <c r="AV150" s="4" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="AU150" s="4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV150" s="4" t="n">
+        <v>0.32</v>
+      </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -21094,7 +21490,7 @@
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21254,7 +21650,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21414,7 +21810,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21574,7 +21970,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21734,7 +22130,7 @@
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -21894,7 +22290,7 @@
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22050,7 +22446,7 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22147,14 +22543,14 @@
       </c>
       <c r="AG157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH157" s="4" t="n">
-        <v>414</v>
+        <v>414.05</v>
       </c>
       <c r="AI157" s="4" t="n">
-        <v>414</v>
+        <v>426.65</v>
       </c>
       <c r="AJ157" s="4" t="n">
         <v>401</v>
@@ -22187,10 +22583,14 @@
         <v>-0.85</v>
       </c>
       <c r="AT157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU157" s="4" t="inlineStr"/>
-      <c r="AV157" s="4" t="inlineStr"/>
+        <v>-2.95</v>
+      </c>
+      <c r="AU157" s="4" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AV157" s="4" t="n">
+        <v>-3.89</v>
+      </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -22210,7 +22610,7 @@
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22790,7 @@
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22945,7 @@
       <c r="AR159" s="4" t="inlineStr"/>
       <c r="AS159" s="4" t="inlineStr"/>
       <c r="AT159" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU159" s="4" t="n">
         <v>2.11</v>
@@ -22570,7 +22970,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22729,7 +23129,7 @@
       <c r="AR160" s="4" t="inlineStr"/>
       <c r="AS160" s="4" t="inlineStr"/>
       <c r="AT160" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU160" s="4" t="n">
         <v>0</v>
@@ -22754,7 +23154,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -22938,7 +23338,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23524,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23683,7 @@
       <c r="AR163" s="4" t="inlineStr"/>
       <c r="AS163" s="4" t="inlineStr"/>
       <c r="AT163" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU163" s="4" t="n">
         <v>0</v>
@@ -23308,7 +23708,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23869,7 @@
       <c r="AR164" s="4" t="inlineStr"/>
       <c r="AS164" s="4" t="inlineStr"/>
       <c r="AT164" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU164" s="4" t="n">
         <v>0</v>
@@ -23494,7 +23894,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -23680,7 +24080,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -23841,7 +24241,7 @@
       <c r="AR166" s="4" t="inlineStr"/>
       <c r="AS166" s="4" t="inlineStr"/>
       <c r="AT166" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU166" s="4" t="n">
         <v>7.39</v>
@@ -23866,7 +24266,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24025,7 +24425,7 @@
       <c r="AR167" s="4" t="inlineStr"/>
       <c r="AS167" s="4" t="inlineStr"/>
       <c r="AT167" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU167" s="4" t="n">
         <v>10.29</v>
@@ -24050,7 +24450,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24634,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24395,7 +24795,7 @@
       <c r="AR169" s="4" t="inlineStr"/>
       <c r="AS169" s="4" t="inlineStr"/>
       <c r="AT169" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU169" s="4" t="n">
         <v>0.99</v>
@@ -24420,7 +24820,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24981,7 @@
       <c r="AR170" s="4" t="inlineStr"/>
       <c r="AS170" s="4" t="inlineStr"/>
       <c r="AT170" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU170" s="4" t="n">
         <v>0</v>
@@ -24606,7 +25006,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24767,7 +25167,7 @@
       <c r="AR171" s="4" t="inlineStr"/>
       <c r="AS171" s="4" t="inlineStr"/>
       <c r="AT171" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU171" s="4" t="n">
         <v>0</v>
@@ -24792,7 +25192,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -24953,7 +25353,7 @@
       <c r="AR172" s="4" t="inlineStr"/>
       <c r="AS172" s="4" t="inlineStr"/>
       <c r="AT172" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU172" s="4" t="n">
         <v>1.09</v>
@@ -24978,7 +25378,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -25107,7 +25507,7 @@
       </c>
       <c r="AR173" s="4" t="inlineStr"/>
       <c r="AT173" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU173" s="4" t="n">
         <v>2.11</v>
@@ -25411,7 +25811,7 @@
       </c>
       <c r="AR175" s="4" t="inlineStr"/>
       <c r="AT175" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU175" s="4" t="n">
         <v>0</v>
@@ -25721,7 +26121,7 @@
       </c>
       <c r="AR177" s="4" t="inlineStr"/>
       <c r="AT177" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU177" s="4" t="n">
         <v>7.39</v>
@@ -26031,7 +26431,7 @@
       </c>
       <c r="AR179" s="4" t="inlineStr"/>
       <c r="AT179" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU179" s="4" t="n">
         <v>0</v>
@@ -26335,7 +26735,7 @@
       </c>
       <c r="AR181" s="4" t="inlineStr"/>
       <c r="AT181" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU181" s="4" t="n">
         <v>0</v>
@@ -26487,7 +26887,7 @@
       </c>
       <c r="AR182" s="4" t="inlineStr"/>
       <c r="AT182" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU182" s="4" t="n">
         <v>10.29</v>
@@ -26683,7 +27083,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -26851,7 +27251,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -27106,14 +27506,14 @@
       </c>
       <c r="AG186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH186" s="4" t="n">
         <v>443.9</v>
       </c>
       <c r="AI186" s="4" t="n">
-        <v>443.9</v>
+        <v>459.25</v>
       </c>
       <c r="AJ186" s="4" t="n">
         <v>439.46</v>
@@ -27146,10 +27546,14 @@
         <v>-1.36</v>
       </c>
       <c r="AT186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU186" s="4" t="inlineStr"/>
-      <c r="AV186" s="4" t="inlineStr"/>
+        <v>-3.34</v>
+      </c>
+      <c r="AU186" s="4" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AV186" s="4" t="n">
+        <v>-3.96</v>
+      </c>
       <c r="AW186" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -27167,7 +27571,7 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -27288,14 +27692,14 @@
       </c>
       <c r="AG187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH187" s="4" t="n">
         <v>278.8</v>
       </c>
       <c r="AI187" s="4" t="n">
-        <v>278.8</v>
+        <v>261</v>
       </c>
       <c r="AJ187" s="4" t="n">
         <v>276.01</v>
@@ -27328,10 +27732,14 @@
         <v>3.64</v>
       </c>
       <c r="AT187" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU187" s="4" t="inlineStr"/>
-      <c r="AV187" s="4" t="inlineStr"/>
+        <v>6.82</v>
+      </c>
+      <c r="AU187" s="4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="AV187" s="4" t="n">
+        <v>0.96</v>
+      </c>
       <c r="AW187" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -27349,7 +27757,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -27523,7 +27931,7 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -27644,14 +28052,14 @@
       </c>
       <c r="AG189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH189" s="4" t="n">
         <v>7531.5</v>
       </c>
       <c r="AI189" s="4" t="n">
-        <v>7531.5</v>
+        <v>7338.5</v>
       </c>
       <c r="AJ189" s="4" t="n">
         <v>7456.18</v>
@@ -27684,10 +28092,14 @@
         <v>1.85</v>
       </c>
       <c r="AT189" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU189" s="4" t="inlineStr"/>
-      <c r="AV189" s="4" t="inlineStr"/>
+        <v>2.63</v>
+      </c>
+      <c r="AU189" s="4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AV189" s="4" t="n">
+        <v>0.68</v>
+      </c>
       <c r="AW189" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -27705,7 +28117,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28029,7 +28441,7 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28142,14 +28554,14 @@
       </c>
       <c r="AG192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH192" s="4" t="n">
         <v>1296.8</v>
       </c>
       <c r="AI192" s="4" t="n">
-        <v>1296.8</v>
+        <v>1298.9</v>
       </c>
       <c r="AJ192" s="4" t="n">
         <v>1283.83</v>
@@ -28182,10 +28594,14 @@
         <v>-2.33</v>
       </c>
       <c r="AT192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU192" s="4" t="inlineStr"/>
-      <c r="AV192" s="4" t="inlineStr"/>
+        <v>-0.16</v>
+      </c>
+      <c r="AU192" s="4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV192" s="4" t="n">
+        <v>-0.16</v>
+      </c>
       <c r="AW192" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -28203,7 +28619,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28270,14 +28686,14 @@
       </c>
       <c r="AG193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH193" s="4" t="n">
         <v>285.8</v>
       </c>
       <c r="AI193" s="4" t="n">
-        <v>285.8</v>
+        <v>280.95</v>
       </c>
       <c r="AJ193" s="4" t="n">
         <v>279</v>
@@ -28308,7 +28724,13 @@
         <v>-1.11</v>
       </c>
       <c r="AT193" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="AW193" s="4" t="inlineStr">
         <is>
@@ -28496,7 +28918,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28670,7 +29092,7 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28763,14 +29185,14 @@
       </c>
       <c r="AG196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AH196" s="4" t="n">
         <v>285.8</v>
       </c>
       <c r="AI196" s="4" t="n">
-        <v>285.8</v>
+        <v>280.95</v>
       </c>
       <c r="AJ196" s="4" t="n">
         <v>279</v>
@@ -28803,10 +29225,14 @@
         <v>-1.11</v>
       </c>
       <c r="AT196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU196" s="4" t="inlineStr"/>
-      <c r="AV196" s="4" t="inlineStr"/>
+        <v>1.73</v>
+      </c>
+      <c r="AU196" s="4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV196" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="AW196" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -28826,7 +29252,7 @@
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -28977,7 +29403,7 @@
       <c r="AR197" s="4" t="inlineStr"/>
       <c r="AS197" s="4" t="inlineStr"/>
       <c r="AT197" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU197" s="4" t="n">
         <v>2.11</v>
@@ -29004,7 +29430,7 @@
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29606,7 @@
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -29329,7 +29755,7 @@
       <c r="AR199" s="4" t="inlineStr"/>
       <c r="AS199" s="4" t="inlineStr"/>
       <c r="AT199" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU199" s="4" t="n">
         <v>0</v>
@@ -29356,7 +29782,7 @@
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -29534,7 +29960,7 @@
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -29685,7 +30111,7 @@
       <c r="AR201" s="4" t="inlineStr"/>
       <c r="AS201" s="4" t="inlineStr"/>
       <c r="AT201" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU201" s="4" t="n">
         <v>7.39</v>
@@ -29712,7 +30138,7 @@
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -29890,7 +30316,7 @@
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30041,7 +30467,7 @@
       <c r="AR203" s="4" t="inlineStr"/>
       <c r="AS203" s="4" t="inlineStr"/>
       <c r="AT203" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU203" s="4" t="n">
         <v>0</v>
@@ -30068,7 +30494,7 @@
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30244,7 +30670,7 @@
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30393,7 +30819,7 @@
       <c r="AR205" s="4" t="inlineStr"/>
       <c r="AS205" s="4" t="inlineStr"/>
       <c r="AT205" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU205" s="4" t="n">
         <v>0</v>
@@ -30420,7 +30846,7 @@
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30569,7 +30995,7 @@
       <c r="AR206" s="4" t="inlineStr"/>
       <c r="AS206" s="4" t="inlineStr"/>
       <c r="AT206" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU206" s="4" t="n">
         <v>10.29</v>
@@ -30596,7 +31022,7 @@
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30689,9 +31115,17 @@
       <c r="AF207" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG207" s="4" t="inlineStr"/>
-      <c r="AH207" s="4" t="inlineStr"/>
-      <c r="AI207" s="4" t="inlineStr"/>
+      <c r="AG207" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH207" s="4" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AI207" s="4" t="n">
+        <v>2376.2</v>
+      </c>
       <c r="AJ207" s="4" t="inlineStr"/>
       <c r="AK207" s="4" t="inlineStr"/>
       <c r="AL207" s="4" t="inlineStr"/>
@@ -30706,9 +31140,15 @@
       <c r="AS207" s="4" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AT207" s="4" t="inlineStr"/>
-      <c r="AU207" s="4" t="inlineStr"/>
-      <c r="AV207" s="4" t="inlineStr"/>
+      <c r="AT207" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AU207" s="4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV207" s="4" t="n">
+        <v>0.32</v>
+      </c>
       <c r="AW207" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -30720,7 +31160,7 @@
       <c r="BA207" s="4" t="inlineStr"/>
       <c r="BB207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30809,9 +31249,17 @@
       <c r="AF208" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG208" s="4" t="inlineStr"/>
-      <c r="AH208" s="4" t="inlineStr"/>
-      <c r="AI208" s="4" t="inlineStr"/>
+      <c r="AG208" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH208" s="4" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="AI208" s="4" t="n">
+        <v>109.29</v>
+      </c>
       <c r="AJ208" s="4" t="inlineStr"/>
       <c r="AK208" s="4" t="inlineStr"/>
       <c r="AL208" s="4" t="inlineStr"/>
@@ -30826,9 +31274,15 @@
       <c r="AS208" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="AT208" s="4" t="inlineStr"/>
-      <c r="AU208" s="4" t="inlineStr"/>
-      <c r="AV208" s="4" t="inlineStr"/>
+      <c r="AT208" s="4" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AU208" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV208" s="4" t="n">
+        <v>1.64</v>
+      </c>
       <c r="AW208" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -30840,7 +31294,7 @@
       <c r="BA208" s="4" t="inlineStr"/>
       <c r="BB208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -30933,9 +31387,17 @@
       <c r="AF209" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG209" s="4" t="inlineStr"/>
-      <c r="AH209" s="4" t="inlineStr"/>
-      <c r="AI209" s="4" t="inlineStr"/>
+      <c r="AG209" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH209" s="4" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="AI209" s="4" t="n">
+        <v>426.65</v>
+      </c>
       <c r="AJ209" s="4" t="inlineStr"/>
       <c r="AK209" s="4" t="inlineStr"/>
       <c r="AL209" s="4" t="inlineStr"/>
@@ -30950,9 +31412,15 @@
       <c r="AS209" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AT209" s="4" t="inlineStr"/>
-      <c r="AU209" s="4" t="inlineStr"/>
-      <c r="AV209" s="4" t="inlineStr"/>
+      <c r="AT209" s="4" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="AU209" s="4" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AV209" s="4" t="n">
+        <v>-3.89</v>
+      </c>
       <c r="AW209" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -30964,7 +31432,7 @@
       <c r="BA209" s="4" t="inlineStr"/>
       <c r="BB209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31053,9 +31521,17 @@
       <c r="AF210" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG210" s="4" t="inlineStr"/>
-      <c r="AH210" s="4" t="inlineStr"/>
-      <c r="AI210" s="4" t="inlineStr"/>
+      <c r="AG210" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH210" s="4" t="n">
+        <v>597.55</v>
+      </c>
+      <c r="AI210" s="4" t="n">
+        <v>526.45</v>
+      </c>
       <c r="AJ210" s="4" t="inlineStr"/>
       <c r="AK210" s="4" t="inlineStr"/>
       <c r="AL210" s="4" t="inlineStr"/>
@@ -31070,9 +31546,15 @@
       <c r="AS210" s="4" t="n">
         <v>6.16</v>
       </c>
-      <c r="AT210" s="4" t="inlineStr"/>
-      <c r="AU210" s="4" t="inlineStr"/>
-      <c r="AV210" s="4" t="inlineStr"/>
+      <c r="AT210" s="4" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="AU210" s="4" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="AV210" s="4" t="n">
+        <v>1.04</v>
+      </c>
       <c r="AW210" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -31084,7 +31566,7 @@
       <c r="BA210" s="4" t="inlineStr"/>
       <c r="BB210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31173,9 +31655,17 @@
       <c r="AF211" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG211" s="4" t="inlineStr"/>
-      <c r="AH211" s="4" t="inlineStr"/>
-      <c r="AI211" s="4" t="inlineStr"/>
+      <c r="AG211" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH211" s="4" t="n">
+        <v>731</v>
+      </c>
+      <c r="AI211" s="4" t="n">
+        <v>673.7</v>
+      </c>
       <c r="AJ211" s="4" t="inlineStr"/>
       <c r="AK211" s="4" t="inlineStr"/>
       <c r="AL211" s="4" t="inlineStr"/>
@@ -31190,9 +31680,15 @@
       <c r="AS211" s="4" t="n">
         <v>3.02</v>
       </c>
-      <c r="AT211" s="4" t="inlineStr"/>
-      <c r="AU211" s="4" t="inlineStr"/>
-      <c r="AV211" s="4" t="inlineStr"/>
+      <c r="AT211" s="4" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AU211" s="4" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AV211" s="4" t="n">
+        <v>2.95</v>
+      </c>
       <c r="AW211" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -31204,7 +31700,7 @@
       <c r="BA211" s="4" t="inlineStr"/>
       <c r="BB211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31816,7 @@
       <c r="BA212" s="4" t="inlineStr"/>
       <c r="BB212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31436,7 +31932,7 @@
       <c r="BA213" s="4" t="inlineStr"/>
       <c r="BB213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31560,7 +32056,7 @@
       <c r="BA214" s="4" t="inlineStr"/>
       <c r="BB214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31684,7 +32180,7 @@
       <c r="BA215" s="4" t="inlineStr"/>
       <c r="BB215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31777,9 +32273,17 @@
       <c r="AF216" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG216" s="4" t="inlineStr"/>
-      <c r="AH216" s="4" t="inlineStr"/>
-      <c r="AI216" s="4" t="inlineStr"/>
+      <c r="AG216" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH216" s="4" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AI216" s="4" t="n">
+        <v>2376.2</v>
+      </c>
       <c r="AJ216" s="4" t="inlineStr"/>
       <c r="AK216" s="4" t="inlineStr"/>
       <c r="AL216" s="4" t="inlineStr"/>
@@ -31794,9 +32298,15 @@
       <c r="AS216" s="4" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AT216" s="4" t="inlineStr"/>
-      <c r="AU216" s="4" t="inlineStr"/>
-      <c r="AV216" s="4" t="inlineStr"/>
+      <c r="AT216" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AU216" s="4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV216" s="4" t="n">
+        <v>0.32</v>
+      </c>
       <c r="AW216" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -31808,7 +32318,7 @@
       <c r="BA216" s="4" t="inlineStr"/>
       <c r="BB216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -31932,7 +32442,7 @@
       <c r="BA217" s="4" t="inlineStr"/>
       <c r="BB217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32056,7 +32566,7 @@
       <c r="BA218" s="4" t="inlineStr"/>
       <c r="BB218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32180,7 +32690,7 @@
       <c r="BA219" s="4" t="inlineStr"/>
       <c r="BB219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32304,7 +32814,7 @@
       <c r="BA220" s="4" t="inlineStr"/>
       <c r="BB220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32938,7 @@
       <c r="BA221" s="4" t="inlineStr"/>
       <c r="BB221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32552,7 +33062,7 @@
       <c r="BA222" s="4" t="inlineStr"/>
       <c r="BB222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32645,9 +33155,17 @@
       <c r="AF223" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="AG223" s="4" t="inlineStr"/>
-      <c r="AH223" s="4" t="inlineStr"/>
-      <c r="AI223" s="4" t="inlineStr"/>
+      <c r="AG223" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AH223" s="4" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="AI223" s="4" t="n">
+        <v>426.65</v>
+      </c>
       <c r="AJ223" s="4" t="inlineStr"/>
       <c r="AK223" s="4" t="inlineStr"/>
       <c r="AL223" s="4" t="inlineStr"/>
@@ -32662,9 +33180,15 @@
       <c r="AS223" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AT223" s="4" t="inlineStr"/>
-      <c r="AU223" s="4" t="inlineStr"/>
-      <c r="AV223" s="4" t="inlineStr"/>
+      <c r="AT223" s="4" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="AU223" s="4" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="AV223" s="4" t="n">
+        <v>-3.89</v>
+      </c>
       <c r="AW223" s="4" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -32676,7 +33200,7 @@
       <c r="BA223" s="4" t="inlineStr"/>
       <c r="BB223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32796,7 +33320,7 @@
       <c r="BA224" s="4" t="inlineStr"/>
       <c r="BB224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>
@@ -32920,7 +33444,7 @@
       <c r="BA225" s="4" t="inlineStr"/>
       <c r="BB225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:05</t>
+          <t>2026-08-06 11:06</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AR29" s="4" t="inlineStr"/>
       <c r="AT29" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU29" s="4" t="n">
         <v>2.11</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AR30" s="4" t="inlineStr"/>
       <c r="AT30" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU30" s="4" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AR33" s="4" t="inlineStr"/>
       <c r="AT33" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU33" s="4" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AR34" s="4" t="inlineStr"/>
       <c r="AT34" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU34" s="4" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AR36" s="4" t="inlineStr"/>
       <c r="AT36" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU36" s="4" t="n">
         <v>7.39</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AR37" s="4" t="inlineStr"/>
       <c r="AT37" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU37" s="4" t="n">
         <v>10.29</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AR39" s="4" t="inlineStr"/>
       <c r="AT39" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU39" s="4" t="n">
         <v>0.99</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AR40" s="4" t="inlineStr"/>
       <c r="AT40" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU40" s="4" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AR41" s="4" t="inlineStr"/>
       <c r="AT41" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU41" s="4" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="AR42" s="4" t="inlineStr"/>
       <c r="AT42" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU42" s="4" t="n">
         <v>1.09</v>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AR68" s="4" t="inlineStr"/>
       <c r="AT68" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU68" s="4" t="n">
         <v>2.11</v>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AR69" s="4" t="inlineStr"/>
       <c r="AT69" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU69" s="4" t="n">
         <v>0</v>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AR72" s="4" t="inlineStr"/>
       <c r="AT72" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU72" s="4" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="AR73" s="4" t="inlineStr"/>
       <c r="AT73" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU73" s="4" t="n">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AR75" s="4" t="inlineStr"/>
       <c r="AT75" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU75" s="4" t="n">
         <v>7.39</v>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AR76" s="4" t="inlineStr"/>
       <c r="AT76" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU76" s="4" t="n">
         <v>10.29</v>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AR78" s="4" t="inlineStr"/>
       <c r="AT78" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU78" s="4" t="n">
         <v>0.99</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AR79" s="4" t="inlineStr"/>
       <c r="AT79" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU79" s="4" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AR80" s="4" t="inlineStr"/>
       <c r="AT80" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU80" s="4" t="n">
         <v>0</v>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="AR81" s="4" t="inlineStr"/>
       <c r="AT81" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU81" s="4" t="n">
         <v>1.09</v>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="AR110" s="4" t="inlineStr"/>
       <c r="AT110" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU110" s="4" t="n">
         <v>2.11</v>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="AR111" s="4" t="inlineStr"/>
       <c r="AT111" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU111" s="4" t="n">
         <v>0</v>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AR114" s="4" t="inlineStr"/>
       <c r="AT114" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU114" s="4" t="n">
         <v>0</v>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="AR115" s="4" t="inlineStr"/>
       <c r="AT115" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU115" s="4" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="AR117" s="4" t="inlineStr"/>
       <c r="AT117" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU117" s="4" t="n">
         <v>7.39</v>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AR118" s="4" t="inlineStr"/>
       <c r="AT118" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU118" s="4" t="n">
         <v>10.29</v>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="AR120" s="4" t="inlineStr"/>
       <c r="AT120" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU120" s="4" t="n">
         <v>0.99</v>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AR121" s="4" t="inlineStr"/>
       <c r="AT121" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU121" s="4" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AR122" s="4" t="inlineStr"/>
       <c r="AT122" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU122" s="4" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="AR123" s="4" t="inlineStr"/>
       <c r="AT123" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU123" s="4" t="n">
         <v>1.09</v>
@@ -18385,7 +18385,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TCS_IND_20260806</t>
+          <t>TCS_IND_20260729</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -18483,7 +18483,7 @@
         <v>2</v>
       </c>
       <c r="AD132" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE132" s="4" t="n">
         <v>17</v>
@@ -18512,19 +18512,19 @@
         <v>2276.59</v>
       </c>
       <c r="AM132" s="4" t="n">
-        <v>-6</v>
+        <v>0.8</v>
       </c>
       <c r="AN132" s="4" t="n">
         <v>2712.53</v>
       </c>
       <c r="AO132" s="4" t="n">
-        <v>12</v>
+        <v>20.1</v>
       </c>
       <c r="AP132" s="4" t="n">
         <v>3003.16</v>
       </c>
       <c r="AQ132" s="4" t="n">
-        <v>24</v>
+        <v>32.97</v>
       </c>
       <c r="AR132" s="4" t="n">
         <v>2460</v>
@@ -18536,10 +18536,10 @@
         <v>7.23</v>
       </c>
       <c r="AU132" s="4" t="n">
-        <v>8.92</v>
+        <v>8.58</v>
       </c>
       <c r="AV132" s="4" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AW132" s="4" t="inlineStr">
         <is>
@@ -18560,14 +18560,14 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO_IND_20260806</t>
+          <t>HEROMOTOCO_IND_20260729</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -18611,7 +18611,7 @@
         </is>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>8</v>
@@ -18671,7 +18671,7 @@
         <v>2</v>
       </c>
       <c r="AD133" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE133" s="4" t="n">
         <v>17</v>
@@ -18691,25 +18691,25 @@
         <v>5057.4</v>
       </c>
       <c r="AJ133" s="4" t="n">
-        <v>5594.98</v>
+        <v>5006.83</v>
       </c>
       <c r="AK133" s="4" t="n">
-        <v>5708.02</v>
+        <v>5107.97</v>
       </c>
       <c r="AL133" s="4" t="n">
-        <v>5368.93</v>
+        <v>4804.53</v>
       </c>
       <c r="AM133" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN133" s="4" t="n">
-        <v>6103.62</v>
+        <v>5461.99</v>
       </c>
       <c r="AO133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP133" s="4" t="n">
-        <v>6499.22</v>
+        <v>5816.01</v>
       </c>
       <c r="AQ133" s="4" t="n">
         <v>15</v>
@@ -18724,10 +18724,10 @@
         <v>11.75</v>
       </c>
       <c r="AU133" s="4" t="n">
-        <v>11.75</v>
+        <v>5.66</v>
       </c>
       <c r="AV133" s="4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW133" s="4" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH_IND_20260806</t>
+          <t>HCLTECH_IND_20260729</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -19140,7 +19140,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
+          <t>🟡 WAIT (Δ+5.9%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y136" s="4" t="inlineStr"/>
@@ -19159,7 +19159,7 @@
         <v>2</v>
       </c>
       <c r="AD136" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE136" s="4" t="n">
         <v>17</v>
@@ -19179,25 +19179,25 @@
         <v>1263.5</v>
       </c>
       <c r="AJ136" s="4" t="n">
-        <v>1337.79</v>
+        <v>1250.87</v>
       </c>
       <c r="AK136" s="4" t="n">
-        <v>1364.81</v>
+        <v>1276.13</v>
       </c>
       <c r="AL136" s="4" t="n">
-        <v>1283.73</v>
+        <v>1200.33</v>
       </c>
       <c r="AM136" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN136" s="4" t="n">
-        <v>1459.4</v>
+        <v>1364.58</v>
       </c>
       <c r="AO136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP136" s="4" t="n">
-        <v>1553.99</v>
+        <v>1453.02</v>
       </c>
       <c r="AQ136" s="4" t="n">
         <v>15</v>
@@ -19212,10 +19212,10 @@
         <v>6.95</v>
       </c>
       <c r="AU136" s="4" t="n">
-        <v>8.42</v>
+        <v>6.58</v>
       </c>
       <c r="AV136" s="4" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AW136" s="4" t="inlineStr">
         <is>
@@ -19234,14 +19234,14 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>OFSS_IND_20260806</t>
+          <t>OFSS_IND_20260730</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -19335,7 +19335,7 @@
         <v>2</v>
       </c>
       <c r="AD137" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE137" s="4" t="n">
         <v>17</v>
@@ -19364,19 +19364,19 @@
         <v>11023.38</v>
       </c>
       <c r="AM137" s="4" t="n">
-        <v>-6</v>
+        <v>-4.99</v>
       </c>
       <c r="AN137" s="4" t="n">
         <v>13134.24</v>
       </c>
       <c r="AO137" s="4" t="n">
-        <v>12</v>
+        <v>13.21</v>
       </c>
       <c r="AP137" s="4" t="n">
         <v>14541.48</v>
       </c>
       <c r="AQ137" s="4" t="n">
-        <v>24</v>
+        <v>25.34</v>
       </c>
       <c r="AR137" s="4" t="n">
         <v>11600</v>
@@ -19388,7 +19388,7 @@
         <v>1.08</v>
       </c>
       <c r="AU137" s="4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AV137" s="4" t="n">
         <v>-4.54</v>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>BIOCON_IND_20260806</t>
+          <t>BIOCON_IND_20260729</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="J143" s="4" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="K143" s="4" t="n">
         <v>12</v>
@@ -20305,7 +20305,7 @@
         <v>2</v>
       </c>
       <c r="AD143" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE143" s="4" t="n">
         <v>17</v>
@@ -20325,25 +20325,25 @@
         <v>429.4</v>
       </c>
       <c r="AJ143" s="4" t="n">
-        <v>423.92</v>
+        <v>425.11</v>
       </c>
       <c r="AK143" s="4" t="n">
-        <v>432.48</v>
+        <v>433.69</v>
       </c>
       <c r="AL143" s="4" t="n">
-        <v>406.79</v>
+        <v>407.93</v>
       </c>
       <c r="AM143" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN143" s="4" t="n">
-        <v>462.46</v>
+        <v>463.75</v>
       </c>
       <c r="AO143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP143" s="4" t="n">
-        <v>492.43</v>
+        <v>493.81</v>
       </c>
       <c r="AQ143" s="4" t="n">
         <v>15</v>
@@ -20361,7 +20361,7 @@
         <v>0.47</v>
       </c>
       <c r="AV143" s="4" t="n">
-        <v>-1.72</v>
+        <v>-0.91</v>
       </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -20950,7 +20950,7 @@
         <v>1449.6</v>
       </c>
       <c r="AI147" s="4" t="n">
-        <v>1449.6</v>
+        <v>1449.599975585938</v>
       </c>
       <c r="AJ147" s="4" t="n">
         <v>1410</v>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -21326,14 +21326,14 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -21413,7 +21413,7 @@
       </c>
       <c r="AC150" s="4" t="inlineStr"/>
       <c r="AD150" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE150" s="4" t="n">
         <v>60</v>
@@ -21442,19 +21442,19 @@
         <v>2270.88</v>
       </c>
       <c r="AM150" s="4" t="n">
-        <v>-5</v>
+        <v>-4.43</v>
       </c>
       <c r="AN150" s="4" t="n">
         <v>2581.632</v>
       </c>
       <c r="AO150" s="4" t="n">
-        <v>8</v>
+        <v>8.65</v>
       </c>
       <c r="AP150" s="4" t="n">
         <v>2762.34624</v>
       </c>
       <c r="AQ150" s="4" t="n">
-        <v>15.56</v>
+        <v>16.25</v>
       </c>
       <c r="AR150" s="4" t="n">
         <v>2410</v>
@@ -21466,10 +21466,10 @@
         <v>0.6</v>
       </c>
       <c r="AU150" s="4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV150" s="4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
@@ -21486,11 +21486,11 @@
         <v>5</v>
       </c>
       <c r="BA150" s="4" t="n">
-        <v>8</v>
+        <v>8.65</v>
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
         <v>346.9</v>
       </c>
       <c r="AI151" s="4" t="n">
-        <v>346.9</v>
+        <v>346.8999938964844</v>
       </c>
       <c r="AJ151" s="4" t="n">
         <v>338</v>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -21754,7 +21754,7 @@
         <v>397.2</v>
       </c>
       <c r="AI152" s="4" t="n">
-        <v>397.2</v>
+        <v>397.2000122070312</v>
       </c>
       <c r="AJ152" s="4" t="n">
         <v>386</v>
@@ -21787,7 +21787,7 @@
         <v>-0.2</v>
       </c>
       <c r="AT152" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU152" s="4" t="inlineStr"/>
       <c r="AV152" s="4" t="inlineStr"/>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -21914,7 +21914,7 @@
         <v>276.8</v>
       </c>
       <c r="AI153" s="4" t="n">
-        <v>276.8</v>
+        <v>276.7999877929688</v>
       </c>
       <c r="AJ153" s="4" t="n">
         <v>270</v>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -22074,7 +22074,7 @@
         <v>510.9</v>
       </c>
       <c r="AI154" s="4" t="n">
-        <v>510.9</v>
+        <v>510.8500061035156</v>
       </c>
       <c r="AJ154" s="4" t="n">
         <v>495</v>
@@ -22086,19 +22086,19 @@
         <v>485.355</v>
       </c>
       <c r="AM154" s="4" t="n">
-        <v>-5</v>
+        <v>-4.99</v>
       </c>
       <c r="AN154" s="4" t="n">
         <v>551.772</v>
       </c>
       <c r="AO154" s="4" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="AP154" s="4" t="n">
         <v>590.3960400000001</v>
       </c>
       <c r="AQ154" s="4" t="n">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
       <c r="AR154" s="4" t="n">
         <v>510.25</v>
@@ -22107,7 +22107,7 @@
         <v>0.12</v>
       </c>
       <c r="AT154" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AU154" s="4" t="inlineStr"/>
       <c r="AV154" s="4" t="inlineStr"/>
@@ -22126,11 +22126,11 @@
         <v>5</v>
       </c>
       <c r="BA154" s="4" t="n">
-        <v>8</v>
+        <v>8.01</v>
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -22234,7 +22234,7 @@
         <v>390</v>
       </c>
       <c r="AI155" s="4" t="n">
-        <v>390</v>
+        <v>390.0499877929688</v>
       </c>
       <c r="AJ155" s="4" t="n">
         <v>378</v>
@@ -22246,19 +22246,19 @@
         <v>370.5</v>
       </c>
       <c r="AM155" s="4" t="n">
-        <v>-5</v>
+        <v>-5.01</v>
       </c>
       <c r="AN155" s="4" t="n">
         <v>421.2</v>
       </c>
       <c r="AO155" s="4" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="AP155" s="4" t="n">
         <v>450.6840000000001</v>
       </c>
       <c r="AQ155" s="4" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="AR155" s="4" t="n">
         <v>391.5</v>
@@ -22267,7 +22267,7 @@
         <v>-0.37</v>
       </c>
       <c r="AT155" s="4" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AU155" s="4" t="inlineStr"/>
       <c r="AV155" s="4" t="inlineStr"/>
@@ -22286,11 +22286,11 @@
         <v>5</v>
       </c>
       <c r="BA155" s="4" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -22446,14 +22446,14 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="AC157" s="4" t="inlineStr"/>
       <c r="AD157" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE157" s="4" t="n">
         <v>60</v>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AH157" s="4" t="n">
-        <v>414.05</v>
+        <v>414</v>
       </c>
       <c r="AI157" s="4" t="n">
         <v>426.65</v>
@@ -22562,19 +22562,19 @@
         <v>393.3</v>
       </c>
       <c r="AM157" s="4" t="n">
-        <v>-5</v>
+        <v>-7.82</v>
       </c>
       <c r="AN157" s="4" t="n">
         <v>447.12</v>
       </c>
       <c r="AO157" s="4" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AP157" s="4" t="n">
         <v>478.4184</v>
       </c>
       <c r="AQ157" s="4" t="n">
-        <v>15.56</v>
+        <v>12.13</v>
       </c>
       <c r="AR157" s="4" t="n">
         <v>417.6</v>
@@ -22583,13 +22583,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT157" s="4" t="n">
-        <v>-2.95</v>
+        <v>-2.96</v>
       </c>
       <c r="AU157" s="4" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="AV157" s="4" t="n">
-        <v>-3.89</v>
+        <v>0</v>
       </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
@@ -22606,11 +22606,11 @@
         <v>5</v>
       </c>
       <c r="BA157" s="4" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -22945,7 +22945,7 @@
       <c r="AR159" s="4" t="inlineStr"/>
       <c r="AS159" s="4" t="inlineStr"/>
       <c r="AT159" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU159" s="4" t="n">
         <v>2.11</v>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       <c r="AR160" s="4" t="inlineStr"/>
       <c r="AS160" s="4" t="inlineStr"/>
       <c r="AT160" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU160" s="4" t="n">
         <v>0</v>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -23683,7 +23683,7 @@
       <c r="AR163" s="4" t="inlineStr"/>
       <c r="AS163" s="4" t="inlineStr"/>
       <c r="AT163" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU163" s="4" t="n">
         <v>0</v>
@@ -23708,7 +23708,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -23869,7 +23869,7 @@
       <c r="AR164" s="4" t="inlineStr"/>
       <c r="AS164" s="4" t="inlineStr"/>
       <c r="AT164" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU164" s="4" t="n">
         <v>0</v>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24080,7 +24080,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24241,7 +24241,7 @@
       <c r="AR166" s="4" t="inlineStr"/>
       <c r="AS166" s="4" t="inlineStr"/>
       <c r="AT166" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU166" s="4" t="n">
         <v>7.39</v>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       <c r="AR167" s="4" t="inlineStr"/>
       <c r="AS167" s="4" t="inlineStr"/>
       <c r="AT167" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU167" s="4" t="n">
         <v>10.29</v>
@@ -24450,7 +24450,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       <c r="AR169" s="4" t="inlineStr"/>
       <c r="AS169" s="4" t="inlineStr"/>
       <c r="AT169" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU169" s="4" t="n">
         <v>0.99</v>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       <c r="AR170" s="4" t="inlineStr"/>
       <c r="AS170" s="4" t="inlineStr"/>
       <c r="AT170" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU170" s="4" t="n">
         <v>0</v>
@@ -25006,7 +25006,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -25167,7 +25167,7 @@
       <c r="AR171" s="4" t="inlineStr"/>
       <c r="AS171" s="4" t="inlineStr"/>
       <c r="AT171" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU171" s="4" t="n">
         <v>0</v>
@@ -25192,7 +25192,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -25353,7 +25353,7 @@
       <c r="AR172" s="4" t="inlineStr"/>
       <c r="AS172" s="4" t="inlineStr"/>
       <c r="AT172" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU172" s="4" t="n">
         <v>1.09</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="AR173" s="4" t="inlineStr"/>
       <c r="AT173" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU173" s="4" t="n">
         <v>2.11</v>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="AR175" s="4" t="inlineStr"/>
       <c r="AT175" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU175" s="4" t="n">
         <v>0</v>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="AR177" s="4" t="inlineStr"/>
       <c r="AT177" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU177" s="4" t="n">
         <v>7.39</v>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AR179" s="4" t="inlineStr"/>
       <c r="AT179" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU179" s="4" t="n">
         <v>0</v>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="AR181" s="4" t="inlineStr"/>
       <c r="AT181" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU181" s="4" t="n">
         <v>0</v>
@@ -26887,7 +26887,7 @@
       </c>
       <c r="AR182" s="4" t="inlineStr"/>
       <c r="AT182" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU182" s="4" t="n">
         <v>10.29</v>
@@ -27027,7 +27027,7 @@
         <v>853.4</v>
       </c>
       <c r="AI183" s="4" t="n">
-        <v>853.4</v>
+        <v>853.4000244140625</v>
       </c>
       <c r="AJ183" s="4" t="n">
         <v>844.87</v>
@@ -27060,7 +27060,7 @@
         <v>0.99</v>
       </c>
       <c r="AT183" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU183" s="4" t="inlineStr"/>
       <c r="AV183" s="4" t="inlineStr"/>
@@ -27083,7 +27083,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>OIL_IND_20260806</t>
+          <t>OIL_IND_20260729</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -27440,7 +27440,7 @@
         </is>
       </c>
       <c r="J186" s="4" t="n">
-        <v>0</v>
+        <v>-3.34</v>
       </c>
       <c r="K186" s="4" t="n">
         <v>7</v>
@@ -27496,7 +27496,7 @@
         <v>1</v>
       </c>
       <c r="AD186" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE186" s="4" t="n">
         <v>17</v>
@@ -27516,25 +27516,25 @@
         <v>459.25</v>
       </c>
       <c r="AJ186" s="4" t="n">
-        <v>439.46</v>
+        <v>454.66</v>
       </c>
       <c r="AK186" s="4" t="n">
-        <v>448.34</v>
+        <v>463.84</v>
       </c>
       <c r="AL186" s="4" t="n">
-        <v>421.7</v>
+        <v>436.29</v>
       </c>
       <c r="AM186" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN186" s="4" t="n">
-        <v>479.41</v>
+        <v>495.99</v>
       </c>
       <c r="AO186" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP186" s="4" t="n">
-        <v>510.48</v>
+        <v>528.14</v>
       </c>
       <c r="AQ186" s="4" t="n">
         <v>15</v>
@@ -27549,10 +27549,10 @@
         <v>-3.34</v>
       </c>
       <c r="AU186" s="4" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="AV186" s="4" t="n">
-        <v>-3.96</v>
+        <v>0</v>
       </c>
       <c r="AW186" s="4" t="inlineStr">
         <is>
@@ -27571,14 +27571,14 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>VEDL_IND_20260806</t>
+          <t>VEDL_IND_20260729</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -27622,7 +27622,7 @@
         </is>
       </c>
       <c r="J187" s="4" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="K187" s="4" t="n">
         <v>9</v>
@@ -27682,7 +27682,7 @@
         <v>1</v>
       </c>
       <c r="AD187" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE187" s="4" t="n">
         <v>60</v>
@@ -27702,25 +27702,25 @@
         <v>261</v>
       </c>
       <c r="AJ187" s="4" t="n">
-        <v>276.01</v>
+        <v>258.39</v>
       </c>
       <c r="AK187" s="4" t="n">
-        <v>281.59</v>
+        <v>263.61</v>
       </c>
       <c r="AL187" s="4" t="n">
-        <v>264.86</v>
+        <v>247.95</v>
       </c>
       <c r="AM187" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN187" s="4" t="n">
-        <v>301.1</v>
+        <v>281.88</v>
       </c>
       <c r="AO187" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP187" s="4" t="n">
-        <v>320.62</v>
+        <v>300.15</v>
       </c>
       <c r="AQ187" s="4" t="n">
         <v>15</v>
@@ -27735,10 +27735,10 @@
         <v>6.82</v>
       </c>
       <c r="AU187" s="4" t="n">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="AV187" s="4" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="AW187" s="4" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
         </is>
       </c>
       <c r="J188" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K188" s="4" t="n">
         <v>10</v>
@@ -27877,7 +27877,7 @@
         <v>380.35</v>
       </c>
       <c r="AI188" s="4" t="n">
-        <v>380.35</v>
+        <v>380.3500061035156</v>
       </c>
       <c r="AJ188" s="4" t="n">
         <v>376.55</v>
@@ -27910,7 +27910,7 @@
         <v>0.89</v>
       </c>
       <c r="AT188" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU188" s="4" t="inlineStr"/>
       <c r="AV188" s="4" t="inlineStr"/>
@@ -27931,14 +27931,14 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>AMBER_IND_20260806</t>
+          <t>AMBER_IND_20260729</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -27982,7 +27982,7 @@
         </is>
       </c>
       <c r="J189" s="4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="K189" s="4" t="n">
         <v>11</v>
@@ -28042,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="AD189" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE189" s="4" t="n">
         <v>60</v>
@@ -28062,25 +28062,25 @@
         <v>7338.5</v>
       </c>
       <c r="AJ189" s="4" t="n">
-        <v>7456.18</v>
+        <v>7265.11</v>
       </c>
       <c r="AK189" s="4" t="n">
-        <v>7606.82</v>
+        <v>7411.89</v>
       </c>
       <c r="AL189" s="4" t="n">
-        <v>7154.92</v>
+        <v>6971.57</v>
       </c>
       <c r="AM189" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN189" s="4" t="n">
-        <v>8134.02</v>
+        <v>7925.58</v>
       </c>
       <c r="AO189" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP189" s="4" t="n">
-        <v>8661.219999999999</v>
+        <v>8439.27</v>
       </c>
       <c r="AQ189" s="4" t="n">
         <v>15</v>
@@ -28095,10 +28095,10 @@
         <v>2.63</v>
       </c>
       <c r="AU189" s="4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV189" s="4" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="AW189" s="4" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -28441,14 +28441,14 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>VOLTAS_IND_20260806</t>
+          <t>VOLTAS_IND_20260729</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -28488,7 +28488,7 @@
         </is>
       </c>
       <c r="J192" s="4" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>15</v>
@@ -28544,7 +28544,7 @@
         <v>1</v>
       </c>
       <c r="AD192" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE192" s="4" t="n">
         <v>17</v>
@@ -28564,25 +28564,25 @@
         <v>1298.9</v>
       </c>
       <c r="AJ192" s="4" t="n">
-        <v>1283.83</v>
+        <v>1285.91</v>
       </c>
       <c r="AK192" s="4" t="n">
-        <v>1309.77</v>
+        <v>1311.89</v>
       </c>
       <c r="AL192" s="4" t="n">
-        <v>1231.96</v>
+        <v>1233.95</v>
       </c>
       <c r="AM192" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN192" s="4" t="n">
-        <v>1400.54</v>
+        <v>1402.81</v>
       </c>
       <c r="AO192" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP192" s="4" t="n">
-        <v>1491.32</v>
+        <v>1493.73</v>
       </c>
       <c r="AQ192" s="4" t="n">
         <v>15</v>
@@ -28597,10 +28597,10 @@
         <v>-0.16</v>
       </c>
       <c r="AU192" s="4" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AV192" s="4" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="AW192" s="4" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -28864,7 +28864,7 @@
         <v>553.3</v>
       </c>
       <c r="AI194" s="4" t="n">
-        <v>553.3</v>
+        <v>553.2999877929688</v>
       </c>
       <c r="AJ194" s="4" t="n">
         <v>547.77</v>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
         </is>
       </c>
       <c r="J195" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K195" s="4" t="n">
         <v>13</v>
@@ -29038,7 +29038,7 @@
         <v>471.2</v>
       </c>
       <c r="AI195" s="4" t="n">
-        <v>471.2</v>
+        <v>471.2000122070312</v>
       </c>
       <c r="AJ195" s="4" t="n">
         <v>466.49</v>
@@ -29071,7 +29071,7 @@
         <v>-2.24</v>
       </c>
       <c r="AT195" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU195" s="4" t="inlineStr"/>
       <c r="AV195" s="4" t="inlineStr"/>
@@ -29092,14 +29092,14 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260806</t>
+          <t>ITC_IND_20260729</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -29175,7 +29175,7 @@
       </c>
       <c r="AC196" s="4" t="inlineStr"/>
       <c r="AD196" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE196" s="4" t="n">
         <v>60</v>
@@ -29204,19 +29204,19 @@
         <v>271.51</v>
       </c>
       <c r="AM196" s="4" t="n">
-        <v>-5</v>
+        <v>-3.36</v>
       </c>
       <c r="AN196" s="4" t="n">
         <v>287</v>
       </c>
       <c r="AO196" s="4" t="n">
-        <v>0.42</v>
+        <v>2.15</v>
       </c>
       <c r="AP196" s="4" t="n">
         <v>307.09</v>
       </c>
       <c r="AQ196" s="4" t="n">
-        <v>7.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR196" s="4" t="n">
         <v>289</v>
@@ -29228,10 +29228,10 @@
         <v>1.73</v>
       </c>
       <c r="AU196" s="4" t="n">
-        <v>3.9</v>
+        <v>2.22</v>
       </c>
       <c r="AV196" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW196" s="4" t="inlineStr">
         <is>
@@ -29248,11 +29248,11 @@
         <v>5</v>
       </c>
       <c r="BA196" s="4" t="n">
-        <v>0.42</v>
+        <v>2.15</v>
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -29403,7 +29403,7 @@
       <c r="AR197" s="4" t="inlineStr"/>
       <c r="AS197" s="4" t="inlineStr"/>
       <c r="AT197" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU197" s="4" t="n">
         <v>2.11</v>
@@ -29430,7 +29430,7 @@
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -29755,7 +29755,7 @@
       <c r="AR199" s="4" t="inlineStr"/>
       <c r="AS199" s="4" t="inlineStr"/>
       <c r="AT199" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU199" s="4" t="n">
         <v>0</v>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -29960,7 +29960,7 @@
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30111,7 +30111,7 @@
       <c r="AR201" s="4" t="inlineStr"/>
       <c r="AS201" s="4" t="inlineStr"/>
       <c r="AT201" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU201" s="4" t="n">
         <v>7.39</v>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30316,7 +30316,7 @@
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30467,7 +30467,7 @@
       <c r="AR203" s="4" t="inlineStr"/>
       <c r="AS203" s="4" t="inlineStr"/>
       <c r="AT203" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU203" s="4" t="n">
         <v>0</v>
@@ -30494,7 +30494,7 @@
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30670,7 +30670,7 @@
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       <c r="AR205" s="4" t="inlineStr"/>
       <c r="AS205" s="4" t="inlineStr"/>
       <c r="AT205" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU205" s="4" t="n">
         <v>0</v>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -30995,7 +30995,7 @@
       <c r="AR206" s="4" t="inlineStr"/>
       <c r="AS206" s="4" t="inlineStr"/>
       <c r="AT206" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU206" s="4" t="n">
         <v>10.29</v>
@@ -31022,14 +31022,14 @@
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -31090,7 +31090,7 @@
       <c r="W207" s="4" t="inlineStr"/>
       <c r="X207" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y207" s="4" t="inlineStr"/>
@@ -31107,7 +31107,7 @@
       </c>
       <c r="AC207" s="4" t="inlineStr"/>
       <c r="AD207" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE207" s="4" t="n">
         <v>60</v>
@@ -31121,19 +31121,35 @@
         </is>
       </c>
       <c r="AH207" s="4" t="n">
-        <v>2390.4</v>
+        <v>2376.2</v>
       </c>
       <c r="AI207" s="4" t="n">
         <v>2376.2</v>
       </c>
-      <c r="AJ207" s="4" t="inlineStr"/>
-      <c r="AK207" s="4" t="inlineStr"/>
-      <c r="AL207" s="4" t="inlineStr"/>
-      <c r="AM207" s="4" t="inlineStr"/>
-      <c r="AN207" s="4" t="inlineStr"/>
-      <c r="AO207" s="4" t="inlineStr"/>
-      <c r="AP207" s="4" t="inlineStr"/>
-      <c r="AQ207" s="4" t="inlineStr"/>
+      <c r="AJ207" s="4" t="n">
+        <v>2352.44</v>
+      </c>
+      <c r="AK207" s="4" t="n">
+        <v>2399.96</v>
+      </c>
+      <c r="AL207" s="4" t="n">
+        <v>2257.39</v>
+      </c>
+      <c r="AM207" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN207" s="4" t="n">
+        <v>2566.296</v>
+      </c>
+      <c r="AO207" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP207" s="4" t="n">
+        <v>2732.63</v>
+      </c>
+      <c r="AQ207" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR207" s="4" t="n">
         <v>2410</v>
       </c>
@@ -31141,13 +31157,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT207" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AU207" s="4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV207" s="4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AW207" s="4" t="inlineStr">
         <is>
@@ -31157,17 +31173,19 @@
       <c r="AX207" s="4" t="inlineStr"/>
       <c r="AY207" s="4" t="inlineStr"/>
       <c r="AZ207" s="4" t="inlineStr"/>
-      <c r="BA207" s="4" t="inlineStr"/>
+      <c r="BA207" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260806</t>
+          <t>PNB_IND_20260729</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -31224,7 +31242,7 @@
       <c r="W208" s="4" t="inlineStr"/>
       <c r="X208" s="4" t="inlineStr">
         <is>
-          <t>Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y208" s="4" t="inlineStr"/>
@@ -31241,7 +31259,7 @@
       </c>
       <c r="AC208" s="4" t="inlineStr"/>
       <c r="AD208" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE208" s="4" t="n">
         <v>60</v>
@@ -31255,19 +31273,35 @@
         </is>
       </c>
       <c r="AH208" s="4" t="n">
-        <v>113.54</v>
+        <v>109.29</v>
       </c>
       <c r="AI208" s="4" t="n">
         <v>109.29</v>
       </c>
-      <c r="AJ208" s="4" t="inlineStr"/>
-      <c r="AK208" s="4" t="inlineStr"/>
-      <c r="AL208" s="4" t="inlineStr"/>
-      <c r="AM208" s="4" t="inlineStr"/>
-      <c r="AN208" s="4" t="inlineStr"/>
-      <c r="AO208" s="4" t="inlineStr"/>
-      <c r="AP208" s="4" t="inlineStr"/>
-      <c r="AQ208" s="4" t="inlineStr"/>
+      <c r="AJ208" s="4" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AK208" s="4" t="n">
+        <v>110.38</v>
+      </c>
+      <c r="AL208" s="4" t="n">
+        <v>103.8255</v>
+      </c>
+      <c r="AM208" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN208" s="4" t="n">
+        <v>118.0332</v>
+      </c>
+      <c r="AO208" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP208" s="4" t="n">
+        <v>125.6835</v>
+      </c>
+      <c r="AQ208" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR208" s="4" t="n">
         <v>113.99</v>
       </c>
@@ -31275,13 +31309,13 @@
         <v>-0.39</v>
       </c>
       <c r="AT208" s="4" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AU208" s="4" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV208" s="4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AW208" s="4" t="inlineStr">
         <is>
@@ -31291,17 +31325,19 @@
       <c r="AX208" s="4" t="inlineStr"/>
       <c r="AY208" s="4" t="inlineStr"/>
       <c r="AZ208" s="4" t="inlineStr"/>
-      <c r="BA208" s="4" t="inlineStr"/>
+      <c r="BA208" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -31362,7 +31398,7 @@
       <c r="W209" s="4" t="inlineStr"/>
       <c r="X209" s="4" t="inlineStr">
         <is>
-          <t>Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y209" s="4" t="inlineStr"/>
@@ -31379,7 +31415,7 @@
       </c>
       <c r="AC209" s="4" t="inlineStr"/>
       <c r="AD209" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE209" s="4" t="n">
         <v>60</v>
@@ -31393,19 +31429,35 @@
         </is>
       </c>
       <c r="AH209" s="4" t="n">
-        <v>414.05</v>
+        <v>426.65</v>
       </c>
       <c r="AI209" s="4" t="n">
         <v>426.65</v>
       </c>
-      <c r="AJ209" s="4" t="inlineStr"/>
-      <c r="AK209" s="4" t="inlineStr"/>
-      <c r="AL209" s="4" t="inlineStr"/>
-      <c r="AM209" s="4" t="inlineStr"/>
-      <c r="AN209" s="4" t="inlineStr"/>
-      <c r="AO209" s="4" t="inlineStr"/>
-      <c r="AP209" s="4" t="inlineStr"/>
-      <c r="AQ209" s="4" t="inlineStr"/>
+      <c r="AJ209" s="4" t="n">
+        <v>422.38</v>
+      </c>
+      <c r="AK209" s="4" t="n">
+        <v>430.92</v>
+      </c>
+      <c r="AL209" s="4" t="n">
+        <v>405.3174999999999</v>
+      </c>
+      <c r="AM209" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN209" s="4" t="n">
+        <v>460.782</v>
+      </c>
+      <c r="AO209" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP209" s="4" t="n">
+        <v>490.6474999999999</v>
+      </c>
+      <c r="AQ209" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR209" s="4" t="n">
         <v>417.6</v>
       </c>
@@ -31413,13 +31465,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT209" s="4" t="n">
-        <v>-2.95</v>
+        <v>0</v>
       </c>
       <c r="AU209" s="4" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="AV209" s="4" t="n">
-        <v>-3.89</v>
+        <v>0</v>
       </c>
       <c r="AW209" s="4" t="inlineStr">
         <is>
@@ -31429,17 +31481,19 @@
       <c r="AX209" s="4" t="inlineStr"/>
       <c r="AY209" s="4" t="inlineStr"/>
       <c r="AZ209" s="4" t="inlineStr"/>
-      <c r="BA209" s="4" t="inlineStr"/>
+      <c r="BA209" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>HINDZINC_IND_20260806</t>
+          <t>HINDZINC_IND_20260729</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -31496,7 +31550,7 @@
       <c r="W210" s="4" t="inlineStr"/>
       <c r="X210" s="4" t="inlineStr">
         <is>
-          <t>Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y210" s="4" t="inlineStr"/>
@@ -31513,7 +31567,7 @@
       </c>
       <c r="AC210" s="4" t="inlineStr"/>
       <c r="AD210" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE210" s="4" t="n">
         <v>60</v>
@@ -31527,19 +31581,35 @@
         </is>
       </c>
       <c r="AH210" s="4" t="n">
-        <v>597.55</v>
+        <v>526.45</v>
       </c>
       <c r="AI210" s="4" t="n">
         <v>526.45</v>
       </c>
-      <c r="AJ210" s="4" t="inlineStr"/>
-      <c r="AK210" s="4" t="inlineStr"/>
-      <c r="AL210" s="4" t="inlineStr"/>
-      <c r="AM210" s="4" t="inlineStr"/>
-      <c r="AN210" s="4" t="inlineStr"/>
-      <c r="AO210" s="4" t="inlineStr"/>
-      <c r="AP210" s="4" t="inlineStr"/>
-      <c r="AQ210" s="4" t="inlineStr"/>
+      <c r="AJ210" s="4" t="n">
+        <v>521.1900000000001</v>
+      </c>
+      <c r="AK210" s="4" t="n">
+        <v>531.71</v>
+      </c>
+      <c r="AL210" s="4" t="n">
+        <v>500.1275</v>
+      </c>
+      <c r="AM210" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN210" s="4" t="n">
+        <v>568.566</v>
+      </c>
+      <c r="AO210" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP210" s="4" t="n">
+        <v>605.4175</v>
+      </c>
+      <c r="AQ210" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR210" s="4" t="n">
         <v>562.9</v>
       </c>
@@ -31547,13 +31617,13 @@
         <v>6.16</v>
       </c>
       <c r="AT210" s="4" t="n">
-        <v>13.51</v>
+        <v>0</v>
       </c>
       <c r="AU210" s="4" t="n">
-        <v>13.51</v>
+        <v>0</v>
       </c>
       <c r="AV210" s="4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AW210" s="4" t="inlineStr">
         <is>
@@ -31563,17 +31633,19 @@
       <c r="AX210" s="4" t="inlineStr"/>
       <c r="AY210" s="4" t="inlineStr"/>
       <c r="AZ210" s="4" t="inlineStr"/>
-      <c r="BA210" s="4" t="inlineStr"/>
+      <c r="BA210" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260806</t>
+          <t>BATAINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -31630,7 +31702,7 @@
       <c r="W211" s="4" t="inlineStr"/>
       <c r="X211" s="4" t="inlineStr">
         <is>
-          <t>Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y211" s="4" t="inlineStr"/>
@@ -31647,7 +31719,7 @@
       </c>
       <c r="AC211" s="4" t="inlineStr"/>
       <c r="AD211" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE211" s="4" t="n">
         <v>60</v>
@@ -31661,19 +31733,35 @@
         </is>
       </c>
       <c r="AH211" s="4" t="n">
-        <v>731</v>
+        <v>673.7</v>
       </c>
       <c r="AI211" s="4" t="n">
         <v>673.7</v>
       </c>
-      <c r="AJ211" s="4" t="inlineStr"/>
-      <c r="AK211" s="4" t="inlineStr"/>
-      <c r="AL211" s="4" t="inlineStr"/>
-      <c r="AM211" s="4" t="inlineStr"/>
-      <c r="AN211" s="4" t="inlineStr"/>
-      <c r="AO211" s="4" t="inlineStr"/>
-      <c r="AP211" s="4" t="inlineStr"/>
-      <c r="AQ211" s="4" t="inlineStr"/>
+      <c r="AJ211" s="4" t="n">
+        <v>666.96</v>
+      </c>
+      <c r="AK211" s="4" t="n">
+        <v>680.4400000000001</v>
+      </c>
+      <c r="AL211" s="4" t="n">
+        <v>640.015</v>
+      </c>
+      <c r="AM211" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN211" s="4" t="n">
+        <v>727.5960000000001</v>
+      </c>
+      <c r="AO211" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP211" s="4" t="n">
+        <v>774.755</v>
+      </c>
+      <c r="AQ211" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR211" s="4" t="n">
         <v>709.55</v>
       </c>
@@ -31681,13 +31769,13 @@
         <v>3.02</v>
       </c>
       <c r="AT211" s="4" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="AU211" s="4" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="AV211" s="4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW211" s="4" t="inlineStr">
         <is>
@@ -31697,10 +31785,12 @@
       <c r="AX211" s="4" t="inlineStr"/>
       <c r="AY211" s="4" t="inlineStr"/>
       <c r="AZ211" s="4" t="inlineStr"/>
-      <c r="BA211" s="4" t="inlineStr"/>
+      <c r="BA211" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -31816,7 +31906,7 @@
       <c r="BA212" s="4" t="inlineStr"/>
       <c r="BB212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -31932,7 +32022,7 @@
       <c r="BA213" s="4" t="inlineStr"/>
       <c r="BB213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32056,7 +32146,7 @@
       <c r="BA214" s="4" t="inlineStr"/>
       <c r="BB214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32180,14 +32270,14 @@
       <c r="BA215" s="4" t="inlineStr"/>
       <c r="BB215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260806</t>
+          <t>LUPIN_IND_20260729</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -32248,7 +32338,7 @@
       <c r="W216" s="4" t="inlineStr"/>
       <c r="X216" s="4" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y216" s="4" t="inlineStr"/>
@@ -32265,7 +32355,7 @@
       </c>
       <c r="AC216" s="4" t="inlineStr"/>
       <c r="AD216" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE216" s="4" t="n">
         <v>60</v>
@@ -32279,19 +32369,35 @@
         </is>
       </c>
       <c r="AH216" s="4" t="n">
-        <v>2390.4</v>
+        <v>2376.2</v>
       </c>
       <c r="AI216" s="4" t="n">
         <v>2376.2</v>
       </c>
-      <c r="AJ216" s="4" t="inlineStr"/>
-      <c r="AK216" s="4" t="inlineStr"/>
-      <c r="AL216" s="4" t="inlineStr"/>
-      <c r="AM216" s="4" t="inlineStr"/>
-      <c r="AN216" s="4" t="inlineStr"/>
-      <c r="AO216" s="4" t="inlineStr"/>
-      <c r="AP216" s="4" t="inlineStr"/>
-      <c r="AQ216" s="4" t="inlineStr"/>
+      <c r="AJ216" s="4" t="n">
+        <v>2352.44</v>
+      </c>
+      <c r="AK216" s="4" t="n">
+        <v>2399.96</v>
+      </c>
+      <c r="AL216" s="4" t="n">
+        <v>2257.39</v>
+      </c>
+      <c r="AM216" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN216" s="4" t="n">
+        <v>2566.296</v>
+      </c>
+      <c r="AO216" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP216" s="4" t="n">
+        <v>2732.63</v>
+      </c>
+      <c r="AQ216" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR216" s="4" t="n">
         <v>2410</v>
       </c>
@@ -32299,13 +32405,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT216" s="4" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AU216" s="4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV216" s="4" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AW216" s="4" t="inlineStr">
         <is>
@@ -32315,10 +32421,12 @@
       <c r="AX216" s="4" t="inlineStr"/>
       <c r="AY216" s="4" t="inlineStr"/>
       <c r="AZ216" s="4" t="inlineStr"/>
-      <c r="BA216" s="4" t="inlineStr"/>
+      <c r="BA216" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32442,7 +32550,7 @@
       <c r="BA217" s="4" t="inlineStr"/>
       <c r="BB217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32566,7 +32674,7 @@
       <c r="BA218" s="4" t="inlineStr"/>
       <c r="BB218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32690,7 +32798,7 @@
       <c r="BA219" s="4" t="inlineStr"/>
       <c r="BB219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32922,7 @@
       <c r="BA220" s="4" t="inlineStr"/>
       <c r="BB220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -32938,7 +33046,7 @@
       <c r="BA221" s="4" t="inlineStr"/>
       <c r="BB221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -33062,14 +33170,14 @@
       <c r="BA222" s="4" t="inlineStr"/>
       <c r="BB222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260806</t>
+          <t>COALINDIA_IND_20260729</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -33130,7 +33238,7 @@
       <c r="W223" s="4" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y223" s="4" t="inlineStr"/>
@@ -33147,7 +33255,7 @@
       </c>
       <c r="AC223" s="4" t="inlineStr"/>
       <c r="AD223" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE223" s="4" t="n">
         <v>60</v>
@@ -33161,19 +33269,35 @@
         </is>
       </c>
       <c r="AH223" s="4" t="n">
-        <v>414.05</v>
+        <v>426.65</v>
       </c>
       <c r="AI223" s="4" t="n">
         <v>426.65</v>
       </c>
-      <c r="AJ223" s="4" t="inlineStr"/>
-      <c r="AK223" s="4" t="inlineStr"/>
-      <c r="AL223" s="4" t="inlineStr"/>
-      <c r="AM223" s="4" t="inlineStr"/>
-      <c r="AN223" s="4" t="inlineStr"/>
-      <c r="AO223" s="4" t="inlineStr"/>
-      <c r="AP223" s="4" t="inlineStr"/>
-      <c r="AQ223" s="4" t="inlineStr"/>
+      <c r="AJ223" s="4" t="n">
+        <v>422.38</v>
+      </c>
+      <c r="AK223" s="4" t="n">
+        <v>430.92</v>
+      </c>
+      <c r="AL223" s="4" t="n">
+        <v>405.3174999999999</v>
+      </c>
+      <c r="AM223" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AN223" s="4" t="n">
+        <v>460.782</v>
+      </c>
+      <c r="AO223" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP223" s="4" t="n">
+        <v>490.6474999999999</v>
+      </c>
+      <c r="AQ223" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="AR223" s="4" t="n">
         <v>417.6</v>
       </c>
@@ -33181,13 +33305,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT223" s="4" t="n">
-        <v>-2.95</v>
+        <v>0</v>
       </c>
       <c r="AU223" s="4" t="n">
-        <v>-2.12</v>
+        <v>0</v>
       </c>
       <c r="AV223" s="4" t="n">
-        <v>-3.89</v>
+        <v>0</v>
       </c>
       <c r="AW223" s="4" t="inlineStr">
         <is>
@@ -33197,10 +33321,12 @@
       <c r="AX223" s="4" t="inlineStr"/>
       <c r="AY223" s="4" t="inlineStr"/>
       <c r="AZ223" s="4" t="inlineStr"/>
-      <c r="BA223" s="4" t="inlineStr"/>
+      <c r="BA223" s="4" t="n">
+        <v>8</v>
+      </c>
       <c r="BB223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -33320,7 +33446,7 @@
       <c r="BA224" s="4" t="inlineStr"/>
       <c r="BB224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>
@@ -33444,7 +33570,7 @@
       <c r="BA225" s="4" t="inlineStr"/>
       <c r="BB225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:06</t>
+          <t>2026-08-06 11:24</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -875,7 +875,7 @@
         <v>2351.3</v>
       </c>
       <c r="AI2" s="4" t="n">
-        <v>2258.5</v>
+        <v>2452.2</v>
       </c>
       <c r="AJ2" s="4" t="n">
         <v>2427.68</v>
@@ -906,13 +906,13 @@
         <v>-3.9</v>
       </c>
       <c r="AT2" s="4" t="n">
-        <v>4.11</v>
+        <v>-4.11</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.58</v>
+        <v>-0</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.11</v>
+        <v>-4.11</v>
       </c>
       <c r="AW2" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>5343.6</v>
       </c>
       <c r="AI3" s="4" t="n">
-        <v>5057.4</v>
+        <v>5196.6</v>
       </c>
       <c r="AJ3" s="4" t="n">
         <v>5144.63</v>
@@ -1032,13 +1032,13 @@
         <v>3.78</v>
       </c>
       <c r="AT3" s="4" t="n">
-        <v>5.66</v>
+        <v>2.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.66</v>
+        <v>2.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.81</v>
+        <v>-0.91</v>
       </c>
       <c r="AW3" s="4" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>133.1</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>133.14</v>
+        <v>134.19</v>
       </c>
       <c r="AJ4" s="4" t="n">
         <v>131.81</v>
@@ -1154,13 +1154,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT4" s="4" t="n">
-        <v>-0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AW4" s="4" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>5322.4</v>
       </c>
       <c r="AI5" s="4" t="n">
-        <v>5524</v>
+        <v>5483.3</v>
       </c>
       <c r="AJ5" s="4" t="n">
         <v>5468.76</v>
@@ -1276,13 +1276,13 @@
         <v>-2.93</v>
       </c>
       <c r="AT5" s="4" t="n">
-        <v>-3.65</v>
+        <v>-2.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.74</v>
+        <v>-0</v>
       </c>
       <c r="AV5" t="n">
-        <v>-3.65</v>
+        <v>-2.93</v>
       </c>
       <c r="AW5" s="4" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>1319.2</v>
       </c>
       <c r="AI6" s="4" t="n">
-        <v>1263.5</v>
+        <v>1346.6</v>
       </c>
       <c r="AJ6" s="4" t="n">
         <v>1333.13</v>
@@ -1402,13 +1402,13 @@
         <v>-1.87</v>
       </c>
       <c r="AT6" s="4" t="n">
-        <v>4.41</v>
+        <v>-2.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.58</v>
+        <v>-0</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.41</v>
+        <v>-2.03</v>
       </c>
       <c r="AW6" s="4" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>11075</v>
       </c>
       <c r="AI7" s="4" t="n">
-        <v>11602</v>
+        <v>11427</v>
       </c>
       <c r="AJ7" s="4" t="n">
         <v>11485.98</v>
@@ -1524,13 +1524,13 @@
         <v>-3.08</v>
       </c>
       <c r="AT7" s="4" t="n">
-        <v>-4.54</v>
+        <v>-3.08</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.51</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>-4.54</v>
+        <v>-3.08</v>
       </c>
       <c r="AW7" s="4" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>1115</v>
       </c>
       <c r="AI8" s="4" t="n">
-        <v>1158</v>
+        <v>1155.6</v>
       </c>
       <c r="AJ8" s="4" t="n">
         <v>1146.42</v>
@@ -1646,13 +1646,13 @@
         <v>-3.51</v>
       </c>
       <c r="AT8" s="4" t="n">
-        <v>-3.71</v>
+        <v>-3.51</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.21</v>
+        <v>-0</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.71</v>
+        <v>-3.51</v>
       </c>
       <c r="AW8" s="4" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>443.35</v>
       </c>
       <c r="AI9" s="4" t="n">
-        <v>430.5</v>
+        <v>449.35</v>
       </c>
       <c r="AJ9" s="4" t="n">
         <v>444.86</v>
@@ -1772,13 +1772,13 @@
         <v>-1.79</v>
       </c>
       <c r="AT9" s="4" t="n">
-        <v>2.98</v>
+        <v>-1.34</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.87</v>
+        <v>0.47</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.98</v>
+        <v>-1.34</v>
       </c>
       <c r="AW9" s="4" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>282.9</v>
       </c>
       <c r="AI10" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ10" s="4" t="n">
         <v>284.33</v>
@@ -1898,13 +1898,13 @@
         <v>-1.17</v>
       </c>
       <c r="AT10" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW10" s="4" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>11127</v>
       </c>
       <c r="AI11" s="4" t="n">
-        <v>10678</v>
+        <v>10880</v>
       </c>
       <c r="AJ11" s="4" t="n">
         <v>10771.2</v>
@@ -2020,13 +2020,13 @@
         <v>1.63</v>
       </c>
       <c r="AT11" s="4" t="n">
-        <v>4.2</v>
+        <v>2.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.2</v>
+        <v>2.27</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AW11" s="4" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>950.2</v>
       </c>
       <c r="AI12" s="4" t="n">
-        <v>943.1</v>
+        <v>952.55</v>
       </c>
       <c r="AJ12" s="4" t="n">
         <v>943.02</v>
@@ -2146,13 +2146,13 @@
         <v>-0.19</v>
       </c>
       <c r="AT12" s="4" t="n">
-        <v>0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>425.5</v>
       </c>
       <c r="AI13" s="4" t="n">
-        <v>429.4</v>
+        <v>431.4</v>
       </c>
       <c r="AJ13" s="4" t="n">
         <v>427.09</v>
@@ -2272,13 +2272,13 @@
         <v>-1.3</v>
       </c>
       <c r="AT13" s="4" t="n">
-        <v>-0.91</v>
+        <v>-1.37</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.47</v>
+        <v>-0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.91</v>
+        <v>-1.37</v>
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>2187.4</v>
       </c>
       <c r="AI14" s="4" t="n">
-        <v>2157.8</v>
+        <v>2171.5</v>
       </c>
       <c r="AJ14" s="4" t="n">
         <v>2136.22</v>
@@ -2394,13 +2394,13 @@
         <v>0.73</v>
       </c>
       <c r="AT14" s="4" t="n">
-        <v>1.37</v>
+        <v>0.73</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.37</v>
+        <v>0.73</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>546</v>
       </c>
       <c r="AI15" s="4" t="n">
-        <v>550.25</v>
+        <v>547.4</v>
       </c>
       <c r="AJ15" s="4" t="n">
         <v>541.9299999999999</v>
@@ -2520,13 +2520,13 @@
         <v>0.05</v>
       </c>
       <c r="AT15" s="4" t="n">
-        <v>-0.77</v>
+        <v>-0.26</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>1360.5</v>
       </c>
       <c r="AI16" s="4" t="n">
-        <v>1363</v>
+        <v>1373.1</v>
       </c>
       <c r="AJ16" s="4" t="n">
         <v>1349.37</v>
@@ -2642,13 +2642,13 @@
         <v>-0.92</v>
       </c>
       <c r="AT16" s="4" t="n">
-        <v>-0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.74</v>
+        <v>-0</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>2417</v>
       </c>
       <c r="AI19" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ19" s="4" t="n">
         <v>2392.83</v>
@@ -2999,13 +2999,13 @@
         <v>-1.23</v>
       </c>
       <c r="AT19" s="4" t="n">
-        <v>1.72</v>
+        <v>-1.08</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.98</v>
+        <v>0.15</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.72</v>
+        <v>-1.08</v>
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>411.3</v>
       </c>
       <c r="AI26" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ26" s="4" t="n">
         <v>407.19</v>
@@ -3824,13 +3824,13 @@
         <v>0.3</v>
       </c>
       <c r="AT26" s="4" t="n">
-        <v>-3.6</v>
+        <v>0.19</v>
       </c>
       <c r="AU26" t="n">
-        <v>-3.6</v>
+        <v>0.19</v>
       </c>
       <c r="AV26" t="n">
-        <v>-3.89</v>
+        <v>-0.11</v>
       </c>
       <c r="AW26" s="4" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AR29" s="4" t="inlineStr"/>
       <c r="AT29" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU29" s="4" t="n">
         <v>2.11</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="AR30" s="4" t="inlineStr"/>
       <c r="AT30" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU30" s="4" t="n">
         <v>0</v>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AR33" s="4" t="inlineStr"/>
       <c r="AT33" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU33" s="4" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AR34" s="4" t="inlineStr"/>
       <c r="AT34" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU34" s="4" t="n">
         <v>0</v>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AR36" s="4" t="inlineStr"/>
       <c r="AT36" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU36" s="4" t="n">
         <v>7.39</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AR37" s="4" t="inlineStr"/>
       <c r="AT37" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU37" s="4" t="n">
         <v>10.29</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AR39" s="4" t="inlineStr"/>
       <c r="AT39" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU39" s="4" t="n">
         <v>0.99</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AR40" s="4" t="inlineStr"/>
       <c r="AT40" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU40" s="4" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AR41" s="4" t="inlineStr"/>
       <c r="AT41" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU41" s="4" t="n">
         <v>0</v>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="AR42" s="4" t="inlineStr"/>
       <c r="AT42" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU42" s="4" t="n">
         <v>1.09</v>
@@ -5984,7 +5984,7 @@
         <v>2383.9</v>
       </c>
       <c r="AI43" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ43" s="4" t="n">
         <v>2352.44</v>
@@ -6015,13 +6015,13 @@
         <v>-0.59</v>
       </c>
       <c r="AT43" s="4" t="n">
-        <v>0.32</v>
+        <v>-2.44</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.98</v>
+        <v>0.15</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.32</v>
+        <v>-2.44</v>
       </c>
       <c r="AW43" s="4" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>5470.5</v>
       </c>
       <c r="AI44" s="4" t="n">
-        <v>5057.4</v>
+        <v>5196.6</v>
       </c>
       <c r="AJ44" s="4" t="n">
         <v>5006.83</v>
@@ -6150,13 +6150,13 @@
         <v>0.6</v>
       </c>
       <c r="AT44" s="4" t="n">
-        <v>8.17</v>
+        <v>5.27</v>
       </c>
       <c r="AU44" t="n">
-        <v>8.17</v>
+        <v>5.27</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.81</v>
+        <v>-0.91</v>
       </c>
       <c r="AW44" s="4" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>452.35</v>
       </c>
       <c r="AI45" s="4" t="n">
-        <v>430.5</v>
+        <v>449.35</v>
       </c>
       <c r="AJ45" s="4" t="n">
         <v>426.19</v>
@@ -6285,13 +6285,13 @@
         <v>1.7</v>
       </c>
       <c r="AT45" s="4" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AU45" t="n">
-        <v>5.08</v>
+        <v>0.67</v>
       </c>
       <c r="AV45" t="n">
-        <v>2.98</v>
+        <v>-1.34</v>
       </c>
       <c r="AW45" s="4" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>113.36</v>
       </c>
       <c r="AI46" s="4" t="n">
-        <v>109.29</v>
+        <v>111.44</v>
       </c>
       <c r="AJ46" s="4" t="n">
         <v>108.2</v>
@@ -6414,13 +6414,13 @@
         <v>0.46</v>
       </c>
       <c r="AT46" s="4" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.64</v>
+        <v>-0.32</v>
       </c>
       <c r="AW46" s="4" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>415.15</v>
       </c>
       <c r="AI47" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ47" s="4" t="n">
         <v>422.38</v>
@@ -6540,13 +6540,13 @@
         <v>0.1</v>
       </c>
       <c r="AT47" s="4" t="n">
-        <v>-2.7</v>
+        <v>1.13</v>
       </c>
       <c r="AU47" t="n">
-        <v>-2.7</v>
+        <v>1.13</v>
       </c>
       <c r="AV47" t="n">
-        <v>-3.89</v>
+        <v>-0.11</v>
       </c>
       <c r="AW47" s="4" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>268.5</v>
       </c>
       <c r="AI48" s="4" t="n">
-        <v>261</v>
+        <v>263.5</v>
       </c>
       <c r="AJ48" s="4" t="n">
         <v>258.39</v>
@@ -6666,13 +6666,13 @@
         <v>0.49</v>
       </c>
       <c r="AT48" s="4" t="n">
-        <v>2.87</v>
+        <v>1.9</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.87</v>
+        <v>1.9</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="AW48" s="4" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>284.85</v>
       </c>
       <c r="AI49" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ49" s="4" t="n">
         <v>278.14</v>
@@ -6798,13 +6798,13 @@
         <v>-2.42</v>
       </c>
       <c r="AT49" s="4" t="n">
-        <v>1.39</v>
+        <v>-0.82</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW49" s="4" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>1363.6</v>
       </c>
       <c r="AI50" s="4" t="n">
-        <v>1263.5</v>
+        <v>1346.6</v>
       </c>
       <c r="AJ50" s="4" t="n">
         <v>1250.87</v>
@@ -6930,13 +6930,13 @@
         <v>1.13</v>
       </c>
       <c r="AT50" s="4" t="n">
-        <v>7.92</v>
+        <v>1.26</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.92</v>
+        <v>1.26</v>
       </c>
       <c r="AV50" t="n">
-        <v>4.41</v>
+        <v>-2.03</v>
       </c>
       <c r="AW50" s="4" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>2439.4</v>
       </c>
       <c r="AI51" s="4" t="n">
-        <v>2258.5</v>
+        <v>2452.2</v>
       </c>
       <c r="AJ51" s="4" t="n">
         <v>2235.91</v>
@@ -7062,13 +7062,13 @@
         <v>1.91</v>
       </c>
       <c r="AT51" s="4" t="n">
-        <v>8.01</v>
+        <v>-0.52</v>
       </c>
       <c r="AU51" t="n">
-        <v>8.58</v>
+        <v>-0</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.11</v>
+        <v>-4.11</v>
       </c>
       <c r="AW51" s="4" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>552.4</v>
       </c>
       <c r="AI52" s="4" t="n">
-        <v>526.45</v>
+        <v>531.9</v>
       </c>
       <c r="AJ52" s="4" t="n">
         <v>521.1900000000001</v>
@@ -7188,13 +7188,13 @@
         <v>1.69</v>
       </c>
       <c r="AT52" s="4" t="n">
-        <v>4.93</v>
+        <v>3.85</v>
       </c>
       <c r="AU52" t="n">
-        <v>4.93</v>
+        <v>3.85</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AW52" s="4" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>425.05</v>
       </c>
       <c r="AI53" s="4" t="n">
-        <v>429.4</v>
+        <v>431.4</v>
       </c>
       <c r="AJ53" s="4" t="n">
         <v>425.11</v>
@@ -7328,13 +7328,13 @@
         <v>-0.01</v>
       </c>
       <c r="AT53" s="4" t="n">
-        <v>-1.01</v>
+        <v>-1.47</v>
       </c>
       <c r="AU53" t="n">
-        <v>0.47</v>
+        <v>-0</v>
       </c>
       <c r="AV53" t="n">
-        <v>-1.01</v>
+        <v>-1.47</v>
       </c>
       <c r="AW53" s="4" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>939.95</v>
       </c>
       <c r="AI54" s="4" t="n">
-        <v>943.1</v>
+        <v>952.55</v>
       </c>
       <c r="AJ54" s="4" t="n">
         <v>933.67</v>
@@ -7468,13 +7468,13 @@
         <v>-2.26</v>
       </c>
       <c r="AT54" s="4" t="n">
-        <v>-0.33</v>
+        <v>-1.32</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.97</v>
+        <v>0.96</v>
       </c>
       <c r="AV54" t="n">
-        <v>-0.33</v>
+        <v>-1.32</v>
       </c>
       <c r="AW54" s="4" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>567.3</v>
       </c>
       <c r="AI55" s="4" t="n">
-        <v>550.25</v>
+        <v>547.4</v>
       </c>
       <c r="AJ55" s="4" t="n">
         <v>544.75</v>
@@ -7608,13 +7608,13 @@
         <v>0.05</v>
       </c>
       <c r="AT55" s="4" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="AW55" s="4" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>7454.5</v>
       </c>
       <c r="AI56" s="4" t="n">
-        <v>7338.5</v>
+        <v>7388.5</v>
       </c>
       <c r="AJ56" s="4" t="n">
         <v>7265.11</v>
@@ -7742,13 +7742,13 @@
         <v>-0.14</v>
       </c>
       <c r="AT56" s="4" t="n">
-        <v>1.58</v>
+        <v>0.89</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="AW56" s="4" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>709</v>
       </c>
       <c r="AI57" s="4" t="n">
-        <v>673.7</v>
+        <v>700</v>
       </c>
       <c r="AJ57" s="4" t="n">
         <v>666.96</v>
@@ -7876,13 +7876,13 @@
         <v>1.39</v>
       </c>
       <c r="AT57" s="4" t="n">
-        <v>5.24</v>
+        <v>1.29</v>
       </c>
       <c r="AU57" t="n">
-        <v>5.24</v>
+        <v>1.29</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.95</v>
+        <v>-0.91</v>
       </c>
       <c r="AW57" s="4" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AR68" s="4" t="inlineStr"/>
       <c r="AT68" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU68" s="4" t="n">
         <v>2.11</v>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AR69" s="4" t="inlineStr"/>
       <c r="AT69" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU69" s="4" t="n">
         <v>0</v>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AR72" s="4" t="inlineStr"/>
       <c r="AT72" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU72" s="4" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="AR73" s="4" t="inlineStr"/>
       <c r="AT73" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU73" s="4" t="n">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AR75" s="4" t="inlineStr"/>
       <c r="AT75" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU75" s="4" t="n">
         <v>7.39</v>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AR76" s="4" t="inlineStr"/>
       <c r="AT76" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU76" s="4" t="n">
         <v>10.29</v>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AR78" s="4" t="inlineStr"/>
       <c r="AT78" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU78" s="4" t="n">
         <v>0.99</v>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="AR79" s="4" t="inlineStr"/>
       <c r="AT79" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU79" s="4" t="n">
         <v>0</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AR80" s="4" t="inlineStr"/>
       <c r="AT80" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU80" s="4" t="n">
         <v>0</v>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="AR81" s="4" t="inlineStr"/>
       <c r="AT81" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU81" s="4" t="n">
         <v>1.09</v>
@@ -11137,7 +11137,7 @@
         <v>2460</v>
       </c>
       <c r="AI82" s="4" t="n">
-        <v>2258.5</v>
+        <v>2452.2</v>
       </c>
       <c r="AJ82" s="4" t="n">
         <v>2427.68</v>
@@ -11168,13 +11168,13 @@
         <v>0.84</v>
       </c>
       <c r="AT82" s="4" t="n">
-        <v>8.92</v>
+        <v>0.32</v>
       </c>
       <c r="AU82" t="n">
-        <v>8.92</v>
+        <v>0.32</v>
       </c>
       <c r="AV82" t="n">
-        <v>4.11</v>
+        <v>-4.11</v>
       </c>
       <c r="AW82" s="4" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>1369.9</v>
       </c>
       <c r="AI83" s="4" t="n">
-        <v>1263.5</v>
+        <v>1346.6</v>
       </c>
       <c r="AJ83" s="4" t="n">
         <v>1333.13</v>
@@ -11321,13 +11321,13 @@
         <v>0.46</v>
       </c>
       <c r="AT83" s="4" t="n">
-        <v>8.42</v>
+        <v>1.73</v>
       </c>
       <c r="AU83" t="n">
-        <v>8.42</v>
+        <v>1.73</v>
       </c>
       <c r="AV83" t="n">
-        <v>4.41</v>
+        <v>-2.03</v>
       </c>
       <c r="AW83" s="4" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>11600</v>
       </c>
       <c r="AI84" s="4" t="n">
-        <v>11602</v>
+        <v>11427</v>
       </c>
       <c r="AJ84" s="4" t="n">
         <v>11485.98</v>
@@ -11470,13 +11470,13 @@
         <v>0.99</v>
       </c>
       <c r="AT84" s="4" t="n">
-        <v>-0.02</v>
+        <v>1.51</v>
       </c>
       <c r="AU84" t="n">
-        <v>-0.02</v>
+        <v>1.51</v>
       </c>
       <c r="AV84" t="n">
-        <v>-4.54</v>
+        <v>-3.08</v>
       </c>
       <c r="AW84" s="4" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>5548</v>
       </c>
       <c r="AI87" s="4" t="n">
-        <v>5057.4</v>
+        <v>5196.6</v>
       </c>
       <c r="AJ87" s="4" t="n">
         <v>5144.63</v>
@@ -11913,13 +11913,13 @@
         <v>1.42</v>
       </c>
       <c r="AT87" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="AU87" t="n">
-        <v>9.699999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="AV87" t="n">
-        <v>1.81</v>
+        <v>-0.91</v>
       </c>
       <c r="AW87" s="4" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>450</v>
       </c>
       <c r="AI89" s="4" t="n">
-        <v>459.25</v>
+        <v>441.05</v>
       </c>
       <c r="AJ89" s="4" t="n">
         <v>445.5</v>
@@ -12209,13 +12209,13 @@
         <v>-0.12</v>
       </c>
       <c r="AT89" s="4" t="n">
-        <v>-2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AU89" t="n">
-        <v>-1.54</v>
+        <v>2.53</v>
       </c>
       <c r="AV89" t="n">
-        <v>-3.96</v>
+        <v>-0</v>
       </c>
       <c r="AW89" s="4" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>11475</v>
       </c>
       <c r="AI91" s="4" t="n">
-        <v>10678</v>
+        <v>10880</v>
       </c>
       <c r="AJ91" s="4" t="n">
         <v>10771.2</v>
@@ -12503,13 +12503,13 @@
         <v>-0.55</v>
       </c>
       <c r="AT91" s="4" t="n">
-        <v>7.46</v>
+        <v>5.47</v>
       </c>
       <c r="AU91" t="n">
-        <v>8.050000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AW91" s="4" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>1327.7</v>
       </c>
       <c r="AI92" s="4" t="n">
-        <v>1298.9</v>
+        <v>1305</v>
       </c>
       <c r="AJ92" s="4" t="n">
         <v>1314.42</v>
@@ -12654,13 +12654,13 @@
         <v>-0.4</v>
       </c>
       <c r="AT92" s="4" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="AU92" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="AW92" s="4" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>932.8</v>
       </c>
       <c r="AI94" s="4" t="n">
-        <v>943.1</v>
+        <v>952.55</v>
       </c>
       <c r="AJ94" s="4" t="n">
         <v>943.02</v>
@@ -12952,13 +12952,13 @@
         <v>-0.76</v>
       </c>
       <c r="AT94" s="4" t="n">
-        <v>-1.09</v>
+        <v>-2.07</v>
       </c>
       <c r="AU94" t="n">
-        <v>1.97</v>
+        <v>0.96</v>
       </c>
       <c r="AV94" t="n">
-        <v>-1.09</v>
+        <v>-2.07</v>
       </c>
       <c r="AW94" s="4" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>422</v>
       </c>
       <c r="AI96" s="4" t="n">
-        <v>429.4</v>
+        <v>431.4</v>
       </c>
       <c r="AJ96" s="4" t="n">
         <v>427.09</v>
@@ -13250,13 +13250,13 @@
         <v>-0.72</v>
       </c>
       <c r="AT96" s="4" t="n">
-        <v>-1.72</v>
+        <v>-2.18</v>
       </c>
       <c r="AU96" t="n">
-        <v>0.47</v>
+        <v>-0</v>
       </c>
       <c r="AV96" t="n">
-        <v>-1.72</v>
+        <v>-2.18</v>
       </c>
       <c r="AW96" s="4" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>2410</v>
       </c>
       <c r="AI100" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ100" s="4" t="n">
         <v>2385.9</v>
@@ -13768,13 +13768,13 @@
         <v>1.09</v>
       </c>
       <c r="AT100" s="4" t="n">
-        <v>1.42</v>
+        <v>-1.37</v>
       </c>
       <c r="AU100" t="n">
-        <v>2.98</v>
+        <v>0.15</v>
       </c>
       <c r="AV100" t="n">
-        <v>0.32</v>
+        <v>-2.44</v>
       </c>
       <c r="AW100" s="4" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>289</v>
       </c>
       <c r="AI104" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ104" s="4" t="n">
         <v>286.11</v>
@@ -14280,13 +14280,13 @@
         <v>1.46</v>
       </c>
       <c r="AT104" s="4" t="n">
-        <v>2.87</v>
+        <v>0.63</v>
       </c>
       <c r="AU104" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="AV104" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW104" s="4" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>417.6</v>
       </c>
       <c r="AI108" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ108" s="4" t="n">
         <v>413.42</v>
@@ -14794,13 +14794,13 @@
         <v>0.59</v>
       </c>
       <c r="AT108" s="4" t="n">
-        <v>-2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AU108" t="n">
-        <v>-2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AV108" t="n">
-        <v>-3.89</v>
+        <v>-0.11</v>
       </c>
       <c r="AW108" s="4" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="AR110" s="4" t="inlineStr"/>
       <c r="AT110" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU110" s="4" t="n">
         <v>2.11</v>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="AR111" s="4" t="inlineStr"/>
       <c r="AT111" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU111" s="4" t="n">
         <v>0</v>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AR114" s="4" t="inlineStr"/>
       <c r="AT114" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU114" s="4" t="n">
         <v>0</v>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="AR115" s="4" t="inlineStr"/>
       <c r="AT115" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU115" s="4" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="AR117" s="4" t="inlineStr"/>
       <c r="AT117" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU117" s="4" t="n">
         <v>7.39</v>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AR118" s="4" t="inlineStr"/>
       <c r="AT118" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU118" s="4" t="n">
         <v>10.29</v>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="AR120" s="4" t="inlineStr"/>
       <c r="AT120" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU120" s="4" t="n">
         <v>0.99</v>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AR121" s="4" t="inlineStr"/>
       <c r="AT121" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU121" s="4" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="AR122" s="4" t="inlineStr"/>
       <c r="AT122" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU122" s="4" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="AR123" s="4" t="inlineStr"/>
       <c r="AT123" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU123" s="4" t="n">
         <v>1.09</v>
@@ -17269,7 +17269,7 @@
         <v>129.2</v>
       </c>
       <c r="AI124" s="4" t="n">
-        <v>133.14</v>
+        <v>134.19</v>
       </c>
       <c r="AJ124" s="4" t="n">
         <v>131.81</v>
@@ -17300,13 +17300,13 @@
         <v>1.33</v>
       </c>
       <c r="AT124" s="4" t="n">
-        <v>-2.96</v>
+        <v>-3.72</v>
       </c>
       <c r="AU124" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AV124" t="n">
-        <v>-4.24</v>
+        <v>-4.99</v>
       </c>
       <c r="AW124" s="4" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>5499</v>
       </c>
       <c r="AI125" s="4" t="n">
-        <v>5524</v>
+        <v>5483.3</v>
       </c>
       <c r="AJ125" s="4" t="n">
         <v>5468.76</v>
@@ -17449,13 +17449,13 @@
         <v>0.26</v>
       </c>
       <c r="AT125" s="4" t="n">
-        <v>-0.45</v>
+        <v>0.29</v>
       </c>
       <c r="AU125" t="n">
-        <v>-0.45</v>
+        <v>0.29</v>
       </c>
       <c r="AV125" t="n">
-        <v>-3.65</v>
+        <v>-2.93</v>
       </c>
       <c r="AW125" s="4" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>1167.5</v>
       </c>
       <c r="AI126" s="4" t="n">
-        <v>1158</v>
+        <v>1155.6</v>
       </c>
       <c r="AJ126" s="4" t="n">
         <v>1146.42</v>
@@ -17598,13 +17598,13 @@
         <v>0.21</v>
       </c>
       <c r="AT126" s="4" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="AU126" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="AV126" t="n">
-        <v>-3.71</v>
+        <v>-3.51</v>
       </c>
       <c r="AW126" s="4" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>454.6</v>
       </c>
       <c r="AI127" s="4" t="n">
-        <v>430.5</v>
+        <v>449.35</v>
       </c>
       <c r="AJ127" s="4" t="n">
         <v>444.86</v>
@@ -17751,13 +17751,13 @@
         <v>0.5</v>
       </c>
       <c r="AT127" s="4" t="n">
-        <v>5.6</v>
+        <v>1.17</v>
       </c>
       <c r="AU127" t="n">
-        <v>5.6</v>
+        <v>1.17</v>
       </c>
       <c r="AV127" t="n">
-        <v>2.98</v>
+        <v>-1.34</v>
       </c>
       <c r="AW127" s="4" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>289</v>
       </c>
       <c r="AI128" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ128" s="4" t="n">
         <v>284.33</v>
@@ -17904,13 +17904,13 @@
         <v>1.46</v>
       </c>
       <c r="AT128" s="4" t="n">
-        <v>2.87</v>
+        <v>0.63</v>
       </c>
       <c r="AU128" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW128" s="4" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>2195</v>
       </c>
       <c r="AI129" s="4" t="n">
-        <v>2157.8</v>
+        <v>2171.5</v>
       </c>
       <c r="AJ129" s="4" t="n">
         <v>2136.22</v>
@@ -18053,13 +18053,13 @@
         <v>-0.25</v>
       </c>
       <c r="AT129" s="4" t="n">
-        <v>1.72</v>
+        <v>1.08</v>
       </c>
       <c r="AU129" t="n">
-        <v>2.87</v>
+        <v>2.22</v>
       </c>
       <c r="AV129" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="AW129" s="4" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>568</v>
       </c>
       <c r="AI130" s="4" t="n">
-        <v>550.25</v>
+        <v>547.4</v>
       </c>
       <c r="AJ130" s="4" t="n">
         <v>541.9299999999999</v>
@@ -18206,13 +18206,13 @@
         <v>0.12</v>
       </c>
       <c r="AT130" s="4" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="AU130" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="AV130" t="n">
-        <v>-0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="AW130" s="4" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>1384</v>
       </c>
       <c r="AI131" s="4" t="n">
-        <v>1363</v>
+        <v>1373.1</v>
       </c>
       <c r="AJ131" s="4" t="n">
         <v>1349.37</v>
@@ -18355,13 +18355,13 @@
         <v>-1.52</v>
       </c>
       <c r="AT131" s="4" t="n">
-        <v>1.54</v>
+        <v>0.79</v>
       </c>
       <c r="AU131" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="AV131" t="n">
-        <v>-0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="AW131" s="4" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>2421.9</v>
       </c>
       <c r="AI132" s="4" t="n">
-        <v>2258.5</v>
+        <v>2452.2</v>
       </c>
       <c r="AJ132" s="4" t="n">
         <v>2397.68</v>
@@ -18533,13 +18533,13 @@
         <v>-1.55</v>
       </c>
       <c r="AT132" s="4" t="n">
-        <v>7.23</v>
+        <v>-1.24</v>
       </c>
       <c r="AU132" s="4" t="n">
-        <v>8.58</v>
+        <v>0.32</v>
       </c>
       <c r="AV132" s="4" t="n">
-        <v>0</v>
+        <v>-4.11</v>
       </c>
       <c r="AW132" s="4" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18688,7 @@
         <v>5651.5</v>
       </c>
       <c r="AI133" s="4" t="n">
-        <v>5057.4</v>
+        <v>5196.6</v>
       </c>
       <c r="AJ133" s="4" t="n">
         <v>5006.83</v>
@@ -18721,13 +18721,13 @@
         <v>1.87</v>
       </c>
       <c r="AT133" s="4" t="n">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="AU133" s="4" t="n">
-        <v>5.66</v>
+        <v>8.75</v>
       </c>
       <c r="AV133" s="4" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="AW133" s="4" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18846,7 @@
         <v>129.61</v>
       </c>
       <c r="AI134" s="4" t="n">
-        <v>133.14</v>
+        <v>134.19</v>
       </c>
       <c r="AJ134" s="4" t="n">
         <v>131.81</v>
@@ -18877,13 +18877,13 @@
         <v>1.33</v>
       </c>
       <c r="AT134" s="4" t="n">
-        <v>-2.65</v>
+        <v>-3.41</v>
       </c>
       <c r="AU134" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AV134" t="n">
-        <v>-4.24</v>
+        <v>-4.99</v>
       </c>
       <c r="AW134" s="4" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>5532.5</v>
       </c>
       <c r="AI135" s="4" t="n">
-        <v>5524</v>
+        <v>5483.3</v>
       </c>
       <c r="AJ135" s="4" t="n">
         <v>5468.76</v>
@@ -19031,13 +19031,13 @@
         <v>0.26</v>
       </c>
       <c r="AT135" s="4" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="AU135" t="n">
-        <v>0.15</v>
+        <v>0.9</v>
       </c>
       <c r="AV135" t="n">
-        <v>-3.65</v>
+        <v>-2.93</v>
       </c>
       <c r="AW135" s="4" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>1351.3</v>
       </c>
       <c r="AI136" s="4" t="n">
-        <v>1263.5</v>
+        <v>1346.6</v>
       </c>
       <c r="AJ136" s="4" t="n">
         <v>1250.87</v>
@@ -19209,13 +19209,13 @@
         <v>-1.36</v>
       </c>
       <c r="AT136" s="4" t="n">
-        <v>6.95</v>
+        <v>0.35</v>
       </c>
       <c r="AU136" s="4" t="n">
-        <v>6.58</v>
+        <v>1.73</v>
       </c>
       <c r="AV136" s="4" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="AW136" s="4" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -19352,7 +19352,7 @@
         <v>11727</v>
       </c>
       <c r="AI137" s="4" t="n">
-        <v>11602</v>
+        <v>11427</v>
       </c>
       <c r="AJ137" s="4" t="n">
         <v>11609.73</v>
@@ -19385,13 +19385,13 @@
         <v>1.09</v>
       </c>
       <c r="AT137" s="4" t="n">
-        <v>1.08</v>
+        <v>2.63</v>
       </c>
       <c r="AU137" s="4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV137" s="4" t="n">
-        <v>-4.54</v>
+        <v>-3.08</v>
       </c>
       <c r="AW137" s="4" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -19512,7 +19512,7 @@
         <v>1177</v>
       </c>
       <c r="AI138" s="4" t="n">
-        <v>1158</v>
+        <v>1155.6</v>
       </c>
       <c r="AJ138" s="4" t="n">
         <v>1146.42</v>
@@ -19543,13 +19543,13 @@
         <v>0.21</v>
       </c>
       <c r="AT138" s="4" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AU138" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AV138" t="n">
-        <v>-3.71</v>
+        <v>-3.51</v>
       </c>
       <c r="AW138" s="4" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>459.55</v>
       </c>
       <c r="AI139" s="4" t="n">
-        <v>430.5</v>
+        <v>449.35</v>
       </c>
       <c r="AJ139" s="4" t="n">
         <v>444.86</v>
@@ -19701,13 +19701,13 @@
         <v>0.5</v>
       </c>
       <c r="AT139" s="4" t="n">
-        <v>6.75</v>
+        <v>2.27</v>
       </c>
       <c r="AU139" t="n">
-        <v>6.75</v>
+        <v>2.27</v>
       </c>
       <c r="AV139" t="n">
-        <v>2.98</v>
+        <v>-1.34</v>
       </c>
       <c r="AW139" s="4" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>285.8</v>
       </c>
       <c r="AI140" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ140" s="4" t="n">
         <v>284.33</v>
@@ -19859,13 +19859,13 @@
         <v>1.46</v>
       </c>
       <c r="AT140" s="4" t="n">
-        <v>1.73</v>
+        <v>-0.49</v>
       </c>
       <c r="AU140" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="AV140" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW140" s="4" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>11456</v>
       </c>
       <c r="AI141" s="4" t="n">
-        <v>10678</v>
+        <v>10880</v>
       </c>
       <c r="AJ141" s="4" t="n">
         <v>10771.2</v>
@@ -20013,13 +20013,13 @@
         <v>-0.55</v>
       </c>
       <c r="AT141" s="4" t="n">
-        <v>7.29</v>
+        <v>5.29</v>
       </c>
       <c r="AU141" t="n">
-        <v>8.050000000000001</v>
+        <v>6.05</v>
       </c>
       <c r="AV141" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AW141" s="4" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>920.65</v>
       </c>
       <c r="AI142" s="4" t="n">
-        <v>943.1</v>
+        <v>952.55</v>
       </c>
       <c r="AJ142" s="4" t="n">
         <v>943.02</v>
@@ -20171,13 +20171,13 @@
         <v>-0.76</v>
       </c>
       <c r="AT142" s="4" t="n">
-        <v>-2.38</v>
+        <v>-3.35</v>
       </c>
       <c r="AU142" t="n">
-        <v>1.97</v>
+        <v>0.96</v>
       </c>
       <c r="AV142" t="n">
-        <v>-2.38</v>
+        <v>-3.35</v>
       </c>
       <c r="AW142" s="4" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>428.2</v>
       </c>
       <c r="AI143" s="4" t="n">
-        <v>429.4</v>
+        <v>431.4</v>
       </c>
       <c r="AJ143" s="4" t="n">
         <v>425.11</v>
@@ -20355,13 +20355,13 @@
         <v>1.47</v>
       </c>
       <c r="AT143" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AU143" s="4" t="n">
-        <v>0.47</v>
+        <v>-0</v>
       </c>
       <c r="AV143" s="4" t="n">
-        <v>-0.91</v>
+        <v>-2.18</v>
       </c>
       <c r="AW143" s="4" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -20480,7 +20480,7 @@
         <v>2182</v>
       </c>
       <c r="AI144" s="4" t="n">
-        <v>2157.8</v>
+        <v>2171.5</v>
       </c>
       <c r="AJ144" s="4" t="n">
         <v>2136.22</v>
@@ -20511,13 +20511,13 @@
         <v>-0.25</v>
       </c>
       <c r="AT144" s="4" t="n">
-        <v>1.12</v>
+        <v>0.48</v>
       </c>
       <c r="AU144" t="n">
-        <v>2.87</v>
+        <v>2.22</v>
       </c>
       <c r="AV144" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="AW144" s="4" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>567.8</v>
       </c>
       <c r="AI145" s="4" t="n">
-        <v>550.25</v>
+        <v>547.4</v>
       </c>
       <c r="AJ145" s="4" t="n">
         <v>541.9299999999999</v>
@@ -20669,13 +20669,13 @@
         <v>0.12</v>
       </c>
       <c r="AT145" s="4" t="n">
-        <v>3.19</v>
+        <v>3.73</v>
       </c>
       <c r="AU145" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="AV145" t="n">
-        <v>-0.83</v>
+        <v>-0.31</v>
       </c>
       <c r="AW145" s="4" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>1378.5</v>
       </c>
       <c r="AI146" s="4" t="n">
-        <v>1363</v>
+        <v>1373.1</v>
       </c>
       <c r="AJ146" s="4" t="n">
         <v>1349.37</v>
@@ -20823,13 +20823,13 @@
         <v>-1.52</v>
       </c>
       <c r="AT146" s="4" t="n">
-        <v>1.14</v>
+        <v>0.39</v>
       </c>
       <c r="AU146" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="AV146" t="n">
-        <v>-0.18</v>
+        <v>-0.92</v>
       </c>
       <c r="AW146" s="4" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21430,7 +21430,7 @@
         <v>2390.4</v>
       </c>
       <c r="AI150" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ150" s="4" t="n">
         <v>2329</v>
@@ -21463,13 +21463,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT150" s="4" t="n">
-        <v>0.6</v>
+        <v>-2.17</v>
       </c>
       <c r="AU150" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV150" s="4" t="n">
-        <v>0</v>
+        <v>-2.44</v>
       </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21787,7 +21787,7 @@
         <v>-0.2</v>
       </c>
       <c r="AT152" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU152" s="4" t="inlineStr"/>
       <c r="AV152" s="4" t="inlineStr"/>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AH157" s="4" t="n">
-        <v>414</v>
+        <v>414.05</v>
       </c>
       <c r="AI157" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ157" s="4" t="n">
         <v>401</v>
@@ -22583,13 +22583,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT157" s="4" t="n">
-        <v>-2.96</v>
+        <v>0.86</v>
       </c>
       <c r="AU157" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AV157" s="4" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW157" s="4" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -22945,7 +22945,7 @@
       <c r="AR159" s="4" t="inlineStr"/>
       <c r="AS159" s="4" t="inlineStr"/>
       <c r="AT159" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU159" s="4" t="n">
         <v>2.11</v>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       <c r="AR160" s="4" t="inlineStr"/>
       <c r="AS160" s="4" t="inlineStr"/>
       <c r="AT160" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU160" s="4" t="n">
         <v>0</v>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -23683,7 +23683,7 @@
       <c r="AR163" s="4" t="inlineStr"/>
       <c r="AS163" s="4" t="inlineStr"/>
       <c r="AT163" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU163" s="4" t="n">
         <v>0</v>
@@ -23708,7 +23708,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -23869,7 +23869,7 @@
       <c r="AR164" s="4" t="inlineStr"/>
       <c r="AS164" s="4" t="inlineStr"/>
       <c r="AT164" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU164" s="4" t="n">
         <v>0</v>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24080,7 +24080,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24241,7 +24241,7 @@
       <c r="AR166" s="4" t="inlineStr"/>
       <c r="AS166" s="4" t="inlineStr"/>
       <c r="AT166" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU166" s="4" t="n">
         <v>7.39</v>
@@ -24266,7 +24266,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24425,7 +24425,7 @@
       <c r="AR167" s="4" t="inlineStr"/>
       <c r="AS167" s="4" t="inlineStr"/>
       <c r="AT167" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU167" s="4" t="n">
         <v>10.29</v>
@@ -24450,7 +24450,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24634,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       <c r="AR169" s="4" t="inlineStr"/>
       <c r="AS169" s="4" t="inlineStr"/>
       <c r="AT169" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU169" s="4" t="n">
         <v>0.99</v>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       <c r="AR170" s="4" t="inlineStr"/>
       <c r="AS170" s="4" t="inlineStr"/>
       <c r="AT170" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU170" s="4" t="n">
         <v>0</v>
@@ -25006,7 +25006,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -25167,7 +25167,7 @@
       <c r="AR171" s="4" t="inlineStr"/>
       <c r="AS171" s="4" t="inlineStr"/>
       <c r="AT171" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU171" s="4" t="n">
         <v>0</v>
@@ -25192,7 +25192,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -25353,7 +25353,7 @@
       <c r="AR172" s="4" t="inlineStr"/>
       <c r="AS172" s="4" t="inlineStr"/>
       <c r="AT172" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU172" s="4" t="n">
         <v>1.09</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="AR173" s="4" t="inlineStr"/>
       <c r="AT173" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU173" s="4" t="n">
         <v>2.11</v>
@@ -25811,7 +25811,7 @@
       </c>
       <c r="AR175" s="4" t="inlineStr"/>
       <c r="AT175" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU175" s="4" t="n">
         <v>0</v>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="AR177" s="4" t="inlineStr"/>
       <c r="AT177" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU177" s="4" t="n">
         <v>7.39</v>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AR179" s="4" t="inlineStr"/>
       <c r="AT179" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU179" s="4" t="n">
         <v>0</v>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="AR181" s="4" t="inlineStr"/>
       <c r="AT181" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU181" s="4" t="n">
         <v>0</v>
@@ -26887,7 +26887,7 @@
       </c>
       <c r="AR182" s="4" t="inlineStr"/>
       <c r="AT182" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU182" s="4" t="n">
         <v>10.29</v>
@@ -27060,7 +27060,7 @@
         <v>0.99</v>
       </c>
       <c r="AT183" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU183" s="4" t="inlineStr"/>
       <c r="AV183" s="4" t="inlineStr"/>
@@ -27083,7 +27083,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27251,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27513,7 @@
         <v>443.9</v>
       </c>
       <c r="AI186" s="4" t="n">
-        <v>459.25</v>
+        <v>441.05</v>
       </c>
       <c r="AJ186" s="4" t="n">
         <v>454.66</v>
@@ -27546,13 +27546,13 @@
         <v>-1.36</v>
       </c>
       <c r="AT186" s="4" t="n">
-        <v>-3.34</v>
+        <v>0.65</v>
       </c>
       <c r="AU186" s="4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AV186" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW186" s="4" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -27699,7 +27699,7 @@
         <v>278.8</v>
       </c>
       <c r="AI187" s="4" t="n">
-        <v>261</v>
+        <v>263.5</v>
       </c>
       <c r="AJ187" s="4" t="n">
         <v>258.39</v>
@@ -27732,10 +27732,10 @@
         <v>3.64</v>
       </c>
       <c r="AT187" s="4" t="n">
-        <v>6.82</v>
+        <v>5.81</v>
       </c>
       <c r="AU187" s="4" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="AV187" s="4" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
         </is>
       </c>
       <c r="J188" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K188" s="4" t="n">
         <v>10</v>
@@ -27910,7 +27910,7 @@
         <v>0.89</v>
       </c>
       <c r="AT188" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU188" s="4" t="inlineStr"/>
       <c r="AV188" s="4" t="inlineStr"/>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -28059,7 +28059,7 @@
         <v>7531.5</v>
       </c>
       <c r="AI189" s="4" t="n">
-        <v>7338.5</v>
+        <v>7388.5</v>
       </c>
       <c r="AJ189" s="4" t="n">
         <v>7265.11</v>
@@ -28092,10 +28092,10 @@
         <v>1.85</v>
       </c>
       <c r="AT189" s="4" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="AU189" s="4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AV189" s="4" t="n">
         <v>0</v>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -28441,7 +28441,7 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -28561,7 +28561,7 @@
         <v>1296.8</v>
       </c>
       <c r="AI192" s="4" t="n">
-        <v>1298.9</v>
+        <v>1305</v>
       </c>
       <c r="AJ192" s="4" t="n">
         <v>1285.91</v>
@@ -28594,13 +28594,13 @@
         <v>-2.33</v>
       </c>
       <c r="AT192" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.63</v>
       </c>
       <c r="AU192" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV192" s="4" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="AW192" s="4" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -28693,7 +28693,7 @@
         <v>285.8</v>
       </c>
       <c r="AI193" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ193" s="4" t="n">
         <v>279</v>
@@ -28724,13 +28724,13 @@
         <v>-1.11</v>
       </c>
       <c r="AT193" s="4" t="n">
-        <v>1.73</v>
+        <v>-0.49</v>
       </c>
       <c r="AU193" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="AV193" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="AW193" s="4" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
         </is>
       </c>
       <c r="J195" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K195" s="4" t="n">
         <v>13</v>
@@ -29071,7 +29071,7 @@
         <v>-2.24</v>
       </c>
       <c r="AT195" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU195" s="4" t="inlineStr"/>
       <c r="AV195" s="4" t="inlineStr"/>
@@ -29092,7 +29092,7 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
         <v>285.8</v>
       </c>
       <c r="AI196" s="4" t="n">
-        <v>280.95</v>
+        <v>287.2</v>
       </c>
       <c r="AJ196" s="4" t="n">
         <v>279</v>
@@ -29225,13 +29225,13 @@
         <v>-1.11</v>
       </c>
       <c r="AT196" s="4" t="n">
-        <v>1.73</v>
+        <v>-0.49</v>
       </c>
       <c r="AU196" s="4" t="n">
-        <v>2.22</v>
+        <v>1.64</v>
       </c>
       <c r="AV196" s="4" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AW196" s="4" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -29403,7 +29403,7 @@
       <c r="AR197" s="4" t="inlineStr"/>
       <c r="AS197" s="4" t="inlineStr"/>
       <c r="AT197" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU197" s="4" t="n">
         <v>2.11</v>
@@ -29430,7 +29430,7 @@
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -29755,7 +29755,7 @@
       <c r="AR199" s="4" t="inlineStr"/>
       <c r="AS199" s="4" t="inlineStr"/>
       <c r="AT199" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU199" s="4" t="n">
         <v>0</v>
@@ -29782,7 +29782,7 @@
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -29960,7 +29960,7 @@
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30111,7 +30111,7 @@
       <c r="AR201" s="4" t="inlineStr"/>
       <c r="AS201" s="4" t="inlineStr"/>
       <c r="AT201" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU201" s="4" t="n">
         <v>7.39</v>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30316,7 +30316,7 @@
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30467,7 +30467,7 @@
       <c r="AR203" s="4" t="inlineStr"/>
       <c r="AS203" s="4" t="inlineStr"/>
       <c r="AT203" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU203" s="4" t="n">
         <v>0</v>
@@ -30494,7 +30494,7 @@
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30670,7 +30670,7 @@
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       <c r="AR205" s="4" t="inlineStr"/>
       <c r="AS205" s="4" t="inlineStr"/>
       <c r="AT205" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU205" s="4" t="n">
         <v>0</v>
@@ -30846,7 +30846,7 @@
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -30995,7 +30995,7 @@
       <c r="AR206" s="4" t="inlineStr"/>
       <c r="AS206" s="4" t="inlineStr"/>
       <c r="AT206" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU206" s="4" t="n">
         <v>10.29</v>
@@ -31022,7 +31022,7 @@
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31121,10 +31121,10 @@
         </is>
       </c>
       <c r="AH207" s="4" t="n">
-        <v>2376.2</v>
+        <v>2390.4</v>
       </c>
       <c r="AI207" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ207" s="4" t="n">
         <v>2352.44</v>
@@ -31157,13 +31157,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT207" s="4" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="AU207" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV207" s="4" t="n">
-        <v>0</v>
+        <v>-2.44</v>
       </c>
       <c r="AW207" s="4" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
       </c>
       <c r="BB207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31273,10 +31273,10 @@
         </is>
       </c>
       <c r="AH208" s="4" t="n">
-        <v>109.29</v>
+        <v>113.54</v>
       </c>
       <c r="AI208" s="4" t="n">
-        <v>109.29</v>
+        <v>111.44</v>
       </c>
       <c r="AJ208" s="4" t="n">
         <v>108.2</v>
@@ -31309,13 +31309,13 @@
         <v>-0.39</v>
       </c>
       <c r="AT208" s="4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AU208" s="4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AV208" s="4" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="AW208" s="4" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="BB208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31429,10 +31429,10 @@
         </is>
       </c>
       <c r="AH209" s="4" t="n">
-        <v>426.65</v>
+        <v>414.05</v>
       </c>
       <c r="AI209" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ209" s="4" t="n">
         <v>422.38</v>
@@ -31465,13 +31465,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT209" s="4" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AU209" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AV209" s="4" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW209" s="4" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
       </c>
       <c r="BB209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31581,10 +31581,10 @@
         </is>
       </c>
       <c r="AH210" s="4" t="n">
-        <v>526.45</v>
+        <v>597.55</v>
       </c>
       <c r="AI210" s="4" t="n">
-        <v>526.45</v>
+        <v>531.9</v>
       </c>
       <c r="AJ210" s="4" t="n">
         <v>521.1900000000001</v>
@@ -31617,10 +31617,10 @@
         <v>6.16</v>
       </c>
       <c r="AT210" s="4" t="n">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="AU210" s="4" t="n">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="AV210" s="4" t="n">
         <v>0</v>
@@ -31638,7 +31638,7 @@
       </c>
       <c r="BB210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31733,10 +31733,10 @@
         </is>
       </c>
       <c r="AH211" s="4" t="n">
-        <v>673.7</v>
+        <v>731</v>
       </c>
       <c r="AI211" s="4" t="n">
-        <v>673.7</v>
+        <v>700</v>
       </c>
       <c r="AJ211" s="4" t="n">
         <v>666.96</v>
@@ -31769,13 +31769,13 @@
         <v>3.02</v>
       </c>
       <c r="AT211" s="4" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AU211" s="4" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AV211" s="4" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="AW211" s="4" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="BB211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -31906,7 +31906,7 @@
       <c r="BA212" s="4" t="inlineStr"/>
       <c r="BB212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32022,7 +32022,7 @@
       <c r="BA213" s="4" t="inlineStr"/>
       <c r="BB213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32146,7 +32146,7 @@
       <c r="BA214" s="4" t="inlineStr"/>
       <c r="BB214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32270,7 @@
       <c r="BA215" s="4" t="inlineStr"/>
       <c r="BB215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32369,10 +32369,10 @@
         </is>
       </c>
       <c r="AH216" s="4" t="n">
-        <v>2376.2</v>
+        <v>2390.4</v>
       </c>
       <c r="AI216" s="4" t="n">
-        <v>2376.2</v>
+        <v>2443.4</v>
       </c>
       <c r="AJ216" s="4" t="n">
         <v>2352.44</v>
@@ -32405,13 +32405,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT216" s="4" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="AU216" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AV216" s="4" t="n">
-        <v>0</v>
+        <v>-2.44</v>
       </c>
       <c r="AW216" s="4" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
       </c>
       <c r="BB216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32550,7 +32550,7 @@
       <c r="BA217" s="4" t="inlineStr"/>
       <c r="BB217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32674,7 +32674,7 @@
       <c r="BA218" s="4" t="inlineStr"/>
       <c r="BB218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32798,7 +32798,7 @@
       <c r="BA219" s="4" t="inlineStr"/>
       <c r="BB219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -32922,7 +32922,7 @@
       <c r="BA220" s="4" t="inlineStr"/>
       <c r="BB220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -33046,7 +33046,7 @@
       <c r="BA221" s="4" t="inlineStr"/>
       <c r="BB221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -33170,7 +33170,7 @@
       <c r="BA222" s="4" t="inlineStr"/>
       <c r="BB222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -33269,10 +33269,10 @@
         </is>
       </c>
       <c r="AH223" s="4" t="n">
-        <v>426.65</v>
+        <v>414.05</v>
       </c>
       <c r="AI223" s="4" t="n">
-        <v>426.65</v>
+        <v>410.5</v>
       </c>
       <c r="AJ223" s="4" t="n">
         <v>422.38</v>
@@ -33305,13 +33305,13 @@
         <v>-0.85</v>
       </c>
       <c r="AT223" s="4" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AU223" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AV223" s="4" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AW223" s="4" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
       </c>
       <c r="BB223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -33446,7 +33446,7 @@
       <c r="BA224" s="4" t="inlineStr"/>
       <c r="BB224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>
@@ -33570,7 +33570,7 @@
       <c r="BA225" s="4" t="inlineStr"/>
       <c r="BB225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:24</t>
+          <t>2026-08-06 11:26</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -909,7 +909,7 @@
         <v>-4.11</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>-4.11</v>
@@ -1279,7 +1279,7 @@
         <v>-2.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
         <v>-2.93</v>
@@ -1405,7 +1405,7 @@
         <v>-2.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
         <v>-2.03</v>
@@ -1649,7 +1649,7 @@
         <v>-3.51</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>-3.51</v>
@@ -2149,7 +2149,7 @@
         <v>-0.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
         <v>-0.25</v>
@@ -2275,7 +2275,7 @@
         <v>-1.37</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
         <v>-1.37</v>
@@ -2645,7 +2645,7 @@
         <v>-0.92</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
         <v>-0.92</v>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="AH28" s="4" t="n">
-        <v>368.98</v>
+        <v>374.36</v>
       </c>
       <c r="AI28" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ28" s="4" t="n">
         <v>365.29</v>
@@ -4060,13 +4060,13 @@
       </c>
       <c r="AR28" s="4" t="inlineStr"/>
       <c r="AT28" s="4" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AU28" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV28" s="4" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AW28" s="4" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="AH29" s="4" t="n">
-        <v>358.56</v>
+        <v>366.13</v>
       </c>
       <c r="AI29" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ29" s="4" t="n">
         <v>354.97</v>
@@ -4186,13 +4186,13 @@
       </c>
       <c r="AR29" s="4" t="inlineStr"/>
       <c r="AT29" s="4" t="n">
-        <v>-0</v>
+        <v>-0.71</v>
       </c>
       <c r="AU29" s="4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AV29" s="4" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="AW29" s="4" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="AH30" s="4" t="n">
-        <v>202.81</v>
+        <v>200.75</v>
       </c>
       <c r="AI30" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ30" s="4" t="n">
         <v>200.78</v>
@@ -4317,13 +4317,13 @@
       </c>
       <c r="AR30" s="4" t="inlineStr"/>
       <c r="AT30" s="4" t="n">
-        <v>-0</v>
+        <v>5.65</v>
       </c>
       <c r="AU30" s="4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV30" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW30" s="4" t="inlineStr">
         <is>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="AH31" s="4" t="n">
-        <v>341.1</v>
+        <v>351.79</v>
       </c>
       <c r="AI31" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ31" s="4" t="n">
         <v>337.69</v>
@@ -4448,10 +4448,10 @@
       </c>
       <c r="AR31" s="4" t="inlineStr"/>
       <c r="AT31" s="4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU31" s="4" t="n">
-        <v>3.13</v>
+        <v>2.05</v>
       </c>
       <c r="AV31" s="4" t="n">
         <v>0</v>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="AH32" s="4" t="n">
-        <v>225.02</v>
+        <v>243.05</v>
       </c>
       <c r="AI32" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ32" s="4" t="n">
         <v>222.77</v>
@@ -4579,10 +4579,10 @@
       </c>
       <c r="AR32" s="4" t="inlineStr"/>
       <c r="AT32" s="4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AU32" s="4" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="AV32" s="4" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="AH33" s="4" t="n">
-        <v>1065.22</v>
+        <v>1018.38</v>
       </c>
       <c r="AI33" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ33" s="4" t="n">
         <v>1054.57</v>
@@ -4710,13 +4710,13 @@
       </c>
       <c r="AR33" s="4" t="inlineStr"/>
       <c r="AT33" s="4" t="n">
-        <v>-0</v>
+        <v>3.84</v>
       </c>
       <c r="AU33" s="4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV33" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW33" s="4" t="inlineStr">
         <is>
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="AH34" s="4" t="n">
-        <v>333.74</v>
+        <v>308.91</v>
       </c>
       <c r="AI34" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ34" s="4" t="n">
         <v>330.4</v>
@@ -4841,13 +4841,13 @@
       </c>
       <c r="AR34" s="4" t="inlineStr"/>
       <c r="AT34" s="4" t="n">
-        <v>-0</v>
+        <v>-8.66</v>
       </c>
       <c r="AU34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV34" s="4" t="n">
-        <v>-7.44</v>
+        <v>-8.66</v>
       </c>
       <c r="AW34" s="4" t="inlineStr">
         <is>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="AH35" s="4" t="n">
-        <v>393.82</v>
+        <v>464.72</v>
       </c>
       <c r="AI35" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ35" s="4" t="n">
         <v>389.88</v>
@@ -4972,10 +4972,10 @@
       </c>
       <c r="AR35" s="4" t="inlineStr"/>
       <c r="AT35" s="4" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU35" s="4" t="n">
-        <v>18</v>
+        <v>3.02</v>
       </c>
       <c r="AV35" s="4" t="n">
         <v>0</v>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="AH36" s="4" t="n">
-        <v>81.56</v>
+        <v>87.59</v>
       </c>
       <c r="AI36" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ36" s="4" t="n">
         <v>80.73999999999999</v>
@@ -5103,13 +5103,13 @@
       </c>
       <c r="AR36" s="4" t="inlineStr"/>
       <c r="AT36" s="4" t="n">
-        <v>-0</v>
+        <v>-1.67</v>
       </c>
       <c r="AU36" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV36" s="4" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AW36" s="4" t="inlineStr">
         <is>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="AH37" s="4" t="n">
-        <v>159.84</v>
+        <v>176.28</v>
       </c>
       <c r="AI37" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ37" s="4" t="n">
         <v>158.24</v>
@@ -5234,10 +5234,10 @@
       </c>
       <c r="AR37" s="4" t="inlineStr"/>
       <c r="AT37" s="4" t="n">
-        <v>-0</v>
+        <v>0.12</v>
       </c>
       <c r="AU37" s="4" t="n">
-        <v>10.29</v>
+        <v>0.12</v>
       </c>
       <c r="AV37" s="4" t="n">
         <v>0</v>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="AH38" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="AI38" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="AJ38" s="4" t="n">
         <v>94.09</v>
@@ -5365,13 +5365,13 @@
       </c>
       <c r="AR38" s="4" t="inlineStr"/>
       <c r="AT38" s="4" t="n">
-        <v>0</v>
+        <v>10.16</v>
       </c>
       <c r="AU38" s="4" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AV38" s="4" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AW38" s="4" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="AH39" s="4" t="n">
-        <v>214.03</v>
+        <v>216.14</v>
       </c>
       <c r="AI39" s="4" t="n">
-        <v>214.03</v>
+        <v>220.9</v>
       </c>
       <c r="AJ39" s="4" t="n">
         <v>211.89</v>
@@ -5496,13 +5496,13 @@
       </c>
       <c r="AR39" s="4" t="inlineStr"/>
       <c r="AT39" s="4" t="n">
-        <v>-0</v>
+        <v>-2.15</v>
       </c>
       <c r="AU39" s="4" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AV39" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="AW39" s="4" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="AH40" s="4" t="n">
-        <v>338.87</v>
+        <v>331.96</v>
       </c>
       <c r="AI40" s="4" t="n">
-        <v>338.87</v>
+        <v>338.27</v>
       </c>
       <c r="AJ40" s="4" t="n">
         <v>335.48</v>
@@ -5627,13 +5627,13 @@
       </c>
       <c r="AR40" s="4" t="inlineStr"/>
       <c r="AT40" s="4" t="n">
-        <v>-0</v>
+        <v>-1.87</v>
       </c>
       <c r="AU40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV40" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="AW40" s="4" t="inlineStr">
         <is>
@@ -5727,10 +5727,10 @@
         </is>
       </c>
       <c r="AH41" s="4" t="n">
-        <v>97.67</v>
+        <v>96.19</v>
       </c>
       <c r="AI41" s="4" t="n">
-        <v>97.67</v>
+        <v>98.48</v>
       </c>
       <c r="AJ41" s="4" t="n">
         <v>96.69</v>
@@ -5758,13 +5758,13 @@
       </c>
       <c r="AR41" s="4" t="inlineStr"/>
       <c r="AT41" s="4" t="n">
-        <v>-0</v>
+        <v>-2.33</v>
       </c>
       <c r="AU41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV41" s="4" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AW41" s="4" t="inlineStr">
         <is>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="AH42" s="4" t="n">
-        <v>267.71</v>
+        <v>270.64</v>
       </c>
       <c r="AI42" s="4" t="n">
-        <v>267.71</v>
+        <v>271.52</v>
       </c>
       <c r="AJ42" s="4" t="n">
         <v>265.03</v>
@@ -5889,13 +5889,13 @@
       </c>
       <c r="AR42" s="4" t="inlineStr"/>
       <c r="AT42" s="4" t="n">
-        <v>-0</v>
+        <v>-0.32</v>
       </c>
       <c r="AU42" s="4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AV42" s="4" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="AW42" s="4" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>-0.52</v>
       </c>
       <c r="AU51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
         <v>-4.11</v>
@@ -7331,7 +7331,7 @@
         <v>-1.47</v>
       </c>
       <c r="AU53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV53" t="n">
         <v>-1.47</v>
@@ -9071,10 +9071,10 @@
         </is>
       </c>
       <c r="AH67" s="4" t="n">
-        <v>368.98</v>
+        <v>377.15</v>
       </c>
       <c r="AI67" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ67" s="4" t="n">
         <v>365.29</v>
@@ -9102,13 +9102,13 @@
       </c>
       <c r="AR67" s="4" t="inlineStr"/>
       <c r="AT67" s="4" t="n">
-        <v>0</v>
+        <v>-3.05</v>
       </c>
       <c r="AU67" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV67" s="4" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="AW67" s="4" t="inlineStr">
         <is>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="AH68" s="4" t="n">
-        <v>358.56</v>
+        <v>369.59</v>
       </c>
       <c r="AI68" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ68" s="4" t="n">
         <v>354.97</v>
@@ -9234,13 +9234,13 @@
       </c>
       <c r="AR68" s="4" t="inlineStr"/>
       <c r="AT68" s="4" t="n">
-        <v>-0</v>
+        <v>0.23</v>
       </c>
       <c r="AU68" s="4" t="n">
-        <v>2.11</v>
+        <v>0.23</v>
       </c>
       <c r="AV68" s="4" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="AW68" s="4" t="inlineStr">
         <is>
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="AH69" s="4" t="n">
-        <v>202.81</v>
+        <v>211.94</v>
       </c>
       <c r="AI69" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ69" s="4" t="n">
         <v>200.78</v>
@@ -9371,13 +9371,13 @@
       </c>
       <c r="AR69" s="4" t="inlineStr"/>
       <c r="AT69" s="4" t="n">
-        <v>-0</v>
+        <v>11.54</v>
       </c>
       <c r="AU69" s="4" t="n">
-        <v>0</v>
+        <v>11.54</v>
       </c>
       <c r="AV69" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW69" s="4" t="inlineStr">
         <is>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="AH70" s="4" t="n">
-        <v>341.1</v>
+        <v>357.52</v>
       </c>
       <c r="AI70" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ70" s="4" t="n">
         <v>337.69</v>
@@ -9508,10 +9508,10 @@
       </c>
       <c r="AR70" s="4" t="inlineStr"/>
       <c r="AT70" s="4" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AU70" s="4" t="n">
-        <v>3.13</v>
+        <v>3.72</v>
       </c>
       <c r="AV70" s="4" t="n">
         <v>0</v>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="AH71" s="4" t="n">
-        <v>225.02</v>
+        <v>248.79</v>
       </c>
       <c r="AI71" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ71" s="4" t="n">
         <v>222.77</v>
@@ -9645,10 +9645,10 @@
       </c>
       <c r="AR71" s="4" t="inlineStr"/>
       <c r="AT71" s="4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU71" s="4" t="n">
-        <v>8.01</v>
+        <v>3.18</v>
       </c>
       <c r="AV71" s="4" t="n">
         <v>0</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="AH72" s="4" t="n">
-        <v>1065.22</v>
+        <v>1052.98</v>
       </c>
       <c r="AI72" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ72" s="4" t="n">
         <v>1054.57</v>
@@ -9782,13 +9782,13 @@
       </c>
       <c r="AR72" s="4" t="inlineStr"/>
       <c r="AT72" s="4" t="n">
-        <v>-0</v>
+        <v>7.36</v>
       </c>
       <c r="AU72" s="4" t="n">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="AV72" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW72" s="4" t="inlineStr">
         <is>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="AH73" s="4" t="n">
-        <v>333.74</v>
+        <v>309.38</v>
       </c>
       <c r="AI73" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ73" s="4" t="n">
         <v>330.4</v>
@@ -9919,13 +9919,13 @@
       </c>
       <c r="AR73" s="4" t="inlineStr"/>
       <c r="AT73" s="4" t="n">
-        <v>-0</v>
+        <v>-8.52</v>
       </c>
       <c r="AU73" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV73" s="4" t="n">
-        <v>-7.44</v>
+        <v>-10.28</v>
       </c>
       <c r="AW73" s="4" t="inlineStr">
         <is>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="AH74" s="4" t="n">
-        <v>393.82</v>
+        <v>492.81</v>
       </c>
       <c r="AI74" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ74" s="4" t="n">
         <v>389.88</v>
@@ -10056,10 +10056,10 @@
       </c>
       <c r="AR74" s="4" t="inlineStr"/>
       <c r="AT74" s="4" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="AU74" s="4" t="n">
-        <v>18</v>
+        <v>9.25</v>
       </c>
       <c r="AV74" s="4" t="n">
         <v>0</v>
@@ -10162,10 +10162,10 @@
         </is>
       </c>
       <c r="AH75" s="4" t="n">
-        <v>81.56</v>
+        <v>86.56</v>
       </c>
       <c r="AI75" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ75" s="4" t="n">
         <v>80.73999999999999</v>
@@ -10193,13 +10193,13 @@
       </c>
       <c r="AR75" s="4" t="inlineStr"/>
       <c r="AT75" s="4" t="n">
-        <v>-0</v>
+        <v>-2.83</v>
       </c>
       <c r="AU75" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV75" s="4" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AW75" s="4" t="inlineStr">
         <is>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="AH76" s="4" t="n">
-        <v>159.84</v>
+        <v>181.45</v>
       </c>
       <c r="AI76" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ76" s="4" t="n">
         <v>158.24</v>
@@ -10330,10 +10330,10 @@
       </c>
       <c r="AR76" s="4" t="inlineStr"/>
       <c r="AT76" s="4" t="n">
-        <v>-0</v>
+        <v>3.06</v>
       </c>
       <c r="AU76" s="4" t="n">
-        <v>10.29</v>
+        <v>3.06</v>
       </c>
       <c r="AV76" s="4" t="n">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="AH77" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>100.86</v>
       </c>
       <c r="AI77" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="AJ77" s="4" t="n">
         <v>94.09</v>
@@ -10467,13 +10467,13 @@
       </c>
       <c r="AR77" s="4" t="inlineStr"/>
       <c r="AT77" s="4" t="n">
-        <v>0</v>
+        <v>23.18</v>
       </c>
       <c r="AU77" s="4" t="n">
-        <v>0</v>
+        <v>23.18</v>
       </c>
       <c r="AV77" s="4" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AW77" s="4" t="inlineStr">
         <is>
@@ -10573,10 +10573,10 @@
         </is>
       </c>
       <c r="AH78" s="4" t="n">
-        <v>214.03</v>
+        <v>237.16</v>
       </c>
       <c r="AI78" s="4" t="n">
-        <v>214.03</v>
+        <v>220.9</v>
       </c>
       <c r="AJ78" s="4" t="n">
         <v>211.89</v>
@@ -10604,13 +10604,13 @@
       </c>
       <c r="AR78" s="4" t="inlineStr"/>
       <c r="AT78" s="4" t="n">
-        <v>-0</v>
+        <v>7.36</v>
       </c>
       <c r="AU78" s="4" t="n">
-        <v>0.99</v>
+        <v>7.36</v>
       </c>
       <c r="AV78" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="AW78" s="4" t="inlineStr">
         <is>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="AH79" s="4" t="n">
-        <v>338.87</v>
+        <v>348.24</v>
       </c>
       <c r="AI79" s="4" t="n">
-        <v>338.87</v>
+        <v>338.27</v>
       </c>
       <c r="AJ79" s="4" t="n">
         <v>335.48</v>
@@ -10741,13 +10741,13 @@
       </c>
       <c r="AR79" s="4" t="inlineStr"/>
       <c r="AT79" s="4" t="n">
-        <v>-0</v>
+        <v>2.95</v>
       </c>
       <c r="AU79" s="4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV79" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="AW79" s="4" t="inlineStr">
         <is>
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="AH80" s="4" t="n">
-        <v>97.67</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="AI80" s="4" t="n">
-        <v>97.67</v>
+        <v>98.48</v>
       </c>
       <c r="AJ80" s="4" t="n">
         <v>96.69</v>
@@ -10878,13 +10878,13 @@
       </c>
       <c r="AR80" s="4" t="inlineStr"/>
       <c r="AT80" s="4" t="n">
-        <v>-0</v>
+        <v>-0.3</v>
       </c>
       <c r="AU80" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV80" s="4" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AW80" s="4" t="inlineStr">
         <is>
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="AH81" s="4" t="n">
-        <v>267.71</v>
+        <v>268.34</v>
       </c>
       <c r="AI81" s="4" t="n">
-        <v>267.71</v>
+        <v>271.52</v>
       </c>
       <c r="AJ81" s="4" t="n">
         <v>265.03</v>
@@ -11015,13 +11015,13 @@
       </c>
       <c r="AR81" s="4" t="inlineStr"/>
       <c r="AT81" s="4" t="n">
-        <v>-0</v>
+        <v>-1.17</v>
       </c>
       <c r="AU81" s="4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AV81" s="4" t="n">
-        <v>0</v>
+        <v>-2.32</v>
       </c>
       <c r="AW81" s="4" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>2.53</v>
       </c>
       <c r="AV89" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW89" s="4" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>-2.18</v>
       </c>
       <c r="AU96" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV96" t="n">
         <v>-2.18</v>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="AH109" s="4" t="n">
-        <v>368.98</v>
+        <v>382.45</v>
       </c>
       <c r="AI109" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ109" s="4" t="n">
         <v>365.29</v>
@@ -14944,13 +14944,13 @@
       </c>
       <c r="AR109" s="4" t="inlineStr"/>
       <c r="AT109" s="4" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
       <c r="AU109" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV109" s="4" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="AW109" s="4" t="inlineStr">
         <is>
@@ -15066,10 +15066,10 @@
         </is>
       </c>
       <c r="AH110" s="4" t="n">
-        <v>358.56</v>
+        <v>368.54</v>
       </c>
       <c r="AI110" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ110" s="4" t="n">
         <v>354.97</v>
@@ -15097,13 +15097,13 @@
       </c>
       <c r="AR110" s="4" t="inlineStr"/>
       <c r="AT110" s="4" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AU110" s="4" t="n">
-        <v>2.11</v>
+        <v>0.23</v>
       </c>
       <c r="AV110" s="4" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="AW110" s="4" t="inlineStr">
         <is>
@@ -15224,10 +15224,10 @@
         </is>
       </c>
       <c r="AH111" s="4" t="n">
-        <v>202.81</v>
+        <v>219.22</v>
       </c>
       <c r="AI111" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ111" s="4" t="n">
         <v>200.78</v>
@@ -15255,13 +15255,13 @@
       </c>
       <c r="AR111" s="4" t="inlineStr"/>
       <c r="AT111" s="4" t="n">
-        <v>-0</v>
+        <v>15.37</v>
       </c>
       <c r="AU111" s="4" t="n">
-        <v>0</v>
+        <v>15.37</v>
       </c>
       <c r="AV111" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW111" s="4" t="inlineStr">
         <is>
@@ -15382,10 +15382,10 @@
         </is>
       </c>
       <c r="AH112" s="4" t="n">
-        <v>341.1</v>
+        <v>359.24</v>
       </c>
       <c r="AI112" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ112" s="4" t="n">
         <v>337.69</v>
@@ -15413,10 +15413,10 @@
       </c>
       <c r="AR112" s="4" t="inlineStr"/>
       <c r="AT112" s="4" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AU112" s="4" t="n">
-        <v>3.13</v>
+        <v>4.22</v>
       </c>
       <c r="AV112" s="4" t="n">
         <v>0</v>
@@ -15540,10 +15540,10 @@
         </is>
       </c>
       <c r="AH113" s="4" t="n">
-        <v>225.02</v>
+        <v>248.12</v>
       </c>
       <c r="AI113" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ113" s="4" t="n">
         <v>222.77</v>
@@ -15571,10 +15571,10 @@
       </c>
       <c r="AR113" s="4" t="inlineStr"/>
       <c r="AT113" s="4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU113" s="4" t="n">
-        <v>8.01</v>
+        <v>3.18</v>
       </c>
       <c r="AV113" s="4" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="AH114" s="4" t="n">
-        <v>1065.22</v>
+        <v>1060.38</v>
       </c>
       <c r="AI114" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ114" s="4" t="n">
         <v>1054.57</v>
@@ -15729,13 +15729,13 @@
       </c>
       <c r="AR114" s="4" t="inlineStr"/>
       <c r="AT114" s="4" t="n">
-        <v>-0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AU114" s="4" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AV114" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW114" s="4" t="inlineStr">
         <is>
@@ -15856,10 +15856,10 @@
         </is>
       </c>
       <c r="AH115" s="4" t="n">
-        <v>333.74</v>
+        <v>311</v>
       </c>
       <c r="AI115" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ115" s="4" t="n">
         <v>330.4</v>
@@ -15887,13 +15887,13 @@
       </c>
       <c r="AR115" s="4" t="inlineStr"/>
       <c r="AT115" s="4" t="n">
-        <v>-0</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="AU115" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV115" s="4" t="n">
-        <v>-7.44</v>
+        <v>-10.28</v>
       </c>
       <c r="AW115" s="4" t="inlineStr">
         <is>
@@ -16014,10 +16014,10 @@
         </is>
       </c>
       <c r="AH116" s="4" t="n">
-        <v>393.82</v>
+        <v>487.46</v>
       </c>
       <c r="AI116" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ116" s="4" t="n">
         <v>389.88</v>
@@ -16045,10 +16045,10 @@
       </c>
       <c r="AR116" s="4" t="inlineStr"/>
       <c r="AT116" s="4" t="n">
-        <v>0</v>
+        <v>8.06</v>
       </c>
       <c r="AU116" s="4" t="n">
-        <v>18</v>
+        <v>9.25</v>
       </c>
       <c r="AV116" s="4" t="n">
         <v>0</v>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="AH117" s="4" t="n">
-        <v>81.56</v>
+        <v>86.83</v>
       </c>
       <c r="AI117" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ117" s="4" t="n">
         <v>80.73999999999999</v>
@@ -16203,13 +16203,13 @@
       </c>
       <c r="AR117" s="4" t="inlineStr"/>
       <c r="AT117" s="4" t="n">
-        <v>-0</v>
+        <v>-2.53</v>
       </c>
       <c r="AU117" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV117" s="4" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AW117" s="4" t="inlineStr">
         <is>
@@ -16330,10 +16330,10 @@
         </is>
       </c>
       <c r="AH118" s="4" t="n">
-        <v>159.84</v>
+        <v>182.08</v>
       </c>
       <c r="AI118" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ118" s="4" t="n">
         <v>158.24</v>
@@ -16361,10 +16361,10 @@
       </c>
       <c r="AR118" s="4" t="inlineStr"/>
       <c r="AT118" s="4" t="n">
-        <v>-0</v>
+        <v>3.41</v>
       </c>
       <c r="AU118" s="4" t="n">
-        <v>10.29</v>
+        <v>3.41</v>
       </c>
       <c r="AV118" s="4" t="n">
         <v>0</v>
@@ -16488,10 +16488,10 @@
         </is>
       </c>
       <c r="AH119" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>101.06</v>
       </c>
       <c r="AI119" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="AJ119" s="4" t="n">
         <v>94.09</v>
@@ -16519,13 +16519,13 @@
       </c>
       <c r="AR119" s="4" t="inlineStr"/>
       <c r="AT119" s="4" t="n">
-        <v>0</v>
+        <v>23.42</v>
       </c>
       <c r="AU119" s="4" t="n">
-        <v>0</v>
+        <v>23.42</v>
       </c>
       <c r="AV119" s="4" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AW119" s="4" t="inlineStr">
         <is>
@@ -16646,10 +16646,10 @@
         </is>
       </c>
       <c r="AH120" s="4" t="n">
-        <v>214.03</v>
+        <v>240.19</v>
       </c>
       <c r="AI120" s="4" t="n">
-        <v>214.03</v>
+        <v>220.9</v>
       </c>
       <c r="AJ120" s="4" t="n">
         <v>211.89</v>
@@ -16677,13 +16677,13 @@
       </c>
       <c r="AR120" s="4" t="inlineStr"/>
       <c r="AT120" s="4" t="n">
-        <v>-0</v>
+        <v>8.73</v>
       </c>
       <c r="AU120" s="4" t="n">
-        <v>0.99</v>
+        <v>8.73</v>
       </c>
       <c r="AV120" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="AW120" s="4" t="inlineStr">
         <is>
@@ -16804,10 +16804,10 @@
         </is>
       </c>
       <c r="AH121" s="4" t="n">
-        <v>338.87</v>
+        <v>353.14</v>
       </c>
       <c r="AI121" s="4" t="n">
-        <v>338.87</v>
+        <v>338.27</v>
       </c>
       <c r="AJ121" s="4" t="n">
         <v>335.48</v>
@@ -16835,13 +16835,13 @@
       </c>
       <c r="AR121" s="4" t="inlineStr"/>
       <c r="AT121" s="4" t="n">
-        <v>-0</v>
+        <v>4.4</v>
       </c>
       <c r="AU121" s="4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV121" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="AW121" s="4" t="inlineStr">
         <is>
@@ -16962,10 +16962,10 @@
         </is>
       </c>
       <c r="AH122" s="4" t="n">
-        <v>97.67</v>
+        <v>101.76</v>
       </c>
       <c r="AI122" s="4" t="n">
-        <v>97.67</v>
+        <v>98.48</v>
       </c>
       <c r="AJ122" s="4" t="n">
         <v>96.69</v>
@@ -16993,13 +16993,13 @@
       </c>
       <c r="AR122" s="4" t="inlineStr"/>
       <c r="AT122" s="4" t="n">
-        <v>-0</v>
+        <v>3.33</v>
       </c>
       <c r="AU122" s="4" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AV122" s="4" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AW122" s="4" t="inlineStr">
         <is>
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="AH123" s="4" t="n">
-        <v>267.71</v>
+        <v>274</v>
       </c>
       <c r="AI123" s="4" t="n">
-        <v>267.71</v>
+        <v>271.52</v>
       </c>
       <c r="AJ123" s="4" t="n">
         <v>265.03</v>
@@ -17151,13 +17151,13 @@
       </c>
       <c r="AR123" s="4" t="inlineStr"/>
       <c r="AT123" s="4" t="n">
-        <v>-0</v>
+        <v>0.91</v>
       </c>
       <c r="AU123" s="4" t="n">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="AV123" s="4" t="n">
-        <v>0</v>
+        <v>-2.32</v>
       </c>
       <c r="AW123" s="4" t="inlineStr">
         <is>
@@ -18449,14 +18449,14 @@
       </c>
       <c r="Q132" s="4" t="inlineStr"/>
       <c r="R132" s="4" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="S132" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T132" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U132" s="4" t="inlineStr"/>
@@ -18512,19 +18512,19 @@
         <v>2276.59</v>
       </c>
       <c r="AM132" s="4" t="n">
-        <v>0.8</v>
+        <v>-7.16</v>
       </c>
       <c r="AN132" s="4" t="n">
         <v>2712.53</v>
       </c>
       <c r="AO132" s="4" t="n">
-        <v>20.1</v>
+        <v>10.62</v>
       </c>
       <c r="AP132" s="4" t="n">
         <v>3003.16</v>
       </c>
       <c r="AQ132" s="4" t="n">
-        <v>32.97</v>
+        <v>22.47</v>
       </c>
       <c r="AR132" s="4" t="n">
         <v>2460</v>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -18611,7 +18611,7 @@
         </is>
       </c>
       <c r="J133" s="4" t="n">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>8</v>
@@ -18637,14 +18637,14 @@
       </c>
       <c r="Q133" s="4" t="inlineStr"/>
       <c r="R133" s="4" t="n">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="S133" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T133" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U133" s="4" t="inlineStr"/>
@@ -18691,25 +18691,25 @@
         <v>5196.6</v>
       </c>
       <c r="AJ133" s="4" t="n">
-        <v>5006.83</v>
+        <v>5144.63</v>
       </c>
       <c r="AK133" s="4" t="n">
-        <v>5107.97</v>
+        <v>5248.57</v>
       </c>
       <c r="AL133" s="4" t="n">
-        <v>4804.53</v>
+        <v>4936.77</v>
       </c>
       <c r="AM133" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN133" s="4" t="n">
-        <v>5461.99</v>
+        <v>5612.33</v>
       </c>
       <c r="AO133" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP133" s="4" t="n">
-        <v>5816.01</v>
+        <v>5976.09</v>
       </c>
       <c r="AQ133" s="4" t="n">
         <v>15</v>
@@ -18724,7 +18724,7 @@
         <v>8.75</v>
       </c>
       <c r="AU133" s="4" t="n">
-        <v>8.75</v>
+        <v>6.76</v>
       </c>
       <c r="AV133" s="4" t="n">
         <v>-0.91</v>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -19125,14 +19125,14 @@
       </c>
       <c r="Q136" s="4" t="inlineStr"/>
       <c r="R136" s="4" t="n">
-        <v>40.4</v>
+        <v>42.4</v>
       </c>
       <c r="S136" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T136" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U136" s="4" t="inlineStr"/>
@@ -19140,7 +19140,7 @@
       <c r="W136" s="4" t="inlineStr"/>
       <c r="X136" s="4" t="inlineStr">
         <is>
-          <t>🟡 WAIT (Δ+5.9%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.6%) · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → HOLD</t>
         </is>
       </c>
       <c r="Y136" s="4" t="inlineStr"/>
@@ -19179,25 +19179,25 @@
         <v>1346.6</v>
       </c>
       <c r="AJ136" s="4" t="n">
-        <v>1250.87</v>
+        <v>1333.13</v>
       </c>
       <c r="AK136" s="4" t="n">
-        <v>1276.13</v>
+        <v>1360.07</v>
       </c>
       <c r="AL136" s="4" t="n">
-        <v>1200.33</v>
+        <v>1279.27</v>
       </c>
       <c r="AM136" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN136" s="4" t="n">
-        <v>1364.58</v>
+        <v>1454.33</v>
       </c>
       <c r="AO136" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP136" s="4" t="n">
-        <v>1453.02</v>
+        <v>1548.59</v>
       </c>
       <c r="AQ136" s="4" t="n">
         <v>15</v>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -19301,14 +19301,14 @@
       </c>
       <c r="Q137" s="4" t="inlineStr"/>
       <c r="R137" s="4" t="n">
-        <v>43.6</v>
+        <v>45.6</v>
       </c>
       <c r="S137" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T137" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U137" s="4" t="inlineStr"/>
@@ -19364,19 +19364,19 @@
         <v>11023.38</v>
       </c>
       <c r="AM137" s="4" t="n">
-        <v>-4.99</v>
+        <v>-3.53</v>
       </c>
       <c r="AN137" s="4" t="n">
         <v>13134.24</v>
       </c>
       <c r="AO137" s="4" t="n">
-        <v>13.21</v>
+        <v>14.94</v>
       </c>
       <c r="AP137" s="4" t="n">
         <v>14541.48</v>
       </c>
       <c r="AQ137" s="4" t="n">
-        <v>25.34</v>
+        <v>27.26</v>
       </c>
       <c r="AR137" s="4" t="n">
         <v>11600</v>
@@ -19388,7 +19388,7 @@
         <v>2.63</v>
       </c>
       <c r="AU137" s="4" t="n">
-        <v>2.63</v>
+        <v>1.51</v>
       </c>
       <c r="AV137" s="4" t="n">
         <v>-3.08</v>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="J143" s="4" t="n">
-        <v>-0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="K143" s="4" t="n">
         <v>12</v>
@@ -20271,14 +20271,14 @@
       </c>
       <c r="Q143" s="4" t="inlineStr"/>
       <c r="R143" s="4" t="n">
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="S143" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T143" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U143" s="4" t="inlineStr"/>
@@ -20325,25 +20325,25 @@
         <v>431.4</v>
       </c>
       <c r="AJ143" s="4" t="n">
-        <v>425.11</v>
+        <v>427.09</v>
       </c>
       <c r="AK143" s="4" t="n">
-        <v>433.69</v>
+        <v>435.71</v>
       </c>
       <c r="AL143" s="4" t="n">
-        <v>407.93</v>
+        <v>409.83</v>
       </c>
       <c r="AM143" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN143" s="4" t="n">
-        <v>463.75</v>
+        <v>465.91</v>
       </c>
       <c r="AO143" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP143" s="4" t="n">
-        <v>493.81</v>
+        <v>496.11</v>
       </c>
       <c r="AQ143" s="4" t="n">
         <v>15</v>
@@ -20358,7 +20358,7 @@
         <v>-0.74</v>
       </c>
       <c r="AU143" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV143" s="4" t="n">
         <v>-2.18</v>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21442,19 +21442,19 @@
         <v>2270.88</v>
       </c>
       <c r="AM150" s="4" t="n">
-        <v>-4.43</v>
+        <v>-7.06</v>
       </c>
       <c r="AN150" s="4" t="n">
         <v>2581.632</v>
       </c>
       <c r="AO150" s="4" t="n">
-        <v>8.65</v>
+        <v>5.66</v>
       </c>
       <c r="AP150" s="4" t="n">
         <v>2762.34624</v>
       </c>
       <c r="AQ150" s="4" t="n">
-        <v>16.25</v>
+        <v>13.05</v>
       </c>
       <c r="AR150" s="4" t="n">
         <v>2410</v>
@@ -21469,7 +21469,7 @@
         <v>0.15</v>
       </c>
       <c r="AV150" s="4" t="n">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="AW150" s="4" t="inlineStr">
         <is>
@@ -21486,11 +21486,11 @@
         <v>5</v>
       </c>
       <c r="BA150" s="4" t="n">
-        <v>8.65</v>
+        <v>5.66</v>
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21787,7 +21787,7 @@
         <v>-0.2</v>
       </c>
       <c r="AT152" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU152" s="4" t="inlineStr"/>
       <c r="AV152" s="4" t="inlineStr"/>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AH157" s="4" t="n">
-        <v>414.05</v>
+        <v>414</v>
       </c>
       <c r="AI157" s="4" t="n">
         <v>410.5</v>
@@ -22562,19 +22562,19 @@
         <v>393.3</v>
       </c>
       <c r="AM157" s="4" t="n">
-        <v>-7.82</v>
+        <v>-4.19</v>
       </c>
       <c r="AN157" s="4" t="n">
         <v>447.12</v>
       </c>
       <c r="AO157" s="4" t="n">
-        <v>4.8</v>
+        <v>8.92</v>
       </c>
       <c r="AP157" s="4" t="n">
         <v>478.4184</v>
       </c>
       <c r="AQ157" s="4" t="n">
-        <v>12.13</v>
+        <v>16.55</v>
       </c>
       <c r="AR157" s="4" t="n">
         <v>417.6</v>
@@ -22583,10 +22583,10 @@
         <v>-0.85</v>
       </c>
       <c r="AT157" s="4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="AU157" s="4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AV157" s="4" t="n">
         <v>-0.11</v>
@@ -22606,11 +22606,11 @@
         <v>5</v>
       </c>
       <c r="BA157" s="4" t="n">
-        <v>4.8</v>
+        <v>8.92</v>
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22734,7 @@
         <v>368.98</v>
       </c>
       <c r="AI158" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ158" s="4" t="n">
         <v>365.29</v>
@@ -22746,30 +22746,34 @@
         <v>346.84</v>
       </c>
       <c r="AM158" s="4" t="n">
-        <v>-6</v>
+        <v>-10.84</v>
       </c>
       <c r="AN158" s="4" t="n">
         <v>413.26</v>
       </c>
       <c r="AO158" s="4" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="AP158" s="4" t="n">
         <v>457.54</v>
       </c>
       <c r="AQ158" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR158" s="4" t="inlineStr"/>
-      <c r="AS158" s="4" t="inlineStr"/>
+        <v>17.62</v>
+      </c>
+      <c r="AR158" s="4" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AS158" s="4" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT158" s="4" t="n">
-        <v>0</v>
+        <v>-5.15</v>
       </c>
       <c r="AU158" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV158" s="4" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AW158" s="4" t="inlineStr">
         <is>
@@ -22786,11 +22790,11 @@
         <v>3</v>
       </c>
       <c r="BA158" s="4" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -22874,13 +22878,11 @@
       <c r="U159" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V159" s="4" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="V159" s="4" t="inlineStr"/>
       <c r="W159" s="4" t="inlineStr"/>
       <c r="X159" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="Y159" s="4" t="inlineStr"/>
@@ -22916,42 +22918,46 @@
         <v>358.56</v>
       </c>
       <c r="AI159" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ159" s="4" t="n">
-        <v>354.97</v>
+        <v>365.04</v>
       </c>
       <c r="AK159" s="4" t="n">
-        <v>362.15</v>
+        <v>372.42</v>
       </c>
       <c r="AL159" s="4" t="n">
-        <v>340.63</v>
+        <v>350.29</v>
       </c>
       <c r="AM159" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN159" s="4" t="n">
-        <v>387.24</v>
+        <v>398.23</v>
       </c>
       <c r="AO159" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP159" s="4" t="n">
-        <v>412.34</v>
+        <v>424.04</v>
       </c>
       <c r="AQ159" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR159" s="4" t="inlineStr"/>
-      <c r="AS159" s="4" t="inlineStr"/>
+      <c r="AR159" s="4" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AS159" s="4" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="AT159" s="4" t="n">
-        <v>-0</v>
+        <v>-2.76</v>
       </c>
       <c r="AU159" s="4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AV159" s="4" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="AW159" s="4" t="inlineStr">
         <is>
@@ -22970,7 +22976,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23021,7 +23027,7 @@
         </is>
       </c>
       <c r="J160" s="4" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="K160" s="4" t="n">
         <v>3</v>
@@ -23100,42 +23106,46 @@
         <v>202.81</v>
       </c>
       <c r="AI160" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ160" s="4" t="n">
-        <v>200.78</v>
+        <v>188.11</v>
       </c>
       <c r="AK160" s="4" t="n">
-        <v>204.84</v>
+        <v>191.91</v>
       </c>
       <c r="AL160" s="4" t="n">
-        <v>192.67</v>
+        <v>180.51</v>
       </c>
       <c r="AM160" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN160" s="4" t="n">
-        <v>219.03</v>
+        <v>205.21</v>
       </c>
       <c r="AO160" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP160" s="4" t="n">
-        <v>233.23</v>
+        <v>218.51</v>
       </c>
       <c r="AQ160" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR160" s="4" t="inlineStr"/>
-      <c r="AS160" s="4" t="inlineStr"/>
+      <c r="AR160" s="4" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AS160" s="4" t="n">
+        <v>3.43</v>
+      </c>
       <c r="AT160" s="4" t="n">
-        <v>-0</v>
+        <v>6.74</v>
       </c>
       <c r="AU160" s="4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV160" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW160" s="4" t="inlineStr">
         <is>
@@ -23154,7 +23164,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23215,7 @@
         </is>
       </c>
       <c r="J161" s="4" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="K161" s="4" t="n">
         <v>4</v>
@@ -23284,39 +23294,43 @@
         <v>341.1</v>
       </c>
       <c r="AI161" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ161" s="4" t="n">
-        <v>337.69</v>
+        <v>341.26</v>
       </c>
       <c r="AK161" s="4" t="n">
-        <v>344.51</v>
+        <v>348.16</v>
       </c>
       <c r="AL161" s="4" t="n">
-        <v>324.05</v>
+        <v>327.47</v>
       </c>
       <c r="AM161" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN161" s="4" t="n">
-        <v>368.39</v>
+        <v>372.29</v>
       </c>
       <c r="AO161" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP161" s="4" t="n">
-        <v>392.26</v>
+        <v>396.42</v>
       </c>
       <c r="AQ161" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR161" s="4" t="inlineStr"/>
-      <c r="AS161" s="4" t="inlineStr"/>
+      <c r="AR161" s="4" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AS161" s="4" t="n">
+        <v>0.48</v>
+      </c>
       <c r="AT161" s="4" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="AU161" s="4" t="n">
-        <v>3.13</v>
+        <v>2.05</v>
       </c>
       <c r="AV161" s="4" t="n">
         <v>0</v>
@@ -23338,7 +23352,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23403,7 @@
         </is>
       </c>
       <c r="J162" s="4" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="K162" s="4" t="n">
         <v>5</v>
@@ -23428,9 +23442,7 @@
       <c r="U162" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="V162" s="4" t="n">
-        <v>0.127</v>
-      </c>
+      <c r="V162" s="4" t="inlineStr"/>
       <c r="W162" s="4" t="inlineStr"/>
       <c r="X162" s="4" t="inlineStr">
         <is>
@@ -23470,39 +23482,43 @@
         <v>225.02</v>
       </c>
       <c r="AI162" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ162" s="4" t="n">
-        <v>222.77</v>
+        <v>238.71</v>
       </c>
       <c r="AK162" s="4" t="n">
-        <v>227.27</v>
+        <v>243.53</v>
       </c>
       <c r="AL162" s="4" t="n">
-        <v>213.77</v>
+        <v>229.06</v>
       </c>
       <c r="AM162" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN162" s="4" t="n">
-        <v>243.02</v>
+        <v>260.41</v>
       </c>
       <c r="AO162" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP162" s="4" t="n">
-        <v>258.77</v>
+        <v>277.29</v>
       </c>
       <c r="AQ162" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR162" s="4" t="inlineStr"/>
-      <c r="AS162" s="4" t="inlineStr"/>
+      <c r="AR162" s="4" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AS162" s="4" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="AT162" s="4" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="AU162" s="4" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="AV162" s="4" t="n">
         <v>0</v>
@@ -23524,7 +23540,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23575,7 +23591,7 @@
         </is>
       </c>
       <c r="J163" s="4" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K163" s="4" t="n">
         <v>6</v>
@@ -23654,42 +23670,46 @@
         <v>1065.22</v>
       </c>
       <c r="AI163" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ163" s="4" t="n">
-        <v>1054.57</v>
+        <v>970.9400000000001</v>
       </c>
       <c r="AK163" s="4" t="n">
-        <v>1075.87</v>
+        <v>990.5599999999999</v>
       </c>
       <c r="AL163" s="4" t="n">
-        <v>1011.96</v>
+        <v>931.71</v>
       </c>
       <c r="AM163" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN163" s="4" t="n">
-        <v>1150.44</v>
+        <v>1059.21</v>
       </c>
       <c r="AO163" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP163" s="4" t="n">
-        <v>1225</v>
+        <v>1127.86</v>
       </c>
       <c r="AQ163" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR163" s="4" t="inlineStr"/>
-      <c r="AS163" s="4" t="inlineStr"/>
+      <c r="AR163" s="4" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AS163" s="4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AT163" s="4" t="n">
-        <v>-0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AU163" s="4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV163" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW163" s="4" t="inlineStr">
         <is>
@@ -23708,7 +23728,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23759,7 +23779,7 @@
         </is>
       </c>
       <c r="J164" s="4" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="K164" s="4" t="n">
         <v>7</v>
@@ -23798,9 +23818,7 @@
       <c r="U164" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V164" s="4" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="V164" s="4" t="inlineStr"/>
       <c r="W164" s="4" t="inlineStr"/>
       <c r="X164" s="4" t="inlineStr">
         <is>
@@ -23840,42 +23858,46 @@
         <v>333.74</v>
       </c>
       <c r="AI164" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ164" s="4" t="n">
-        <v>330.4</v>
+        <v>334.81</v>
       </c>
       <c r="AK164" s="4" t="n">
-        <v>337.08</v>
+        <v>341.57</v>
       </c>
       <c r="AL164" s="4" t="n">
-        <v>317.05</v>
+        <v>321.28</v>
       </c>
       <c r="AM164" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN164" s="4" t="n">
-        <v>360.44</v>
+        <v>365.25</v>
       </c>
       <c r="AO164" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP164" s="4" t="n">
-        <v>383.8</v>
+        <v>388.92</v>
       </c>
       <c r="AQ164" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR164" s="4" t="inlineStr"/>
-      <c r="AS164" s="4" t="inlineStr"/>
+      <c r="AR164" s="4" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AS164" s="4" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AT164" s="4" t="n">
-        <v>-0</v>
+        <v>-1.32</v>
       </c>
       <c r="AU164" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV164" s="4" t="n">
-        <v>-7.44</v>
+        <v>-8.66</v>
       </c>
       <c r="AW164" s="4" t="inlineStr">
         <is>
@@ -23894,7 +23916,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23967,7 @@
         </is>
       </c>
       <c r="J165" s="4" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="K165" s="4" t="n">
         <v>8</v>
@@ -23984,9 +24006,7 @@
       <c r="U165" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V165" s="4" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="V165" s="4" t="inlineStr"/>
       <c r="W165" s="4" t="inlineStr"/>
       <c r="X165" s="4" t="inlineStr">
         <is>
@@ -24026,39 +24046,43 @@
         <v>393.82</v>
       </c>
       <c r="AI165" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ165" s="4" t="n">
-        <v>389.88</v>
+        <v>446.59</v>
       </c>
       <c r="AK165" s="4" t="n">
-        <v>397.76</v>
+        <v>455.61</v>
       </c>
       <c r="AL165" s="4" t="n">
-        <v>374.13</v>
+        <v>428.55</v>
       </c>
       <c r="AM165" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN165" s="4" t="n">
-        <v>425.33</v>
+        <v>487.19</v>
       </c>
       <c r="AO165" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP165" s="4" t="n">
-        <v>452.89</v>
+        <v>518.76</v>
       </c>
       <c r="AQ165" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR165" s="4" t="inlineStr"/>
-      <c r="AS165" s="4" t="inlineStr"/>
+      <c r="AR165" s="4" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AS165" s="4" t="n">
+        <v>-1.09</v>
+      </c>
       <c r="AT165" s="4" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="AU165" s="4" t="n">
-        <v>18</v>
+        <v>3.02</v>
       </c>
       <c r="AV165" s="4" t="n">
         <v>0</v>
@@ -24080,7 +24104,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -24131,7 +24155,7 @@
         </is>
       </c>
       <c r="J166" s="4" t="n">
-        <v>0</v>
+        <v>-8.44</v>
       </c>
       <c r="K166" s="4" t="n">
         <v>9</v>
@@ -24170,9 +24194,7 @@
       <c r="U166" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="V166" s="4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="V166" s="4" t="inlineStr"/>
       <c r="W166" s="4" t="inlineStr"/>
       <c r="X166" s="4" t="inlineStr">
         <is>
@@ -24212,42 +24234,46 @@
         <v>81.56</v>
       </c>
       <c r="AI166" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ166" s="4" t="n">
-        <v>80.73999999999999</v>
+        <v>88.19</v>
       </c>
       <c r="AK166" s="4" t="n">
-        <v>82.38</v>
+        <v>89.97</v>
       </c>
       <c r="AL166" s="4" t="n">
-        <v>77.48</v>
+        <v>84.63</v>
       </c>
       <c r="AM166" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN166" s="4" t="n">
-        <v>88.08</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="AO166" s="4" t="n">
-        <v>7.99</v>
+        <v>8</v>
       </c>
       <c r="AP166" s="4" t="n">
-        <v>93.79000000000001</v>
+        <v>102.44</v>
       </c>
       <c r="AQ166" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR166" s="4" t="inlineStr"/>
-      <c r="AS166" s="4" t="inlineStr"/>
+      <c r="AR166" s="4" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AS166" s="4" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AT166" s="4" t="n">
-        <v>-0</v>
+        <v>-8.44</v>
       </c>
       <c r="AU166" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV166" s="4" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AW166" s="4" t="inlineStr">
         <is>
@@ -24266,7 +24292,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -24317,7 +24343,7 @@
         </is>
       </c>
       <c r="J167" s="4" t="n">
-        <v>0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="K167" s="4" t="n">
         <v>10</v>
@@ -24396,39 +24422,43 @@
         <v>159.84</v>
       </c>
       <c r="AI167" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ167" s="4" t="n">
-        <v>158.24</v>
+        <v>174.31</v>
       </c>
       <c r="AK167" s="4" t="n">
-        <v>161.44</v>
+        <v>177.83</v>
       </c>
       <c r="AL167" s="4" t="n">
-        <v>151.85</v>
+        <v>167.27</v>
       </c>
       <c r="AM167" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN167" s="4" t="n">
-        <v>172.63</v>
+        <v>190.16</v>
       </c>
       <c r="AO167" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP167" s="4" t="n">
-        <v>183.82</v>
+        <v>202.48</v>
       </c>
       <c r="AQ167" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR167" s="4" t="inlineStr"/>
-      <c r="AS167" s="4" t="inlineStr"/>
+      <c r="AR167" s="4" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AS167" s="4" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AT167" s="4" t="n">
-        <v>-0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AU167" s="4" t="n">
-        <v>10.29</v>
+        <v>0.12</v>
       </c>
       <c r="AV167" s="4" t="n">
         <v>0</v>
@@ -24450,7 +24480,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24531,7 @@
         </is>
       </c>
       <c r="J168" s="4" t="n">
-        <v>0</v>
+        <v>16.07</v>
       </c>
       <c r="K168" s="4" t="n">
         <v>11</v>
@@ -24580,42 +24610,46 @@
         <v>95.04000000000001</v>
       </c>
       <c r="AI168" s="4" t="n">
-        <v>95.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="AJ168" s="4" t="n">
-        <v>94.09</v>
+        <v>81.06</v>
       </c>
       <c r="AK168" s="4" t="n">
-        <v>95.98999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="AL168" s="4" t="n">
-        <v>90.29000000000001</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="AM168" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN168" s="4" t="n">
-        <v>102.64</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="AO168" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP168" s="4" t="n">
-        <v>109.3</v>
+        <v>94.16</v>
       </c>
       <c r="AQ168" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR168" s="4" t="inlineStr"/>
-      <c r="AS168" s="4" t="inlineStr"/>
+      <c r="AR168" s="4" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="AS168" s="4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AT168" s="4" t="n">
-        <v>0</v>
+        <v>16.07</v>
       </c>
       <c r="AU168" s="4" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AV168" s="4" t="n">
-        <v>-5.09</v>
+        <v>0</v>
       </c>
       <c r="AW168" s="4" t="inlineStr">
         <is>
@@ -24634,7 +24668,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24719,7 @@
         </is>
       </c>
       <c r="J169" s="4" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="K169" s="4" t="n">
         <v>12</v>
@@ -24724,9 +24758,7 @@
       <c r="U169" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="V169" s="4" t="n">
-        <v>0.122</v>
-      </c>
+      <c r="V169" s="4" t="inlineStr"/>
       <c r="W169" s="4" t="inlineStr"/>
       <c r="X169" s="4" t="inlineStr">
         <is>
@@ -24766,42 +24798,46 @@
         <v>214.03</v>
       </c>
       <c r="AI169" s="4" t="n">
-        <v>214.03</v>
+        <v>220.9</v>
       </c>
       <c r="AJ169" s="4" t="n">
-        <v>211.89</v>
+        <v>218.69</v>
       </c>
       <c r="AK169" s="4" t="n">
-        <v>216.17</v>
+        <v>223.11</v>
       </c>
       <c r="AL169" s="4" t="n">
-        <v>203.33</v>
+        <v>209.85</v>
       </c>
       <c r="AM169" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN169" s="4" t="n">
-        <v>231.15</v>
+        <v>238.57</v>
       </c>
       <c r="AO169" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP169" s="4" t="n">
-        <v>246.13</v>
+        <v>254.03</v>
       </c>
       <c r="AQ169" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR169" s="4" t="inlineStr"/>
-      <c r="AS169" s="4" t="inlineStr"/>
+      <c r="AR169" s="4" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="AS169" s="4" t="n">
+        <v>1.28</v>
+      </c>
       <c r="AT169" s="4" t="n">
-        <v>-0</v>
+        <v>-3.11</v>
       </c>
       <c r="AU169" s="4" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="AV169" s="4" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="AW169" s="4" t="inlineStr">
         <is>
@@ -24820,7 +24856,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -24871,7 +24907,7 @@
         </is>
       </c>
       <c r="J170" s="4" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K170" s="4" t="n">
         <v>13</v>
@@ -24911,7 +24947,7 @@
         <v>13</v>
       </c>
       <c r="V170" s="4" t="n">
-        <v>0.156</v>
+        <v>0.237</v>
       </c>
       <c r="W170" s="4" t="inlineStr"/>
       <c r="X170" s="4" t="inlineStr">
@@ -24952,42 +24988,46 @@
         <v>338.87</v>
       </c>
       <c r="AI170" s="4" t="n">
-        <v>338.87</v>
+        <v>338.27</v>
       </c>
       <c r="AJ170" s="4" t="n">
-        <v>335.48</v>
+        <v>334.89</v>
       </c>
       <c r="AK170" s="4" t="n">
-        <v>342.26</v>
+        <v>341.65</v>
       </c>
       <c r="AL170" s="4" t="n">
-        <v>321.93</v>
+        <v>321.36</v>
       </c>
       <c r="AM170" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN170" s="4" t="n">
-        <v>365.98</v>
+        <v>365.33</v>
       </c>
       <c r="AO170" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP170" s="4" t="n">
-        <v>389.7</v>
+        <v>389.01</v>
       </c>
       <c r="AQ170" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR170" s="4" t="inlineStr"/>
-      <c r="AS170" s="4" t="inlineStr"/>
+      <c r="AR170" s="4" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="AS170" s="4" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT170" s="4" t="n">
-        <v>-0</v>
+        <v>0.18</v>
       </c>
       <c r="AU170" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV170" s="4" t="n">
-        <v>-2.04</v>
+        <v>-1.87</v>
       </c>
       <c r="AW170" s="4" t="inlineStr">
         <is>
@@ -25006,7 +25046,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -25057,7 +25097,7 @@
         </is>
       </c>
       <c r="J171" s="4" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="K171" s="4" t="n">
         <v>14</v>
@@ -25096,9 +25136,7 @@
       <c r="U171" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="V171" s="4" t="n">
-        <v>0.193</v>
-      </c>
+      <c r="V171" s="4" t="inlineStr"/>
       <c r="W171" s="4" t="inlineStr"/>
       <c r="X171" s="4" t="inlineStr">
         <is>
@@ -25138,42 +25176,46 @@
         <v>97.67</v>
       </c>
       <c r="AI171" s="4" t="n">
-        <v>97.67</v>
+        <v>98.48</v>
       </c>
       <c r="AJ171" s="4" t="n">
-        <v>96.69</v>
+        <v>97.5</v>
       </c>
       <c r="AK171" s="4" t="n">
-        <v>98.65000000000001</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="AL171" s="4" t="n">
-        <v>92.79000000000001</v>
+        <v>93.56</v>
       </c>
       <c r="AM171" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN171" s="4" t="n">
-        <v>105.48</v>
+        <v>106.36</v>
       </c>
       <c r="AO171" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP171" s="4" t="n">
-        <v>112.32</v>
+        <v>113.25</v>
       </c>
       <c r="AQ171" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR171" s="4" t="inlineStr"/>
-      <c r="AS171" s="4" t="inlineStr"/>
+      <c r="AR171" s="4" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="AS171" s="4" t="n">
+        <v>3.65</v>
+      </c>
       <c r="AT171" s="4" t="n">
-        <v>-0</v>
+        <v>-0.82</v>
       </c>
       <c r="AU171" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV171" s="4" t="n">
-        <v>-1.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AW171" s="4" t="inlineStr">
         <is>
@@ -25192,7 +25234,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -25243,7 +25285,7 @@
         </is>
       </c>
       <c r="J172" s="4" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="K172" s="4" t="n">
         <v>15</v>
@@ -25282,9 +25324,7 @@
       <c r="U172" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="V172" s="4" t="n">
-        <v>0.192</v>
-      </c>
+      <c r="V172" s="4" t="inlineStr"/>
       <c r="W172" s="4" t="inlineStr"/>
       <c r="X172" s="4" t="inlineStr">
         <is>
@@ -25324,42 +25364,46 @@
         <v>267.71</v>
       </c>
       <c r="AI172" s="4" t="n">
-        <v>267.71</v>
+        <v>271.52</v>
       </c>
       <c r="AJ172" s="4" t="n">
-        <v>265.03</v>
+        <v>268.8</v>
       </c>
       <c r="AK172" s="4" t="n">
-        <v>270.39</v>
+        <v>274.24</v>
       </c>
       <c r="AL172" s="4" t="n">
-        <v>254.32</v>
+        <v>257.94</v>
       </c>
       <c r="AM172" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN172" s="4" t="n">
-        <v>289.13</v>
+        <v>293.24</v>
       </c>
       <c r="AO172" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP172" s="4" t="n">
-        <v>307.87</v>
+        <v>312.25</v>
       </c>
       <c r="AQ172" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="AR172" s="4" t="inlineStr"/>
-      <c r="AS172" s="4" t="inlineStr"/>
+      <c r="AR172" s="4" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="AS172" s="4" t="n">
+        <v>2.11</v>
+      </c>
       <c r="AT172" s="4" t="n">
-        <v>-0</v>
+        <v>-1.4</v>
       </c>
       <c r="AU172" s="4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AV172" s="4" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="AW172" s="4" t="inlineStr">
         <is>
@@ -25378,7 +25422,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -25476,10 +25520,10 @@
         </is>
       </c>
       <c r="AH173" s="4" t="n">
-        <v>358.56</v>
+        <v>368.54</v>
       </c>
       <c r="AI173" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ173" s="4" t="n">
         <v>351.39</v>
@@ -25507,13 +25551,13 @@
       </c>
       <c r="AR173" s="4" t="inlineStr"/>
       <c r="AT173" s="4" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AU173" s="4" t="n">
-        <v>2.11</v>
+        <v>0.23</v>
       </c>
       <c r="AV173" s="4" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="AW173" s="4" t="inlineStr">
         <is>
@@ -25628,10 +25672,10 @@
         </is>
       </c>
       <c r="AH174" s="4" t="n">
-        <v>368.98</v>
+        <v>382.45</v>
       </c>
       <c r="AI174" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ174" s="4" t="n">
         <v>365.29</v>
@@ -25659,13 +25703,13 @@
       </c>
       <c r="AR174" s="4" t="inlineStr"/>
       <c r="AT174" s="4" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
       <c r="AU174" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV174" s="4" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="AW174" s="4" t="inlineStr">
         <is>
@@ -25780,10 +25824,10 @@
         </is>
       </c>
       <c r="AH175" s="4" t="n">
-        <v>202.81</v>
+        <v>219.22</v>
       </c>
       <c r="AI175" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ175" s="4" t="n">
         <v>198.75</v>
@@ -25811,13 +25855,13 @@
       </c>
       <c r="AR175" s="4" t="inlineStr"/>
       <c r="AT175" s="4" t="n">
-        <v>-0</v>
+        <v>15.37</v>
       </c>
       <c r="AU175" s="4" t="n">
-        <v>0</v>
+        <v>15.37</v>
       </c>
       <c r="AV175" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW175" s="4" t="inlineStr">
         <is>
@@ -25935,10 +25979,10 @@
         </is>
       </c>
       <c r="AH176" s="4" t="n">
-        <v>393.82</v>
+        <v>487.46</v>
       </c>
       <c r="AI176" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ176" s="4" t="n">
         <v>385.94</v>
@@ -25966,10 +26010,10 @@
       </c>
       <c r="AR176" s="4" t="inlineStr"/>
       <c r="AT176" s="4" t="n">
-        <v>0</v>
+        <v>8.06</v>
       </c>
       <c r="AU176" s="4" t="n">
-        <v>18</v>
+        <v>9.25</v>
       </c>
       <c r="AV176" s="4" t="n">
         <v>0</v>
@@ -26090,10 +26134,10 @@
         </is>
       </c>
       <c r="AH177" s="4" t="n">
-        <v>81.56</v>
+        <v>86.83</v>
       </c>
       <c r="AI177" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ177" s="4" t="n">
         <v>79.93000000000001</v>
@@ -26121,13 +26165,13 @@
       </c>
       <c r="AR177" s="4" t="inlineStr"/>
       <c r="AT177" s="4" t="n">
-        <v>-0</v>
+        <v>-2.53</v>
       </c>
       <c r="AU177" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV177" s="4" t="n">
-        <v>0</v>
+        <v>-2.83</v>
       </c>
       <c r="AW177" s="4" t="inlineStr">
         <is>
@@ -26245,10 +26289,10 @@
         </is>
       </c>
       <c r="AH178" s="4" t="n">
-        <v>225.02</v>
+        <v>248.12</v>
       </c>
       <c r="AI178" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ178" s="4" t="n">
         <v>220.52</v>
@@ -26276,10 +26320,10 @@
       </c>
       <c r="AR178" s="4" t="inlineStr"/>
       <c r="AT178" s="4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU178" s="4" t="n">
-        <v>8.01</v>
+        <v>3.18</v>
       </c>
       <c r="AV178" s="4" t="n">
         <v>0</v>
@@ -26400,10 +26444,10 @@
         </is>
       </c>
       <c r="AH179" s="4" t="n">
-        <v>333.74</v>
+        <v>311</v>
       </c>
       <c r="AI179" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ179" s="4" t="n">
         <v>327.07</v>
@@ -26431,13 +26475,13 @@
       </c>
       <c r="AR179" s="4" t="inlineStr"/>
       <c r="AT179" s="4" t="n">
-        <v>-0</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="AU179" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV179" s="4" t="n">
-        <v>-7.44</v>
+        <v>-10.28</v>
       </c>
       <c r="AW179" s="4" t="inlineStr">
         <is>
@@ -26552,10 +26596,10 @@
         </is>
       </c>
       <c r="AH180" s="4" t="n">
-        <v>341.1</v>
+        <v>359.24</v>
       </c>
       <c r="AI180" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ180" s="4" t="n">
         <v>334.28</v>
@@ -26583,10 +26627,10 @@
       </c>
       <c r="AR180" s="4" t="inlineStr"/>
       <c r="AT180" s="4" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AU180" s="4" t="n">
-        <v>3.13</v>
+        <v>4.22</v>
       </c>
       <c r="AV180" s="4" t="n">
         <v>0</v>
@@ -26704,10 +26748,10 @@
         </is>
       </c>
       <c r="AH181" s="4" t="n">
-        <v>1065.22</v>
+        <v>1060.38</v>
       </c>
       <c r="AI181" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ181" s="4" t="n">
         <v>1043.92</v>
@@ -26735,13 +26779,13 @@
       </c>
       <c r="AR181" s="4" t="inlineStr"/>
       <c r="AT181" s="4" t="n">
-        <v>-0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AU181" s="4" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AV181" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW181" s="4" t="inlineStr">
         <is>
@@ -26856,10 +26900,10 @@
         </is>
       </c>
       <c r="AH182" s="4" t="n">
-        <v>159.84</v>
+        <v>182.08</v>
       </c>
       <c r="AI182" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ182" s="4" t="n">
         <v>156.64</v>
@@ -26887,10 +26931,10 @@
       </c>
       <c r="AR182" s="4" t="inlineStr"/>
       <c r="AT182" s="4" t="n">
-        <v>-0</v>
+        <v>3.41</v>
       </c>
       <c r="AU182" s="4" t="n">
-        <v>10.29</v>
+        <v>3.41</v>
       </c>
       <c r="AV182" s="4" t="n">
         <v>0</v>
@@ -26976,14 +27020,14 @@
       </c>
       <c r="Q183" s="4" t="inlineStr"/>
       <c r="R183" s="4" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="S183" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T183" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U183" s="4" t="inlineStr"/>
@@ -27060,7 +27104,7 @@
         <v>0.99</v>
       </c>
       <c r="AT183" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU183" s="4" t="inlineStr"/>
       <c r="AV183" s="4" t="inlineStr"/>
@@ -27083,7 +27127,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -27146,14 +27190,14 @@
       </c>
       <c r="Q184" s="4" t="inlineStr"/>
       <c r="R184" s="4" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T184" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U184" s="4" t="inlineStr"/>
@@ -27251,7 +27295,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27484,7 @@
         </is>
       </c>
       <c r="J186" s="4" t="n">
-        <v>-3.34</v>
+        <v>0.65</v>
       </c>
       <c r="K186" s="4" t="n">
         <v>7</v>
@@ -27462,14 +27506,14 @@
       </c>
       <c r="Q186" s="4" t="inlineStr"/>
       <c r="R186" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S186" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T186" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U186" s="4" t="inlineStr"/>
@@ -27516,25 +27560,25 @@
         <v>441.05</v>
       </c>
       <c r="AJ186" s="4" t="n">
-        <v>454.66</v>
+        <v>436.64</v>
       </c>
       <c r="AK186" s="4" t="n">
-        <v>463.84</v>
+        <v>445.46</v>
       </c>
       <c r="AL186" s="4" t="n">
-        <v>436.29</v>
+        <v>419</v>
       </c>
       <c r="AM186" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN186" s="4" t="n">
-        <v>495.99</v>
+        <v>476.33</v>
       </c>
       <c r="AO186" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP186" s="4" t="n">
-        <v>528.14</v>
+        <v>507.21</v>
       </c>
       <c r="AQ186" s="4" t="n">
         <v>15</v>
@@ -27549,10 +27593,10 @@
         <v>0.65</v>
       </c>
       <c r="AU186" s="4" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AV186" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW186" s="4" t="inlineStr">
         <is>
@@ -27571,7 +27615,7 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -27622,7 +27666,7 @@
         </is>
       </c>
       <c r="J187" s="4" t="n">
-        <v>6.82</v>
+        <v>5.81</v>
       </c>
       <c r="K187" s="4" t="n">
         <v>9</v>
@@ -27648,14 +27692,14 @@
       </c>
       <c r="Q187" s="4" t="inlineStr"/>
       <c r="R187" s="4" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="S187" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T187" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U187" s="4" t="inlineStr"/>
@@ -27702,25 +27746,25 @@
         <v>263.5</v>
       </c>
       <c r="AJ187" s="4" t="n">
-        <v>258.39</v>
+        <v>260.87</v>
       </c>
       <c r="AK187" s="4" t="n">
-        <v>263.61</v>
+        <v>266.13</v>
       </c>
       <c r="AL187" s="4" t="n">
-        <v>247.95</v>
+        <v>250.32</v>
       </c>
       <c r="AM187" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN187" s="4" t="n">
-        <v>281.88</v>
+        <v>284.58</v>
       </c>
       <c r="AO187" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP187" s="4" t="n">
-        <v>300.15</v>
+        <v>303.02</v>
       </c>
       <c r="AQ187" s="4" t="n">
         <v>15</v>
@@ -27735,7 +27779,7 @@
         <v>5.81</v>
       </c>
       <c r="AU187" s="4" t="n">
-        <v>5.81</v>
+        <v>0.38</v>
       </c>
       <c r="AV187" s="4" t="n">
         <v>0</v>
@@ -27757,7 +27801,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27848,7 @@
         </is>
       </c>
       <c r="J188" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K188" s="4" t="n">
         <v>10</v>
@@ -27826,14 +27870,14 @@
       </c>
       <c r="Q188" s="4" t="inlineStr"/>
       <c r="R188" s="4" t="n">
-        <v>37.9</v>
+        <v>39.9</v>
       </c>
       <c r="S188" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T188" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U188" s="4" t="inlineStr"/>
@@ -27910,7 +27954,7 @@
         <v>0.89</v>
       </c>
       <c r="AT188" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU188" s="4" t="inlineStr"/>
       <c r="AV188" s="4" t="inlineStr"/>
@@ -27931,7 +27975,7 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -27982,7 +28026,7 @@
         </is>
       </c>
       <c r="J189" s="4" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="K189" s="4" t="n">
         <v>11</v>
@@ -28008,14 +28052,14 @@
       </c>
       <c r="Q189" s="4" t="inlineStr"/>
       <c r="R189" s="4" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="S189" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T189" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U189" s="4" t="inlineStr"/>
@@ -28062,25 +28106,25 @@
         <v>7388.5</v>
       </c>
       <c r="AJ189" s="4" t="n">
-        <v>7265.11</v>
+        <v>7314.61</v>
       </c>
       <c r="AK189" s="4" t="n">
-        <v>7411.89</v>
+        <v>7462.39</v>
       </c>
       <c r="AL189" s="4" t="n">
-        <v>6971.57</v>
+        <v>7019.07</v>
       </c>
       <c r="AM189" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN189" s="4" t="n">
-        <v>7925.58</v>
+        <v>7979.58</v>
       </c>
       <c r="AO189" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP189" s="4" t="n">
-        <v>8439.27</v>
+        <v>8496.77</v>
       </c>
       <c r="AQ189" s="4" t="n">
         <v>15</v>
@@ -28095,7 +28139,7 @@
         <v>1.94</v>
       </c>
       <c r="AU189" s="4" t="n">
-        <v>1.94</v>
+        <v>0.31</v>
       </c>
       <c r="AV189" s="4" t="n">
         <v>0</v>
@@ -28117,7 +28161,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -28336,14 +28380,14 @@
       </c>
       <c r="Q191" s="4" t="inlineStr"/>
       <c r="R191" s="4" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="S191" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T191" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U191" s="4" t="inlineStr"/>
@@ -28441,7 +28485,7 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -28488,7 +28532,7 @@
         </is>
       </c>
       <c r="J192" s="4" t="n">
-        <v>-0.16</v>
+        <v>-0.63</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>15</v>
@@ -28510,14 +28554,14 @@
       </c>
       <c r="Q192" s="4" t="inlineStr"/>
       <c r="R192" s="4" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="S192" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T192" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U192" s="4" t="inlineStr"/>
@@ -28564,25 +28608,25 @@
         <v>1305</v>
       </c>
       <c r="AJ192" s="4" t="n">
-        <v>1285.91</v>
+        <v>1291.95</v>
       </c>
       <c r="AK192" s="4" t="n">
-        <v>1311.89</v>
+        <v>1318.05</v>
       </c>
       <c r="AL192" s="4" t="n">
-        <v>1233.95</v>
+        <v>1239.75</v>
       </c>
       <c r="AM192" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN192" s="4" t="n">
-        <v>1402.81</v>
+        <v>1409.4</v>
       </c>
       <c r="AO192" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP192" s="4" t="n">
-        <v>1493.73</v>
+        <v>1500.75</v>
       </c>
       <c r="AQ192" s="4" t="n">
         <v>15</v>
@@ -28597,10 +28641,10 @@
         <v>-0.63</v>
       </c>
       <c r="AU192" s="4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV192" s="4" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="AW192" s="4" t="inlineStr">
         <is>
@@ -28619,7 +28663,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -28813,14 +28857,14 @@
       </c>
       <c r="Q194" s="4" t="inlineStr"/>
       <c r="R194" s="4" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="S194" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T194" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U194" s="4" t="inlineStr"/>
@@ -28918,7 +28962,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -28965,7 +29009,7 @@
         </is>
       </c>
       <c r="J195" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K195" s="4" t="n">
         <v>13</v>
@@ -28987,14 +29031,14 @@
       </c>
       <c r="Q195" s="4" t="inlineStr"/>
       <c r="R195" s="4" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="S195" s="4" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="T195" s="4" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="U195" s="4" t="inlineStr"/>
@@ -29071,7 +29115,7 @@
         <v>-2.24</v>
       </c>
       <c r="AT195" s="4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU195" s="4" t="inlineStr"/>
       <c r="AV195" s="4" t="inlineStr"/>
@@ -29092,7 +29136,7 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -29204,19 +29248,19 @@
         <v>271.51</v>
       </c>
       <c r="AM196" s="4" t="n">
-        <v>-3.36</v>
+        <v>-5.46</v>
       </c>
       <c r="AN196" s="4" t="n">
         <v>287</v>
       </c>
       <c r="AO196" s="4" t="n">
-        <v>2.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AP196" s="4" t="n">
         <v>307.09</v>
       </c>
       <c r="AQ196" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>6.93</v>
       </c>
       <c r="AR196" s="4" t="n">
         <v>289</v>
@@ -29248,11 +29292,11 @@
         <v>5</v>
       </c>
       <c r="BA196" s="4" t="n">
-        <v>2.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -29334,9 +29378,7 @@
       <c r="U197" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V197" s="4" t="n">
-        <v>0.184</v>
-      </c>
+      <c r="V197" s="4" t="inlineStr"/>
       <c r="W197" s="4" t="inlineStr"/>
       <c r="X197" s="4" t="inlineStr">
         <is>
@@ -29374,7 +29416,7 @@
         <v>358.56</v>
       </c>
       <c r="AI197" s="4" t="n">
-        <v>358.56</v>
+        <v>368.73</v>
       </c>
       <c r="AJ197" s="4" t="n">
         <v>351.39</v>
@@ -29386,30 +29428,34 @@
         <v>340.632</v>
       </c>
       <c r="AM197" s="4" t="n">
-        <v>-5</v>
+        <v>-7.62</v>
       </c>
       <c r="AN197" s="4" t="n">
         <v>387.2448000000001</v>
       </c>
       <c r="AO197" s="4" t="n">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="AP197" s="4" t="n">
         <v>414.3519360000001</v>
       </c>
       <c r="AQ197" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR197" s="4" t="inlineStr"/>
-      <c r="AS197" s="4" t="inlineStr"/>
+        <v>12.37</v>
+      </c>
+      <c r="AR197" s="4" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AS197" s="4" t="n">
+        <v>-0.28</v>
+      </c>
       <c r="AT197" s="4" t="n">
-        <v>-0</v>
+        <v>-2.76</v>
       </c>
       <c r="AU197" s="4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AV197" s="4" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="AW197" s="4" t="inlineStr">
         <is>
@@ -29426,11 +29472,11 @@
         <v>5</v>
       </c>
       <c r="BA197" s="4" t="n">
-        <v>8</v>
+        <v>5.02</v>
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -29550,7 +29596,7 @@
         <v>368.98</v>
       </c>
       <c r="AI198" s="4" t="n">
-        <v>368.98</v>
+        <v>389.01</v>
       </c>
       <c r="AJ198" s="4" t="n">
         <v>365.29</v>
@@ -29562,30 +29608,34 @@
         <v>350.531</v>
       </c>
       <c r="AM198" s="4" t="n">
-        <v>-5</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="AN198" s="4" t="n">
         <v>413.26</v>
       </c>
       <c r="AO198" s="4" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="AP198" s="4" t="n">
         <v>442.1882</v>
       </c>
       <c r="AQ198" s="4" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="AR198" s="4" t="inlineStr"/>
-      <c r="AS198" s="4" t="inlineStr"/>
+        <v>13.67</v>
+      </c>
+      <c r="AR198" s="4" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AS198" s="4" t="n">
+        <v>1.41</v>
+      </c>
       <c r="AT198" s="4" t="n">
-        <v>0</v>
+        <v>-5.15</v>
       </c>
       <c r="AU198" s="4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AV198" s="4" t="n">
-        <v>0</v>
+        <v>-3.77</v>
       </c>
       <c r="AW198" s="4" t="inlineStr">
         <is>
@@ -29602,11 +29652,11 @@
         <v>5</v>
       </c>
       <c r="BA198" s="4" t="n">
-        <v>12</v>
+        <v>6.23</v>
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29776,7 @@
         <v>202.81</v>
       </c>
       <c r="AI199" s="4" t="n">
-        <v>202.81</v>
+        <v>190.01</v>
       </c>
       <c r="AJ199" s="4" t="n">
         <v>198.75</v>
@@ -29738,30 +29788,34 @@
         <v>192.6695</v>
       </c>
       <c r="AM199" s="4" t="n">
-        <v>-5</v>
+        <v>1.4</v>
       </c>
       <c r="AN199" s="4" t="n">
         <v>219.0348</v>
       </c>
       <c r="AO199" s="4" t="n">
-        <v>8</v>
+        <v>15.28</v>
       </c>
       <c r="AP199" s="4" t="n">
         <v>234.367236</v>
       </c>
       <c r="AQ199" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR199" s="4" t="inlineStr"/>
-      <c r="AS199" s="4" t="inlineStr"/>
+        <v>23.34</v>
+      </c>
+      <c r="AR199" s="4" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AS199" s="4" t="n">
+        <v>3.43</v>
+      </c>
       <c r="AT199" s="4" t="n">
-        <v>-0</v>
+        <v>6.74</v>
       </c>
       <c r="AU199" s="4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AV199" s="4" t="n">
-        <v>-1.02</v>
+        <v>0</v>
       </c>
       <c r="AW199" s="4" t="inlineStr">
         <is>
@@ -29778,11 +29832,11 @@
         <v>5</v>
       </c>
       <c r="BA199" s="4" t="n">
-        <v>8</v>
+        <v>15.28</v>
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -29864,9 +29918,7 @@
       <c r="U200" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="V200" s="4" t="n">
-        <v>0.15</v>
-      </c>
+      <c r="V200" s="4" t="inlineStr"/>
       <c r="W200" s="4" t="inlineStr"/>
       <c r="X200" s="4" t="inlineStr">
         <is>
@@ -29904,7 +29956,7 @@
         <v>393.82</v>
       </c>
       <c r="AI200" s="4" t="n">
-        <v>393.82</v>
+        <v>451.1</v>
       </c>
       <c r="AJ200" s="4" t="n">
         <v>385.94</v>
@@ -29916,27 +29968,31 @@
         <v>374.129</v>
       </c>
       <c r="AM200" s="4" t="n">
-        <v>-5</v>
+        <v>-17.06</v>
       </c>
       <c r="AN200" s="4" t="n">
         <v>425.3256</v>
       </c>
       <c r="AO200" s="4" t="n">
-        <v>8</v>
+        <v>-5.71</v>
       </c>
       <c r="AP200" s="4" t="n">
         <v>455.098392</v>
       </c>
       <c r="AQ200" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR200" s="4" t="inlineStr"/>
-      <c r="AS200" s="4" t="inlineStr"/>
+        <v>0.89</v>
+      </c>
+      <c r="AR200" s="4" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AS200" s="4" t="n">
+        <v>-1.09</v>
+      </c>
       <c r="AT200" s="4" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="AU200" s="4" t="n">
-        <v>18</v>
+        <v>3.02</v>
       </c>
       <c r="AV200" s="4" t="n">
         <v>0</v>
@@ -29956,11 +30012,11 @@
         <v>5</v>
       </c>
       <c r="BA200" s="4" t="n">
-        <v>8</v>
+        <v>-5.71</v>
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30042,9 +30098,7 @@
       <c r="U201" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="V201" s="4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
+      <c r="V201" s="4" t="inlineStr"/>
       <c r="W201" s="4" t="inlineStr"/>
       <c r="X201" s="4" t="inlineStr">
         <is>
@@ -30082,7 +30136,7 @@
         <v>81.56</v>
       </c>
       <c r="AI201" s="4" t="n">
-        <v>81.56</v>
+        <v>89.08</v>
       </c>
       <c r="AJ201" s="4" t="n">
         <v>79.93000000000001</v>
@@ -30094,30 +30148,34 @@
         <v>77.482</v>
       </c>
       <c r="AM201" s="4" t="n">
-        <v>-5</v>
+        <v>-13.02</v>
       </c>
       <c r="AN201" s="4" t="n">
         <v>88.0848</v>
       </c>
       <c r="AO201" s="4" t="n">
-        <v>8</v>
+        <v>-1.12</v>
       </c>
       <c r="AP201" s="4" t="n">
         <v>94.250736</v>
       </c>
       <c r="AQ201" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR201" s="4" t="inlineStr"/>
-      <c r="AS201" s="4" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="AR201" s="4" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AS201" s="4" t="n">
+        <v>0.31</v>
+      </c>
       <c r="AT201" s="4" t="n">
-        <v>-0</v>
+        <v>-8.44</v>
       </c>
       <c r="AU201" s="4" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AV201" s="4" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AW201" s="4" t="inlineStr">
         <is>
@@ -30134,11 +30192,11 @@
         <v>5</v>
       </c>
       <c r="BA201" s="4" t="n">
-        <v>8</v>
+        <v>-1.12</v>
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30220,9 +30278,7 @@
       <c r="U202" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="V202" s="4" t="n">
-        <v>0.127</v>
-      </c>
+      <c r="V202" s="4" t="inlineStr"/>
       <c r="W202" s="4" t="inlineStr"/>
       <c r="X202" s="4" t="inlineStr">
         <is>
@@ -30260,7 +30316,7 @@
         <v>225.02</v>
       </c>
       <c r="AI202" s="4" t="n">
-        <v>225.02</v>
+        <v>241.12</v>
       </c>
       <c r="AJ202" s="4" t="n">
         <v>220.52</v>
@@ -30272,27 +30328,31 @@
         <v>213.769</v>
       </c>
       <c r="AM202" s="4" t="n">
-        <v>-5</v>
+        <v>-11.34</v>
       </c>
       <c r="AN202" s="4" t="n">
         <v>243.0216</v>
       </c>
       <c r="AO202" s="4" t="n">
-        <v>8</v>
+        <v>0.79</v>
       </c>
       <c r="AP202" s="4" t="n">
         <v>260.0331120000001</v>
       </c>
       <c r="AQ202" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR202" s="4" t="inlineStr"/>
-      <c r="AS202" s="4" t="inlineStr"/>
+        <v>7.84</v>
+      </c>
+      <c r="AR202" s="4" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AS202" s="4" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="AT202" s="4" t="n">
-        <v>0</v>
+        <v>-6.68</v>
       </c>
       <c r="AU202" s="4" t="n">
-        <v>8.01</v>
+        <v>0.8</v>
       </c>
       <c r="AV202" s="4" t="n">
         <v>0</v>
@@ -30312,11 +30372,11 @@
         <v>5</v>
       </c>
       <c r="BA202" s="4" t="n">
-        <v>8</v>
+        <v>0.79</v>
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30398,9 +30458,7 @@
       <c r="U203" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="V203" s="4" t="n">
-        <v>0.109</v>
-      </c>
+      <c r="V203" s="4" t="inlineStr"/>
       <c r="W203" s="4" t="inlineStr"/>
       <c r="X203" s="4" t="inlineStr">
         <is>
@@ -30438,7 +30496,7 @@
         <v>333.74</v>
       </c>
       <c r="AI203" s="4" t="n">
-        <v>333.74</v>
+        <v>338.19</v>
       </c>
       <c r="AJ203" s="4" t="n">
         <v>327.07</v>
@@ -30450,30 +30508,34 @@
         <v>317.053</v>
       </c>
       <c r="AM203" s="4" t="n">
-        <v>-5</v>
+        <v>-6.25</v>
       </c>
       <c r="AN203" s="4" t="n">
         <v>360.4392</v>
       </c>
       <c r="AO203" s="4" t="n">
-        <v>8</v>
+        <v>6.58</v>
       </c>
       <c r="AP203" s="4" t="n">
         <v>385.669944</v>
       </c>
       <c r="AQ203" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR203" s="4" t="inlineStr"/>
-      <c r="AS203" s="4" t="inlineStr"/>
+        <v>14.04</v>
+      </c>
+      <c r="AR203" s="4" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AS203" s="4" t="n">
+        <v>0.52</v>
+      </c>
       <c r="AT203" s="4" t="n">
-        <v>-0</v>
+        <v>-1.32</v>
       </c>
       <c r="AU203" s="4" t="n">
         <v>0</v>
       </c>
       <c r="AV203" s="4" t="n">
-        <v>-7.44</v>
+        <v>-8.66</v>
       </c>
       <c r="AW203" s="4" t="inlineStr">
         <is>
@@ -30490,11 +30552,11 @@
         <v>5</v>
       </c>
       <c r="BA203" s="4" t="n">
-        <v>8</v>
+        <v>6.58</v>
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30614,7 +30676,7 @@
         <v>341.1</v>
       </c>
       <c r="AI204" s="4" t="n">
-        <v>341.1</v>
+        <v>344.71</v>
       </c>
       <c r="AJ204" s="4" t="n">
         <v>334.28</v>
@@ -30626,27 +30688,31 @@
         <v>324.045</v>
       </c>
       <c r="AM204" s="4" t="n">
-        <v>-5</v>
+        <v>-5.99</v>
       </c>
       <c r="AN204" s="4" t="n">
         <v>368.388</v>
       </c>
       <c r="AO204" s="4" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="AP204" s="4" t="n">
         <v>394.1751600000001</v>
       </c>
       <c r="AQ204" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR204" s="4" t="inlineStr"/>
-      <c r="AS204" s="4" t="inlineStr"/>
+        <v>14.35</v>
+      </c>
+      <c r="AR204" s="4" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AS204" s="4" t="n">
+        <v>0.48</v>
+      </c>
       <c r="AT204" s="4" t="n">
-        <v>0</v>
+        <v>-1.05</v>
       </c>
       <c r="AU204" s="4" t="n">
-        <v>3.13</v>
+        <v>2.05</v>
       </c>
       <c r="AV204" s="4" t="n">
         <v>0</v>
@@ -30666,11 +30732,11 @@
         <v>5</v>
       </c>
       <c r="BA204" s="4" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30856,7 @@
         <v>1065.22</v>
       </c>
       <c r="AI205" s="4" t="n">
-        <v>1065.22</v>
+        <v>980.75</v>
       </c>
       <c r="AJ205" s="4" t="n">
         <v>1043.92</v>
@@ -30802,30 +30868,34 @@
         <v>1011.959</v>
       </c>
       <c r="AM205" s="4" t="n">
-        <v>-5</v>
+        <v>3.18</v>
       </c>
       <c r="AN205" s="4" t="n">
         <v>1150.4376</v>
       </c>
       <c r="AO205" s="4" t="n">
-        <v>8</v>
+        <v>17.3</v>
       </c>
       <c r="AP205" s="4" t="n">
         <v>1230.968232</v>
       </c>
       <c r="AQ205" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR205" s="4" t="inlineStr"/>
-      <c r="AS205" s="4" t="inlineStr"/>
+        <v>25.51</v>
+      </c>
+      <c r="AR205" s="4" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AS205" s="4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="AT205" s="4" t="n">
-        <v>-0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AU205" s="4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV205" s="4" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="AW205" s="4" t="inlineStr">
         <is>
@@ -30842,11 +30912,11 @@
         <v>5</v>
       </c>
       <c r="BA205" s="4" t="n">
-        <v>8</v>
+        <v>17.3</v>
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -30966,7 +31036,7 @@
         <v>159.84</v>
       </c>
       <c r="AI206" s="4" t="n">
-        <v>159.84</v>
+        <v>176.07</v>
       </c>
       <c r="AJ206" s="4" t="n">
         <v>156.64</v>
@@ -30978,27 +31048,31 @@
         <v>151.848</v>
       </c>
       <c r="AM206" s="4" t="n">
-        <v>-5</v>
+        <v>-13.76</v>
       </c>
       <c r="AN206" s="4" t="n">
         <v>172.6272</v>
       </c>
       <c r="AO206" s="4" t="n">
-        <v>8</v>
+        <v>-1.96</v>
       </c>
       <c r="AP206" s="4" t="n">
         <v>184.711104</v>
       </c>
       <c r="AQ206" s="4" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AR206" s="4" t="inlineStr"/>
-      <c r="AS206" s="4" t="inlineStr"/>
+        <v>4.91</v>
+      </c>
+      <c r="AR206" s="4" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AS206" s="4" t="n">
+        <v>0.35</v>
+      </c>
       <c r="AT206" s="4" t="n">
-        <v>-0</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AU206" s="4" t="n">
-        <v>10.29</v>
+        <v>0.12</v>
       </c>
       <c r="AV206" s="4" t="n">
         <v>0</v>
@@ -31018,11 +31092,11 @@
         <v>5</v>
       </c>
       <c r="BA206" s="4" t="n">
-        <v>8</v>
+        <v>-1.96</v>
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31090,7 +31164,7 @@
       <c r="W207" s="4" t="inlineStr"/>
       <c r="X207" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.8%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y207" s="4" t="inlineStr"/>
@@ -31121,31 +31195,31 @@
         </is>
       </c>
       <c r="AH207" s="4" t="n">
-        <v>2390.4</v>
+        <v>2447</v>
       </c>
       <c r="AI207" s="4" t="n">
         <v>2443.4</v>
       </c>
       <c r="AJ207" s="4" t="n">
-        <v>2352.44</v>
+        <v>2418.97</v>
       </c>
       <c r="AK207" s="4" t="n">
-        <v>2399.96</v>
+        <v>2467.83</v>
       </c>
       <c r="AL207" s="4" t="n">
-        <v>2257.39</v>
+        <v>2321.23</v>
       </c>
       <c r="AM207" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN207" s="4" t="n">
-        <v>2566.296</v>
+        <v>2638.872</v>
       </c>
       <c r="AO207" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP207" s="4" t="n">
-        <v>2732.63</v>
+        <v>2809.91</v>
       </c>
       <c r="AQ207" s="4" t="n">
         <v>15</v>
@@ -31157,13 +31231,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT207" s="4" t="n">
-        <v>-2.17</v>
+        <v>0.15</v>
       </c>
       <c r="AU207" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="AV207" s="4" t="n">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="AW207" s="4" t="inlineStr">
         <is>
@@ -31178,7 +31252,7 @@
       </c>
       <c r="BB207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31242,7 +31316,7 @@
       <c r="W208" s="4" t="inlineStr"/>
       <c r="X208" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.3%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y208" s="4" t="inlineStr"/>
@@ -31273,31 +31347,31 @@
         </is>
       </c>
       <c r="AH208" s="4" t="n">
-        <v>113.54</v>
+        <v>111.08</v>
       </c>
       <c r="AI208" s="4" t="n">
         <v>111.44</v>
       </c>
       <c r="AJ208" s="4" t="n">
-        <v>108.2</v>
+        <v>110.33</v>
       </c>
       <c r="AK208" s="4" t="n">
-        <v>110.38</v>
+        <v>112.55</v>
       </c>
       <c r="AL208" s="4" t="n">
-        <v>103.8255</v>
+        <v>105.868</v>
       </c>
       <c r="AM208" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN208" s="4" t="n">
-        <v>118.0332</v>
+        <v>120.3552</v>
       </c>
       <c r="AO208" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP208" s="4" t="n">
-        <v>125.6835</v>
+        <v>128.156</v>
       </c>
       <c r="AQ208" s="4" t="n">
         <v>15</v>
@@ -31309,10 +31383,10 @@
         <v>-0.39</v>
       </c>
       <c r="AT208" s="4" t="n">
-        <v>1.88</v>
+        <v>-0.32</v>
       </c>
       <c r="AU208" s="4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AV208" s="4" t="n">
         <v>-0.32</v>
@@ -31330,7 +31404,7 @@
       </c>
       <c r="BB208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31398,7 +31472,7 @@
       <c r="W209" s="4" t="inlineStr"/>
       <c r="X209" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.1%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y209" s="4" t="inlineStr"/>
@@ -31429,31 +31503,31 @@
         </is>
       </c>
       <c r="AH209" s="4" t="n">
-        <v>414.05</v>
+        <v>410.05</v>
       </c>
       <c r="AI209" s="4" t="n">
         <v>410.5</v>
       </c>
       <c r="AJ209" s="4" t="n">
-        <v>422.38</v>
+        <v>406.39</v>
       </c>
       <c r="AK209" s="4" t="n">
-        <v>430.92</v>
+        <v>414.61</v>
       </c>
       <c r="AL209" s="4" t="n">
-        <v>405.3174999999999</v>
+        <v>389.975</v>
       </c>
       <c r="AM209" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN209" s="4" t="n">
-        <v>460.782</v>
+        <v>443.34</v>
       </c>
       <c r="AO209" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP209" s="4" t="n">
-        <v>490.6474999999999</v>
+        <v>472.075</v>
       </c>
       <c r="AQ209" s="4" t="n">
         <v>15</v>
@@ -31465,10 +31539,10 @@
         <v>-0.85</v>
       </c>
       <c r="AT209" s="4" t="n">
-        <v>0.86</v>
+        <v>-0.11</v>
       </c>
       <c r="AU209" s="4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AV209" s="4" t="n">
         <v>-0.11</v>
@@ -31486,7 +31560,7 @@
       </c>
       <c r="BB209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31550,7 +31624,7 @@
       <c r="W210" s="4" t="inlineStr"/>
       <c r="X210" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.1%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y210" s="4" t="inlineStr"/>
@@ -31581,31 +31655,31 @@
         </is>
       </c>
       <c r="AH210" s="4" t="n">
-        <v>597.55</v>
+        <v>536.7</v>
       </c>
       <c r="AI210" s="4" t="n">
         <v>531.9</v>
       </c>
       <c r="AJ210" s="4" t="n">
-        <v>521.1900000000001</v>
+        <v>526.58</v>
       </c>
       <c r="AK210" s="4" t="n">
-        <v>531.71</v>
+        <v>537.22</v>
       </c>
       <c r="AL210" s="4" t="n">
-        <v>500.1275</v>
+        <v>505.3049999999999</v>
       </c>
       <c r="AM210" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN210" s="4" t="n">
-        <v>568.566</v>
+        <v>574.452</v>
       </c>
       <c r="AO210" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP210" s="4" t="n">
-        <v>605.4175</v>
+        <v>611.6849999999999</v>
       </c>
       <c r="AQ210" s="4" t="n">
         <v>15</v>
@@ -31617,10 +31691,10 @@
         <v>6.16</v>
       </c>
       <c r="AT210" s="4" t="n">
-        <v>12.34</v>
+        <v>0.9</v>
       </c>
       <c r="AU210" s="4" t="n">
-        <v>12.34</v>
+        <v>0.9</v>
       </c>
       <c r="AV210" s="4" t="n">
         <v>0</v>
@@ -31638,7 +31712,7 @@
       </c>
       <c r="BB210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31702,7 +31776,7 @@
       <c r="W211" s="4" t="inlineStr"/>
       <c r="X211" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.2%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y211" s="4" t="inlineStr"/>
@@ -31733,31 +31807,31 @@
         </is>
       </c>
       <c r="AH211" s="4" t="n">
-        <v>731</v>
+        <v>698.35</v>
       </c>
       <c r="AI211" s="4" t="n">
         <v>700</v>
       </c>
       <c r="AJ211" s="4" t="n">
-        <v>666.96</v>
+        <v>693</v>
       </c>
       <c r="AK211" s="4" t="n">
-        <v>680.4400000000001</v>
+        <v>707</v>
       </c>
       <c r="AL211" s="4" t="n">
-        <v>640.015</v>
+        <v>665</v>
       </c>
       <c r="AM211" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN211" s="4" t="n">
-        <v>727.5960000000001</v>
+        <v>756</v>
       </c>
       <c r="AO211" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP211" s="4" t="n">
-        <v>774.755</v>
+        <v>804.9999999999999</v>
       </c>
       <c r="AQ211" s="4" t="n">
         <v>15</v>
@@ -31769,13 +31843,13 @@
         <v>3.02</v>
       </c>
       <c r="AT211" s="4" t="n">
-        <v>4.43</v>
+        <v>-0.24</v>
       </c>
       <c r="AU211" s="4" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AV211" s="4" t="n">
-        <v>-0.91</v>
+        <v>-0.24</v>
       </c>
       <c r="AW211" s="4" t="inlineStr">
         <is>
@@ -31790,7 +31864,7 @@
       </c>
       <c r="BB211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -31906,7 +31980,7 @@
       <c r="BA212" s="4" t="inlineStr"/>
       <c r="BB212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32022,7 +32096,7 @@
       <c r="BA213" s="4" t="inlineStr"/>
       <c r="BB213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32146,7 +32220,7 @@
       <c r="BA214" s="4" t="inlineStr"/>
       <c r="BB214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32344,7 @@
       <c r="BA215" s="4" t="inlineStr"/>
       <c r="BB215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32338,7 +32412,7 @@
       <c r="W216" s="4" t="inlineStr"/>
       <c r="X216" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.8%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y216" s="4" t="inlineStr"/>
@@ -32369,31 +32443,31 @@
         </is>
       </c>
       <c r="AH216" s="4" t="n">
-        <v>2390.4</v>
+        <v>2447</v>
       </c>
       <c r="AI216" s="4" t="n">
         <v>2443.4</v>
       </c>
       <c r="AJ216" s="4" t="n">
-        <v>2352.44</v>
+        <v>2418.97</v>
       </c>
       <c r="AK216" s="4" t="n">
-        <v>2399.96</v>
+        <v>2467.83</v>
       </c>
       <c r="AL216" s="4" t="n">
-        <v>2257.39</v>
+        <v>2321.23</v>
       </c>
       <c r="AM216" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN216" s="4" t="n">
-        <v>2566.296</v>
+        <v>2638.872</v>
       </c>
       <c r="AO216" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP216" s="4" t="n">
-        <v>2732.63</v>
+        <v>2809.91</v>
       </c>
       <c r="AQ216" s="4" t="n">
         <v>15</v>
@@ -32405,13 +32479,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="AT216" s="4" t="n">
-        <v>-2.17</v>
+        <v>0.15</v>
       </c>
       <c r="AU216" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="AV216" s="4" t="n">
-        <v>-2.44</v>
+        <v>0</v>
       </c>
       <c r="AW216" s="4" t="inlineStr">
         <is>
@@ -32426,7 +32500,7 @@
       </c>
       <c r="BB216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32550,7 +32624,7 @@
       <c r="BA217" s="4" t="inlineStr"/>
       <c r="BB217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32674,7 +32748,7 @@
       <c r="BA218" s="4" t="inlineStr"/>
       <c r="BB218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32798,7 +32872,7 @@
       <c r="BA219" s="4" t="inlineStr"/>
       <c r="BB219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -32922,7 +32996,7 @@
       <c r="BA220" s="4" t="inlineStr"/>
       <c r="BB220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -33046,7 +33120,7 @@
       <c r="BA221" s="4" t="inlineStr"/>
       <c r="BB221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -33170,7 +33244,7 @@
       <c r="BA222" s="4" t="inlineStr"/>
       <c r="BB222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -33238,7 +33312,7 @@
       <c r="W223" s="4" t="inlineStr"/>
       <c r="X223" s="4" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.1%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="Y223" s="4" t="inlineStr"/>
@@ -33269,31 +33343,31 @@
         </is>
       </c>
       <c r="AH223" s="4" t="n">
-        <v>414.05</v>
+        <v>410.05</v>
       </c>
       <c r="AI223" s="4" t="n">
         <v>410.5</v>
       </c>
       <c r="AJ223" s="4" t="n">
-        <v>422.38</v>
+        <v>406.39</v>
       </c>
       <c r="AK223" s="4" t="n">
-        <v>430.92</v>
+        <v>414.61</v>
       </c>
       <c r="AL223" s="4" t="n">
-        <v>405.3174999999999</v>
+        <v>389.975</v>
       </c>
       <c r="AM223" s="4" t="n">
         <v>-5</v>
       </c>
       <c r="AN223" s="4" t="n">
-        <v>460.782</v>
+        <v>443.34</v>
       </c>
       <c r="AO223" s="4" t="n">
         <v>8</v>
       </c>
       <c r="AP223" s="4" t="n">
-        <v>490.6474999999999</v>
+        <v>472.075</v>
       </c>
       <c r="AQ223" s="4" t="n">
         <v>15</v>
@@ -33305,10 +33379,10 @@
         <v>-0.85</v>
       </c>
       <c r="AT223" s="4" t="n">
-        <v>0.86</v>
+        <v>-0.11</v>
       </c>
       <c r="AU223" s="4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AV223" s="4" t="n">
         <v>-0.11</v>
@@ -33326,7 +33400,7 @@
       </c>
       <c r="BB223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -33446,7 +33520,7 @@
       <c r="BA224" s="4" t="inlineStr"/>
       <c r="BB224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>
@@ -33570,7 +33644,7 @@
       <c r="BA225" s="4" t="inlineStr"/>
       <c r="BB225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:26</t>
+          <t>2026-08-06 12:10</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -18560,7 +18560,7 @@
       </c>
       <c r="BB132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="BB133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="BB136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -19412,7 +19412,7 @@
       </c>
       <c r="BB137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -20380,7 +20380,7 @@
       </c>
       <c r="BB143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="BB147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="BB148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="BB149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21490,7 +21490,7 @@
       </c>
       <c r="BB150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="BB151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21810,7 +21810,7 @@
       </c>
       <c r="BB152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -21970,7 +21970,7 @@
       </c>
       <c r="BB153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="BB154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="BB155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="BB156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="BB157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="BB158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -22976,7 +22976,7 @@
       </c>
       <c r="BB159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -23164,7 +23164,7 @@
       </c>
       <c r="BB160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="BB161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23540,7 @@
       </c>
       <c r="BB162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -23728,7 +23728,7 @@
       </c>
       <c r="BB163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -23916,7 +23916,7 @@
       </c>
       <c r="BB164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="BB165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -24292,7 +24292,7 @@
       </c>
       <c r="BB166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -24480,7 +24480,7 @@
       </c>
       <c r="BB167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="BB168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="BB169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="BB170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="BB171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -25422,7 +25422,7 @@
       </c>
       <c r="BB172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -27127,7 +27127,7 @@
       </c>
       <c r="BB183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -27295,7 +27295,7 @@
       </c>
       <c r="BB184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -27615,7 +27615,7 @@
       </c>
       <c r="BB186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="BB187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="BB188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="BB189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="BB191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -28663,7 +28663,7 @@
       </c>
       <c r="BB192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -28962,7 +28962,7 @@
       </c>
       <c r="BB194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -29136,7 +29136,7 @@
       </c>
       <c r="BB195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -29296,7 +29296,7 @@
       </c>
       <c r="BB196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -29476,7 +29476,7 @@
       </c>
       <c r="BB197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29656,7 @@
       </c>
       <c r="BB198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -29836,7 +29836,7 @@
       </c>
       <c r="BB199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="BB200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30196,7 +30196,7 @@
       </c>
       <c r="BB201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30376,7 +30376,7 @@
       </c>
       <c r="BB202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30556,7 +30556,7 @@
       </c>
       <c r="BB203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="BB204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -30916,7 +30916,7 @@
       </c>
       <c r="BB205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31096,7 +31096,7 @@
       </c>
       <c r="BB206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31252,7 +31252,7 @@
       </c>
       <c r="BB207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31404,7 +31404,7 @@
       </c>
       <c r="BB208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31560,7 +31560,7 @@
       </c>
       <c r="BB209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31712,7 +31712,7 @@
       </c>
       <c r="BB210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="BB211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -31980,7 +31980,7 @@
       <c r="BA212" s="4" t="inlineStr"/>
       <c r="BB212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32096,7 +32096,7 @@
       <c r="BA213" s="4" t="inlineStr"/>
       <c r="BB213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32220,7 +32220,7 @@
       <c r="BA214" s="4" t="inlineStr"/>
       <c r="BB214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32344,7 +32344,7 @@
       <c r="BA215" s="4" t="inlineStr"/>
       <c r="BB215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32500,7 +32500,7 @@
       </c>
       <c r="BB216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32624,7 +32624,7 @@
       <c r="BA217" s="4" t="inlineStr"/>
       <c r="BB217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32748,7 +32748,7 @@
       <c r="BA218" s="4" t="inlineStr"/>
       <c r="BB218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32872,7 +32872,7 @@
       <c r="BA219" s="4" t="inlineStr"/>
       <c r="BB219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -32996,7 +32996,7 @@
       <c r="BA220" s="4" t="inlineStr"/>
       <c r="BB220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -33120,7 +33120,7 @@
       <c r="BA221" s="4" t="inlineStr"/>
       <c r="BB221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -33244,7 +33244,7 @@
       <c r="BA222" s="4" t="inlineStr"/>
       <c r="BB222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -33400,7 +33400,7 @@
       </c>
       <c r="BB223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -33520,7 +33520,7 @@
       <c r="BA224" s="4" t="inlineStr"/>
       <c r="BB224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33644,7 @@
       <c r="BA225" s="4" t="inlineStr"/>
       <c r="BB225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 12:10</t>
+          <t>2026-08-06 12:21</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX225"/>
+  <dimension ref="A1:AX281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20871,7 +20871,7 @@
         <v>-0.2</v>
       </c>
       <c r="AP152" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ152" s="4" t="inlineStr"/>
       <c r="AR152" s="4" t="inlineStr"/>
@@ -25957,7 +25957,7 @@
         <v>0.99</v>
       </c>
       <c r="AP183" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ183" s="4" t="inlineStr"/>
       <c r="AR183" s="4" t="inlineStr"/>
@@ -26683,7 +26683,7 @@
         </is>
       </c>
       <c r="J188" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K188" s="4" t="n">
         <v>10</v>
@@ -26785,7 +26785,7 @@
         <v>0.89</v>
       </c>
       <c r="AP188" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ188" s="4" t="inlineStr"/>
       <c r="AR188" s="4" t="inlineStr"/>
@@ -27812,7 +27812,7 @@
         </is>
       </c>
       <c r="J195" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K195" s="4" t="n">
         <v>13</v>
@@ -27914,7 +27914,7 @@
         <v>-2.24</v>
       </c>
       <c r="AP195" s="4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ195" s="4" t="inlineStr"/>
       <c r="AR195" s="4" t="inlineStr"/>
@@ -32285,8 +32285,8410 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>GNFC_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>R2_NEW</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr"/>
+      <c r="J226" s="4" t="inlineStr"/>
+      <c r="K226" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="inlineStr"/>
+      <c r="N226" s="4" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="O226" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P226" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q226" s="4" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R226" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S226" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T226" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U226" s="4" t="inlineStr"/>
+      <c r="V226" s="4" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="W226" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X226" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Y226" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA226" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB226" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC226" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD226" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AE226" s="4" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AF226" s="4" t="n">
+        <v>547.77</v>
+      </c>
+      <c r="AG226" s="4" t="n">
+        <v>558.83</v>
+      </c>
+      <c r="AH226" s="4" t="n">
+        <v>520.1</v>
+      </c>
+      <c r="AI226" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ226" s="4" t="n">
+        <v>619.7</v>
+      </c>
+      <c r="AK226" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL226" s="4" t="n">
+        <v>686.09</v>
+      </c>
+      <c r="AM226" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN226" s="4" t="n">
+        <v>519.75</v>
+      </c>
+      <c r="AO226" s="4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="AP226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS226" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT226" s="4" t="inlineStr">
+        <is>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AU226" s="4" t="inlineStr"/>
+      <c r="AV226" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW226" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX226" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>TCS_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr"/>
+      <c r="J227" s="4" t="inlineStr"/>
+      <c r="K227" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L227" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M227" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="N227" s="4" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="O227" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P227" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q227" s="4" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="R227" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S227" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T227" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→2 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U227" s="4" t="inlineStr"/>
+      <c r="V227" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="W227" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X227" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="Y227" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z227" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA227" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB227" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC227" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD227" s="4" t="n">
+        <v>2421.9</v>
+      </c>
+      <c r="AE227" s="4" t="n">
+        <v>2452.2</v>
+      </c>
+      <c r="AF227" s="4" t="n">
+        <v>2397.68</v>
+      </c>
+      <c r="AG227" s="4" t="n">
+        <v>2446.12</v>
+      </c>
+      <c r="AH227" s="4" t="n">
+        <v>2276.59</v>
+      </c>
+      <c r="AI227" s="4" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="AJ227" s="4" t="n">
+        <v>2712.53</v>
+      </c>
+      <c r="AK227" s="4" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AL227" s="4" t="n">
+        <v>3003.16</v>
+      </c>
+      <c r="AM227" s="4" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="AN227" s="4" t="n">
+        <v>2460</v>
+      </c>
+      <c r="AO227" s="4" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AP227" s="4" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AQ227" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR227" s="4" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="AS227" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT227" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AU227" s="4" t="inlineStr"/>
+      <c r="AV227" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW227" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX227" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>OFSS_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr"/>
+      <c r="J228" s="4" t="inlineStr"/>
+      <c r="K228" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L228" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M228" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N228" s="4" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="O228" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P228" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="R228" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S228" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T228" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→3 · Conf 46% · band HOLD · 16d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U228" s="4" t="inlineStr"/>
+      <c r="V228" s="4" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="W228" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X228" s="4" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="Y228" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z228" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA228" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB228" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC228" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD228" s="4" t="n">
+        <v>11727</v>
+      </c>
+      <c r="AE228" s="4" t="n">
+        <v>11427</v>
+      </c>
+      <c r="AF228" s="4" t="n">
+        <v>11609.73</v>
+      </c>
+      <c r="AG228" s="4" t="n">
+        <v>11844.27</v>
+      </c>
+      <c r="AH228" s="4" t="n">
+        <v>11023.38</v>
+      </c>
+      <c r="AI228" s="4" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="AJ228" s="4" t="n">
+        <v>13134.24</v>
+      </c>
+      <c r="AK228" s="4" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="AL228" s="4" t="n">
+        <v>14541.48</v>
+      </c>
+      <c r="AM228" s="4" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="AN228" s="4" t="n">
+        <v>11600</v>
+      </c>
+      <c r="AO228" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP228" s="4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AQ228" s="4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AR228" s="4" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AS228" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT228" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Momentum</t>
+        </is>
+      </c>
+      <c r="AU228" s="4" t="inlineStr"/>
+      <c r="AV228" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW228" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX228" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>INDIANB_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L229" s="4" t="inlineStr"/>
+      <c r="M229" s="4" t="inlineStr"/>
+      <c r="N229" s="4" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="O229" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P229" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q229" s="4" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="R229" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S229" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T229" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #4 · Conf 35% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U229" s="4" t="inlineStr"/>
+      <c r="V229" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="W229" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X229" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="Y229" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA229" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB229" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC229" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD229" s="4" t="n">
+        <v>853.4</v>
+      </c>
+      <c r="AE229" s="4" t="n">
+        <v>853.4</v>
+      </c>
+      <c r="AF229" s="4" t="n">
+        <v>844.87</v>
+      </c>
+      <c r="AG229" s="4" t="n">
+        <v>861.9299999999999</v>
+      </c>
+      <c r="AH229" s="4" t="n">
+        <v>810.73</v>
+      </c>
+      <c r="AI229" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ229" s="4" t="n">
+        <v>921.67</v>
+      </c>
+      <c r="AK229" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL229" s="4" t="n">
+        <v>981.41</v>
+      </c>
+      <c r="AM229" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN229" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="AO229" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AP229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS229" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT229" s="4" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AU229" s="4" t="inlineStr"/>
+      <c r="AV229" s="4" t="inlineStr"/>
+      <c r="AW229" s="4" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="AX229" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>HCLTECH_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>HCL Tech</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +7.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K230" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L230" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M230" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N230" s="4" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="O230" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P230" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="R230" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S230" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T230" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↑ 8→5 · Conf 43% · band HOLD→STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U230" s="4" t="inlineStr"/>
+      <c r="V230" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="W230" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X230" s="4" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Y230" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z230" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA230" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB230" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC230" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD230" s="4" t="n">
+        <v>1351.3</v>
+      </c>
+      <c r="AE230" s="4" t="n">
+        <v>1346.6</v>
+      </c>
+      <c r="AF230" s="4" t="n">
+        <v>1333.13</v>
+      </c>
+      <c r="AG230" s="4" t="n">
+        <v>1360.07</v>
+      </c>
+      <c r="AH230" s="4" t="n">
+        <v>1279.27</v>
+      </c>
+      <c r="AI230" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ230" s="4" t="n">
+        <v>1454.33</v>
+      </c>
+      <c r="AK230" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL230" s="4" t="n">
+        <v>1548.59</v>
+      </c>
+      <c r="AM230" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN230" s="4" t="n">
+        <v>1369.9</v>
+      </c>
+      <c r="AO230" s="4" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AP230" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AQ230" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR230" s="4" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="AS230" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT230" s="4" t="inlineStr">
+        <is>
+          <t>Quality · Trend · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AU230" s="4" t="inlineStr"/>
+      <c r="AV230" s="4" t="inlineStr"/>
+      <c r="AW230" s="4" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="AX230" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>ATUL_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>ATUL</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L231" s="4" t="inlineStr"/>
+      <c r="M231" s="4" t="inlineStr"/>
+      <c r="N231" s="4" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="O231" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P231" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q231" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="R231" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S231" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T231" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #6 · Conf 35% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U231" s="4" t="inlineStr"/>
+      <c r="V231" s="4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="W231" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X231" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Y231" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA231" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB231" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC231" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD231" s="4" t="n">
+        <v>6834</v>
+      </c>
+      <c r="AE231" s="4" t="n">
+        <v>6834</v>
+      </c>
+      <c r="AF231" s="4" t="n">
+        <v>6765.66</v>
+      </c>
+      <c r="AG231" s="4" t="n">
+        <v>6902.34</v>
+      </c>
+      <c r="AH231" s="4" t="n">
+        <v>6492.3</v>
+      </c>
+      <c r="AI231" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ231" s="4" t="n">
+        <v>7380.72</v>
+      </c>
+      <c r="AK231" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL231" s="4" t="n">
+        <v>7859.1</v>
+      </c>
+      <c r="AM231" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN231" s="4" t="n">
+        <v>6793.5</v>
+      </c>
+      <c r="AO231" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR231" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS231" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT231" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AU231" s="4" t="inlineStr"/>
+      <c r="AV231" s="4" t="inlineStr"/>
+      <c r="AW231" s="4" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="AX231" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>OIL_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.3pp alpha</t>
+        </is>
+      </c>
+      <c r="J232" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K232" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L232" s="4" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr"/>
+      <c r="N232" s="4" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="O232" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P232" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q232" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="R232" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S232" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T232" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #7 · Conf 41% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U232" s="4" t="inlineStr"/>
+      <c r="V232" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="W232" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X232" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y232" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z232" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA232" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB232" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC232" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD232" s="4" t="n">
+        <v>443.9</v>
+      </c>
+      <c r="AE232" s="4" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="AF232" s="4" t="n">
+        <v>436.64</v>
+      </c>
+      <c r="AG232" s="4" t="n">
+        <v>445.46</v>
+      </c>
+      <c r="AH232" s="4" t="n">
+        <v>419</v>
+      </c>
+      <c r="AI232" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ232" s="4" t="n">
+        <v>476.33</v>
+      </c>
+      <c r="AK232" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL232" s="4" t="n">
+        <v>507.21</v>
+      </c>
+      <c r="AM232" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN232" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="AO232" s="4" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="AP232" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AQ232" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AR232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS232" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT232" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AU232" s="4" t="inlineStr"/>
+      <c r="AV232" s="4" t="inlineStr"/>
+      <c r="AW232" s="4" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="AX232" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Hero MotoCorp</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +10.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="K233" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L233" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M233" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N233" s="4" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="O233" s="4" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P233" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="R233" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S233" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T233" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band HOLD→STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U233" s="4" t="inlineStr"/>
+      <c r="V233" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W233" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X233" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y233" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z233" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA233" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB233" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC233" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD233" s="4" t="n">
+        <v>5651.5</v>
+      </c>
+      <c r="AE233" s="4" t="n">
+        <v>5196.6</v>
+      </c>
+      <c r="AF233" s="4" t="n">
+        <v>5144.63</v>
+      </c>
+      <c r="AG233" s="4" t="n">
+        <v>5248.57</v>
+      </c>
+      <c r="AH233" s="4" t="n">
+        <v>4936.77</v>
+      </c>
+      <c r="AI233" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ233" s="4" t="n">
+        <v>5612.33</v>
+      </c>
+      <c r="AK233" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL233" s="4" t="n">
+        <v>5976.09</v>
+      </c>
+      <c r="AM233" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN233" s="4" t="n">
+        <v>5548</v>
+      </c>
+      <c r="AO233" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AP233" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AQ233" s="4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AR233" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AS233" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT233" s="4" t="inlineStr">
+        <is>
+          <t>Trend · Quality · Growth</t>
+        </is>
+      </c>
+      <c r="AU233" s="4" t="inlineStr"/>
+      <c r="AV233" s="4" t="inlineStr"/>
+      <c r="AW233" s="4" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="AX233" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>VEDL_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Vedanta</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="K234" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L234" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M234" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P234" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R234" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S234" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T234" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 6→9 · Conf 33% · band HOLD · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U234" s="4" t="inlineStr"/>
+      <c r="V234" s="4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="W234" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X234" s="4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y234" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z234" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA234" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB234" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC234" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD234" s="4" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="AE234" s="4" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="AF234" s="4" t="n">
+        <v>260.87</v>
+      </c>
+      <c r="AG234" s="4" t="n">
+        <v>266.13</v>
+      </c>
+      <c r="AH234" s="4" t="n">
+        <v>250.32</v>
+      </c>
+      <c r="AI234" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ234" s="4" t="n">
+        <v>284.58</v>
+      </c>
+      <c r="AK234" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL234" s="4" t="n">
+        <v>303.02</v>
+      </c>
+      <c r="AM234" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN234" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="AO234" s="4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AP234" s="4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AQ234" s="4" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="AR234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS234" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT234" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Growth</t>
+        </is>
+      </c>
+      <c r="AU234" s="4" t="inlineStr"/>
+      <c r="AV234" s="4" t="inlineStr"/>
+      <c r="AW234" s="4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AX234" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>INFY_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H235" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +11.7pp alpha</t>
+        </is>
+      </c>
+      <c r="J235" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K235" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L235" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M235" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N235" s="4" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="O235" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P235" s="4" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="R235" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S235" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T235" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 7→10 · Conf 41% · band HOLD · 59d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U235" s="4" t="inlineStr"/>
+      <c r="V235" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="W235" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X235" s="4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y235" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z235" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA235" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB235" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC235" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD235" s="4" t="n">
+        <v>1177</v>
+      </c>
+      <c r="AE235" s="4" t="n">
+        <v>1155.6</v>
+      </c>
+      <c r="AF235" s="4" t="n">
+        <v>1144.04</v>
+      </c>
+      <c r="AG235" s="4" t="n">
+        <v>1167.16</v>
+      </c>
+      <c r="AH235" s="4" t="n">
+        <v>1097.82</v>
+      </c>
+      <c r="AI235" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ235" s="4" t="n">
+        <v>1248.05</v>
+      </c>
+      <c r="AK235" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL235" s="4" t="n">
+        <v>1328.94</v>
+      </c>
+      <c r="AM235" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN235" s="4" t="n">
+        <v>1167.5</v>
+      </c>
+      <c r="AO235" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP235" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ235" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR235" s="4" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="AS235" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT235" s="4" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Quality · Momentum</t>
+        </is>
+      </c>
+      <c r="AU235" s="4" t="inlineStr"/>
+      <c r="AV235" s="4" t="inlineStr"/>
+      <c r="AW235" s="4" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="AX235" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +59.7pp alpha</t>
+        </is>
+      </c>
+      <c r="J236" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K236" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L236" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="M236" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N236" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O236" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P236" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q236" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R236" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S236" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T236" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↑ 13→11 · Conf 30% · band EXIT · 59d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U236" s="4" t="inlineStr"/>
+      <c r="V236" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W236" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X236" s="4" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="Y236" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z236" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA236" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB236" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC236" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD236" s="4" t="n">
+        <v>2182</v>
+      </c>
+      <c r="AE236" s="4" t="n">
+        <v>2171.5</v>
+      </c>
+      <c r="AF236" s="4" t="n">
+        <v>2149.78</v>
+      </c>
+      <c r="AG236" s="4" t="n">
+        <v>2193.22</v>
+      </c>
+      <c r="AH236" s="4" t="n">
+        <v>2062.92</v>
+      </c>
+      <c r="AI236" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ236" s="4" t="n">
+        <v>2345.22</v>
+      </c>
+      <c r="AK236" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL236" s="4" t="n">
+        <v>2497.22</v>
+      </c>
+      <c r="AM236" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN236" s="4" t="n">
+        <v>2195</v>
+      </c>
+      <c r="AO236" s="4" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="AP236" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AQ236" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS236" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT236" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AU236" s="4" t="inlineStr"/>
+      <c r="AV236" s="4" t="inlineStr"/>
+      <c r="AW236" s="4" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="AX236" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>BIOCON_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H237" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +59.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J237" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="K237" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L237" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M237" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N237" s="4" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O237" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P237" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q237" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R237" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S237" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T237" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank ↓ 11→12 · Conf 30% · band EXIT · 16d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U237" s="4" t="inlineStr"/>
+      <c r="V237" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W237" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X237" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="Y237" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z237" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA237" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB237" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC237" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD237" s="4" t="n">
+        <v>428.2</v>
+      </c>
+      <c r="AE237" s="4" t="n">
+        <v>431.4</v>
+      </c>
+      <c r="AF237" s="4" t="n">
+        <v>427.09</v>
+      </c>
+      <c r="AG237" s="4" t="n">
+        <v>435.71</v>
+      </c>
+      <c r="AH237" s="4" t="n">
+        <v>409.83</v>
+      </c>
+      <c r="AI237" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ237" s="4" t="n">
+        <v>465.91</v>
+      </c>
+      <c r="AK237" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL237" s="4" t="n">
+        <v>496.11</v>
+      </c>
+      <c r="AM237" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN237" s="4" t="n">
+        <v>422</v>
+      </c>
+      <c r="AO237" s="4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AP237" s="4" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AQ237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR237" s="4" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="AS237" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT237" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AU237" s="4" t="inlineStr"/>
+      <c r="AV237" s="4" t="inlineStr"/>
+      <c r="AW237" s="4" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="AX237" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>R2_NEW</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +60.7pp alpha</t>
+        </is>
+      </c>
+      <c r="J238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L238" s="4" t="inlineStr"/>
+      <c r="M238" s="4" t="inlineStr"/>
+      <c r="N238" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O238" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P238" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q238" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R238" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S238" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T238" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #13 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U238" s="4" t="inlineStr"/>
+      <c r="V238" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W238" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X238" s="4" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="Y238" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA238" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB238" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC238" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD238" s="4" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="AE238" s="4" t="n">
+        <v>471.2</v>
+      </c>
+      <c r="AF238" s="4" t="n">
+        <v>466.49</v>
+      </c>
+      <c r="AG238" s="4" t="n">
+        <v>475.91</v>
+      </c>
+      <c r="AH238" s="4" t="n">
+        <v>447.64</v>
+      </c>
+      <c r="AI238" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ238" s="4" t="n">
+        <v>508.9</v>
+      </c>
+      <c r="AK238" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL238" s="4" t="n">
+        <v>541.88</v>
+      </c>
+      <c r="AM238" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN238" s="4" t="n">
+        <v>482</v>
+      </c>
+      <c r="AO238" s="4" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="AP238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS238" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT238" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AU238" s="4" t="inlineStr"/>
+      <c r="AV238" s="4" t="inlineStr"/>
+      <c r="AW238" s="4" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="AX238" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H239" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +62.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L239" s="4" t="inlineStr"/>
+      <c r="M239" s="4" t="inlineStr"/>
+      <c r="N239" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O239" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P239" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R239" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S239" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T239" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #14 · Conf 25% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U239" s="4" t="inlineStr"/>
+      <c r="V239" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W239" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X239" s="4" t="n">
+        <v>-29.7</v>
+      </c>
+      <c r="Y239" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA239" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB239" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC239" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD239" s="4" t="n">
+        <v>1594.5</v>
+      </c>
+      <c r="AE239" s="4" t="n">
+        <v>1594.5</v>
+      </c>
+      <c r="AF239" s="4" t="n">
+        <v>1578.56</v>
+      </c>
+      <c r="AG239" s="4" t="n">
+        <v>1610.44</v>
+      </c>
+      <c r="AH239" s="4" t="n">
+        <v>1514.77</v>
+      </c>
+      <c r="AI239" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ239" s="4" t="n">
+        <v>1722.06</v>
+      </c>
+      <c r="AK239" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL239" s="4" t="n">
+        <v>1833.67</v>
+      </c>
+      <c r="AM239" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN239" s="4" t="n">
+        <v>1595</v>
+      </c>
+      <c r="AO239" s="4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AP239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS239" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT239" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AU239" s="4" t="inlineStr"/>
+      <c r="AV239" s="4" t="inlineStr"/>
+      <c r="AW239" s="4" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="AX239" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAS_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I240" s="4" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +64.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J240" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="K240" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L240" s="4" t="inlineStr"/>
+      <c r="M240" s="4" t="inlineStr"/>
+      <c r="N240" s="4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="O240" s="4" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P240" s="4" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R240" s="4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S240" s="4" t="inlineStr">
+        <is>
+          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="T240" s="4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #15 · Conf 24% · band EXIT · 17d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="U240" s="4" t="inlineStr"/>
+      <c r="V240" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="W240" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X240" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Y240" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z240" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA240" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB240" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC240" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD240" s="4" t="n">
+        <v>1296.8</v>
+      </c>
+      <c r="AE240" s="4" t="n">
+        <v>1305</v>
+      </c>
+      <c r="AF240" s="4" t="n">
+        <v>1291.95</v>
+      </c>
+      <c r="AG240" s="4" t="n">
+        <v>1318.05</v>
+      </c>
+      <c r="AH240" s="4" t="n">
+        <v>1239.75</v>
+      </c>
+      <c r="AI240" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ240" s="4" t="n">
+        <v>1409.4</v>
+      </c>
+      <c r="AK240" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL240" s="4" t="n">
+        <v>1500.75</v>
+      </c>
+      <c r="AM240" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN240" s="4" t="n">
+        <v>1327.7</v>
+      </c>
+      <c r="AO240" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AP240" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AQ240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR240" s="4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AS240" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT240" s="4" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AU240" s="4" t="inlineStr"/>
+      <c r="AV240" s="4" t="inlineStr"/>
+      <c r="AW240" s="4" t="n">
+        <v>64.81999999999999</v>
+      </c>
+      <c r="AX240" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr"/>
+      <c r="J241" s="4" t="inlineStr"/>
+      <c r="K241" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M241" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N241" s="4" t="inlineStr"/>
+      <c r="O241" s="4" t="inlineStr"/>
+      <c r="P241" s="4" t="inlineStr"/>
+      <c r="Q241" s="4" t="inlineStr"/>
+      <c r="R241" s="4" t="inlineStr"/>
+      <c r="S241" s="4" t="inlineStr"/>
+      <c r="T241" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↑ 2→1 · Conf 83% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U241" s="4" t="inlineStr"/>
+      <c r="V241" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="W241" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X241" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y241" s="4" t="inlineStr"/>
+      <c r="Z241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA241" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB241" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC241" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD241" s="4" t="n">
+        <v>1449.6</v>
+      </c>
+      <c r="AE241" s="4" t="n">
+        <v>1449.599975585938</v>
+      </c>
+      <c r="AF241" s="4" t="n">
+        <v>1410</v>
+      </c>
+      <c r="AG241" s="4" t="n">
+        <v>1489</v>
+      </c>
+      <c r="AH241" s="4" t="n">
+        <v>1377.12</v>
+      </c>
+      <c r="AI241" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ241" s="4" t="n">
+        <v>1527</v>
+      </c>
+      <c r="AK241" s="4" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AL241" s="4" t="n">
+        <v>1633.89</v>
+      </c>
+      <c r="AM241" s="4" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AN241" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="AO241" s="4" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AP241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ241" s="4" t="inlineStr"/>
+      <c r="AR241" s="4" t="inlineStr"/>
+      <c r="AS241" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT241" s="4" t="inlineStr"/>
+      <c r="AU241" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AV241" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW241" s="4" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="AX241" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G242" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr"/>
+      <c r="J242" s="4" t="inlineStr"/>
+      <c r="K242" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N242" s="4" t="inlineStr"/>
+      <c r="O242" s="4" t="inlineStr"/>
+      <c r="P242" s="4" t="inlineStr"/>
+      <c r="Q242" s="4" t="inlineStr"/>
+      <c r="R242" s="4" t="inlineStr"/>
+      <c r="S242" s="4" t="inlineStr"/>
+      <c r="T242" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U242" s="4" t="inlineStr"/>
+      <c r="V242" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="W242" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X242" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y242" s="4" t="inlineStr"/>
+      <c r="Z242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA242" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB242" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC242" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD242" s="4" t="n">
+        <v>1949</v>
+      </c>
+      <c r="AE242" s="4" t="n">
+        <v>1949</v>
+      </c>
+      <c r="AF242" s="4" t="n">
+        <v>1897</v>
+      </c>
+      <c r="AG242" s="4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="AH242" s="4" t="n">
+        <v>1851.55</v>
+      </c>
+      <c r="AI242" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ242" s="4" t="n">
+        <v>2038</v>
+      </c>
+      <c r="AK242" s="4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AL242" s="4" t="n">
+        <v>2180.66</v>
+      </c>
+      <c r="AM242" s="4" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="AN242" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="AO242" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AP242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ242" s="4" t="inlineStr"/>
+      <c r="AR242" s="4" t="inlineStr"/>
+      <c r="AS242" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT242" s="4" t="inlineStr"/>
+      <c r="AU242" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AV242" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW242" s="4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AX242" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr"/>
+      <c r="J243" s="4" t="inlineStr"/>
+      <c r="K243" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L243" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" s="4" t="inlineStr"/>
+      <c r="O243" s="4" t="inlineStr"/>
+      <c r="P243" s="4" t="inlineStr"/>
+      <c r="Q243" s="4" t="inlineStr"/>
+      <c r="R243" s="4" t="inlineStr"/>
+      <c r="S243" s="4" t="inlineStr"/>
+      <c r="T243" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U243" s="4" t="inlineStr"/>
+      <c r="V243" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W243" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X243" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y243" s="4" t="inlineStr"/>
+      <c r="Z243" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA243" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB243" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC243" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD243" s="4" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AE243" s="4" t="n">
+        <v>2443.4</v>
+      </c>
+      <c r="AF243" s="4" t="n">
+        <v>2329</v>
+      </c>
+      <c r="AG243" s="4" t="n">
+        <v>2451</v>
+      </c>
+      <c r="AH243" s="4" t="n">
+        <v>2270.88</v>
+      </c>
+      <c r="AI243" s="4" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="AJ243" s="4" t="n">
+        <v>2581.632</v>
+      </c>
+      <c r="AK243" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AL243" s="4" t="n">
+        <v>2762.34624</v>
+      </c>
+      <c r="AM243" s="4" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="AN243" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AO243" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AP243" s="4" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="AQ243" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR243" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS243" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT243" s="4" t="inlineStr"/>
+      <c r="AU243" s="4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AV243" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW243" s="4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AX243" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr"/>
+      <c r="J244" s="4" t="inlineStr"/>
+      <c r="K244" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L244" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M244" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N244" s="4" t="inlineStr"/>
+      <c r="O244" s="4" t="inlineStr"/>
+      <c r="P244" s="4" t="inlineStr"/>
+      <c r="Q244" s="4" t="inlineStr"/>
+      <c r="R244" s="4" t="inlineStr"/>
+      <c r="S244" s="4" t="inlineStr"/>
+      <c r="T244" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank ↓ 3→4 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U244" s="4" t="inlineStr"/>
+      <c r="V244" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="W244" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X244" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y244" s="4" t="inlineStr"/>
+      <c r="Z244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA244" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB244" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC244" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD244" s="4" t="n">
+        <v>1657</v>
+      </c>
+      <c r="AE244" s="4" t="n">
+        <v>1657</v>
+      </c>
+      <c r="AF244" s="4" t="n">
+        <v>1604</v>
+      </c>
+      <c r="AG244" s="4" t="n">
+        <v>1710</v>
+      </c>
+      <c r="AH244" s="4" t="n">
+        <v>1574.15</v>
+      </c>
+      <c r="AI244" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ244" s="4" t="n">
+        <v>1680</v>
+      </c>
+      <c r="AK244" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL244" s="4" t="n">
+        <v>1797.6</v>
+      </c>
+      <c r="AM244" s="4" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AN244" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AO244" s="4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP244" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ244" s="4" t="inlineStr"/>
+      <c r="AR244" s="4" t="inlineStr"/>
+      <c r="AS244" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT244" s="4" t="inlineStr"/>
+      <c r="AU244" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="AV244" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW244" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AX244" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H245" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr"/>
+      <c r="J245" s="4" t="inlineStr"/>
+      <c r="K245" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L245" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" s="4" t="inlineStr"/>
+      <c r="O245" s="4" t="inlineStr"/>
+      <c r="P245" s="4" t="inlineStr"/>
+      <c r="Q245" s="4" t="inlineStr"/>
+      <c r="R245" s="4" t="inlineStr"/>
+      <c r="S245" s="4" t="inlineStr"/>
+      <c r="T245" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank → 5→5 · Conf 73% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="U245" s="4" t="inlineStr"/>
+      <c r="V245" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="W245" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X245" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y245" s="4" t="inlineStr"/>
+      <c r="Z245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA245" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB245" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC245" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD245" s="4" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="AE245" s="4" t="n">
+        <v>397.2000122070312</v>
+      </c>
+      <c r="AF245" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="AG245" s="4" t="n">
+        <v>409</v>
+      </c>
+      <c r="AH245" s="4" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="AI245" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ245" s="4" t="n">
+        <v>428.976</v>
+      </c>
+      <c r="AK245" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL245" s="4" t="n">
+        <v>459.00432</v>
+      </c>
+      <c r="AM245" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN245" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="AO245" s="4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AP245" s="4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ245" s="4" t="inlineStr"/>
+      <c r="AR245" s="4" t="inlineStr"/>
+      <c r="AS245" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT245" s="4" t="inlineStr"/>
+      <c r="AU245" s="4" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AV245" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW245" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX245" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="inlineStr"/>
+      <c r="J246" s="4" t="inlineStr"/>
+      <c r="K246" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L246" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M246" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N246" s="4" t="inlineStr"/>
+      <c r="O246" s="4" t="inlineStr"/>
+      <c r="P246" s="4" t="inlineStr"/>
+      <c r="Q246" s="4" t="inlineStr"/>
+      <c r="R246" s="4" t="inlineStr"/>
+      <c r="S246" s="4" t="inlineStr"/>
+      <c r="T246" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 4→6 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U246" s="4" t="inlineStr"/>
+      <c r="V246" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W246" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X246" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y246" s="4" t="inlineStr"/>
+      <c r="Z246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA246" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB246" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC246" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD246" s="4" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="AE246" s="4" t="n">
+        <v>346.8999938964844</v>
+      </c>
+      <c r="AF246" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="AG246" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="AH246" s="4" t="n">
+        <v>329.5549999999999</v>
+      </c>
+      <c r="AI246" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ246" s="4" t="n">
+        <v>374.652</v>
+      </c>
+      <c r="AK246" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL246" s="4" t="n">
+        <v>400.87764</v>
+      </c>
+      <c r="AM246" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN246" s="4" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="AO246" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AP246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ246" s="4" t="inlineStr"/>
+      <c r="AR246" s="4" t="inlineStr"/>
+      <c r="AS246" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT246" s="4" t="inlineStr"/>
+      <c r="AU246" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AV246" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW246" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX246" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H247" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="inlineStr"/>
+      <c r="J247" s="4" t="inlineStr"/>
+      <c r="K247" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L247" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" s="4" t="inlineStr"/>
+      <c r="O247" s="4" t="inlineStr"/>
+      <c r="P247" s="4" t="inlineStr"/>
+      <c r="Q247" s="4" t="inlineStr"/>
+      <c r="R247" s="4" t="inlineStr"/>
+      <c r="S247" s="4" t="inlineStr"/>
+      <c r="T247" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 68% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U247" s="4" t="inlineStr"/>
+      <c r="V247" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="W247" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X247" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y247" s="4" t="inlineStr"/>
+      <c r="Z247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA247" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB247" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC247" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD247" s="4" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="AE247" s="4" t="n">
+        <v>276.7999877929688</v>
+      </c>
+      <c r="AF247" s="4" t="n">
+        <v>270</v>
+      </c>
+      <c r="AG247" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="AH247" s="4" t="n">
+        <v>262.96</v>
+      </c>
+      <c r="AI247" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ247" s="4" t="n">
+        <v>298.944</v>
+      </c>
+      <c r="AK247" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL247" s="4" t="n">
+        <v>319.87008</v>
+      </c>
+      <c r="AM247" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN247" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="AO247" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AP247" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ247" s="4" t="inlineStr"/>
+      <c r="AR247" s="4" t="inlineStr"/>
+      <c r="AS247" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT247" s="4" t="inlineStr"/>
+      <c r="AU247" s="4" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AV247" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW247" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX247" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G248" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr"/>
+      <c r="J248" s="4" t="inlineStr"/>
+      <c r="K248" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr"/>
+      <c r="N248" s="4" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr"/>
+      <c r="P248" s="4" t="inlineStr"/>
+      <c r="Q248" s="4" t="inlineStr"/>
+      <c r="R248" s="4" t="inlineStr"/>
+      <c r="S248" s="4" t="inlineStr"/>
+      <c r="T248" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank #8 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U248" s="4" t="inlineStr"/>
+      <c r="V248" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W248" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X248" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y248" s="4" t="inlineStr"/>
+      <c r="Z248" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA248" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB248" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC248" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD248" s="4" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="AE248" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AF248" s="4" t="n">
+        <v>279</v>
+      </c>
+      <c r="AG248" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="AH248" s="4" t="n">
+        <v>271.51</v>
+      </c>
+      <c r="AI248" s="4" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="AJ248" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="AK248" s="4" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AL248" s="4" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="AM248" s="4" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AN248" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="AO248" s="4" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AP248" s="4" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="AQ248" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR248" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS248" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT248" s="4" t="inlineStr"/>
+      <c r="AU248" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AV248" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW248" s="4" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AX248" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H249" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr"/>
+      <c r="J249" s="4" t="inlineStr"/>
+      <c r="K249" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L249" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M249" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N249" s="4" t="inlineStr"/>
+      <c r="O249" s="4" t="inlineStr"/>
+      <c r="P249" s="4" t="inlineStr"/>
+      <c r="Q249" s="4" t="inlineStr"/>
+      <c r="R249" s="4" t="inlineStr"/>
+      <c r="S249" s="4" t="inlineStr"/>
+      <c r="T249" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U249" s="4" t="inlineStr"/>
+      <c r="V249" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="W249" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X249" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y249" s="4" t="inlineStr"/>
+      <c r="Z249" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA249" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB249" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC249" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD249" s="4" t="n">
+        <v>510.9</v>
+      </c>
+      <c r="AE249" s="4" t="n">
+        <v>510.8500061035156</v>
+      </c>
+      <c r="AF249" s="4" t="n">
+        <v>495</v>
+      </c>
+      <c r="AG249" s="4" t="n">
+        <v>526</v>
+      </c>
+      <c r="AH249" s="4" t="n">
+        <v>485.355</v>
+      </c>
+      <c r="AI249" s="4" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="AJ249" s="4" t="n">
+        <v>551.772</v>
+      </c>
+      <c r="AK249" s="4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AL249" s="4" t="n">
+        <v>590.3960400000001</v>
+      </c>
+      <c r="AM249" s="4" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN249" s="4" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="AO249" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP249" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AQ249" s="4" t="inlineStr"/>
+      <c r="AR249" s="4" t="inlineStr"/>
+      <c r="AS249" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT249" s="4" t="inlineStr"/>
+      <c r="AU249" s="4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AV249" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW249" s="4" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AX249" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G250" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr"/>
+      <c r="J250" s="4" t="inlineStr"/>
+      <c r="K250" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L250" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M250" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N250" s="4" t="inlineStr"/>
+      <c r="O250" s="4" t="inlineStr"/>
+      <c r="P250" s="4" t="inlineStr"/>
+      <c r="Q250" s="4" t="inlineStr"/>
+      <c r="R250" s="4" t="inlineStr"/>
+      <c r="S250" s="4" t="inlineStr"/>
+      <c r="T250" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 8→10 · Conf 63% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U250" s="4" t="inlineStr"/>
+      <c r="V250" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="W250" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X250" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y250" s="4" t="inlineStr"/>
+      <c r="Z250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA250" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB250" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC250" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD250" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="AE250" s="4" t="n">
+        <v>390.0499877929688</v>
+      </c>
+      <c r="AF250" s="4" t="n">
+        <v>378</v>
+      </c>
+      <c r="AG250" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="AH250" s="4" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="AI250" s="4" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="AJ250" s="4" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="AK250" s="4" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AL250" s="4" t="n">
+        <v>450.6840000000001</v>
+      </c>
+      <c r="AM250" s="4" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AN250" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="AO250" s="4" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AP250" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AQ250" s="4" t="inlineStr"/>
+      <c r="AR250" s="4" t="inlineStr"/>
+      <c r="AS250" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT250" s="4" t="inlineStr"/>
+      <c r="AU250" s="4" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AV250" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW250" s="4" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AX250" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr"/>
+      <c r="J251" s="4" t="inlineStr"/>
+      <c r="K251" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L251" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M251" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N251" s="4" t="inlineStr"/>
+      <c r="O251" s="4" t="inlineStr"/>
+      <c r="P251" s="4" t="inlineStr"/>
+      <c r="Q251" s="4" t="inlineStr"/>
+      <c r="R251" s="4" t="inlineStr"/>
+      <c r="S251" s="4" t="inlineStr"/>
+      <c r="T251" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U251" s="4" t="inlineStr"/>
+      <c r="V251" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="W251" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X251" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y251" s="4" t="inlineStr"/>
+      <c r="Z251" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA251" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB251" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC251" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD251" s="4" t="n">
+        <v>414</v>
+      </c>
+      <c r="AE251" s="4" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="AF251" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="AG251" s="4" t="n">
+        <v>427</v>
+      </c>
+      <c r="AH251" s="4" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="AI251" s="4" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="AJ251" s="4" t="n">
+        <v>447.12</v>
+      </c>
+      <c r="AK251" s="4" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AL251" s="4" t="n">
+        <v>478.4184</v>
+      </c>
+      <c r="AM251" s="4" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="AN251" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AO251" s="4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AP251" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR251" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AS251" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT251" s="4" t="inlineStr"/>
+      <c r="AU251" s="4" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="AV251" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW251" s="4" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="AX251" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr"/>
+      <c r="J252" s="4" t="inlineStr"/>
+      <c r="K252" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L252" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M252" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N252" s="4" t="inlineStr"/>
+      <c r="O252" s="4" t="inlineStr"/>
+      <c r="P252" s="4" t="inlineStr"/>
+      <c r="Q252" s="4" t="inlineStr"/>
+      <c r="R252" s="4" t="inlineStr"/>
+      <c r="S252" s="4" t="inlineStr"/>
+      <c r="T252" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→12 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U252" s="4" t="inlineStr"/>
+      <c r="V252" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="W252" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X252" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y252" s="4" t="inlineStr"/>
+      <c r="Z252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA252" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB252" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC252" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD252" s="4" t="n">
+        <v>5429</v>
+      </c>
+      <c r="AE252" s="4" t="n">
+        <v>5429</v>
+      </c>
+      <c r="AF252" s="4" t="n">
+        <v>5287</v>
+      </c>
+      <c r="AG252" s="4" t="n">
+        <v>5571</v>
+      </c>
+      <c r="AH252" s="4" t="n">
+        <v>5157.55</v>
+      </c>
+      <c r="AI252" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ252" s="4" t="n">
+        <v>5863.320000000001</v>
+      </c>
+      <c r="AK252" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL252" s="4" t="n">
+        <v>6273.752400000001</v>
+      </c>
+      <c r="AM252" s="4" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN252" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="AO252" s="4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AP252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ252" s="4" t="inlineStr"/>
+      <c r="AR252" s="4" t="inlineStr"/>
+      <c r="AS252" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT252" s="4" t="inlineStr"/>
+      <c r="AU252" s="4" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AV252" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW252" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX252" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr"/>
+      <c r="J253" s="4" t="inlineStr"/>
+      <c r="K253" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M253" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N253" s="4" t="inlineStr"/>
+      <c r="O253" s="4" t="inlineStr"/>
+      <c r="P253" s="4" t="inlineStr"/>
+      <c r="Q253" s="4" t="inlineStr"/>
+      <c r="R253" s="4" t="inlineStr"/>
+      <c r="S253" s="4" t="inlineStr"/>
+      <c r="T253" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.8%) · Rank ↑ 3→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U253" s="4" t="inlineStr"/>
+      <c r="V253" s="4" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W253" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X253" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y253" s="4" t="inlineStr"/>
+      <c r="Z253" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA253" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB253" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC253" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD253" s="4" t="n">
+        <v>2447</v>
+      </c>
+      <c r="AE253" s="4" t="n">
+        <v>2443.4</v>
+      </c>
+      <c r="AF253" s="4" t="n">
+        <v>2418.97</v>
+      </c>
+      <c r="AG253" s="4" t="n">
+        <v>2467.83</v>
+      </c>
+      <c r="AH253" s="4" t="n">
+        <v>2321.23</v>
+      </c>
+      <c r="AI253" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ253" s="4" t="n">
+        <v>2638.872</v>
+      </c>
+      <c r="AK253" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL253" s="4" t="n">
+        <v>2809.91</v>
+      </c>
+      <c r="AM253" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN253" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AO253" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AP253" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AQ253" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS253" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT253" s="4" t="inlineStr"/>
+      <c r="AU253" s="4" t="inlineStr"/>
+      <c r="AV253" s="4" t="inlineStr"/>
+      <c r="AW253" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX253" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="G254" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr"/>
+      <c r="J254" s="4" t="inlineStr"/>
+      <c r="K254" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L254" s="4" t="inlineStr"/>
+      <c r="M254" s="4" t="inlineStr"/>
+      <c r="N254" s="4" t="inlineStr"/>
+      <c r="O254" s="4" t="inlineStr"/>
+      <c r="P254" s="4" t="inlineStr"/>
+      <c r="Q254" s="4" t="inlineStr"/>
+      <c r="R254" s="4" t="inlineStr"/>
+      <c r="S254" s="4" t="inlineStr"/>
+      <c r="T254" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ+0.2%) · Rank #8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U254" s="4" t="inlineStr"/>
+      <c r="V254" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W254" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X254" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Y254" s="4" t="inlineStr"/>
+      <c r="Z254" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA254" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB254" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC254" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD254" s="4" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="AE254" s="4" t="n">
+        <v>449.35</v>
+      </c>
+      <c r="AF254" s="4" t="n">
+        <v>444.86</v>
+      </c>
+      <c r="AG254" s="4" t="n">
+        <v>453.84</v>
+      </c>
+      <c r="AH254" s="4" t="n">
+        <v>426.8825</v>
+      </c>
+      <c r="AI254" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ254" s="4" t="n">
+        <v>485.2980000000001</v>
+      </c>
+      <c r="AK254" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL254" s="4" t="n">
+        <v>516.7524999999999</v>
+      </c>
+      <c r="AM254" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN254" s="4" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="AO254" s="4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP254" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ254" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR254" s="4" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="AS254" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT254" s="4" t="inlineStr"/>
+      <c r="AU254" s="4" t="inlineStr"/>
+      <c r="AV254" s="4" t="inlineStr"/>
+      <c r="AW254" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX254" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>PNB_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Punjab Natl. Bank</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr"/>
+      <c r="K255" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L255" s="4" t="inlineStr"/>
+      <c r="M255" s="4" t="inlineStr"/>
+      <c r="N255" s="4" t="inlineStr"/>
+      <c r="O255" s="4" t="inlineStr"/>
+      <c r="P255" s="4" t="inlineStr"/>
+      <c r="Q255" s="4" t="inlineStr"/>
+      <c r="R255" s="4" t="inlineStr"/>
+      <c r="S255" s="4" t="inlineStr"/>
+      <c r="T255" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.3%) · Rank #4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U255" s="4" t="inlineStr"/>
+      <c r="V255" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="W255" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X255" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y255" s="4" t="inlineStr"/>
+      <c r="Z255" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA255" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB255" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC255" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD255" s="4" t="n">
+        <v>111.08</v>
+      </c>
+      <c r="AE255" s="4" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="AF255" s="4" t="n">
+        <v>110.33</v>
+      </c>
+      <c r="AG255" s="4" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="AH255" s="4" t="n">
+        <v>105.868</v>
+      </c>
+      <c r="AI255" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ255" s="4" t="n">
+        <v>120.3552</v>
+      </c>
+      <c r="AK255" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL255" s="4" t="n">
+        <v>128.156</v>
+      </c>
+      <c r="AM255" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN255" s="4" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="AO255" s="4" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="AP255" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AQ255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR255" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AS255" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT255" s="4" t="inlineStr"/>
+      <c r="AU255" s="4" t="inlineStr"/>
+      <c r="AV255" s="4" t="inlineStr"/>
+      <c r="AW255" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX255" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr"/>
+      <c r="J256" s="4" t="inlineStr"/>
+      <c r="K256" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L256" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M256" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N256" s="4" t="inlineStr"/>
+      <c r="O256" s="4" t="inlineStr"/>
+      <c r="P256" s="4" t="inlineStr"/>
+      <c r="Q256" s="4" t="inlineStr"/>
+      <c r="R256" s="4" t="inlineStr"/>
+      <c r="S256" s="4" t="inlineStr"/>
+      <c r="T256" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.1%) · Rank ↑ 10→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U256" s="4" t="inlineStr"/>
+      <c r="V256" s="4" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="W256" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X256" s="4" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y256" s="4" t="inlineStr"/>
+      <c r="Z256" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA256" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB256" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC256" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD256" s="4" t="n">
+        <v>410.05</v>
+      </c>
+      <c r="AE256" s="4" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="AF256" s="4" t="n">
+        <v>406.39</v>
+      </c>
+      <c r="AG256" s="4" t="n">
+        <v>414.61</v>
+      </c>
+      <c r="AH256" s="4" t="n">
+        <v>389.975</v>
+      </c>
+      <c r="AI256" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ256" s="4" t="n">
+        <v>443.34</v>
+      </c>
+      <c r="AK256" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL256" s="4" t="n">
+        <v>472.075</v>
+      </c>
+      <c r="AM256" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN256" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AO256" s="4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AP256" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AQ256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR256" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AS256" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT256" s="4" t="inlineStr"/>
+      <c r="AU256" s="4" t="inlineStr"/>
+      <c r="AV256" s="4" t="inlineStr"/>
+      <c r="AW256" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX256" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr"/>
+      <c r="K257" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="inlineStr"/>
+      <c r="N257" s="4" t="inlineStr"/>
+      <c r="O257" s="4" t="inlineStr"/>
+      <c r="P257" s="4" t="inlineStr"/>
+      <c r="Q257" s="4" t="inlineStr"/>
+      <c r="R257" s="4" t="inlineStr"/>
+      <c r="S257" s="4" t="inlineStr"/>
+      <c r="T257" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.4%) · Rank #9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U257" s="4" t="inlineStr"/>
+      <c r="V257" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W257" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X257" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y257" s="4" t="inlineStr"/>
+      <c r="Z257" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA257" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB257" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC257" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD257" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="AE257" s="4" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AF257" s="4" t="n">
+        <v>284.33</v>
+      </c>
+      <c r="AG257" s="4" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="AH257" s="4" t="n">
+        <v>272.84</v>
+      </c>
+      <c r="AI257" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ257" s="4" t="n">
+        <v>310.176</v>
+      </c>
+      <c r="AK257" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL257" s="4" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="AM257" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN257" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="AO257" s="4" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AP257" s="4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AQ257" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR257" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AS257" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT257" s="4" t="inlineStr"/>
+      <c r="AU257" s="4" t="inlineStr"/>
+      <c r="AV257" s="4" t="inlineStr"/>
+      <c r="AW257" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX257" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr"/>
+      <c r="J258" s="4" t="inlineStr"/>
+      <c r="K258" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="inlineStr"/>
+      <c r="N258" s="4" t="inlineStr"/>
+      <c r="O258" s="4" t="inlineStr"/>
+      <c r="P258" s="4" t="inlineStr"/>
+      <c r="Q258" s="4" t="inlineStr"/>
+      <c r="R258" s="4" t="inlineStr"/>
+      <c r="S258" s="4" t="inlineStr"/>
+      <c r="T258" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.1%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U258" s="4" t="inlineStr"/>
+      <c r="V258" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W258" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X258" s="4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y258" s="4" t="inlineStr"/>
+      <c r="Z258" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA258" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB258" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC258" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD258" s="4" t="n">
+        <v>536.7</v>
+      </c>
+      <c r="AE258" s="4" t="n">
+        <v>531.9</v>
+      </c>
+      <c r="AF258" s="4" t="n">
+        <v>526.58</v>
+      </c>
+      <c r="AG258" s="4" t="n">
+        <v>537.22</v>
+      </c>
+      <c r="AH258" s="4" t="n">
+        <v>505.3049999999999</v>
+      </c>
+      <c r="AI258" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ258" s="4" t="n">
+        <v>574.452</v>
+      </c>
+      <c r="AK258" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL258" s="4" t="n">
+        <v>611.6849999999999</v>
+      </c>
+      <c r="AM258" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN258" s="4" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="AO258" s="4" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="AP258" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AQ258" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR258" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS258" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT258" s="4" t="inlineStr"/>
+      <c r="AU258" s="4" t="inlineStr"/>
+      <c r="AV258" s="4" t="inlineStr"/>
+      <c r="AW258" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX258" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>FORTIS_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare</t>
+        </is>
+      </c>
+      <c r="G259" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr"/>
+      <c r="J259" s="4" t="inlineStr"/>
+      <c r="K259" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L259" s="4" t="inlineStr"/>
+      <c r="M259" s="4" t="inlineStr"/>
+      <c r="N259" s="4" t="inlineStr"/>
+      <c r="O259" s="4" t="inlineStr"/>
+      <c r="P259" s="4" t="inlineStr"/>
+      <c r="Q259" s="4" t="inlineStr"/>
+      <c r="R259" s="4" t="inlineStr"/>
+      <c r="S259" s="4" t="inlineStr"/>
+      <c r="T259" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank #11 · Conf 25% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U259" s="4" t="inlineStr"/>
+      <c r="V259" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W259" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X259" s="4" t="n">
+        <v>-26.6</v>
+      </c>
+      <c r="Y259" s="4" t="inlineStr"/>
+      <c r="Z259" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA259" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB259" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC259" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD259" s="4" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="AE259" s="4" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="AF259" s="4" t="n">
+        <v>943.02</v>
+      </c>
+      <c r="AG259" s="4" t="n">
+        <v>962.08</v>
+      </c>
+      <c r="AH259" s="4" t="n">
+        <v>904.9224999999999</v>
+      </c>
+      <c r="AI259" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ259" s="4" t="n">
+        <v>1028.754</v>
+      </c>
+      <c r="AK259" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL259" s="4" t="n">
+        <v>1095.4325</v>
+      </c>
+      <c r="AM259" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN259" s="4" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="AO259" s="4" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AP259" s="4" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AQ259" s="4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AR259" s="4" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AS259" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT259" s="4" t="inlineStr"/>
+      <c r="AU259" s="4" t="inlineStr"/>
+      <c r="AV259" s="4" t="inlineStr"/>
+      <c r="AW259" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX259" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>JSW Energy</t>
+        </is>
+      </c>
+      <c r="G260" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr"/>
+      <c r="J260" s="4" t="inlineStr"/>
+      <c r="K260" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L260" s="4" t="inlineStr"/>
+      <c r="M260" s="4" t="inlineStr"/>
+      <c r="N260" s="4" t="inlineStr"/>
+      <c r="O260" s="4" t="inlineStr"/>
+      <c r="P260" s="4" t="inlineStr"/>
+      <c r="Q260" s="4" t="inlineStr"/>
+      <c r="R260" s="4" t="inlineStr"/>
+      <c r="S260" s="4" t="inlineStr"/>
+      <c r="T260" s="4" t="inlineStr">
+        <is>
+          <t>🟡 WAIT (Δ+2.7%) · Rank #14 · Conf 25% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U260" s="4" t="inlineStr"/>
+      <c r="V260" s="4" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W260" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X260" s="4" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="Y260" s="4" t="inlineStr"/>
+      <c r="Z260" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA260" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB260" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC260" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD260" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="AE260" s="4" t="n">
+        <v>547.4</v>
+      </c>
+      <c r="AF260" s="4" t="n">
+        <v>541.9299999999999</v>
+      </c>
+      <c r="AG260" s="4" t="n">
+        <v>552.87</v>
+      </c>
+      <c r="AH260" s="4" t="n">
+        <v>520.03</v>
+      </c>
+      <c r="AI260" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ260" s="4" t="n">
+        <v>591.192</v>
+      </c>
+      <c r="AK260" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL260" s="4" t="n">
+        <v>629.5099999999999</v>
+      </c>
+      <c r="AM260" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN260" s="4" t="n">
+        <v>568</v>
+      </c>
+      <c r="AO260" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP260" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AQ260" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AR260" s="4" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AS260" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT260" s="4" t="inlineStr"/>
+      <c r="AU260" s="4" t="inlineStr"/>
+      <c r="AV260" s="4" t="inlineStr"/>
+      <c r="AW260" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX260" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>AMBER_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Amber Ent.</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr"/>
+      <c r="J261" s="4" t="inlineStr"/>
+      <c r="K261" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="inlineStr"/>
+      <c r="N261" s="4" t="inlineStr"/>
+      <c r="O261" s="4" t="inlineStr"/>
+      <c r="P261" s="4" t="inlineStr"/>
+      <c r="Q261" s="4" t="inlineStr"/>
+      <c r="R261" s="4" t="inlineStr"/>
+      <c r="S261" s="4" t="inlineStr"/>
+      <c r="T261" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.7%) · Rank #14 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U261" s="4" t="inlineStr"/>
+      <c r="V261" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="W261" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X261" s="4" t="n">
+        <v>-28.1</v>
+      </c>
+      <c r="Y261" s="4" t="inlineStr"/>
+      <c r="Z261" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA261" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB261" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC261" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD261" s="4" t="n">
+        <v>7411.5</v>
+      </c>
+      <c r="AE261" s="4" t="n">
+        <v>7388.5</v>
+      </c>
+      <c r="AF261" s="4" t="n">
+        <v>7314.61</v>
+      </c>
+      <c r="AG261" s="4" t="n">
+        <v>7462.39</v>
+      </c>
+      <c r="AH261" s="4" t="n">
+        <v>7019.075</v>
+      </c>
+      <c r="AI261" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ261" s="4" t="n">
+        <v>7979.580000000001</v>
+      </c>
+      <c r="AK261" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL261" s="4" t="n">
+        <v>8496.775</v>
+      </c>
+      <c r="AM261" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN261" s="4" t="n">
+        <v>7395</v>
+      </c>
+      <c r="AO261" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AP261" s="4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AQ261" s="4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR261" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS261" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT261" s="4" t="inlineStr"/>
+      <c r="AU261" s="4" t="inlineStr"/>
+      <c r="AV261" s="4" t="inlineStr"/>
+      <c r="AW261" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX261" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>BATAINDIA_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
+      <c r="G262" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr"/>
+      <c r="J262" s="4" t="inlineStr"/>
+      <c r="K262" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L262" s="4" t="inlineStr"/>
+      <c r="M262" s="4" t="inlineStr"/>
+      <c r="N262" s="4" t="inlineStr"/>
+      <c r="O262" s="4" t="inlineStr"/>
+      <c r="P262" s="4" t="inlineStr"/>
+      <c r="Q262" s="4" t="inlineStr"/>
+      <c r="R262" s="4" t="inlineStr"/>
+      <c r="S262" s="4" t="inlineStr"/>
+      <c r="T262" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.2%) · Rank #15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U262" s="4" t="inlineStr"/>
+      <c r="V262" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="W262" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X262" s="4" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="Y262" s="4" t="inlineStr"/>
+      <c r="Z262" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA262" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB262" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC262" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD262" s="4" t="n">
+        <v>698.35</v>
+      </c>
+      <c r="AE262" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF262" s="4" t="n">
+        <v>693</v>
+      </c>
+      <c r="AG262" s="4" t="n">
+        <v>707</v>
+      </c>
+      <c r="AH262" s="4" t="n">
+        <v>665</v>
+      </c>
+      <c r="AI262" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ262" s="4" t="n">
+        <v>756</v>
+      </c>
+      <c r="AK262" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL262" s="4" t="n">
+        <v>804.9999999999999</v>
+      </c>
+      <c r="AM262" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN262" s="4" t="n">
+        <v>709.55</v>
+      </c>
+      <c r="AO262" s="4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AP262" s="4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AQ262" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR262" s="4" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AS262" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT262" s="4" t="inlineStr"/>
+      <c r="AU262" s="4" t="inlineStr"/>
+      <c r="AV262" s="4" t="inlineStr"/>
+      <c r="AW262" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX262" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>IEX_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr"/>
+      <c r="G263" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr"/>
+      <c r="J263" s="4" t="inlineStr"/>
+      <c r="K263" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L263" s="4" t="inlineStr"/>
+      <c r="M263" s="4" t="inlineStr"/>
+      <c r="N263" s="4" t="inlineStr"/>
+      <c r="O263" s="4" t="inlineStr"/>
+      <c r="P263" s="4" t="inlineStr"/>
+      <c r="Q263" s="4" t="inlineStr"/>
+      <c r="R263" s="4" t="inlineStr"/>
+      <c r="S263" s="4" t="inlineStr"/>
+      <c r="T263" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-4.7%) · Rank #3 · Conf 39% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U263" s="4" t="inlineStr"/>
+      <c r="V263" s="4" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="W263" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X263" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="Y263" s="4" t="inlineStr"/>
+      <c r="Z263" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA263" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB263" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC263" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD263" s="4" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="AE263" s="4" t="n">
+        <v>134.19</v>
+      </c>
+      <c r="AF263" s="4" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="AG263" s="4" t="n">
+        <v>135.53</v>
+      </c>
+      <c r="AH263" s="4" t="n">
+        <v>127.4805</v>
+      </c>
+      <c r="AI263" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ263" s="4" t="n">
+        <v>144.9252</v>
+      </c>
+      <c r="AK263" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL263" s="4" t="n">
+        <v>154.3185</v>
+      </c>
+      <c r="AM263" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN263" s="4" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="AO263" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AP263" s="4" t="n">
+        <v>-3.72</v>
+      </c>
+      <c r="AQ263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR263" s="4" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="AS263" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT263" s="4" t="inlineStr"/>
+      <c r="AU263" s="4" t="inlineStr"/>
+      <c r="AV263" s="4" t="inlineStr"/>
+      <c r="AW263" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX263" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr"/>
+      <c r="G264" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr"/>
+      <c r="J264" s="4" t="inlineStr"/>
+      <c r="K264" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L264" s="4" t="inlineStr"/>
+      <c r="M264" s="4" t="inlineStr"/>
+      <c r="N264" s="4" t="inlineStr"/>
+      <c r="O264" s="4" t="inlineStr"/>
+      <c r="P264" s="4" t="inlineStr"/>
+      <c r="Q264" s="4" t="inlineStr"/>
+      <c r="R264" s="4" t="inlineStr"/>
+      <c r="S264" s="4" t="inlineStr"/>
+      <c r="T264" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.7%) · Rank #4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U264" s="4" t="inlineStr"/>
+      <c r="V264" s="4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="W264" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X264" s="4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Y264" s="4" t="inlineStr"/>
+      <c r="Z264" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA264" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB264" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC264" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD264" s="4" t="n">
+        <v>5499</v>
+      </c>
+      <c r="AE264" s="4" t="n">
+        <v>5483.3</v>
+      </c>
+      <c r="AF264" s="4" t="n">
+        <v>5428.47</v>
+      </c>
+      <c r="AG264" s="4" t="n">
+        <v>5538.13</v>
+      </c>
+      <c r="AH264" s="4" t="n">
+        <v>5209.135</v>
+      </c>
+      <c r="AI264" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ264" s="4" t="n">
+        <v>5921.964000000001</v>
+      </c>
+      <c r="AK264" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL264" s="4" t="n">
+        <v>6305.795</v>
+      </c>
+      <c r="AM264" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN264" s="4" t="n">
+        <v>5499</v>
+      </c>
+      <c r="AO264" s="4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AP264" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AQ264" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AR264" s="4" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="AS264" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT264" s="4" t="inlineStr"/>
+      <c r="AU264" s="4" t="inlineStr"/>
+      <c r="AV264" s="4" t="inlineStr"/>
+      <c r="AW264" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX264" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr"/>
+      <c r="G265" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr"/>
+      <c r="J265" s="4" t="inlineStr"/>
+      <c r="K265" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L265" s="4" t="inlineStr"/>
+      <c r="M265" s="4" t="inlineStr"/>
+      <c r="N265" s="4" t="inlineStr"/>
+      <c r="O265" s="4" t="inlineStr"/>
+      <c r="P265" s="4" t="inlineStr"/>
+      <c r="Q265" s="4" t="inlineStr"/>
+      <c r="R265" s="4" t="inlineStr"/>
+      <c r="S265" s="4" t="inlineStr"/>
+      <c r="T265" s="4" t="inlineStr">
+        <is>
+          <t>🟡 WAIT (Δ+4.4%) · Rank #10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U265" s="4" t="inlineStr"/>
+      <c r="V265" s="4" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="W265" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X265" s="4" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="Y265" s="4" t="inlineStr"/>
+      <c r="Z265" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA265" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB265" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC265" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD265" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="AE265" s="4" t="n">
+        <v>10880</v>
+      </c>
+      <c r="AF265" s="4" t="n">
+        <v>10771.2</v>
+      </c>
+      <c r="AG265" s="4" t="n">
+        <v>10988.8</v>
+      </c>
+      <c r="AH265" s="4" t="n">
+        <v>10336</v>
+      </c>
+      <c r="AI265" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ265" s="4" t="n">
+        <v>11750.4</v>
+      </c>
+      <c r="AK265" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL265" s="4" t="n">
+        <v>12512</v>
+      </c>
+      <c r="AM265" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN265" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="AO265" s="4" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AP265" s="4" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AQ265" s="4" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AR265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS265" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT265" s="4" t="inlineStr"/>
+      <c r="AU265" s="4" t="inlineStr"/>
+      <c r="AV265" s="4" t="inlineStr"/>
+      <c r="AW265" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX265" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN_IND_20260730</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr"/>
+      <c r="J266" s="4" t="inlineStr"/>
+      <c r="K266" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L266" s="4" t="inlineStr"/>
+      <c r="M266" s="4" t="inlineStr"/>
+      <c r="N266" s="4" t="inlineStr"/>
+      <c r="O266" s="4" t="inlineStr"/>
+      <c r="P266" s="4" t="inlineStr"/>
+      <c r="Q266" s="4" t="inlineStr"/>
+      <c r="R266" s="4" t="inlineStr"/>
+      <c r="S266" s="4" t="inlineStr"/>
+      <c r="T266" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.2%) · Rank #15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U266" s="4" t="inlineStr"/>
+      <c r="V266" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W266" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X266" s="4" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="Y266" s="4" t="inlineStr"/>
+      <c r="Z266" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA266" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB266" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC266" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD266" s="4" t="n">
+        <v>1384</v>
+      </c>
+      <c r="AE266" s="4" t="n">
+        <v>1373.1</v>
+      </c>
+      <c r="AF266" s="4" t="n">
+        <v>1359.37</v>
+      </c>
+      <c r="AG266" s="4" t="n">
+        <v>1386.83</v>
+      </c>
+      <c r="AH266" s="4" t="n">
+        <v>1304.445</v>
+      </c>
+      <c r="AI266" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ266" s="4" t="n">
+        <v>1482.948</v>
+      </c>
+      <c r="AK266" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL266" s="4" t="n">
+        <v>1579.065</v>
+      </c>
+      <c r="AM266" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN266" s="4" t="n">
+        <v>1384</v>
+      </c>
+      <c r="AO266" s="4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AP266" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AQ266" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR266" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="AS266" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT266" s="4" t="inlineStr"/>
+      <c r="AU266" s="4" t="inlineStr"/>
+      <c r="AV266" s="4" t="inlineStr"/>
+      <c r="AW266" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX266" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>NATIONALUM_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr"/>
+      <c r="J267" s="4" t="inlineStr"/>
+      <c r="K267" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L267" s="4" t="inlineStr"/>
+      <c r="M267" s="4" t="inlineStr"/>
+      <c r="N267" s="4" t="inlineStr"/>
+      <c r="O267" s="4" t="inlineStr"/>
+      <c r="P267" s="4" t="inlineStr"/>
+      <c r="Q267" s="4" t="inlineStr"/>
+      <c r="R267" s="4" t="inlineStr"/>
+      <c r="S267" s="4" t="inlineStr"/>
+      <c r="T267" s="4" t="inlineStr">
+        <is>
+          <t>Rank #7 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U267" s="4" t="inlineStr"/>
+      <c r="V267" s="4" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="W267" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X267" s="4" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y267" s="4" t="inlineStr"/>
+      <c r="Z267" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA267" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB267" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC267" s="4" t="inlineStr"/>
+      <c r="AD267" s="4" t="inlineStr"/>
+      <c r="AE267" s="4" t="inlineStr"/>
+      <c r="AF267" s="4" t="inlineStr"/>
+      <c r="AG267" s="4" t="inlineStr"/>
+      <c r="AH267" s="4" t="inlineStr"/>
+      <c r="AI267" s="4" t="inlineStr"/>
+      <c r="AJ267" s="4" t="inlineStr"/>
+      <c r="AK267" s="4" t="inlineStr"/>
+      <c r="AL267" s="4" t="inlineStr"/>
+      <c r="AM267" s="4" t="inlineStr"/>
+      <c r="AN267" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="AO267" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP267" s="4" t="inlineStr"/>
+      <c r="AQ267" s="4" t="inlineStr"/>
+      <c r="AR267" s="4" t="inlineStr"/>
+      <c r="AS267" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT267" s="4" t="inlineStr"/>
+      <c r="AU267" s="4" t="inlineStr"/>
+      <c r="AV267" s="4" t="inlineStr"/>
+      <c r="AW267" s="4" t="inlineStr"/>
+      <c r="AX267" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>LICI_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr"/>
+      <c r="G268" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr"/>
+      <c r="J268" s="4" t="inlineStr"/>
+      <c r="K268" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L268" s="4" t="inlineStr"/>
+      <c r="M268" s="4" t="inlineStr"/>
+      <c r="N268" s="4" t="inlineStr"/>
+      <c r="O268" s="4" t="inlineStr"/>
+      <c r="P268" s="4" t="inlineStr"/>
+      <c r="Q268" s="4" t="inlineStr"/>
+      <c r="R268" s="4" t="inlineStr"/>
+      <c r="S268" s="4" t="inlineStr"/>
+      <c r="T268" s="4" t="inlineStr">
+        <is>
+          <t>Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U268" s="4" t="inlineStr"/>
+      <c r="V268" s="4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="W268" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X268" s="4" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y268" s="4" t="inlineStr"/>
+      <c r="Z268" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA268" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB268" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC268" s="4" t="inlineStr"/>
+      <c r="AD268" s="4" t="inlineStr"/>
+      <c r="AE268" s="4" t="inlineStr"/>
+      <c r="AF268" s="4" t="inlineStr"/>
+      <c r="AG268" s="4" t="inlineStr"/>
+      <c r="AH268" s="4" t="inlineStr"/>
+      <c r="AI268" s="4" t="inlineStr"/>
+      <c r="AJ268" s="4" t="inlineStr"/>
+      <c r="AK268" s="4" t="inlineStr"/>
+      <c r="AL268" s="4" t="inlineStr"/>
+      <c r="AM268" s="4" t="inlineStr"/>
+      <c r="AN268" s="4" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AO268" s="4" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AP268" s="4" t="inlineStr"/>
+      <c r="AQ268" s="4" t="inlineStr"/>
+      <c r="AR268" s="4" t="inlineStr"/>
+      <c r="AS268" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT268" s="4" t="inlineStr"/>
+      <c r="AU268" s="4" t="inlineStr"/>
+      <c r="AV268" s="4" t="inlineStr"/>
+      <c r="AW268" s="4" t="inlineStr"/>
+      <c r="AX268" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>R2_ARCH</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr"/>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr"/>
+      <c r="J269" s="4" t="inlineStr"/>
+      <c r="K269" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L269" s="4" t="inlineStr"/>
+      <c r="M269" s="4" t="inlineStr"/>
+      <c r="N269" s="4" t="inlineStr"/>
+      <c r="O269" s="4" t="inlineStr"/>
+      <c r="P269" s="4" t="inlineStr"/>
+      <c r="Q269" s="4" t="inlineStr"/>
+      <c r="R269" s="4" t="inlineStr"/>
+      <c r="S269" s="4" t="inlineStr"/>
+      <c r="T269" s="4" t="inlineStr">
+        <is>
+          <t>Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U269" s="4" t="inlineStr"/>
+      <c r="V269" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W269" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X269" s="4" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="Y269" s="4" t="inlineStr"/>
+      <c r="Z269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA269" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB269" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC269" s="4" t="inlineStr"/>
+      <c r="AD269" s="4" t="inlineStr"/>
+      <c r="AE269" s="4" t="inlineStr"/>
+      <c r="AF269" s="4" t="inlineStr"/>
+      <c r="AG269" s="4" t="inlineStr"/>
+      <c r="AH269" s="4" t="inlineStr"/>
+      <c r="AI269" s="4" t="inlineStr"/>
+      <c r="AJ269" s="4" t="inlineStr"/>
+      <c r="AK269" s="4" t="inlineStr"/>
+      <c r="AL269" s="4" t="inlineStr"/>
+      <c r="AM269" s="4" t="inlineStr"/>
+      <c r="AN269" s="4" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AO269" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP269" s="4" t="inlineStr"/>
+      <c r="AQ269" s="4" t="inlineStr"/>
+      <c r="AR269" s="4" t="inlineStr"/>
+      <c r="AS269" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT269" s="4" t="inlineStr"/>
+      <c r="AU269" s="4" t="inlineStr"/>
+      <c r="AV269" s="4" t="inlineStr"/>
+      <c r="AW269" s="4" t="inlineStr"/>
+      <c r="AX269" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr"/>
+      <c r="J270" s="4" t="inlineStr"/>
+      <c r="K270" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L270" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M270" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" s="4" t="inlineStr"/>
+      <c r="O270" s="4" t="inlineStr"/>
+      <c r="P270" s="4" t="inlineStr"/>
+      <c r="Q270" s="4" t="inlineStr"/>
+      <c r="R270" s="4" t="inlineStr"/>
+      <c r="S270" s="4" t="inlineStr"/>
+      <c r="T270" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U270" s="4" t="inlineStr"/>
+      <c r="V270" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="W270" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X270" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y270" s="4" t="inlineStr"/>
+      <c r="Z270" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA270" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB270" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC270" s="4" t="inlineStr"/>
+      <c r="AD270" s="4" t="inlineStr"/>
+      <c r="AE270" s="4" t="inlineStr"/>
+      <c r="AF270" s="4" t="inlineStr"/>
+      <c r="AG270" s="4" t="inlineStr"/>
+      <c r="AH270" s="4" t="inlineStr"/>
+      <c r="AI270" s="4" t="inlineStr"/>
+      <c r="AJ270" s="4" t="inlineStr"/>
+      <c r="AK270" s="4" t="inlineStr"/>
+      <c r="AL270" s="4" t="inlineStr"/>
+      <c r="AM270" s="4" t="inlineStr"/>
+      <c r="AN270" s="4" t="n">
+        <v>1454.6</v>
+      </c>
+      <c r="AO270" s="4" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AP270" s="4" t="inlineStr"/>
+      <c r="AQ270" s="4" t="inlineStr"/>
+      <c r="AR270" s="4" t="inlineStr"/>
+      <c r="AS270" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT270" s="4" t="inlineStr"/>
+      <c r="AU270" s="4" t="inlineStr"/>
+      <c r="AV270" s="4" t="inlineStr"/>
+      <c r="AW270" s="4" t="inlineStr"/>
+      <c r="AX270" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G271" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr"/>
+      <c r="J271" s="4" t="inlineStr"/>
+      <c r="K271" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" s="4" t="inlineStr"/>
+      <c r="O271" s="4" t="inlineStr"/>
+      <c r="P271" s="4" t="inlineStr"/>
+      <c r="Q271" s="4" t="inlineStr"/>
+      <c r="R271" s="4" t="inlineStr"/>
+      <c r="S271" s="4" t="inlineStr"/>
+      <c r="T271" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U271" s="4" t="inlineStr"/>
+      <c r="V271" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="W271" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X271" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y271" s="4" t="inlineStr"/>
+      <c r="Z271" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA271" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB271" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC271" s="4" t="inlineStr"/>
+      <c r="AD271" s="4" t="inlineStr"/>
+      <c r="AE271" s="4" t="inlineStr"/>
+      <c r="AF271" s="4" t="inlineStr"/>
+      <c r="AG271" s="4" t="inlineStr"/>
+      <c r="AH271" s="4" t="inlineStr"/>
+      <c r="AI271" s="4" t="inlineStr"/>
+      <c r="AJ271" s="4" t="inlineStr"/>
+      <c r="AK271" s="4" t="inlineStr"/>
+      <c r="AL271" s="4" t="inlineStr"/>
+      <c r="AM271" s="4" t="inlineStr"/>
+      <c r="AN271" s="4" t="n">
+        <v>1964</v>
+      </c>
+      <c r="AO271" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="AP271" s="4" t="inlineStr"/>
+      <c r="AQ271" s="4" t="inlineStr"/>
+      <c r="AR271" s="4" t="inlineStr"/>
+      <c r="AS271" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT271" s="4" t="inlineStr"/>
+      <c r="AU271" s="4" t="inlineStr"/>
+      <c r="AV271" s="4" t="inlineStr"/>
+      <c r="AW271" s="4" t="inlineStr"/>
+      <c r="AX271" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G272" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr"/>
+      <c r="J272" s="4" t="inlineStr"/>
+      <c r="K272" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L272" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" s="4" t="inlineStr"/>
+      <c r="O272" s="4" t="inlineStr"/>
+      <c r="P272" s="4" t="inlineStr"/>
+      <c r="Q272" s="4" t="inlineStr"/>
+      <c r="R272" s="4" t="inlineStr"/>
+      <c r="S272" s="4" t="inlineStr"/>
+      <c r="T272" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-0.8%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U272" s="4" t="inlineStr"/>
+      <c r="V272" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W272" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X272" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y272" s="4" t="inlineStr"/>
+      <c r="Z272" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA272" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB272" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC272" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD272" s="4" t="n">
+        <v>2447</v>
+      </c>
+      <c r="AE272" s="4" t="n">
+        <v>2443.4</v>
+      </c>
+      <c r="AF272" s="4" t="n">
+        <v>2418.97</v>
+      </c>
+      <c r="AG272" s="4" t="n">
+        <v>2467.83</v>
+      </c>
+      <c r="AH272" s="4" t="n">
+        <v>2321.23</v>
+      </c>
+      <c r="AI272" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ272" s="4" t="n">
+        <v>2638.872</v>
+      </c>
+      <c r="AK272" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL272" s="4" t="n">
+        <v>2809.91</v>
+      </c>
+      <c r="AM272" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN272" s="4" t="n">
+        <v>2410</v>
+      </c>
+      <c r="AO272" s="4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AP272" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AQ272" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR272" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS272" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT272" s="4" t="inlineStr"/>
+      <c r="AU272" s="4" t="inlineStr"/>
+      <c r="AV272" s="4" t="inlineStr"/>
+      <c r="AW272" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX272" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G273" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr"/>
+      <c r="J273" s="4" t="inlineStr"/>
+      <c r="K273" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L273" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" s="4" t="inlineStr"/>
+      <c r="O273" s="4" t="inlineStr"/>
+      <c r="P273" s="4" t="inlineStr"/>
+      <c r="Q273" s="4" t="inlineStr"/>
+      <c r="R273" s="4" t="inlineStr"/>
+      <c r="S273" s="4" t="inlineStr"/>
+      <c r="T273" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U273" s="4" t="inlineStr"/>
+      <c r="V273" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="W273" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X273" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y273" s="4" t="inlineStr"/>
+      <c r="Z273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA273" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB273" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC273" s="4" t="inlineStr"/>
+      <c r="AD273" s="4" t="inlineStr"/>
+      <c r="AE273" s="4" t="inlineStr"/>
+      <c r="AF273" s="4" t="inlineStr"/>
+      <c r="AG273" s="4" t="inlineStr"/>
+      <c r="AH273" s="4" t="inlineStr"/>
+      <c r="AI273" s="4" t="inlineStr"/>
+      <c r="AJ273" s="4" t="inlineStr"/>
+      <c r="AK273" s="4" t="inlineStr"/>
+      <c r="AL273" s="4" t="inlineStr"/>
+      <c r="AM273" s="4" t="inlineStr"/>
+      <c r="AN273" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="AO273" s="4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AP273" s="4" t="inlineStr"/>
+      <c r="AQ273" s="4" t="inlineStr"/>
+      <c r="AR273" s="4" t="inlineStr"/>
+      <c r="AS273" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT273" s="4" t="inlineStr"/>
+      <c r="AU273" s="4" t="inlineStr"/>
+      <c r="AV273" s="4" t="inlineStr"/>
+      <c r="AW273" s="4" t="inlineStr"/>
+      <c r="AX273" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G274" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr"/>
+      <c r="J274" s="4" t="inlineStr"/>
+      <c r="K274" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L274" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" s="4" t="inlineStr"/>
+      <c r="O274" s="4" t="inlineStr"/>
+      <c r="P274" s="4" t="inlineStr"/>
+      <c r="Q274" s="4" t="inlineStr"/>
+      <c r="R274" s="4" t="inlineStr"/>
+      <c r="S274" s="4" t="inlineStr"/>
+      <c r="T274" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U274" s="4" t="inlineStr"/>
+      <c r="V274" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="W274" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X274" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y274" s="4" t="inlineStr"/>
+      <c r="Z274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA274" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB274" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC274" s="4" t="inlineStr"/>
+      <c r="AD274" s="4" t="inlineStr"/>
+      <c r="AE274" s="4" t="inlineStr"/>
+      <c r="AF274" s="4" t="inlineStr"/>
+      <c r="AG274" s="4" t="inlineStr"/>
+      <c r="AH274" s="4" t="inlineStr"/>
+      <c r="AI274" s="4" t="inlineStr"/>
+      <c r="AJ274" s="4" t="inlineStr"/>
+      <c r="AK274" s="4" t="inlineStr"/>
+      <c r="AL274" s="4" t="inlineStr"/>
+      <c r="AM274" s="4" t="inlineStr"/>
+      <c r="AN274" s="4" t="n">
+        <v>343.65</v>
+      </c>
+      <c r="AO274" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AP274" s="4" t="inlineStr"/>
+      <c r="AQ274" s="4" t="inlineStr"/>
+      <c r="AR274" s="4" t="inlineStr"/>
+      <c r="AS274" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT274" s="4" t="inlineStr"/>
+      <c r="AU274" s="4" t="inlineStr"/>
+      <c r="AV274" s="4" t="inlineStr"/>
+      <c r="AW274" s="4" t="inlineStr"/>
+      <c r="AX274" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr"/>
+      <c r="J275" s="4" t="inlineStr"/>
+      <c r="K275" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L275" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" s="4" t="inlineStr"/>
+      <c r="O275" s="4" t="inlineStr"/>
+      <c r="P275" s="4" t="inlineStr"/>
+      <c r="Q275" s="4" t="inlineStr"/>
+      <c r="R275" s="4" t="inlineStr"/>
+      <c r="S275" s="4" t="inlineStr"/>
+      <c r="T275" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U275" s="4" t="inlineStr"/>
+      <c r="V275" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="W275" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X275" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y275" s="4" t="inlineStr"/>
+      <c r="Z275" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA275" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB275" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC275" s="4" t="inlineStr"/>
+      <c r="AD275" s="4" t="inlineStr"/>
+      <c r="AE275" s="4" t="inlineStr"/>
+      <c r="AF275" s="4" t="inlineStr"/>
+      <c r="AG275" s="4" t="inlineStr"/>
+      <c r="AH275" s="4" t="inlineStr"/>
+      <c r="AI275" s="4" t="inlineStr"/>
+      <c r="AJ275" s="4" t="inlineStr"/>
+      <c r="AK275" s="4" t="inlineStr"/>
+      <c r="AL275" s="4" t="inlineStr"/>
+      <c r="AM275" s="4" t="inlineStr"/>
+      <c r="AN275" s="4" t="n">
+        <v>398</v>
+      </c>
+      <c r="AO275" s="4" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AP275" s="4" t="inlineStr"/>
+      <c r="AQ275" s="4" t="inlineStr"/>
+      <c r="AR275" s="4" t="inlineStr"/>
+      <c r="AS275" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT275" s="4" t="inlineStr"/>
+      <c r="AU275" s="4" t="inlineStr"/>
+      <c r="AV275" s="4" t="inlineStr"/>
+      <c r="AW275" s="4" t="inlineStr"/>
+      <c r="AX275" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr"/>
+      <c r="J276" s="4" t="inlineStr"/>
+      <c r="K276" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L276" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" s="4" t="inlineStr"/>
+      <c r="O276" s="4" t="inlineStr"/>
+      <c r="P276" s="4" t="inlineStr"/>
+      <c r="Q276" s="4" t="inlineStr"/>
+      <c r="R276" s="4" t="inlineStr"/>
+      <c r="S276" s="4" t="inlineStr"/>
+      <c r="T276" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U276" s="4" t="inlineStr"/>
+      <c r="V276" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="W276" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X276" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="Y276" s="4" t="inlineStr"/>
+      <c r="Z276" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA276" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB276" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC276" s="4" t="inlineStr"/>
+      <c r="AD276" s="4" t="inlineStr"/>
+      <c r="AE276" s="4" t="inlineStr"/>
+      <c r="AF276" s="4" t="inlineStr"/>
+      <c r="AG276" s="4" t="inlineStr"/>
+      <c r="AH276" s="4" t="inlineStr"/>
+      <c r="AI276" s="4" t="inlineStr"/>
+      <c r="AJ276" s="4" t="inlineStr"/>
+      <c r="AK276" s="4" t="inlineStr"/>
+      <c r="AL276" s="4" t="inlineStr"/>
+      <c r="AM276" s="4" t="inlineStr"/>
+      <c r="AN276" s="4" t="n">
+        <v>283.4</v>
+      </c>
+      <c r="AO276" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="AP276" s="4" t="inlineStr"/>
+      <c r="AQ276" s="4" t="inlineStr"/>
+      <c r="AR276" s="4" t="inlineStr"/>
+      <c r="AS276" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT276" s="4" t="inlineStr"/>
+      <c r="AU276" s="4" t="inlineStr"/>
+      <c r="AV276" s="4" t="inlineStr"/>
+      <c r="AW276" s="4" t="inlineStr"/>
+      <c r="AX276" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G277" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr"/>
+      <c r="J277" s="4" t="inlineStr"/>
+      <c r="K277" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L277" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M277" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" s="4" t="inlineStr"/>
+      <c r="O277" s="4" t="inlineStr"/>
+      <c r="P277" s="4" t="inlineStr"/>
+      <c r="Q277" s="4" t="inlineStr"/>
+      <c r="R277" s="4" t="inlineStr"/>
+      <c r="S277" s="4" t="inlineStr"/>
+      <c r="T277" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U277" s="4" t="inlineStr"/>
+      <c r="V277" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="W277" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X277" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y277" s="4" t="inlineStr"/>
+      <c r="Z277" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA277" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB277" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC277" s="4" t="inlineStr"/>
+      <c r="AD277" s="4" t="inlineStr"/>
+      <c r="AE277" s="4" t="inlineStr"/>
+      <c r="AF277" s="4" t="inlineStr"/>
+      <c r="AG277" s="4" t="inlineStr"/>
+      <c r="AH277" s="4" t="inlineStr"/>
+      <c r="AI277" s="4" t="inlineStr"/>
+      <c r="AJ277" s="4" t="inlineStr"/>
+      <c r="AK277" s="4" t="inlineStr"/>
+      <c r="AL277" s="4" t="inlineStr"/>
+      <c r="AM277" s="4" t="inlineStr"/>
+      <c r="AN277" s="4" t="n">
+        <v>510.25</v>
+      </c>
+      <c r="AO277" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP277" s="4" t="inlineStr"/>
+      <c r="AQ277" s="4" t="inlineStr"/>
+      <c r="AR277" s="4" t="inlineStr"/>
+      <c r="AS277" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT277" s="4" t="inlineStr"/>
+      <c r="AU277" s="4" t="inlineStr"/>
+      <c r="AV277" s="4" t="inlineStr"/>
+      <c r="AW277" s="4" t="inlineStr"/>
+      <c r="AX277" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G278" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr"/>
+      <c r="J278" s="4" t="inlineStr"/>
+      <c r="K278" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L278" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M278" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" s="4" t="inlineStr"/>
+      <c r="O278" s="4" t="inlineStr"/>
+      <c r="P278" s="4" t="inlineStr"/>
+      <c r="Q278" s="4" t="inlineStr"/>
+      <c r="R278" s="4" t="inlineStr"/>
+      <c r="S278" s="4" t="inlineStr"/>
+      <c r="T278" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U278" s="4" t="inlineStr"/>
+      <c r="V278" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="W278" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X278" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y278" s="4" t="inlineStr"/>
+      <c r="Z278" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA278" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB278" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC278" s="4" t="inlineStr"/>
+      <c r="AD278" s="4" t="inlineStr"/>
+      <c r="AE278" s="4" t="inlineStr"/>
+      <c r="AF278" s="4" t="inlineStr"/>
+      <c r="AG278" s="4" t="inlineStr"/>
+      <c r="AH278" s="4" t="inlineStr"/>
+      <c r="AI278" s="4" t="inlineStr"/>
+      <c r="AJ278" s="4" t="inlineStr"/>
+      <c r="AK278" s="4" t="inlineStr"/>
+      <c r="AL278" s="4" t="inlineStr"/>
+      <c r="AM278" s="4" t="inlineStr"/>
+      <c r="AN278" s="4" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="AO278" s="4" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="AP278" s="4" t="inlineStr"/>
+      <c r="AQ278" s="4" t="inlineStr"/>
+      <c r="AR278" s="4" t="inlineStr"/>
+      <c r="AS278" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT278" s="4" t="inlineStr"/>
+      <c r="AU278" s="4" t="inlineStr"/>
+      <c r="AV278" s="4" t="inlineStr"/>
+      <c r="AW278" s="4" t="inlineStr"/>
+      <c r="AX278" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260729</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G279" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr"/>
+      <c r="J279" s="4" t="inlineStr"/>
+      <c r="K279" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L279" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M279" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" s="4" t="inlineStr"/>
+      <c r="O279" s="4" t="inlineStr"/>
+      <c r="P279" s="4" t="inlineStr"/>
+      <c r="Q279" s="4" t="inlineStr"/>
+      <c r="R279" s="4" t="inlineStr"/>
+      <c r="S279" s="4" t="inlineStr"/>
+      <c r="T279" s="4" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.1%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U279" s="4" t="inlineStr"/>
+      <c r="V279" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="W279" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X279" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y279" s="4" t="inlineStr"/>
+      <c r="Z279" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA279" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB279" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC279" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD279" s="4" t="n">
+        <v>410.05</v>
+      </c>
+      <c r="AE279" s="4" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="AF279" s="4" t="n">
+        <v>406.39</v>
+      </c>
+      <c r="AG279" s="4" t="n">
+        <v>414.61</v>
+      </c>
+      <c r="AH279" s="4" t="n">
+        <v>389.975</v>
+      </c>
+      <c r="AI279" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ279" s="4" t="n">
+        <v>443.34</v>
+      </c>
+      <c r="AK279" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL279" s="4" t="n">
+        <v>472.075</v>
+      </c>
+      <c r="AM279" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN279" s="4" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AO279" s="4" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AP279" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AQ279" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR279" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AS279" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT279" s="4" t="inlineStr"/>
+      <c r="AU279" s="4" t="inlineStr"/>
+      <c r="AV279" s="4" t="inlineStr"/>
+      <c r="AW279" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX279" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr"/>
+      <c r="J280" s="4" t="inlineStr"/>
+      <c r="K280" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L280" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="4" t="inlineStr"/>
+      <c r="O280" s="4" t="inlineStr"/>
+      <c r="P280" s="4" t="inlineStr"/>
+      <c r="Q280" s="4" t="inlineStr"/>
+      <c r="R280" s="4" t="inlineStr"/>
+      <c r="S280" s="4" t="inlineStr"/>
+      <c r="T280" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U280" s="4" t="inlineStr"/>
+      <c r="V280" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="W280" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X280" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y280" s="4" t="inlineStr"/>
+      <c r="Z280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA280" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB280" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC280" s="4" t="inlineStr"/>
+      <c r="AD280" s="4" t="inlineStr"/>
+      <c r="AE280" s="4" t="inlineStr"/>
+      <c r="AF280" s="4" t="inlineStr"/>
+      <c r="AG280" s="4" t="inlineStr"/>
+      <c r="AH280" s="4" t="inlineStr"/>
+      <c r="AI280" s="4" t="inlineStr"/>
+      <c r="AJ280" s="4" t="inlineStr"/>
+      <c r="AK280" s="4" t="inlineStr"/>
+      <c r="AL280" s="4" t="inlineStr"/>
+      <c r="AM280" s="4" t="inlineStr"/>
+      <c r="AN280" s="4" t="n">
+        <v>5478</v>
+      </c>
+      <c r="AO280" s="4" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AP280" s="4" t="inlineStr"/>
+      <c r="AQ280" s="4" t="inlineStr"/>
+      <c r="AR280" s="4" t="inlineStr"/>
+      <c r="AS280" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT280" s="4" t="inlineStr"/>
+      <c r="AU280" s="4" t="inlineStr"/>
+      <c r="AV280" s="4" t="inlineStr"/>
+      <c r="AW280" s="4" t="inlineStr"/>
+      <c r="AX280" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260807</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>R1_ARCH</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="G281" s="4" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr"/>
+      <c r="J281" s="4" t="inlineStr"/>
+      <c r="K281" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L281" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M281" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" s="4" t="inlineStr"/>
+      <c r="O281" s="4" t="inlineStr"/>
+      <c r="P281" s="4" t="inlineStr"/>
+      <c r="Q281" s="4" t="inlineStr"/>
+      <c r="R281" s="4" t="inlineStr"/>
+      <c r="S281" s="4" t="inlineStr"/>
+      <c r="T281" s="4" t="inlineStr">
+        <is>
+          <t>Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U281" s="4" t="inlineStr"/>
+      <c r="V281" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="W281" s="4" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X281" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y281" s="4" t="inlineStr"/>
+      <c r="Z281" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA281" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB281" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AC281" s="4" t="inlineStr"/>
+      <c r="AD281" s="4" t="inlineStr"/>
+      <c r="AE281" s="4" t="inlineStr"/>
+      <c r="AF281" s="4" t="inlineStr"/>
+      <c r="AG281" s="4" t="inlineStr"/>
+      <c r="AH281" s="4" t="inlineStr"/>
+      <c r="AI281" s="4" t="inlineStr"/>
+      <c r="AJ281" s="4" t="inlineStr"/>
+      <c r="AK281" s="4" t="inlineStr"/>
+      <c r="AL281" s="4" t="inlineStr"/>
+      <c r="AM281" s="4" t="inlineStr"/>
+      <c r="AN281" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="AO281" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AP281" s="4" t="inlineStr"/>
+      <c r="AQ281" s="4" t="inlineStr"/>
+      <c r="AR281" s="4" t="inlineStr"/>
+      <c r="AS281" s="4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AT281" s="4" t="inlineStr"/>
+      <c r="AU281" s="4" t="inlineStr"/>
+      <c r="AV281" s="4" t="inlineStr"/>
+      <c r="AW281" s="4" t="inlineStr"/>
+      <c r="AX281" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AX225"/>
+  <autoFilter ref="A1:AX281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU126"/>
+  <dimension ref="A1:AU171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18698,8 +18698,6511 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>TCS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr"/>
+      <c r="I127" s="13" t="inlineStr"/>
+      <c r="J127" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L127" s="13" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="N127" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P127" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q127" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R127" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→1 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S127" s="13" t="inlineStr"/>
+      <c r="T127" s="13" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U127" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V127" s="13" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W127" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X127" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y127" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z127" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA127" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB127" s="13" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="AC127" s="13" t="n">
+        <v>2351.3</v>
+      </c>
+      <c r="AD127" s="13" t="n">
+        <v>2428.17</v>
+      </c>
+      <c r="AE127" s="13" t="n">
+        <v>2477.23</v>
+      </c>
+      <c r="AF127" s="13" t="n">
+        <v>2305.54</v>
+      </c>
+      <c r="AG127" s="13" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="AH127" s="13" t="n">
+        <v>2747.02</v>
+      </c>
+      <c r="AI127" s="13" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="AJ127" s="13" t="n">
+        <v>3041.35</v>
+      </c>
+      <c r="AK127" s="13" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="AL127" s="13" t="n">
+        <v>2421.9</v>
+      </c>
+      <c r="AM127" s="13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN127" s="13" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AO127" s="13" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AP127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ127" s="13" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Momentum</t>
+        </is>
+      </c>
+      <c r="AR127" s="13" t="inlineStr"/>
+      <c r="AS127" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>GNFC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="inlineStr"/>
+      <c r="I128" s="13" t="inlineStr"/>
+      <c r="J128" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K128" s="13" t="inlineStr"/>
+      <c r="L128" s="13" t="inlineStr"/>
+      <c r="M128" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="N128" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O128" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P128" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q128" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R128" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S128" s="13" t="inlineStr"/>
+      <c r="T128" s="13" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="U128" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V128" s="13" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="W128" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X128" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y128" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z128" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA128" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB128" s="13" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="AC128" s="13" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AD128" s="13" t="n">
+        <v>530.14</v>
+      </c>
+      <c r="AE128" s="13" t="n">
+        <v>540.86</v>
+      </c>
+      <c r="AF128" s="13" t="n">
+        <v>503.37</v>
+      </c>
+      <c r="AG128" s="13" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="AH128" s="13" t="n">
+        <v>599.76</v>
+      </c>
+      <c r="AI128" s="13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ128" s="13" t="n">
+        <v>664.02</v>
+      </c>
+      <c r="AK128" s="13" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="AL128" s="13" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AM128" s="13" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AN128" s="13" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AO128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" s="13" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AQ128" s="13" t="inlineStr">
+        <is>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AR128" s="13" t="inlineStr"/>
+      <c r="AS128" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>OFSS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="inlineStr"/>
+      <c r="I129" s="14" t="inlineStr"/>
+      <c r="J129" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K129" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L129" s="14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M129" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="N129" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O129" s="14" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="P129" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q129" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R129" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 6→3 · Conf 46% · band HOLD · 16d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S129" s="14" t="inlineStr"/>
+      <c r="T129" s="14" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="U129" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V129" s="14" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="W129" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X129" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y129" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z129" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA129" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB129" s="14" t="n">
+        <v>11805</v>
+      </c>
+      <c r="AC129" s="14" t="n">
+        <v>11075</v>
+      </c>
+      <c r="AD129" s="14" t="n">
+        <v>11686.95</v>
+      </c>
+      <c r="AE129" s="14" t="n">
+        <v>11923.05</v>
+      </c>
+      <c r="AF129" s="14" t="n">
+        <v>11096.7</v>
+      </c>
+      <c r="AG129" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH129" s="14" t="n">
+        <v>13221.6</v>
+      </c>
+      <c r="AI129" s="14" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="AJ129" s="14" t="n">
+        <v>14638.2</v>
+      </c>
+      <c r="AK129" s="14" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="AL129" s="14" t="n">
+        <v>11727</v>
+      </c>
+      <c r="AM129" s="14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN129" s="14" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AO129" s="14" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="AP129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ129" s="14" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Momentum</t>
+        </is>
+      </c>
+      <c r="AR129" s="14" t="inlineStr"/>
+      <c r="AS129" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>CANBK_IND_20260810</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr"/>
+      <c r="G130" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +6.5pp alpha</t>
+        </is>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K130" s="15" t="inlineStr"/>
+      <c r="L130" s="15" t="inlineStr"/>
+      <c r="M130" s="15" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="N130" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O130" s="15" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P130" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q130" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R130" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #5 · Conf 32% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="S130" s="15" t="inlineStr"/>
+      <c r="T130" s="15" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="U130" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V130" s="15" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="W130" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z130" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA130" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB130" s="15" t="n">
+        <v>131.95</v>
+      </c>
+      <c r="AC130" s="15" t="n">
+        <v>131.95</v>
+      </c>
+      <c r="AD130" s="15" t="n">
+        <v>130.63</v>
+      </c>
+      <c r="AE130" s="15" t="n">
+        <v>133.27</v>
+      </c>
+      <c r="AF130" s="15" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="AG130" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH130" s="15" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="AI130" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ130" s="15" t="n">
+        <v>151.74</v>
+      </c>
+      <c r="AK130" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL130" s="15" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="AM130" s="15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AN130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ130" s="15" t="inlineStr">
+        <is>
+          <t>Value · Mean Reversion · Quality</t>
+        </is>
+      </c>
+      <c r="AR130" s="15" t="inlineStr"/>
+      <c r="AS130" s="15" t="inlineStr"/>
+      <c r="AT130" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AU130" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>UNIONBANK_IND_20260810</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr"/>
+      <c r="G131" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +9.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K131" s="15" t="inlineStr"/>
+      <c r="L131" s="15" t="inlineStr"/>
+      <c r="M131" s="15" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N131" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O131" s="15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="P131" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q131" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R131" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #10 · Conf 30% · band HOLD · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="S131" s="15" t="inlineStr"/>
+      <c r="T131" s="15" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="U131" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V131" s="15" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W131" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z131" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA131" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB131" s="15" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AC131" s="15" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AD131" s="15" t="n">
+        <v>181.76</v>
+      </c>
+      <c r="AE131" s="15" t="n">
+        <v>185.44</v>
+      </c>
+      <c r="AF131" s="15" t="n">
+        <v>174.42</v>
+      </c>
+      <c r="AG131" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH131" s="15" t="n">
+        <v>198.29</v>
+      </c>
+      <c r="AI131" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ131" s="15" t="n">
+        <v>211.14</v>
+      </c>
+      <c r="AK131" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL131" s="15" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="AM131" s="15" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AN131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ131" s="15" t="inlineStr">
+        <is>
+          <t>Value · Momentum · Quality</t>
+        </is>
+      </c>
+      <c r="AR131" s="15" t="inlineStr"/>
+      <c r="AS131" s="15" t="inlineStr"/>
+      <c r="AT131" s="15" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AU131" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPHARM_IND_20260810</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +60.1pp alpha</t>
+        </is>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K132" s="15" t="inlineStr"/>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="N132" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O132" s="15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="P132" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q132" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R132" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #12 · Conf 26% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="S132" s="15" t="inlineStr"/>
+      <c r="T132" s="15" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="U132" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V132" s="15" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="W132" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z132" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA132" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB132" s="15" t="n">
+        <v>4924</v>
+      </c>
+      <c r="AC132" s="15" t="n">
+        <v>4924</v>
+      </c>
+      <c r="AD132" s="15" t="n">
+        <v>4874.76</v>
+      </c>
+      <c r="AE132" s="15" t="n">
+        <v>4973.24</v>
+      </c>
+      <c r="AF132" s="15" t="n">
+        <v>4677.8</v>
+      </c>
+      <c r="AG132" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH132" s="15" t="n">
+        <v>5317.92</v>
+      </c>
+      <c r="AI132" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ132" s="15" t="n">
+        <v>5662.6</v>
+      </c>
+      <c r="AK132" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL132" s="15" t="n">
+        <v>5020.5</v>
+      </c>
+      <c r="AM132" s="15" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="AN132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ132" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AR132" s="15" t="inlineStr"/>
+      <c r="AS132" s="15" t="inlineStr"/>
+      <c r="AT132" s="15" t="n">
+        <v>60.07</v>
+      </c>
+      <c r="AU132" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>AMBER_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Amber Ent.</t>
+        </is>
+      </c>
+      <c r="G133" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H133" s="15" t="inlineStr">
+        <is>
+          <t>→ TCS.NS · +62.1pp alpha</t>
+        </is>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J133" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K133" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="L133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="15" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="N133" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O133" s="15" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="P133" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q133" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+31 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R133" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 14→14 · Conf 24% · band EXIT · 60d left · → EXIT (rotate to TCS.NS)</t>
+        </is>
+      </c>
+      <c r="S133" s="15" t="inlineStr"/>
+      <c r="T133" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="U133" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V133" s="15" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="W133" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X133" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y133" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z133" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA133" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB133" s="15" t="n">
+        <v>7435</v>
+      </c>
+      <c r="AC133" s="15" t="n">
+        <v>7454.5</v>
+      </c>
+      <c r="AD133" s="15" t="n">
+        <v>7379.95</v>
+      </c>
+      <c r="AE133" s="15" t="n">
+        <v>7529.05</v>
+      </c>
+      <c r="AF133" s="15" t="n">
+        <v>7081.77</v>
+      </c>
+      <c r="AG133" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH133" s="15" t="n">
+        <v>8050.86</v>
+      </c>
+      <c r="AI133" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ133" s="15" t="n">
+        <v>8572.67</v>
+      </c>
+      <c r="AK133" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL133" s="15" t="n">
+        <v>7531.5</v>
+      </c>
+      <c r="AM133" s="15" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AN133" s="15" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AO133" s="15" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AP133" s="15" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AQ133" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Fund Debt To Equity</t>
+        </is>
+      </c>
+      <c r="AR133" s="15" t="inlineStr"/>
+      <c r="AS133" s="15" t="inlineStr"/>
+      <c r="AT133" s="15" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="AU133" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr"/>
+      <c r="I134" s="13" t="inlineStr"/>
+      <c r="J134" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L134" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M134" s="13" t="inlineStr"/>
+      <c r="N134" s="13" t="inlineStr"/>
+      <c r="O134" s="13" t="inlineStr"/>
+      <c r="P134" s="13" t="inlineStr"/>
+      <c r="Q134" s="13" t="inlineStr"/>
+      <c r="R134" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S134" s="13" t="inlineStr"/>
+      <c r="T134" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="U134" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V134" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="W134" s="13" t="inlineStr"/>
+      <c r="X134" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y134" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z134" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA134" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB134" s="13" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AC134" s="13" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD134" s="13" t="n">
+        <v>1382</v>
+      </c>
+      <c r="AE134" s="13" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AF134" s="13" t="n">
+        <v>1349.95</v>
+      </c>
+      <c r="AG134" s="13" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="AH134" s="13" t="n">
+        <v>1497</v>
+      </c>
+      <c r="AI134" s="13" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AJ134" s="13" t="n">
+        <v>1601.79</v>
+      </c>
+      <c r="AK134" s="13" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="AL134" s="13" t="n">
+        <v>1449.6</v>
+      </c>
+      <c r="AM134" s="13" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="AN134" s="13" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="AO134" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP134" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ134" s="13" t="inlineStr"/>
+      <c r="AR134" s="13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS134" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT134" s="13" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AU134" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr"/>
+      <c r="I135" s="13" t="inlineStr"/>
+      <c r="J135" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="13" t="inlineStr"/>
+      <c r="N135" s="13" t="inlineStr"/>
+      <c r="O135" s="13" t="inlineStr"/>
+      <c r="P135" s="13" t="inlineStr"/>
+      <c r="Q135" s="13" t="inlineStr"/>
+      <c r="R135" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 88% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S135" s="13" t="inlineStr"/>
+      <c r="T135" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="U135" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V135" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="W135" s="13" t="inlineStr"/>
+      <c r="X135" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y135" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z135" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA135" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB135" s="13" t="n">
+        <v>1945</v>
+      </c>
+      <c r="AC135" s="13" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AD135" s="13" t="n">
+        <v>1893</v>
+      </c>
+      <c r="AE135" s="13" t="n">
+        <v>1997</v>
+      </c>
+      <c r="AF135" s="13" t="n">
+        <v>1847.75</v>
+      </c>
+      <c r="AG135" s="13" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="AH135" s="13" t="n">
+        <v>2034</v>
+      </c>
+      <c r="AI135" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ135" s="13" t="n">
+        <v>2176.38</v>
+      </c>
+      <c r="AK135" s="13" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AL135" s="13" t="n">
+        <v>1949</v>
+      </c>
+      <c r="AM135" s="13" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AN135" s="13" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="AO135" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP135" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ135" s="13" t="inlineStr"/>
+      <c r="AR135" s="13" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS135" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT135" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AU135" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr"/>
+      <c r="I136" s="13" t="inlineStr"/>
+      <c r="J136" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="13" t="inlineStr"/>
+      <c r="N136" s="13" t="inlineStr"/>
+      <c r="O136" s="13" t="inlineStr"/>
+      <c r="P136" s="13" t="inlineStr"/>
+      <c r="Q136" s="13" t="inlineStr"/>
+      <c r="R136" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S136" s="13" t="inlineStr"/>
+      <c r="T136" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="U136" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V136" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="W136" s="13" t="inlineStr"/>
+      <c r="X136" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y136" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z136" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA136" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB136" s="13" t="n">
+        <v>1660</v>
+      </c>
+      <c r="AC136" s="13" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AD136" s="13" t="n">
+        <v>1607</v>
+      </c>
+      <c r="AE136" s="13" t="n">
+        <v>1713</v>
+      </c>
+      <c r="AF136" s="13" t="n">
+        <v>1577</v>
+      </c>
+      <c r="AG136" s="13" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="AH136" s="13" t="n">
+        <v>1683</v>
+      </c>
+      <c r="AI136" s="13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AJ136" s="13" t="n">
+        <v>1800.81</v>
+      </c>
+      <c r="AK136" s="13" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AL136" s="13" t="n">
+        <v>1657</v>
+      </c>
+      <c r="AM136" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN136" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ136" s="13" t="inlineStr"/>
+      <c r="AR136" s="13" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="AS136" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT136" s="13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AU136" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr"/>
+      <c r="I137" s="13" t="inlineStr"/>
+      <c r="J137" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="13" t="inlineStr"/>
+      <c r="N137" s="13" t="inlineStr"/>
+      <c r="O137" s="13" t="inlineStr"/>
+      <c r="P137" s="13" t="inlineStr"/>
+      <c r="Q137" s="13" t="inlineStr"/>
+      <c r="R137" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→4 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S137" s="13" t="inlineStr"/>
+      <c r="T137" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="U137" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V137" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="W137" s="13" t="inlineStr"/>
+      <c r="X137" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y137" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z137" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA137" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB137" s="13" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AC137" s="13" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD137" s="13" t="n">
+        <v>2303</v>
+      </c>
+      <c r="AE137" s="13" t="n">
+        <v>2424</v>
+      </c>
+      <c r="AF137" s="13" t="n">
+        <v>2245.325</v>
+      </c>
+      <c r="AG137" s="13" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="AH137" s="13" t="n">
+        <v>2552.58</v>
+      </c>
+      <c r="AI137" s="13" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AJ137" s="13" t="n">
+        <v>2731.260600000001</v>
+      </c>
+      <c r="AK137" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL137" s="13" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AM137" s="13" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AN137" s="13" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="AO137" s="13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP137" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ137" s="13" t="inlineStr"/>
+      <c r="AR137" s="13" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS137" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT137" s="13" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AU137" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G138" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="inlineStr"/>
+      <c r="I138" s="13" t="inlineStr"/>
+      <c r="J138" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K138" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L138" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="13" t="inlineStr"/>
+      <c r="N138" s="13" t="inlineStr"/>
+      <c r="O138" s="13" t="inlineStr"/>
+      <c r="P138" s="13" t="inlineStr"/>
+      <c r="Q138" s="13" t="inlineStr"/>
+      <c r="R138" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.8%) · Rank → 5→5 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S138" s="13" t="inlineStr"/>
+      <c r="T138" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="U138" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V138" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="W138" s="13" t="inlineStr"/>
+      <c r="X138" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y138" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z138" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA138" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB138" s="13" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="AC138" s="13" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD138" s="13" t="n">
+        <v>379</v>
+      </c>
+      <c r="AE138" s="13" t="n">
+        <v>402</v>
+      </c>
+      <c r="AF138" s="13" t="n">
+        <v>371.26</v>
+      </c>
+      <c r="AG138" s="13" t="n">
+        <v>-4.63</v>
+      </c>
+      <c r="AH138" s="13" t="n">
+        <v>422.064</v>
+      </c>
+      <c r="AI138" s="13" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AJ138" s="13" t="n">
+        <v>451.60848</v>
+      </c>
+      <c r="AK138" s="13" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="AL138" s="13" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="AM138" s="13" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="AN138" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AO138" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP138" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ138" s="13" t="inlineStr"/>
+      <c r="AR138" s="13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS138" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT138" s="13" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="AU138" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr"/>
+      <c r="I139" s="14" t="inlineStr"/>
+      <c r="J139" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L139" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M139" s="14" t="inlineStr"/>
+      <c r="N139" s="14" t="inlineStr"/>
+      <c r="O139" s="14" t="inlineStr"/>
+      <c r="P139" s="14" t="inlineStr"/>
+      <c r="Q139" s="14" t="inlineStr"/>
+      <c r="R139" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank ↓ 4→6 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S139" s="14" t="inlineStr"/>
+      <c r="T139" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="U139" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V139" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="W139" s="14" t="inlineStr"/>
+      <c r="X139" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y139" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z139" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA139" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB139" s="14" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AC139" s="14" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD139" s="14" t="n">
+        <v>334</v>
+      </c>
+      <c r="AE139" s="14" t="n">
+        <v>351</v>
+      </c>
+      <c r="AF139" s="14" t="n">
+        <v>325.375</v>
+      </c>
+      <c r="AG139" s="14" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="AH139" s="14" t="n">
+        <v>369.9</v>
+      </c>
+      <c r="AI139" s="14" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AJ139" s="14" t="n">
+        <v>395.7930000000001</v>
+      </c>
+      <c r="AK139" s="14" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AL139" s="14" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="AM139" s="14" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AN139" s="14" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO139" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP139" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ139" s="14" t="inlineStr"/>
+      <c r="AR139" s="14" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS139" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT139" s="14" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="AU139" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr"/>
+      <c r="I140" s="14" t="inlineStr"/>
+      <c r="J140" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K140" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L140" s="14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M140" s="14" t="inlineStr"/>
+      <c r="N140" s="14" t="inlineStr"/>
+      <c r="O140" s="14" t="inlineStr"/>
+      <c r="P140" s="14" t="inlineStr"/>
+      <c r="Q140" s="14" t="inlineStr"/>
+      <c r="R140" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.1%) · Rank ↑ 8→7 · Conf 65% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S140" s="14" t="inlineStr"/>
+      <c r="T140" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="U140" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V140" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="W140" s="14" t="inlineStr"/>
+      <c r="X140" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y140" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z140" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA140" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB140" s="14" t="n">
+        <v>401</v>
+      </c>
+      <c r="AC140" s="14" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD140" s="14" t="n">
+        <v>388</v>
+      </c>
+      <c r="AE140" s="14" t="n">
+        <v>414</v>
+      </c>
+      <c r="AF140" s="14" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="AG140" s="14" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="AH140" s="14" t="n">
+        <v>433.08</v>
+      </c>
+      <c r="AI140" s="14" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="AJ140" s="14" t="n">
+        <v>463.3956000000001</v>
+      </c>
+      <c r="AK140" s="14" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="AL140" s="14" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="AM140" s="14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AN140" s="14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AO140" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP140" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ140" s="14" t="inlineStr"/>
+      <c r="AR140" s="14" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AS140" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT140" s="14" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="AU140" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="inlineStr"/>
+      <c r="I141" s="14" t="inlineStr"/>
+      <c r="J141" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K141" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L141" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="14" t="inlineStr"/>
+      <c r="N141" s="14" t="inlineStr"/>
+      <c r="O141" s="14" t="inlineStr"/>
+      <c r="P141" s="14" t="inlineStr"/>
+      <c r="Q141" s="14" t="inlineStr"/>
+      <c r="R141" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.3%) · Rank ↓ 7→8 · Conf 68% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S141" s="14" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T141" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="U141" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V141" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="W141" s="14" t="inlineStr"/>
+      <c r="X141" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y141" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z141" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA141" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB141" s="14" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AC141" s="14" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD141" s="14" t="n">
+        <v>265</v>
+      </c>
+      <c r="AE141" s="14" t="n">
+        <v>278</v>
+      </c>
+      <c r="AF141" s="14" t="n">
+        <v>258.02</v>
+      </c>
+      <c r="AG141" s="14" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="AH141" s="14" t="n">
+        <v>293.328</v>
+      </c>
+      <c r="AI141" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ141" s="14" t="n">
+        <v>313.86096</v>
+      </c>
+      <c r="AK141" s="14" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="AL141" s="14" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="AM141" s="14" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="AN141" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AO141" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP141" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ141" s="14" t="inlineStr"/>
+      <c r="AR141" s="14" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS141" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT141" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU141" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr"/>
+      <c r="I142" s="16" t="inlineStr"/>
+      <c r="J142" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K142" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L142" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" s="16" t="inlineStr"/>
+      <c r="N142" s="16" t="inlineStr"/>
+      <c r="O142" s="16" t="inlineStr"/>
+      <c r="P142" s="16" t="inlineStr"/>
+      <c r="Q142" s="16" t="inlineStr"/>
+      <c r="R142" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 68% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S142" s="16" t="inlineStr"/>
+      <c r="T142" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="U142" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V142" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="W142" s="16" t="inlineStr"/>
+      <c r="X142" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y142" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z142" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA142" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB142" s="16" t="n">
+        <v>520</v>
+      </c>
+      <c r="AC142" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD142" s="16" t="n">
+        <v>504</v>
+      </c>
+      <c r="AE142" s="16" t="n">
+        <v>536</v>
+      </c>
+      <c r="AF142" s="16" t="n">
+        <v>494</v>
+      </c>
+      <c r="AG142" s="16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AH142" s="16" t="n">
+        <v>561.6</v>
+      </c>
+      <c r="AI142" s="16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AJ142" s="16" t="n">
+        <v>600.912</v>
+      </c>
+      <c r="AK142" s="16" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AL142" s="16" t="n">
+        <v>510.85</v>
+      </c>
+      <c r="AM142" s="16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN142" s="16" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="AO142" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP142" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ142" s="16" t="inlineStr"/>
+      <c r="AR142" s="16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AS142" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT142" s="16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AU142" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr"/>
+      <c r="I143" s="14" t="inlineStr"/>
+      <c r="J143" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K143" s="14" t="inlineStr"/>
+      <c r="L143" s="14" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+      <c r="N143" s="14" t="inlineStr"/>
+      <c r="O143" s="14" t="inlineStr"/>
+      <c r="P143" s="14" t="inlineStr"/>
+      <c r="Q143" s="14" t="inlineStr"/>
+      <c r="R143" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank #10 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S143" s="14" t="inlineStr"/>
+      <c r="T143" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="U143" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V143" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="W143" s="14" t="inlineStr"/>
+      <c r="X143" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y143" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z143" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA143" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB143" s="14" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AC143" s="14" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD143" s="14" t="n">
+        <v>279</v>
+      </c>
+      <c r="AE143" s="14" t="n">
+        <v>293</v>
+      </c>
+      <c r="AF143" s="14" t="n">
+        <v>271.795</v>
+      </c>
+      <c r="AG143" s="14" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AH143" s="14" t="n">
+        <v>287</v>
+      </c>
+      <c r="AI143" s="14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ143" s="14" t="n">
+        <v>307.09</v>
+      </c>
+      <c r="AK143" s="14" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AL143" s="14" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="AM143" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN143" s="14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO143" s="14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP143" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ143" s="14" t="inlineStr"/>
+      <c r="AR143" s="14" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS143" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT143" s="14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU143" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr"/>
+      <c r="I144" s="14" t="inlineStr"/>
+      <c r="J144" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K144" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L144" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="14" t="inlineStr"/>
+      <c r="N144" s="14" t="inlineStr"/>
+      <c r="O144" s="14" t="inlineStr"/>
+      <c r="P144" s="14" t="inlineStr"/>
+      <c r="Q144" s="14" t="inlineStr"/>
+      <c r="R144" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 10→11 · Conf 67% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S144" s="14" t="inlineStr"/>
+      <c r="T144" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="U144" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V144" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="W144" s="14" t="inlineStr"/>
+      <c r="X144" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y144" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z144" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA144" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB144" s="14" t="n">
+        <v>415.2</v>
+      </c>
+      <c r="AC144" s="14" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD144" s="14" t="n">
+        <v>403</v>
+      </c>
+      <c r="AE144" s="14" t="n">
+        <v>428</v>
+      </c>
+      <c r="AF144" s="14" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="AG144" s="14" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="AH144" s="14" t="n">
+        <v>448.416</v>
+      </c>
+      <c r="AI144" s="14" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AJ144" s="14" t="n">
+        <v>479.80512</v>
+      </c>
+      <c r="AK144" s="14" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="AL144" s="14" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="AM144" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN144" s="14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AO144" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP144" s="14" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ144" s="14" t="inlineStr"/>
+      <c r="AR144" s="14" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="AS144" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT144" s="14" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="AU144" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H145" s="16" t="inlineStr"/>
+      <c r="I145" s="16" t="inlineStr"/>
+      <c r="J145" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K145" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L145" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M145" s="16" t="inlineStr"/>
+      <c r="N145" s="16" t="inlineStr"/>
+      <c r="O145" s="16" t="inlineStr"/>
+      <c r="P145" s="16" t="inlineStr"/>
+      <c r="Q145" s="16" t="inlineStr"/>
+      <c r="R145" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→12 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S145" s="16" t="inlineStr"/>
+      <c r="T145" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U145" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V145" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="W145" s="16" t="inlineStr"/>
+      <c r="X145" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y145" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z145" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA145" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB145" s="16" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AC145" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD145" s="16" t="n">
+        <v>5366</v>
+      </c>
+      <c r="AE145" s="16" t="n">
+        <v>5654</v>
+      </c>
+      <c r="AF145" s="16" t="n">
+        <v>5234.5</v>
+      </c>
+      <c r="AG145" s="16" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="AH145" s="16" t="n">
+        <v>5950.8</v>
+      </c>
+      <c r="AI145" s="16" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AJ145" s="16" t="n">
+        <v>6367.356000000001</v>
+      </c>
+      <c r="AK145" s="16" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AL145" s="16" t="n">
+        <v>5429</v>
+      </c>
+      <c r="AM145" s="16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN145" s="16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO145" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP145" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ145" s="16" t="inlineStr"/>
+      <c r="AR145" s="16" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS145" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT145" s="16" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="AU145" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G146" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H146" s="16" t="inlineStr"/>
+      <c r="I146" s="16" t="inlineStr"/>
+      <c r="J146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="16" t="inlineStr"/>
+      <c r="N146" s="16" t="inlineStr"/>
+      <c r="O146" s="16" t="inlineStr"/>
+      <c r="P146" s="16" t="inlineStr"/>
+      <c r="Q146" s="16" t="inlineStr"/>
+      <c r="R146" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S146" s="16" t="inlineStr"/>
+      <c r="T146" s="16" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="U146" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V146" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="W146" s="16" t="inlineStr"/>
+      <c r="X146" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y146" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z146" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA146" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB146" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AC146" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD146" s="16" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE146" s="16" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF146" s="16" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG146" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH146" s="16" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI146" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ146" s="16" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK146" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL146" s="16" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AM146" s="16" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AN146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO146" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP146" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ146" s="16" t="inlineStr"/>
+      <c r="AR146" s="16" t="inlineStr"/>
+      <c r="AS146" s="16" t="inlineStr"/>
+      <c r="AT146" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU146" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H147" s="16" t="inlineStr"/>
+      <c r="I147" s="16" t="inlineStr"/>
+      <c r="J147" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K147" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L147" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M147" s="16" t="inlineStr"/>
+      <c r="N147" s="16" t="inlineStr"/>
+      <c r="O147" s="16" t="inlineStr"/>
+      <c r="P147" s="16" t="inlineStr"/>
+      <c r="Q147" s="16" t="inlineStr"/>
+      <c r="R147" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S147" s="16" t="inlineStr"/>
+      <c r="T147" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U147" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V147" s="16" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W147" s="16" t="inlineStr"/>
+      <c r="X147" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y147" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z147" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA147" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB147" s="16" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="AC147" s="16" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="AD147" s="16" t="n">
+        <v>438.92</v>
+      </c>
+      <c r="AE147" s="16" t="n">
+        <v>447.78</v>
+      </c>
+      <c r="AF147" s="16" t="n">
+        <v>421.1825</v>
+      </c>
+      <c r="AG147" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH147" s="16" t="n">
+        <v>478.818</v>
+      </c>
+      <c r="AI147" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ147" s="16" t="n">
+        <v>509.8525</v>
+      </c>
+      <c r="AK147" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL147" s="16" t="n">
+        <v>459.55</v>
+      </c>
+      <c r="AM147" s="16" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AN147" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO147" s="16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP147" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ147" s="16" t="inlineStr"/>
+      <c r="AR147" s="16" t="inlineStr"/>
+      <c r="AS147" s="16" t="inlineStr"/>
+      <c r="AT147" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU147" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>PNB_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Punjab Natl. Bank</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="inlineStr"/>
+      <c r="J148" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K148" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="16" t="inlineStr"/>
+      <c r="N148" s="16" t="inlineStr"/>
+      <c r="O148" s="16" t="inlineStr"/>
+      <c r="P148" s="16" t="inlineStr"/>
+      <c r="Q148" s="16" t="inlineStr"/>
+      <c r="R148" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S148" s="16" t="inlineStr"/>
+      <c r="T148" s="16" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="U148" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V148" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W148" s="16" t="inlineStr"/>
+      <c r="X148" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y148" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z148" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA148" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB148" s="16" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="AC148" s="16" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="AD148" s="16" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AE148" s="16" t="n">
+        <v>114.49</v>
+      </c>
+      <c r="AF148" s="16" t="n">
+        <v>107.692</v>
+      </c>
+      <c r="AG148" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH148" s="16" t="n">
+        <v>122.4288</v>
+      </c>
+      <c r="AI148" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ148" s="16" t="n">
+        <v>130.364</v>
+      </c>
+      <c r="AK148" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL148" s="16" t="n">
+        <v>113.54</v>
+      </c>
+      <c r="AM148" s="16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP148" s="16" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AQ148" s="16" t="inlineStr"/>
+      <c r="AR148" s="16" t="inlineStr"/>
+      <c r="AS148" s="16" t="inlineStr"/>
+      <c r="AT148" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU148" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="inlineStr"/>
+      <c r="J149" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K149" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L149" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="16" t="inlineStr"/>
+      <c r="N149" s="16" t="inlineStr"/>
+      <c r="O149" s="16" t="inlineStr"/>
+      <c r="P149" s="16" t="inlineStr"/>
+      <c r="Q149" s="16" t="inlineStr"/>
+      <c r="R149" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S149" s="16" t="inlineStr"/>
+      <c r="T149" s="16" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U149" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V149" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W149" s="16" t="inlineStr"/>
+      <c r="X149" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y149" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z149" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA149" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB149" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AC149" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD149" s="16" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE149" s="16" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF149" s="16" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG149" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH149" s="16" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI149" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ149" s="16" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK149" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL149" s="16" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="AM149" s="16" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN149" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO149" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ149" s="16" t="inlineStr"/>
+      <c r="AR149" s="16" t="inlineStr"/>
+      <c r="AS149" s="16" t="inlineStr"/>
+      <c r="AT149" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU149" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr"/>
+      <c r="I150" s="16" t="inlineStr"/>
+      <c r="J150" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K150" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L150" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" s="16" t="inlineStr"/>
+      <c r="N150" s="16" t="inlineStr"/>
+      <c r="O150" s="16" t="inlineStr"/>
+      <c r="P150" s="16" t="inlineStr"/>
+      <c r="Q150" s="16" t="inlineStr"/>
+      <c r="R150" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S150" s="16" t="inlineStr"/>
+      <c r="T150" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U150" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V150" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W150" s="16" t="inlineStr"/>
+      <c r="X150" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y150" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z150" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA150" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB150" s="16" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AC150" s="16" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD150" s="16" t="n">
+        <v>280.07</v>
+      </c>
+      <c r="AE150" s="16" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="AF150" s="16" t="n">
+        <v>268.7549999999999</v>
+      </c>
+      <c r="AG150" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH150" s="16" t="n">
+        <v>305.532</v>
+      </c>
+      <c r="AI150" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ150" s="16" t="n">
+        <v>325.3349999999999</v>
+      </c>
+      <c r="AK150" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL150" s="16" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="AM150" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN150" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO150" s="16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP150" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ150" s="16" t="inlineStr"/>
+      <c r="AR150" s="16" t="inlineStr"/>
+      <c r="AS150" s="16" t="inlineStr"/>
+      <c r="AT150" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU150" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H151" s="16" t="inlineStr"/>
+      <c r="I151" s="16" t="inlineStr"/>
+      <c r="J151" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K151" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="16" t="inlineStr"/>
+      <c r="N151" s="16" t="inlineStr"/>
+      <c r="O151" s="16" t="inlineStr"/>
+      <c r="P151" s="16" t="inlineStr"/>
+      <c r="Q151" s="16" t="inlineStr"/>
+      <c r="R151" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S151" s="16" t="inlineStr"/>
+      <c r="T151" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U151" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V151" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W151" s="16" t="inlineStr"/>
+      <c r="X151" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y151" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z151" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA151" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB151" s="16" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="AC151" s="16" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="AD151" s="16" t="n">
+        <v>546.88</v>
+      </c>
+      <c r="AE151" s="16" t="n">
+        <v>557.92</v>
+      </c>
+      <c r="AF151" s="16" t="n">
+        <v>524.78</v>
+      </c>
+      <c r="AG151" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH151" s="16" t="n">
+        <v>596.592</v>
+      </c>
+      <c r="AI151" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ151" s="16" t="n">
+        <v>635.2599999999999</v>
+      </c>
+      <c r="AK151" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL151" s="16" t="n">
+        <v>597.55</v>
+      </c>
+      <c r="AM151" s="16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="16" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="AP151" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ151" s="16" t="inlineStr"/>
+      <c r="AR151" s="16" t="inlineStr"/>
+      <c r="AS151" s="16" t="inlineStr"/>
+      <c r="AT151" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU151" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>BATAINDIA_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr"/>
+      <c r="I152" s="16" t="inlineStr"/>
+      <c r="J152" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K152" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="16" t="inlineStr"/>
+      <c r="N152" s="16" t="inlineStr"/>
+      <c r="O152" s="16" t="inlineStr"/>
+      <c r="P152" s="16" t="inlineStr"/>
+      <c r="Q152" s="16" t="inlineStr"/>
+      <c r="R152" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S152" s="16" t="inlineStr"/>
+      <c r="T152" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U152" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V152" s="16" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="W152" s="16" t="inlineStr"/>
+      <c r="X152" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y152" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z152" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA152" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB152" s="16" t="n">
+        <v>709</v>
+      </c>
+      <c r="AC152" s="16" t="n">
+        <v>709</v>
+      </c>
+      <c r="AD152" s="16" t="n">
+        <v>701.91</v>
+      </c>
+      <c r="AE152" s="16" t="n">
+        <v>716.09</v>
+      </c>
+      <c r="AF152" s="16" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="AG152" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH152" s="16" t="n">
+        <v>765.72</v>
+      </c>
+      <c r="AI152" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ152" s="16" t="n">
+        <v>815.3499999999999</v>
+      </c>
+      <c r="AK152" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL152" s="16" t="n">
+        <v>731</v>
+      </c>
+      <c r="AM152" s="16" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="AN152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO152" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP152" s="16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ152" s="16" t="inlineStr"/>
+      <c r="AR152" s="16" t="inlineStr"/>
+      <c r="AS152" s="16" t="inlineStr"/>
+      <c r="AT152" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU152" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>IEX_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr"/>
+      <c r="G153" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H153" s="16" t="inlineStr"/>
+      <c r="I153" s="16" t="inlineStr"/>
+      <c r="J153" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="16" t="inlineStr"/>
+      <c r="N153" s="16" t="inlineStr"/>
+      <c r="O153" s="16" t="inlineStr"/>
+      <c r="P153" s="16" t="inlineStr"/>
+      <c r="Q153" s="16" t="inlineStr"/>
+      <c r="R153" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 39% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S153" s="16" t="inlineStr"/>
+      <c r="T153" s="16" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U153" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V153" s="16" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W153" s="16" t="inlineStr"/>
+      <c r="X153" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y153" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z153" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA153" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB153" s="16" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AC153" s="16" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AD153" s="16" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="AE153" s="16" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="AF153" s="16" t="n">
+        <v>126.445</v>
+      </c>
+      <c r="AG153" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH153" s="16" t="n">
+        <v>143.748</v>
+      </c>
+      <c r="AI153" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ153" s="16" t="n">
+        <v>153.065</v>
+      </c>
+      <c r="AK153" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL153" s="16" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="AM153" s="16" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="AN153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO153" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP153" s="16" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="AQ153" s="16" t="inlineStr"/>
+      <c r="AR153" s="16" t="inlineStr"/>
+      <c r="AS153" s="16" t="inlineStr"/>
+      <c r="AT153" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU153" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr"/>
+      <c r="I154" s="16" t="inlineStr"/>
+      <c r="J154" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="16" t="inlineStr"/>
+      <c r="N154" s="16" t="inlineStr"/>
+      <c r="O154" s="16" t="inlineStr"/>
+      <c r="P154" s="16" t="inlineStr"/>
+      <c r="Q154" s="16" t="inlineStr"/>
+      <c r="R154" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S154" s="16" t="inlineStr"/>
+      <c r="T154" s="16" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="U154" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V154" s="16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W154" s="16" t="inlineStr"/>
+      <c r="X154" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y154" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z154" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA154" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB154" s="16" t="n">
+        <v>5322.4</v>
+      </c>
+      <c r="AC154" s="16" t="n">
+        <v>5322.4</v>
+      </c>
+      <c r="AD154" s="16" t="n">
+        <v>5269.18</v>
+      </c>
+      <c r="AE154" s="16" t="n">
+        <v>5375.62</v>
+      </c>
+      <c r="AF154" s="16" t="n">
+        <v>5056.28</v>
+      </c>
+      <c r="AG154" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH154" s="16" t="n">
+        <v>5748.192</v>
+      </c>
+      <c r="AI154" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ154" s="16" t="n">
+        <v>6120.759999999999</v>
+      </c>
+      <c r="AK154" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL154" s="16" t="n">
+        <v>5532.5</v>
+      </c>
+      <c r="AM154" s="16" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AN154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO154" s="16" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AP154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ154" s="16" t="inlineStr"/>
+      <c r="AR154" s="16" t="inlineStr"/>
+      <c r="AS154" s="16" t="inlineStr"/>
+      <c r="AT154" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU154" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H155" s="16" t="inlineStr"/>
+      <c r="I155" s="16" t="inlineStr"/>
+      <c r="J155" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K155" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="16" t="inlineStr"/>
+      <c r="N155" s="16" t="inlineStr"/>
+      <c r="O155" s="16" t="inlineStr"/>
+      <c r="P155" s="16" t="inlineStr"/>
+      <c r="Q155" s="16" t="inlineStr"/>
+      <c r="R155" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S155" s="16" t="inlineStr"/>
+      <c r="T155" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U155" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V155" s="16" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W155" s="16" t="inlineStr"/>
+      <c r="X155" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y155" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z155" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA155" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB155" s="16" t="n">
+        <v>11127</v>
+      </c>
+      <c r="AC155" s="16" t="n">
+        <v>11127</v>
+      </c>
+      <c r="AD155" s="16" t="n">
+        <v>11015.73</v>
+      </c>
+      <c r="AE155" s="16" t="n">
+        <v>11238.27</v>
+      </c>
+      <c r="AF155" s="16" t="n">
+        <v>10570.65</v>
+      </c>
+      <c r="AG155" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH155" s="16" t="n">
+        <v>12017.16</v>
+      </c>
+      <c r="AI155" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ155" s="16" t="n">
+        <v>12796.05</v>
+      </c>
+      <c r="AK155" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL155" s="16" t="n">
+        <v>11456</v>
+      </c>
+      <c r="AM155" s="16" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AN155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO155" s="16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AP155" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ155" s="16" t="inlineStr"/>
+      <c r="AR155" s="16" t="inlineStr"/>
+      <c r="AS155" s="16" t="inlineStr"/>
+      <c r="AT155" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU155" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr"/>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr"/>
+      <c r="I156" s="16" t="inlineStr"/>
+      <c r="J156" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K156" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="16" t="inlineStr"/>
+      <c r="N156" s="16" t="inlineStr"/>
+      <c r="O156" s="16" t="inlineStr"/>
+      <c r="P156" s="16" t="inlineStr"/>
+      <c r="Q156" s="16" t="inlineStr"/>
+      <c r="R156" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S156" s="16" t="inlineStr"/>
+      <c r="T156" s="16" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U156" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V156" s="16" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="W156" s="16" t="inlineStr"/>
+      <c r="X156" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y156" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z156" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA156" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB156" s="16" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="AC156" s="16" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="AD156" s="16" t="n">
+        <v>1346.89</v>
+      </c>
+      <c r="AE156" s="16" t="n">
+        <v>1374.11</v>
+      </c>
+      <c r="AF156" s="16" t="n">
+        <v>1292.475</v>
+      </c>
+      <c r="AG156" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH156" s="16" t="n">
+        <v>1469.34</v>
+      </c>
+      <c r="AI156" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ156" s="16" t="n">
+        <v>1564.575</v>
+      </c>
+      <c r="AK156" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL156" s="16" t="n">
+        <v>1378.5</v>
+      </c>
+      <c r="AM156" s="16" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AN156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO156" s="16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AP156" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ156" s="16" t="inlineStr"/>
+      <c r="AR156" s="16" t="inlineStr"/>
+      <c r="AS156" s="16" t="inlineStr"/>
+      <c r="AT156" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU156" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr"/>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H157" s="16" t="inlineStr"/>
+      <c r="I157" s="16" t="inlineStr"/>
+      <c r="J157" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K157" s="16" t="inlineStr"/>
+      <c r="L157" s="16" t="inlineStr"/>
+      <c r="M157" s="16" t="inlineStr"/>
+      <c r="N157" s="16" t="inlineStr"/>
+      <c r="O157" s="16" t="inlineStr"/>
+      <c r="P157" s="16" t="inlineStr"/>
+      <c r="Q157" s="16" t="inlineStr"/>
+      <c r="R157" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S157" s="16" t="inlineStr"/>
+      <c r="T157" s="16" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="U157" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V157" s="16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W157" s="16" t="inlineStr"/>
+      <c r="X157" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y157" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z157" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA157" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB157" s="16" t="n">
+        <v>377</v>
+      </c>
+      <c r="AC157" s="16" t="n">
+        <v>377</v>
+      </c>
+      <c r="AD157" s="16" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="AE157" s="16" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="AF157" s="16" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="AG157" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH157" s="16" t="n">
+        <v>407.16</v>
+      </c>
+      <c r="AI157" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ157" s="16" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="AK157" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL157" s="16" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="AM157" s="16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN157" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP157" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ157" s="16" t="inlineStr"/>
+      <c r="AR157" s="16" t="inlineStr"/>
+      <c r="AS157" s="16" t="inlineStr"/>
+      <c r="AT157" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU157" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>LICI_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr"/>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr"/>
+      <c r="I158" s="16" t="inlineStr"/>
+      <c r="J158" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K158" s="16" t="inlineStr"/>
+      <c r="L158" s="16" t="inlineStr"/>
+      <c r="M158" s="16" t="inlineStr"/>
+      <c r="N158" s="16" t="inlineStr"/>
+      <c r="O158" s="16" t="inlineStr"/>
+      <c r="P158" s="16" t="inlineStr"/>
+      <c r="Q158" s="16" t="inlineStr"/>
+      <c r="R158" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S158" s="16" t="inlineStr"/>
+      <c r="T158" s="16" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="U158" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V158" s="16" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W158" s="16" t="inlineStr"/>
+      <c r="X158" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y158" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z158" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA158" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB158" s="16" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AC158" s="16" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AD158" s="16" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="AE158" s="16" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="AF158" s="16" t="n">
+        <v>371.735</v>
+      </c>
+      <c r="AG158" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH158" s="16" t="n">
+        <v>422.604</v>
+      </c>
+      <c r="AI158" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ158" s="16" t="n">
+        <v>449.995</v>
+      </c>
+      <c r="AK158" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL158" s="16" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="AM158" s="16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ158" s="16" t="inlineStr"/>
+      <c r="AR158" s="16" t="inlineStr"/>
+      <c r="AS158" s="16" t="inlineStr"/>
+      <c r="AT158" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU158" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>TIINDIA_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr"/>
+      <c r="G159" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H159" s="16" t="inlineStr"/>
+      <c r="I159" s="16" t="inlineStr"/>
+      <c r="J159" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K159" s="16" t="inlineStr"/>
+      <c r="L159" s="16" t="inlineStr"/>
+      <c r="M159" s="16" t="inlineStr"/>
+      <c r="N159" s="16" t="inlineStr"/>
+      <c r="O159" s="16" t="inlineStr"/>
+      <c r="P159" s="16" t="inlineStr"/>
+      <c r="Q159" s="16" t="inlineStr"/>
+      <c r="R159" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S159" s="16" t="inlineStr"/>
+      <c r="T159" s="16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U159" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V159" s="16" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="W159" s="16" t="inlineStr"/>
+      <c r="X159" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y159" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z159" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA159" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB159" s="16" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AC159" s="16" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AD159" s="16" t="n">
+        <v>2716.86</v>
+      </c>
+      <c r="AE159" s="16" t="n">
+        <v>2771.74</v>
+      </c>
+      <c r="AF159" s="16" t="n">
+        <v>2607.085</v>
+      </c>
+      <c r="AG159" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH159" s="16" t="n">
+        <v>2963.844000000001</v>
+      </c>
+      <c r="AI159" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ159" s="16" t="n">
+        <v>3155.945</v>
+      </c>
+      <c r="AK159" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL159" s="16" t="n">
+        <v>2764.2</v>
+      </c>
+      <c r="AM159" s="16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AN159" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO159" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP159" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ159" s="16" t="inlineStr"/>
+      <c r="AR159" s="16" t="inlineStr"/>
+      <c r="AS159" s="16" t="inlineStr"/>
+      <c r="AT159" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU159" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H160" s="16" t="inlineStr"/>
+      <c r="I160" s="16" t="inlineStr"/>
+      <c r="J160" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="16" t="inlineStr"/>
+      <c r="N160" s="16" t="inlineStr"/>
+      <c r="O160" s="16" t="inlineStr"/>
+      <c r="P160" s="16" t="inlineStr"/>
+      <c r="Q160" s="16" t="inlineStr"/>
+      <c r="R160" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S160" s="16" t="inlineStr"/>
+      <c r="T160" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="U160" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V160" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="W160" s="16" t="inlineStr"/>
+      <c r="X160" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y160" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z160" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA160" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB160" s="16" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AC160" s="16" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD160" s="16" t="n">
+        <v>1424.12</v>
+      </c>
+      <c r="AE160" s="16" t="n">
+        <v>1452.88</v>
+      </c>
+      <c r="AF160" s="16" t="n">
+        <v>1366.575</v>
+      </c>
+      <c r="AG160" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH160" s="16" t="n">
+        <v>1553.58</v>
+      </c>
+      <c r="AI160" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ160" s="16" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="AK160" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL160" s="16" t="n">
+        <v>1449.6</v>
+      </c>
+      <c r="AM160" s="16" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="AN160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ160" s="16" t="inlineStr"/>
+      <c r="AR160" s="16" t="inlineStr"/>
+      <c r="AS160" s="16" t="inlineStr"/>
+      <c r="AT160" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU160" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H161" s="16" t="inlineStr"/>
+      <c r="I161" s="16" t="inlineStr"/>
+      <c r="J161" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="16" t="inlineStr"/>
+      <c r="N161" s="16" t="inlineStr"/>
+      <c r="O161" s="16" t="inlineStr"/>
+      <c r="P161" s="16" t="inlineStr"/>
+      <c r="Q161" s="16" t="inlineStr"/>
+      <c r="R161" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S161" s="16" t="inlineStr"/>
+      <c r="T161" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="U161" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V161" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="W161" s="16" t="inlineStr"/>
+      <c r="X161" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y161" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z161" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA161" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB161" s="16" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AC161" s="16" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AD161" s="16" t="n">
+        <v>1994.65</v>
+      </c>
+      <c r="AE161" s="16" t="n">
+        <v>2034.95</v>
+      </c>
+      <c r="AF161" s="16" t="n">
+        <v>1914.06</v>
+      </c>
+      <c r="AG161" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH161" s="16" t="n">
+        <v>2175.984</v>
+      </c>
+      <c r="AI161" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ161" s="16" t="n">
+        <v>2317.02</v>
+      </c>
+      <c r="AK161" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL161" s="16" t="n">
+        <v>1949</v>
+      </c>
+      <c r="AM161" s="16" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AN161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP161" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ161" s="16" t="inlineStr"/>
+      <c r="AR161" s="16" t="inlineStr"/>
+      <c r="AS161" s="16" t="inlineStr"/>
+      <c r="AT161" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU161" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H162" s="16" t="inlineStr"/>
+      <c r="I162" s="16" t="inlineStr"/>
+      <c r="J162" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="16" t="inlineStr"/>
+      <c r="N162" s="16" t="inlineStr"/>
+      <c r="O162" s="16" t="inlineStr"/>
+      <c r="P162" s="16" t="inlineStr"/>
+      <c r="Q162" s="16" t="inlineStr"/>
+      <c r="R162" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S162" s="16" t="inlineStr"/>
+      <c r="T162" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="U162" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V162" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="W162" s="16" t="inlineStr"/>
+      <c r="X162" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y162" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z162" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA162" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB162" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AC162" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD162" s="16" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE162" s="16" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF162" s="16" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG162" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH162" s="16" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI162" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ162" s="16" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK162" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL162" s="16" t="n">
+        <v>2390.4</v>
+      </c>
+      <c r="AM162" s="16" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AN162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ162" s="16" t="inlineStr"/>
+      <c r="AR162" s="16" t="inlineStr"/>
+      <c r="AS162" s="16" t="inlineStr"/>
+      <c r="AT162" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU162" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H163" s="16" t="inlineStr"/>
+      <c r="I163" s="16" t="inlineStr"/>
+      <c r="J163" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L163" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="16" t="inlineStr"/>
+      <c r="N163" s="16" t="inlineStr"/>
+      <c r="O163" s="16" t="inlineStr"/>
+      <c r="P163" s="16" t="inlineStr"/>
+      <c r="Q163" s="16" t="inlineStr"/>
+      <c r="R163" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S163" s="16" t="inlineStr"/>
+      <c r="T163" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="U163" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V163" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="W163" s="16" t="inlineStr"/>
+      <c r="X163" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y163" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z163" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA163" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB163" s="16" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AC163" s="16" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AD163" s="16" t="n">
+        <v>1609.24</v>
+      </c>
+      <c r="AE163" s="16" t="n">
+        <v>1641.76</v>
+      </c>
+      <c r="AF163" s="16" t="n">
+        <v>1544.225</v>
+      </c>
+      <c r="AG163" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH163" s="16" t="n">
+        <v>1755.54</v>
+      </c>
+      <c r="AI163" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ163" s="16" t="n">
+        <v>1869.325</v>
+      </c>
+      <c r="AK163" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL163" s="16" t="n">
+        <v>1657</v>
+      </c>
+      <c r="AM163" s="16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN163" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO163" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP163" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ163" s="16" t="inlineStr"/>
+      <c r="AR163" s="16" t="inlineStr"/>
+      <c r="AS163" s="16" t="inlineStr"/>
+      <c r="AT163" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU163" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H164" s="16" t="inlineStr"/>
+      <c r="I164" s="16" t="inlineStr"/>
+      <c r="J164" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K164" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="16" t="inlineStr"/>
+      <c r="N164" s="16" t="inlineStr"/>
+      <c r="O164" s="16" t="inlineStr"/>
+      <c r="P164" s="16" t="inlineStr"/>
+      <c r="Q164" s="16" t="inlineStr"/>
+      <c r="R164" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S164" s="16" t="inlineStr"/>
+      <c r="T164" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="U164" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V164" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="W164" s="16" t="inlineStr"/>
+      <c r="X164" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y164" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z164" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA164" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB164" s="16" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AC164" s="16" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD164" s="16" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="AE164" s="16" t="n">
+        <v>349.21</v>
+      </c>
+      <c r="AF164" s="16" t="n">
+        <v>328.4625</v>
+      </c>
+      <c r="AG164" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH164" s="16" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="AI164" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ164" s="16" t="n">
+        <v>397.6125</v>
+      </c>
+      <c r="AK164" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL164" s="16" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="AM164" s="16" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AN164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ164" s="16" t="inlineStr"/>
+      <c r="AR164" s="16" t="inlineStr"/>
+      <c r="AS164" s="16" t="inlineStr"/>
+      <c r="AT164" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU164" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H165" s="16" t="inlineStr"/>
+      <c r="I165" s="16" t="inlineStr"/>
+      <c r="J165" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K165" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L165" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="16" t="inlineStr"/>
+      <c r="N165" s="16" t="inlineStr"/>
+      <c r="O165" s="16" t="inlineStr"/>
+      <c r="P165" s="16" t="inlineStr"/>
+      <c r="Q165" s="16" t="inlineStr"/>
+      <c r="R165" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S165" s="16" t="inlineStr"/>
+      <c r="T165" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="U165" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V165" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="W165" s="16" t="inlineStr"/>
+      <c r="X165" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y165" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z165" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA165" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB165" s="16" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AC165" s="16" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD165" s="16" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="AE165" s="16" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="AF165" s="16" t="n">
+        <v>369.835</v>
+      </c>
+      <c r="AG165" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH165" s="16" t="n">
+        <v>420.444</v>
+      </c>
+      <c r="AI165" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ165" s="16" t="n">
+        <v>447.695</v>
+      </c>
+      <c r="AK165" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL165" s="16" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="AM165" s="16" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="AN165" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP165" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ165" s="16" t="inlineStr"/>
+      <c r="AR165" s="16" t="inlineStr"/>
+      <c r="AS165" s="16" t="inlineStr"/>
+      <c r="AT165" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU165" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G166" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H166" s="16" t="inlineStr"/>
+      <c r="I166" s="16" t="inlineStr"/>
+      <c r="J166" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K166" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="16" t="inlineStr"/>
+      <c r="N166" s="16" t="inlineStr"/>
+      <c r="O166" s="16" t="inlineStr"/>
+      <c r="P166" s="16" t="inlineStr"/>
+      <c r="Q166" s="16" t="inlineStr"/>
+      <c r="R166" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S166" s="16" t="inlineStr"/>
+      <c r="T166" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="U166" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V166" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="W166" s="16" t="inlineStr"/>
+      <c r="X166" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y166" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z166" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA166" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB166" s="16" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AC166" s="16" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD166" s="16" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="AE166" s="16" t="n">
+        <v>288.76</v>
+      </c>
+      <c r="AF166" s="16" t="n">
+        <v>271.605</v>
+      </c>
+      <c r="AG166" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH166" s="16" t="n">
+        <v>308.772</v>
+      </c>
+      <c r="AI166" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ166" s="16" t="n">
+        <v>328.785</v>
+      </c>
+      <c r="AK166" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL166" s="16" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="AM166" s="16" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="AN166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ166" s="16" t="inlineStr"/>
+      <c r="AR166" s="16" t="inlineStr"/>
+      <c r="AS166" s="16" t="inlineStr"/>
+      <c r="AT166" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU166" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G167" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H167" s="16" t="inlineStr"/>
+      <c r="I167" s="16" t="inlineStr"/>
+      <c r="J167" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K167" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="16" t="inlineStr"/>
+      <c r="N167" s="16" t="inlineStr"/>
+      <c r="O167" s="16" t="inlineStr"/>
+      <c r="P167" s="16" t="inlineStr"/>
+      <c r="Q167" s="16" t="inlineStr"/>
+      <c r="R167" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S167" s="16" t="inlineStr"/>
+      <c r="T167" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="U167" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V167" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="W167" s="16" t="inlineStr"/>
+      <c r="X167" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y167" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z167" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA167" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB167" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AC167" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD167" s="16" t="n">
+        <v>489.41</v>
+      </c>
+      <c r="AE167" s="16" t="n">
+        <v>499.29</v>
+      </c>
+      <c r="AF167" s="16" t="n">
+        <v>469.6325</v>
+      </c>
+      <c r="AG167" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH167" s="16" t="n">
+        <v>533.898</v>
+      </c>
+      <c r="AI167" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ167" s="16" t="n">
+        <v>568.5024999999999</v>
+      </c>
+      <c r="AK167" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL167" s="16" t="n">
+        <v>510.85</v>
+      </c>
+      <c r="AM167" s="16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP167" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ167" s="16" t="inlineStr"/>
+      <c r="AR167" s="16" t="inlineStr"/>
+      <c r="AS167" s="16" t="inlineStr"/>
+      <c r="AT167" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU167" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G168" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H168" s="16" t="inlineStr"/>
+      <c r="I168" s="16" t="inlineStr"/>
+      <c r="J168" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K168" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="16" t="inlineStr"/>
+      <c r="N168" s="16" t="inlineStr"/>
+      <c r="O168" s="16" t="inlineStr"/>
+      <c r="P168" s="16" t="inlineStr"/>
+      <c r="Q168" s="16" t="inlineStr"/>
+      <c r="R168" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S168" s="16" t="inlineStr"/>
+      <c r="T168" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="U168" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V168" s="16" t="n">
+        <v>53</v>
+      </c>
+      <c r="W168" s="16" t="inlineStr"/>
+      <c r="X168" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y168" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z168" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA168" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB168" s="16" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AC168" s="16" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD168" s="16" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="AE168" s="16" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="AF168" s="16" t="n">
+        <v>369.265</v>
+      </c>
+      <c r="AG168" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH168" s="16" t="n">
+        <v>419.796</v>
+      </c>
+      <c r="AI168" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ168" s="16" t="n">
+        <v>447.0049999999999</v>
+      </c>
+      <c r="AK168" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL168" s="16" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="AM168" s="16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AN168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP168" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ168" s="16" t="inlineStr"/>
+      <c r="AR168" s="16" t="inlineStr"/>
+      <c r="AS168" s="16" t="inlineStr"/>
+      <c r="AT168" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU168" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G169" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H169" s="16" t="inlineStr"/>
+      <c r="I169" s="16" t="inlineStr"/>
+      <c r="J169" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K169" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="16" t="inlineStr"/>
+      <c r="N169" s="16" t="inlineStr"/>
+      <c r="O169" s="16" t="inlineStr"/>
+      <c r="P169" s="16" t="inlineStr"/>
+      <c r="Q169" s="16" t="inlineStr"/>
+      <c r="R169" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S169" s="16" t="inlineStr"/>
+      <c r="T169" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U169" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V169" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="W169" s="16" t="inlineStr"/>
+      <c r="X169" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y169" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z169" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA169" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB169" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AC169" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD169" s="16" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE169" s="16" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF169" s="16" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG169" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH169" s="16" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI169" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ169" s="16" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK169" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL169" s="16" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="AM169" s="16" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP169" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ169" s="16" t="inlineStr"/>
+      <c r="AR169" s="16" t="inlineStr"/>
+      <c r="AS169" s="16" t="inlineStr"/>
+      <c r="AT169" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU169" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr"/>
+      <c r="G170" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H170" s="16" t="inlineStr"/>
+      <c r="I170" s="16" t="inlineStr"/>
+      <c r="J170" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K170" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="16" t="inlineStr"/>
+      <c r="N170" s="16" t="inlineStr"/>
+      <c r="O170" s="16" t="inlineStr"/>
+      <c r="P170" s="16" t="inlineStr"/>
+      <c r="Q170" s="16" t="inlineStr"/>
+      <c r="R170" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S170" s="16" t="inlineStr"/>
+      <c r="T170" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U170" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V170" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="W170" s="16" t="inlineStr"/>
+      <c r="X170" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y170" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z170" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA170" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB170" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AC170" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD170" s="16" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="AE170" s="16" t="n">
+        <v>5460.06</v>
+      </c>
+      <c r="AF170" s="16" t="n">
+        <v>5135.7</v>
+      </c>
+      <c r="AG170" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH170" s="16" t="n">
+        <v>5838.48</v>
+      </c>
+      <c r="AI170" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ170" s="16" t="n">
+        <v>6216.9</v>
+      </c>
+      <c r="AK170" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL170" s="16" t="n">
+        <v>5429</v>
+      </c>
+      <c r="AM170" s="16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP170" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ170" s="16" t="inlineStr"/>
+      <c r="AR170" s="16" t="inlineStr"/>
+      <c r="AS170" s="16" t="inlineStr"/>
+      <c r="AT170" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU170" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H171" s="16" t="inlineStr"/>
+      <c r="I171" s="16" t="inlineStr"/>
+      <c r="J171" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K171" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="16" t="inlineStr"/>
+      <c r="N171" s="16" t="inlineStr"/>
+      <c r="O171" s="16" t="inlineStr"/>
+      <c r="P171" s="16" t="inlineStr"/>
+      <c r="Q171" s="16" t="inlineStr"/>
+      <c r="R171" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S171" s="16" t="inlineStr"/>
+      <c r="T171" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="U171" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V171" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="W171" s="16" t="inlineStr"/>
+      <c r="X171" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y171" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z171" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA171" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB171" s="16" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AC171" s="16" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AD171" s="16" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="AE171" s="16" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="AF171" s="16" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG171" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH171" s="16" t="n">
+        <v>412.128</v>
+      </c>
+      <c r="AI171" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ171" s="16" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="AK171" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL171" s="16" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="AM171" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP171" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ171" s="16" t="inlineStr"/>
+      <c r="AR171" s="16" t="inlineStr"/>
+      <c r="AS171" s="16" t="inlineStr"/>
+      <c r="AT171" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU171" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AU126"/>
+  <autoFilter ref="A1:AU171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU171"/>
+  <dimension ref="A1:AU196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="AU127" s="13" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -18996,7 +18996,7 @@
         <v>0</v>
       </c>
       <c r="AP128" s="13" t="n">
-        <v>-3.22</v>
+        <v>0</v>
       </c>
       <c r="AQ128" s="13" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="AU128" s="13" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
         <v>6.59</v>
       </c>
       <c r="AO129" s="14" t="n">
-        <v>6.59</v>
+        <v>4.74</v>
       </c>
       <c r="AP129" s="14" t="n">
         <v>0</v>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="AU129" s="14" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AU143" s="14" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -21716,7 +21716,7 @@
       </c>
       <c r="AU146" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="AU147" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -21998,7 +21998,7 @@
       </c>
       <c r="AU148" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="AU149" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AU150" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22421,7 +22421,7 @@
       </c>
       <c r="AU151" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22562,7 +22562,7 @@
       </c>
       <c r="AU152" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22699,7 +22699,7 @@
       </c>
       <c r="AU153" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22836,7 +22836,7 @@
       </c>
       <c r="AU154" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AU155" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23110,7 +23110,7 @@
       </c>
       <c r="AU156" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="AU157" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23376,7 +23376,7 @@
       </c>
       <c r="AU158" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23509,7 +23509,7 @@
       </c>
       <c r="AU159" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AU160" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23791,7 +23791,7 @@
       </c>
       <c r="AU161" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -23932,7 +23932,7 @@
       </c>
       <c r="AU162" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24073,7 +24073,7 @@
       </c>
       <c r="AU163" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AU164" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24355,7 +24355,7 @@
       </c>
       <c r="AU165" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24496,7 +24496,7 @@
       </c>
       <c r="AU166" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24637,7 +24637,7 @@
       </c>
       <c r="AU167" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="AU168" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -24919,7 +24919,7 @@
       </c>
       <c r="AU169" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="AU170" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
         </is>
       </c>
     </row>
@@ -25197,12 +25197,3973 @@
       </c>
       <c r="AU171" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 02:45</t>
+          <t>2026-08-10 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G172" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H172" s="14" t="inlineStr"/>
+      <c r="I172" s="14" t="inlineStr"/>
+      <c r="J172" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" s="14" t="inlineStr"/>
+      <c r="L172" s="14" t="inlineStr"/>
+      <c r="M172" s="14" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N172" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O172" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P172" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q172" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R172" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S172" s="14" t="inlineStr"/>
+      <c r="T172" s="14" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U172" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V172" s="14" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="W172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X172" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y172" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z172" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA172" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB172" s="14" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AC172" s="14" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD172" s="14" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE172" s="14" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF172" s="14" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AG172" s="14" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AH172" s="14" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI172" s="14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ172" s="14" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AK172" s="14" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AL172" s="14" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AM172" s="14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN172" s="14" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="AO172" s="14" t="inlineStr"/>
+      <c r="AP172" s="14" t="inlineStr"/>
+      <c r="AQ172" s="14" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AR172" s="14" t="inlineStr"/>
+      <c r="AS172" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT172" s="14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU172" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>V_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G173" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H173" s="16" t="inlineStr"/>
+      <c r="I173" s="16" t="inlineStr"/>
+      <c r="J173" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" s="16" t="inlineStr"/>
+      <c r="L173" s="16" t="inlineStr"/>
+      <c r="M173" s="16" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N173" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O173" s="16" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P173" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q173" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R173" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank #2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S173" s="16" t="inlineStr"/>
+      <c r="T173" s="16" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U173" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V173" s="16" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W173" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="X173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z173" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA173" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB173" s="16" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AC173" s="16" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD173" s="16" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="AE173" s="16" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="AF173" s="16" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="AG173" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH173" s="16" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AI173" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ173" s="16" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AK173" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL173" s="16" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AM173" s="16" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AN173" s="16" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="AO173" s="16" t="inlineStr"/>
+      <c r="AP173" s="16" t="inlineStr"/>
+      <c r="AQ173" s="16" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AR173" s="16" t="inlineStr"/>
+      <c r="AS173" s="16" t="inlineStr"/>
+      <c r="AT173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G174" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H174" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I174" s="15" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="J174" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" s="15" t="inlineStr"/>
+      <c r="L174" s="15" t="inlineStr"/>
+      <c r="M174" s="15" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N174" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O174" s="15" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="P174" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q174" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R174" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S174" s="15" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T174" s="15" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U174" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V174" s="15" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W174" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X174" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y174" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z174" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA174" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB174" s="15" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AC174" s="15" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="AD174" s="15" t="n">
+        <v>217.03</v>
+      </c>
+      <c r="AE174" s="15" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="AF174" s="15" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="AG174" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH174" s="15" t="n">
+        <v>236.76</v>
+      </c>
+      <c r="AI174" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ174" s="15" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="AK174" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL174" s="15" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AM174" s="15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AN174" s="15" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="AO174" s="15" t="inlineStr"/>
+      <c r="AP174" s="15" t="inlineStr"/>
+      <c r="AQ174" s="15" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AR174" s="15" t="inlineStr"/>
+      <c r="AS174" s="15" t="inlineStr"/>
+      <c r="AT174" s="15" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AU174" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G175" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H175" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +13.0pp alpha</t>
+        </is>
+      </c>
+      <c r="I175" s="15" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="J175" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K175" s="15" t="inlineStr"/>
+      <c r="L175" s="15" t="inlineStr"/>
+      <c r="M175" s="15" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N175" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O175" s="15" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="P175" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q175" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R175" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S175" s="15" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T175" s="15" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U175" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V175" s="15" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W175" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X175" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z175" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA175" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB175" s="15" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AC175" s="15" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="AD175" s="15" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="AE175" s="15" t="n">
+        <v>362.83</v>
+      </c>
+      <c r="AF175" s="15" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="AG175" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH175" s="15" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="AI175" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ175" s="15" t="n">
+        <v>413.13</v>
+      </c>
+      <c r="AK175" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL175" s="15" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AM175" s="15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN175" s="15" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="AO175" s="15" t="inlineStr"/>
+      <c r="AP175" s="15" t="inlineStr"/>
+      <c r="AQ175" s="15" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AR175" s="15" t="inlineStr"/>
+      <c r="AS175" s="15" t="inlineStr"/>
+      <c r="AT175" s="15" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AU175" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>HON_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G176" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H176" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I176" s="15" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="J176" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K176" s="15" t="inlineStr"/>
+      <c r="L176" s="15" t="inlineStr"/>
+      <c r="M176" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="N176" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O176" s="15" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P176" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q176" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R176" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S176" s="15" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T176" s="15" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U176" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V176" s="15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W176" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X176" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z176" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA176" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB176" s="15" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AC176" s="15" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="AD176" s="15" t="n">
+        <v>245.64</v>
+      </c>
+      <c r="AE176" s="15" t="n">
+        <v>250.6</v>
+      </c>
+      <c r="AF176" s="15" t="n">
+        <v>235.71</v>
+      </c>
+      <c r="AG176" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH176" s="15" t="n">
+        <v>267.97</v>
+      </c>
+      <c r="AI176" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ176" s="15" t="n">
+        <v>285.34</v>
+      </c>
+      <c r="AK176" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL176" s="15" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AM176" s="15" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AN176" s="15" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AO176" s="15" t="inlineStr"/>
+      <c r="AP176" s="15" t="inlineStr"/>
+      <c r="AQ176" s="15" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AR176" s="15" t="inlineStr"/>
+      <c r="AS176" s="15" t="inlineStr"/>
+      <c r="AT176" s="15" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AU176" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>GS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G177" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H177" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.8pp alpha</t>
+        </is>
+      </c>
+      <c r="I177" s="15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J177" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K177" s="15" t="inlineStr"/>
+      <c r="L177" s="15" t="inlineStr"/>
+      <c r="M177" s="15" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="N177" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O177" s="15" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="P177" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q177" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R177" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S177" s="15" t="inlineStr"/>
+      <c r="T177" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="U177" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V177" s="15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W177" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X177" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y177" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z177" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA177" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB177" s="15" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AC177" s="15" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="AD177" s="15" t="n">
+        <v>1049.78</v>
+      </c>
+      <c r="AE177" s="15" t="n">
+        <v>1070.98</v>
+      </c>
+      <c r="AF177" s="15" t="n">
+        <v>1007.36</v>
+      </c>
+      <c r="AG177" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH177" s="15" t="n">
+        <v>1145.21</v>
+      </c>
+      <c r="AI177" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ177" s="15" t="n">
+        <v>1219.44</v>
+      </c>
+      <c r="AK177" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL177" s="15" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AM177" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN177" s="15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AO177" s="15" t="inlineStr"/>
+      <c r="AP177" s="15" t="inlineStr"/>
+      <c r="AQ177" s="15" t="inlineStr">
+        <is>
+          <t>Value · News · Event Driven</t>
+        </is>
+      </c>
+      <c r="AR177" s="15" t="inlineStr"/>
+      <c r="AS177" s="15" t="inlineStr"/>
+      <c r="AT177" s="15" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AU177" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G178" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H178" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I178" s="15" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J178" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K178" s="15" t="inlineStr"/>
+      <c r="L178" s="15" t="inlineStr"/>
+      <c r="M178" s="15" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N178" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O178" s="15" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P178" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q178" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R178" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S178" s="15" t="inlineStr"/>
+      <c r="T178" s="15" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U178" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V178" s="15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W178" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X178" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y178" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z178" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA178" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB178" s="15" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AC178" s="15" t="n">
+        <v>311</v>
+      </c>
+      <c r="AD178" s="15" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="AE178" s="15" t="n">
+        <v>314.11</v>
+      </c>
+      <c r="AF178" s="15" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="AG178" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH178" s="15" t="n">
+        <v>335.88</v>
+      </c>
+      <c r="AI178" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ178" s="15" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="AK178" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL178" s="15" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AM178" s="15" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AN178" s="15" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AO178" s="15" t="inlineStr"/>
+      <c r="AP178" s="15" t="inlineStr"/>
+      <c r="AQ178" s="15" t="inlineStr">
+        <is>
+          <t>Value · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AR178" s="15" t="inlineStr"/>
+      <c r="AS178" s="15" t="inlineStr"/>
+      <c r="AT178" s="15" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AU178" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G179" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H179" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I179" s="15" t="n">
+        <v>-19.21</v>
+      </c>
+      <c r="J179" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K179" s="15" t="inlineStr"/>
+      <c r="L179" s="15" t="inlineStr"/>
+      <c r="M179" s="15" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N179" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O179" s="15" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P179" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q179" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R179" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S179" s="15" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T179" s="15" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U179" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V179" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="W179" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X179" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z179" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA179" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB179" s="15" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AC179" s="15" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="AD179" s="15" t="n">
+        <v>482.59</v>
+      </c>
+      <c r="AE179" s="15" t="n">
+        <v>492.33</v>
+      </c>
+      <c r="AF179" s="15" t="n">
+        <v>463.09</v>
+      </c>
+      <c r="AG179" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH179" s="15" t="n">
+        <v>526.46</v>
+      </c>
+      <c r="AI179" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ179" s="15" t="n">
+        <v>560.58</v>
+      </c>
+      <c r="AK179" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL179" s="15" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AM179" s="15" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AN179" s="15" t="n">
+        <v>-19.21</v>
+      </c>
+      <c r="AO179" s="15" t="inlineStr"/>
+      <c r="AP179" s="15" t="inlineStr"/>
+      <c r="AQ179" s="15" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AR179" s="15" t="inlineStr"/>
+      <c r="AS179" s="15" t="inlineStr"/>
+      <c r="AT179" s="15" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AU179" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>KO_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G180" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H180" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.5pp alpha</t>
+        </is>
+      </c>
+      <c r="I180" s="15" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="J180" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K180" s="15" t="inlineStr"/>
+      <c r="L180" s="15" t="inlineStr"/>
+      <c r="M180" s="15" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N180" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O180" s="15" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P180" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q180" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R180" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S180" s="15" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T180" s="15" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U180" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V180" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W180" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X180" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z180" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA180" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB180" s="15" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AC180" s="15" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="AD180" s="15" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="AE180" s="15" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AF180" s="15" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="AG180" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH180" s="15" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="AI180" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ180" s="15" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="AK180" s="15" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AL180" s="15" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AM180" s="15" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN180" s="15" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="AO180" s="15" t="inlineStr"/>
+      <c r="AP180" s="15" t="inlineStr"/>
+      <c r="AQ180" s="15" t="inlineStr">
+        <is>
+          <t>Momentum · News · Quality</t>
+        </is>
+      </c>
+      <c r="AR180" s="15" t="inlineStr"/>
+      <c r="AS180" s="15" t="inlineStr"/>
+      <c r="AT180" s="15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU180" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G181" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H181" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +16.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I181" s="15" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="J181" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K181" s="15" t="inlineStr"/>
+      <c r="L181" s="15" t="inlineStr"/>
+      <c r="M181" s="15" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N181" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O181" s="15" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P181" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q181" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R181" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S181" s="15" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T181" s="15" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U181" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V181" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W181" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X181" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z181" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA181" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB181" s="15" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AC181" s="15" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="AD181" s="15" t="n">
+        <v>180.26</v>
+      </c>
+      <c r="AE181" s="15" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AF181" s="15" t="n">
+        <v>172.98</v>
+      </c>
+      <c r="AG181" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH181" s="15" t="n">
+        <v>196.65</v>
+      </c>
+      <c r="AI181" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ181" s="15" t="n">
+        <v>209.39</v>
+      </c>
+      <c r="AK181" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL181" s="15" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AM181" s="15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AN181" s="15" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="AO181" s="15" t="inlineStr"/>
+      <c r="AP181" s="15" t="inlineStr"/>
+      <c r="AQ181" s="15" t="inlineStr">
+        <is>
+          <t>Momentum · News · Value</t>
+        </is>
+      </c>
+      <c r="AR181" s="15" t="inlineStr"/>
+      <c r="AS181" s="15" t="inlineStr"/>
+      <c r="AT181" s="15" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AU181" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>INTC_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="G182" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I182" s="15" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="J182" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K182" s="15" t="inlineStr"/>
+      <c r="L182" s="15" t="inlineStr"/>
+      <c r="M182" s="15" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N182" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O182" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="P182" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q182" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R182" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S182" s="15" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T182" s="15" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U182" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V182" s="15" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="W182" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X182" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y182" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z182" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA182" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB182" s="15" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="AC182" s="15" t="n">
+        <v>101.0599975585938</v>
+      </c>
+      <c r="AD182" s="15" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="AE182" s="15" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="AF182" s="15" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="AG182" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH182" s="15" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="AI182" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ182" s="15" t="n">
+        <v>116.22</v>
+      </c>
+      <c r="AK182" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL182" s="15" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="AM182" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN182" s="15" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="AO182" s="15" t="inlineStr"/>
+      <c r="AP182" s="15" t="inlineStr"/>
+      <c r="AQ182" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AR182" s="15" t="inlineStr"/>
+      <c r="AS182" s="15" t="inlineStr"/>
+      <c r="AT182" s="15" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AU182" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>BA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="G183" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H183" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.8pp alpha</t>
+        </is>
+      </c>
+      <c r="I183" s="15" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="J183" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K183" s="15" t="inlineStr"/>
+      <c r="L183" s="15" t="inlineStr"/>
+      <c r="M183" s="15" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N183" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O183" s="15" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="P183" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q183" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R183" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S183" s="15" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-10.9% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T183" s="15" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="U183" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V183" s="15" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="W183" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X183" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z183" s="15" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA183" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB183" s="15" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AC183" s="15" t="n">
+        <v>240.1900024414062</v>
+      </c>
+      <c r="AD183" s="15" t="n">
+        <v>237.79</v>
+      </c>
+      <c r="AE183" s="15" t="n">
+        <v>242.59</v>
+      </c>
+      <c r="AF183" s="15" t="n">
+        <v>228.18</v>
+      </c>
+      <c r="AG183" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH183" s="15" t="n">
+        <v>259.41</v>
+      </c>
+      <c r="AI183" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ183" s="15" t="n">
+        <v>276.22</v>
+      </c>
+      <c r="AK183" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL183" s="15" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="AM183" s="15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN183" s="15" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="AO183" s="15" t="inlineStr"/>
+      <c r="AP183" s="15" t="inlineStr"/>
+      <c r="AQ183" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AR183" s="15" t="inlineStr"/>
+      <c r="AS183" s="15" t="inlineStr"/>
+      <c r="AT183" s="15" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="AU183" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>HD_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +43.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I184" s="15" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="J184" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K184" s="15" t="inlineStr"/>
+      <c r="L184" s="15" t="inlineStr"/>
+      <c r="M184" s="15" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N184" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O184" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="P184" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q184" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R184" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S184" s="15" t="inlineStr"/>
+      <c r="T184" s="15" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="U184" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V184" s="15" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="W184" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X184" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z184" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA184" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB184" s="15" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="AC184" s="15" t="n">
+        <v>353.1400146484375</v>
+      </c>
+      <c r="AD184" s="15" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="AE184" s="15" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="AF184" s="15" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="AG184" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH184" s="15" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="AI184" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ184" s="15" t="n">
+        <v>406.11</v>
+      </c>
+      <c r="AK184" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL184" s="15" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="AM184" s="15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN184" s="15" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="AO184" s="15" t="inlineStr"/>
+      <c r="AP184" s="15" t="inlineStr"/>
+      <c r="AQ184" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR184" s="15" t="inlineStr"/>
+      <c r="AS184" s="15" t="inlineStr"/>
+      <c r="AT184" s="15" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AU184" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="G185" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H185" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.6pp alpha</t>
+        </is>
+      </c>
+      <c r="I185" s="15" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="J185" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K185" s="15" t="inlineStr"/>
+      <c r="L185" s="15" t="inlineStr"/>
+      <c r="M185" s="15" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N185" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O185" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="P185" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q185" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R185" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S185" s="15" t="inlineStr"/>
+      <c r="T185" s="15" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="U185" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V185" s="15" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="W185" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X185" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z185" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA185" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB185" s="15" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="AC185" s="15" t="n">
+        <v>101.7600021362305</v>
+      </c>
+      <c r="AD185" s="15" t="n">
+        <v>100.74</v>
+      </c>
+      <c r="AE185" s="15" t="n">
+        <v>102.78</v>
+      </c>
+      <c r="AF185" s="15" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="AG185" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH185" s="15" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="AI185" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ185" s="15" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="AK185" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL185" s="15" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="AM185" s="15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AN185" s="15" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="AO185" s="15" t="inlineStr"/>
+      <c r="AP185" s="15" t="inlineStr"/>
+      <c r="AQ185" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR185" s="15" t="inlineStr"/>
+      <c r="AS185" s="15" t="inlineStr"/>
+      <c r="AT185" s="15" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AU185" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="G186" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H186" s="15" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J186" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K186" s="15" t="inlineStr"/>
+      <c r="L186" s="15" t="inlineStr"/>
+      <c r="M186" s="15" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N186" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O186" s="15" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="P186" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q186" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R186" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S186" s="15" t="inlineStr"/>
+      <c r="T186" s="15" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="U186" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V186" s="15" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="W186" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="X186" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z186" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA186" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB186" s="15" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="AC186" s="15" t="n">
+        <v>274</v>
+      </c>
+      <c r="AD186" s="15" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="AE186" s="15" t="n">
+        <v>276.74</v>
+      </c>
+      <c r="AF186" s="15" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="AG186" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH186" s="15" t="n">
+        <v>295.92</v>
+      </c>
+      <c r="AI186" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ186" s="15" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="AK186" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL186" s="15" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="AM186" s="15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AN186" s="15" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AO186" s="15" t="inlineStr"/>
+      <c r="AP186" s="15" t="inlineStr"/>
+      <c r="AQ186" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR186" s="15" t="inlineStr"/>
+      <c r="AS186" s="15" t="inlineStr"/>
+      <c r="AT186" s="15" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AU186" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>V_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G187" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H187" s="14" t="inlineStr"/>
+      <c r="I187" s="14" t="inlineStr"/>
+      <c r="J187" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" s="14" t="inlineStr"/>
+      <c r="L187" s="14" t="inlineStr"/>
+      <c r="M187" s="14" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N187" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O187" s="14" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P187" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q187" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R187" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S187" s="14" t="inlineStr"/>
+      <c r="T187" s="14" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U187" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V187" s="14" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="W187" s="14" t="inlineStr"/>
+      <c r="X187" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z187" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA187" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB187" s="14" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AC187" s="14" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD187" s="14" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AE187" s="14" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AF187" s="14" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AG187" s="14" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="AH187" s="14" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AI187" s="14" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AJ187" s="14" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AK187" s="14" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AL187" s="14" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AM187" s="14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AN187" s="14" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="AO187" s="14" t="inlineStr"/>
+      <c r="AP187" s="14" t="inlineStr"/>
+      <c r="AQ187" s="14" t="inlineStr"/>
+      <c r="AR187" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS187" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT187" s="14" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AU187" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G188" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H188" s="14" t="inlineStr"/>
+      <c r="I188" s="14" t="inlineStr"/>
+      <c r="J188" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" s="14" t="inlineStr"/>
+      <c r="L188" s="14" t="inlineStr"/>
+      <c r="M188" s="14" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N188" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O188" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P188" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q188" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R188" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S188" s="14" t="inlineStr"/>
+      <c r="T188" s="14" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U188" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V188" s="14" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="W188" s="14" t="inlineStr"/>
+      <c r="X188" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y188" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z188" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA188" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB188" s="14" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AC188" s="14" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD188" s="14" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE188" s="14" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF188" s="14" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AG188" s="14" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="AH188" s="14" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI188" s="14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ188" s="14" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AK188" s="14" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AL188" s="14" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AM188" s="14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN188" s="14" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="AO188" s="14" t="inlineStr"/>
+      <c r="AP188" s="14" t="inlineStr"/>
+      <c r="AQ188" s="14" t="inlineStr"/>
+      <c r="AR188" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS188" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT188" s="14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU188" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G189" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H189" s="14" t="inlineStr"/>
+      <c r="I189" s="14" t="inlineStr"/>
+      <c r="J189" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" s="14" t="inlineStr"/>
+      <c r="L189" s="14" t="inlineStr"/>
+      <c r="M189" s="14" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N189" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O189" s="14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="P189" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q189" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R189" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S189" s="14" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T189" s="14" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U189" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V189" s="14" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="W189" s="14" t="inlineStr"/>
+      <c r="X189" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y189" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z189" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA189" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB189" s="14" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AC189" s="14" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="AD189" s="14" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AE189" s="14" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AF189" s="14" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AG189" s="14" t="n">
+        <v>-12.11</v>
+      </c>
+      <c r="AH189" s="14" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AI189" s="14" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AJ189" s="14" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AK189" s="14" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AL189" s="14" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AM189" s="14" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AN189" s="14" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="AO189" s="14" t="inlineStr"/>
+      <c r="AP189" s="14" t="inlineStr"/>
+      <c r="AQ189" s="14" t="inlineStr"/>
+      <c r="AR189" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS189" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT189" s="14" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AU189" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G190" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H190" s="14" t="inlineStr"/>
+      <c r="I190" s="14" t="inlineStr"/>
+      <c r="J190" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K190" s="14" t="inlineStr"/>
+      <c r="L190" s="14" t="inlineStr"/>
+      <c r="M190" s="14" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N190" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O190" s="14" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P190" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q190" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R190" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S190" s="14" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T190" s="14" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U190" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V190" s="14" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W190" s="14" t="inlineStr"/>
+      <c r="X190" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z190" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA190" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB190" s="14" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AC190" s="14" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="AD190" s="14" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AE190" s="14" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AF190" s="14" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AG190" s="14" t="n">
+        <v>-23.25</v>
+      </c>
+      <c r="AH190" s="14" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AI190" s="14" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AJ190" s="14" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AK190" s="14" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="AL190" s="14" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AM190" s="14" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AN190" s="14" t="n">
+        <v>-19.21</v>
+      </c>
+      <c r="AO190" s="14" t="inlineStr"/>
+      <c r="AP190" s="14" t="inlineStr"/>
+      <c r="AQ190" s="14" t="inlineStr"/>
+      <c r="AR190" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS190" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT190" s="14" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AU190" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>KO_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G191" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H191" s="16" t="inlineStr"/>
+      <c r="I191" s="16" t="inlineStr"/>
+      <c r="J191" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K191" s="16" t="inlineStr"/>
+      <c r="L191" s="16" t="inlineStr"/>
+      <c r="M191" s="16" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N191" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O191" s="16" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P191" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q191" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R191" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S191" s="16" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T191" s="16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U191" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V191" s="16" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W191" s="16" t="inlineStr"/>
+      <c r="X191" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z191" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA191" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB191" s="16" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AC191" s="16" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="AD191" s="16" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AE191" s="16" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AF191" s="16" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AG191" s="16" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="AH191" s="16" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AI191" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ191" s="16" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AK191" s="16" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AL191" s="16" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AM191" s="16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN191" s="16" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="AO191" s="16" t="inlineStr"/>
+      <c r="AP191" s="16" t="inlineStr"/>
+      <c r="AQ191" s="16" t="inlineStr"/>
+      <c r="AR191" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS191" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT191" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU191" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>HON_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G192" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H192" s="16" t="inlineStr"/>
+      <c r="I192" s="16" t="inlineStr"/>
+      <c r="J192" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K192" s="16" t="inlineStr"/>
+      <c r="L192" s="16" t="inlineStr"/>
+      <c r="M192" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="N192" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O192" s="16" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P192" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q192" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R192" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S192" s="16" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T192" s="16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U192" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V192" s="16" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="W192" s="16" t="inlineStr"/>
+      <c r="X192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z192" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA192" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB192" s="16" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AC192" s="16" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="AD192" s="16" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AE192" s="16" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AF192" s="16" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AG192" s="16" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="AH192" s="16" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AI192" s="16" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AJ192" s="16" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AK192" s="16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AL192" s="16" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AM192" s="16" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AN192" s="16" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AO192" s="16" t="inlineStr"/>
+      <c r="AP192" s="16" t="inlineStr"/>
+      <c r="AQ192" s="16" t="inlineStr"/>
+      <c r="AR192" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS192" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT192" s="16" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AU192" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G193" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H193" s="16" t="inlineStr"/>
+      <c r="I193" s="16" t="inlineStr"/>
+      <c r="J193" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K193" s="16" t="inlineStr"/>
+      <c r="L193" s="16" t="inlineStr"/>
+      <c r="M193" s="16" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N193" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O193" s="16" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P193" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q193" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R193" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S193" s="16" t="inlineStr"/>
+      <c r="T193" s="16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U193" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V193" s="16" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="W193" s="16" t="inlineStr"/>
+      <c r="X193" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z193" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA193" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB193" s="16" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AC193" s="16" t="n">
+        <v>311</v>
+      </c>
+      <c r="AD193" s="16" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AE193" s="16" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AF193" s="16" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AG193" s="16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH193" s="16" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AI193" s="16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AJ193" s="16" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AK193" s="16" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AL193" s="16" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AM193" s="16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AN193" s="16" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AO193" s="16" t="inlineStr"/>
+      <c r="AP193" s="16" t="inlineStr"/>
+      <c r="AQ193" s="16" t="inlineStr"/>
+      <c r="AR193" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS193" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT193" s="16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AU193" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G194" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H194" s="16" t="inlineStr"/>
+      <c r="I194" s="16" t="inlineStr"/>
+      <c r="J194" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K194" s="16" t="inlineStr"/>
+      <c r="L194" s="16" t="inlineStr"/>
+      <c r="M194" s="16" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N194" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O194" s="16" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="P194" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q194" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R194" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S194" s="16" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T194" s="16" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U194" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V194" s="16" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="W194" s="16" t="inlineStr"/>
+      <c r="X194" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z194" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA194" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB194" s="16" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AC194" s="16" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="AD194" s="16" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AE194" s="16" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AF194" s="16" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AG194" s="16" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AH194" s="16" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AI194" s="16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ194" s="16" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AK194" s="16" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="AL194" s="16" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AM194" s="16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN194" s="16" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="AO194" s="16" t="inlineStr"/>
+      <c r="AP194" s="16" t="inlineStr"/>
+      <c r="AQ194" s="16" t="inlineStr"/>
+      <c r="AR194" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS194" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT194" s="16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU194" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>GS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G195" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H195" s="16" t="inlineStr"/>
+      <c r="I195" s="16" t="inlineStr"/>
+      <c r="J195" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K195" s="16" t="inlineStr"/>
+      <c r="L195" s="16" t="inlineStr"/>
+      <c r="M195" s="16" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="N195" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O195" s="16" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="P195" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q195" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R195" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S195" s="16" t="inlineStr"/>
+      <c r="T195" s="16" t="n">
+        <v>51</v>
+      </c>
+      <c r="U195" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V195" s="16" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="W195" s="16" t="inlineStr"/>
+      <c r="X195" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z195" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA195" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB195" s="16" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AC195" s="16" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="AD195" s="16" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AE195" s="16" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AF195" s="16" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AG195" s="16" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="AH195" s="16" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AI195" s="16" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AJ195" s="16" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AK195" s="16" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="AL195" s="16" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AM195" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN195" s="16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AO195" s="16" t="inlineStr"/>
+      <c r="AP195" s="16" t="inlineStr"/>
+      <c r="AQ195" s="16" t="inlineStr"/>
+      <c r="AR195" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS195" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT195" s="16" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AU195" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G196" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H196" s="16" t="inlineStr"/>
+      <c r="I196" s="16" t="inlineStr"/>
+      <c r="J196" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" s="16" t="inlineStr"/>
+      <c r="L196" s="16" t="inlineStr"/>
+      <c r="M196" s="16" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N196" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O196" s="16" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P196" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q196" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R196" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S196" s="16" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T196" s="16" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U196" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V196" s="16" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="W196" s="16" t="inlineStr"/>
+      <c r="X196" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z196" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA196" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB196" s="16" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AC196" s="16" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="AD196" s="16" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AE196" s="16" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AF196" s="16" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AG196" s="16" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AH196" s="16" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AI196" s="16" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AJ196" s="16" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AK196" s="16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL196" s="16" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AM196" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AN196" s="16" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="AO196" s="16" t="inlineStr"/>
+      <c r="AP196" s="16" t="inlineStr"/>
+      <c r="AQ196" s="16" t="inlineStr"/>
+      <c r="AR196" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS196" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT196" s="16" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AU196" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AU171"/>
+  <autoFilter ref="A1:AU196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU196"/>
+  <dimension ref="A1:AU217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28110,12 +28110,12 @@
       <c r="H190" s="14" t="inlineStr"/>
       <c r="I190" s="14" t="inlineStr"/>
       <c r="J190" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K190" s="14" t="inlineStr"/>
       <c r="L190" s="14" t="inlineStr"/>
       <c r="M190" s="14" t="n">
-        <v>79.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="N190" s="14" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         </is>
       </c>
       <c r="O190" s="14" t="n">
-        <v>52.9</v>
+        <v>53.2</v>
       </c>
       <c r="P190" s="14" t="n">
         <v>-0.8</v>
@@ -28135,16 +28135,12 @@
       </c>
       <c r="R190" s="14" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S190" s="14" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S190" s="14" t="inlineStr"/>
       <c r="T190" s="14" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="U190" s="14" t="inlineStr">
         <is>
@@ -28152,7 +28148,7 @@
         </is>
       </c>
       <c r="V190" s="14" t="n">
-        <v>51.8</v>
+        <v>65.7</v>
       </c>
       <c r="W190" s="14" t="inlineStr"/>
       <c r="X190" s="14" t="n">
@@ -28170,46 +28166,50 @@
         </is>
       </c>
       <c r="AB190" s="14" t="n">
-        <v>393.82</v>
+        <v>506.06</v>
       </c>
       <c r="AC190" s="14" t="n">
-        <v>487.4599914550781</v>
+        <v>506.06</v>
       </c>
       <c r="AD190" s="14" t="n">
-        <v>385.94</v>
+        <v>495.94</v>
       </c>
       <c r="AE190" s="14" t="n">
-        <v>401.7</v>
+        <v>516.1799999999999</v>
       </c>
       <c r="AF190" s="14" t="n">
-        <v>374.129</v>
+        <v>480.757</v>
       </c>
       <c r="AG190" s="14" t="n">
-        <v>-23.25</v>
+        <v>-5</v>
       </c>
       <c r="AH190" s="14" t="n">
-        <v>425.3256</v>
+        <v>546.5448</v>
       </c>
       <c r="AI190" s="14" t="n">
-        <v>-12.75</v>
+        <v>8</v>
       </c>
       <c r="AJ190" s="14" t="n">
-        <v>455.098392</v>
+        <v>584.802936</v>
       </c>
       <c r="AK190" s="14" t="n">
-        <v>-6.64</v>
+        <v>15.56</v>
       </c>
       <c r="AL190" s="14" t="n">
-        <v>492.81</v>
+        <v>499.99</v>
       </c>
       <c r="AM190" s="14" t="n">
-        <v>-1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AN190" s="14" t="n">
-        <v>-19.21</v>
-      </c>
-      <c r="AO190" s="14" t="inlineStr"/>
-      <c r="AP190" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AO190" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP190" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ190" s="14" t="inlineStr"/>
       <c r="AR190" s="14" t="inlineStr">
         <is>
@@ -28220,11 +28220,11 @@
         <v>5</v>
       </c>
       <c r="AT190" s="14" t="n">
-        <v>-12.75</v>
+        <v>8</v>
       </c>
       <c r="AU190" s="14" t="inlineStr">
         <is>
-          <t>2026-08-10 06:27</t>
+          <t>2026-08-10 21:39</t>
         </is>
       </c>
     </row>
@@ -28424,12 +28424,12 @@
       <c r="H192" s="16" t="inlineStr"/>
       <c r="I192" s="16" t="inlineStr"/>
       <c r="J192" s="16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K192" s="16" t="inlineStr"/>
       <c r="L192" s="16" t="inlineStr"/>
       <c r="M192" s="16" t="n">
-        <v>76</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="N192" s="16" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         </is>
       </c>
       <c r="O192" s="16" t="n">
-        <v>49.7</v>
+        <v>56.1</v>
       </c>
       <c r="P192" s="16" t="n">
         <v>-0.8</v>
@@ -28449,16 +28449,12 @@
       </c>
       <c r="R192" s="16" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S192" s="16" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 57% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S192" s="16" t="inlineStr"/>
       <c r="T192" s="16" t="n">
-        <v>50.5</v>
+        <v>56.8</v>
       </c>
       <c r="U192" s="16" t="inlineStr">
         <is>
@@ -28466,7 +28462,7 @@
         </is>
       </c>
       <c r="V192" s="16" t="n">
-        <v>46.5</v>
+        <v>44.7</v>
       </c>
       <c r="W192" s="16" t="inlineStr"/>
       <c r="X192" s="16" t="n">
@@ -28484,46 +28480,50 @@
         </is>
       </c>
       <c r="AB192" s="16" t="n">
-        <v>225.02</v>
+        <v>242.93</v>
       </c>
       <c r="AC192" s="16" t="n">
-        <v>248.1199951171875</v>
+        <v>242.93</v>
       </c>
       <c r="AD192" s="16" t="n">
-        <v>220.52</v>
+        <v>238.07</v>
       </c>
       <c r="AE192" s="16" t="n">
-        <v>229.52</v>
+        <v>247.79</v>
       </c>
       <c r="AF192" s="16" t="n">
-        <v>213.769</v>
+        <v>230.7835</v>
       </c>
       <c r="AG192" s="16" t="n">
-        <v>-13.84</v>
+        <v>-5</v>
       </c>
       <c r="AH192" s="16" t="n">
-        <v>243.0216</v>
+        <v>262.3644</v>
       </c>
       <c r="AI192" s="16" t="n">
-        <v>-2.05</v>
+        <v>8</v>
       </c>
       <c r="AJ192" s="16" t="n">
-        <v>260.0331120000001</v>
+        <v>280.7299080000001</v>
       </c>
       <c r="AK192" s="16" t="n">
-        <v>4.8</v>
+        <v>15.56</v>
       </c>
       <c r="AL192" s="16" t="n">
-        <v>248.79</v>
+        <v>246.21</v>
       </c>
       <c r="AM192" s="16" t="n">
-        <v>-0.27</v>
+        <v>-1.33</v>
       </c>
       <c r="AN192" s="16" t="n">
-        <v>-9.31</v>
-      </c>
-      <c r="AO192" s="16" t="inlineStr"/>
-      <c r="AP192" s="16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AO192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP192" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ192" s="16" t="inlineStr"/>
       <c r="AR192" s="16" t="inlineStr">
         <is>
@@ -28534,11 +28534,11 @@
         <v>5</v>
       </c>
       <c r="AT192" s="16" t="n">
-        <v>-2.05</v>
+        <v>8</v>
       </c>
       <c r="AU192" s="16" t="inlineStr">
         <is>
-          <t>2026-08-10 06:27</t>
+          <t>2026-08-10 21:39</t>
         </is>
       </c>
     </row>
@@ -29162,8 +29162,3277 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>PLTR_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr"/>
+      <c r="G197" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H197" s="13" t="inlineStr"/>
+      <c r="I197" s="13" t="inlineStr"/>
+      <c r="J197" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" s="13" t="inlineStr"/>
+      <c r="L197" s="13" t="inlineStr"/>
+      <c r="M197" s="13" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="N197" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O197" s="13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="P197" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q197" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R197" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 51% · band HOLD · 60d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S197" s="13" t="inlineStr"/>
+      <c r="T197" s="13" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="U197" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V197" s="13" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="W197" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z197" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA197" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB197" s="13" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="AC197" s="13" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="AD197" s="13" t="n">
+        <v>173.48</v>
+      </c>
+      <c r="AE197" s="13" t="n">
+        <v>176.98</v>
+      </c>
+      <c r="AF197" s="13" t="n">
+        <v>164.72</v>
+      </c>
+      <c r="AG197" s="13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH197" s="13" t="n">
+        <v>196.26</v>
+      </c>
+      <c r="AI197" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ197" s="13" t="n">
+        <v>217.29</v>
+      </c>
+      <c r="AK197" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL197" s="13" t="n">
+        <v>172.01</v>
+      </c>
+      <c r="AM197" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ197" s="13" t="inlineStr">
+        <is>
+          <t>Value · Quality · Growth</t>
+        </is>
+      </c>
+      <c r="AR197" s="13" t="inlineStr"/>
+      <c r="AS197" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT197" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>IT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr"/>
+      <c r="G198" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H198" s="13" t="inlineStr"/>
+      <c r="I198" s="13" t="inlineStr"/>
+      <c r="J198" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K198" s="13" t="inlineStr"/>
+      <c r="L198" s="13" t="inlineStr"/>
+      <c r="M198" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="N198" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O198" s="13" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="P198" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q198" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R198" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 50% · band HOLD · 60d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S198" s="13" t="inlineStr"/>
+      <c r="T198" s="13" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="U198" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V198" s="13" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W198" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z198" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA198" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB198" s="13" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="AC198" s="13" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="AD198" s="13" t="n">
+        <v>191.24</v>
+      </c>
+      <c r="AE198" s="13" t="n">
+        <v>195.1</v>
+      </c>
+      <c r="AF198" s="13" t="n">
+        <v>181.58</v>
+      </c>
+      <c r="AG198" s="13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH198" s="13" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="AI198" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ198" s="13" t="n">
+        <v>239.53</v>
+      </c>
+      <c r="AK198" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL198" s="13" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="AM198" s="13" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AN198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ198" s="13" t="inlineStr">
+        <is>
+          <t>Trend · Growth · News</t>
+        </is>
+      </c>
+      <c r="AR198" s="13" t="inlineStr"/>
+      <c r="AS198" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT198" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU198" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>APA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr"/>
+      <c r="G199" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H199" s="14" t="inlineStr"/>
+      <c r="I199" s="14" t="inlineStr"/>
+      <c r="J199" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" s="14" t="inlineStr"/>
+      <c r="L199" s="14" t="inlineStr"/>
+      <c r="M199" s="14" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="N199" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O199" s="14" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="P199" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q199" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R199" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 60% · band HOLD · 60d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S199" s="14" t="inlineStr"/>
+      <c r="T199" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="U199" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V199" s="14" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="W199" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X199" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z199" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA199" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB199" s="14" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AC199" s="14" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AD199" s="14" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AE199" s="14" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="AF199" s="14" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AG199" s="14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH199" s="14" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AI199" s="14" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AJ199" s="14" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="AK199" s="14" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="AL199" s="14" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="AM199" s="14" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="AN199" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO199" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP199" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ199" s="14" t="inlineStr">
+        <is>
+          <t>Value · News · Momentum</t>
+        </is>
+      </c>
+      <c r="AR199" s="14" t="inlineStr"/>
+      <c r="AS199" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT199" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU199" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>ADBE_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="G200" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H200" s="16" t="inlineStr"/>
+      <c r="I200" s="16" t="inlineStr"/>
+      <c r="J200" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K200" s="16" t="inlineStr"/>
+      <c r="L200" s="16" t="inlineStr"/>
+      <c r="M200" s="16" t="n">
+        <v>80</v>
+      </c>
+      <c r="N200" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O200" s="16" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P200" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q200" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R200" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 57% · band STRONG · 60d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S200" s="16" t="inlineStr"/>
+      <c r="T200" s="16" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U200" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V200" s="16" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="W200" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X200" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z200" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA200" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB200" s="16" t="n">
+        <v>272.96</v>
+      </c>
+      <c r="AC200" s="16" t="n">
+        <v>272.96</v>
+      </c>
+      <c r="AD200" s="16" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="AE200" s="16" t="n">
+        <v>275.69</v>
+      </c>
+      <c r="AF200" s="16" t="n">
+        <v>259.31</v>
+      </c>
+      <c r="AG200" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH200" s="16" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="AI200" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ200" s="16" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="AK200" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL200" s="16" t="n">
+        <v>265.21</v>
+      </c>
+      <c r="AM200" s="16" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AN200" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP200" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ200" s="16" t="inlineStr">
+        <is>
+          <t>Momentum · Quality · Event Driven</t>
+        </is>
+      </c>
+      <c r="AR200" s="16" t="inlineStr"/>
+      <c r="AS200" s="16" t="inlineStr"/>
+      <c r="AT200" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU200" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>ADSK_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H201" s="16" t="inlineStr"/>
+      <c r="I201" s="16" t="inlineStr"/>
+      <c r="J201" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K201" s="16" t="inlineStr"/>
+      <c r="L201" s="16" t="inlineStr"/>
+      <c r="M201" s="16" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N201" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O201" s="16" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="P201" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q201" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R201" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 54% · band HOLD · 60d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S201" s="16" t="inlineStr"/>
+      <c r="T201" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="U201" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V201" s="16" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="W201" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y201" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z201" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA201" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB201" s="16" t="n">
+        <v>256.07</v>
+      </c>
+      <c r="AC201" s="16" t="n">
+        <v>256.07</v>
+      </c>
+      <c r="AD201" s="16" t="n">
+        <v>253.51</v>
+      </c>
+      <c r="AE201" s="16" t="n">
+        <v>258.63</v>
+      </c>
+      <c r="AF201" s="16" t="n">
+        <v>243.27</v>
+      </c>
+      <c r="AG201" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH201" s="16" t="n">
+        <v>276.56</v>
+      </c>
+      <c r="AI201" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ201" s="16" t="n">
+        <v>294.48</v>
+      </c>
+      <c r="AK201" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL201" s="16" t="n">
+        <v>249.08</v>
+      </c>
+      <c r="AM201" s="16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AN201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ201" s="16" t="inlineStr">
+        <is>
+          <t>Growth · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AR201" s="16" t="inlineStr"/>
+      <c r="AS201" s="16" t="inlineStr"/>
+      <c r="AT201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU201" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>UBER_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr"/>
+      <c r="G202" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H202" s="16" t="inlineStr"/>
+      <c r="I202" s="16" t="inlineStr"/>
+      <c r="J202" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K202" s="16" t="inlineStr"/>
+      <c r="L202" s="16" t="inlineStr"/>
+      <c r="M202" s="16" t="n">
+        <v>76</v>
+      </c>
+      <c r="N202" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O202" s="16" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P202" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q202" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R202" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 57% · band HOLD · 60d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S202" s="16" t="inlineStr"/>
+      <c r="T202" s="16" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U202" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V202" s="16" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W202" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y202" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z202" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA202" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB202" s="16" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="AC202" s="16" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="AD202" s="16" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AE202" s="16" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="AF202" s="16" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="AG202" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH202" s="16" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="AI202" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ202" s="16" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="AK202" s="16" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AL202" s="16" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="AM202" s="16" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AN202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ202" s="16" t="inlineStr">
+        <is>
+          <t>Growth · Quality · Trend</t>
+        </is>
+      </c>
+      <c r="AR202" s="16" t="inlineStr"/>
+      <c r="AS202" s="16" t="inlineStr"/>
+      <c r="AT202" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU202" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>CF_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr"/>
+      <c r="G203" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H203" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +6.0pp alpha</t>
+        </is>
+      </c>
+      <c r="I203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K203" s="15" t="inlineStr"/>
+      <c r="L203" s="15" t="inlineStr"/>
+      <c r="M203" s="15" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N203" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O203" s="15" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="P203" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q203" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R203" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #8 · Conf 57% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S203" s="15" t="inlineStr"/>
+      <c r="T203" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="U203" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V203" s="15" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W203" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y203" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z203" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA203" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB203" s="15" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="AC203" s="15" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="AD203" s="15" t="n">
+        <v>120.27</v>
+      </c>
+      <c r="AE203" s="15" t="n">
+        <v>122.69</v>
+      </c>
+      <c r="AF203" s="15" t="n">
+        <v>115.41</v>
+      </c>
+      <c r="AG203" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH203" s="15" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="AI203" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ203" s="15" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="AK203" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL203" s="15" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="AM203" s="15" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AN203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ203" s="15" t="inlineStr">
+        <is>
+          <t>Growth · Quality · Value</t>
+        </is>
+      </c>
+      <c r="AR203" s="15" t="inlineStr"/>
+      <c r="AS203" s="15" t="inlineStr"/>
+      <c r="AT203" s="15" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="AU203" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>ROST_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr"/>
+      <c r="G204" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H204" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +6.6pp alpha</t>
+        </is>
+      </c>
+      <c r="I204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K204" s="15" t="inlineStr"/>
+      <c r="L204" s="15" t="inlineStr"/>
+      <c r="M204" s="15" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N204" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O204" s="15" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="P204" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q204" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R204" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #9 · Conf 54% · band STRONG · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S204" s="15" t="inlineStr"/>
+      <c r="T204" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="U204" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V204" s="15" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W204" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y204" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z204" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA204" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB204" s="15" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="AC204" s="15" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="AD204" s="15" t="n">
+        <v>252.27</v>
+      </c>
+      <c r="AE204" s="15" t="n">
+        <v>257.37</v>
+      </c>
+      <c r="AF204" s="15" t="n">
+        <v>242.08</v>
+      </c>
+      <c r="AG204" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH204" s="15" t="n">
+        <v>275.21</v>
+      </c>
+      <c r="AI204" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ204" s="15" t="n">
+        <v>293.04</v>
+      </c>
+      <c r="AK204" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL204" s="15" t="n">
+        <v>255.23</v>
+      </c>
+      <c r="AM204" s="15" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AN204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP204" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ204" s="15" t="inlineStr">
+        <is>
+          <t>Trend · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AR204" s="15" t="inlineStr"/>
+      <c r="AS204" s="15" t="inlineStr"/>
+      <c r="AT204" s="15" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AU204" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>HONA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>HONA</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr"/>
+      <c r="G205" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H205" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +58.0pp alpha</t>
+        </is>
+      </c>
+      <c r="I205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K205" s="15" t="inlineStr"/>
+      <c r="L205" s="15" t="inlineStr"/>
+      <c r="M205" s="15" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="N205" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O205" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P205" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q205" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R205" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #11 · Conf 18% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S205" s="15" t="inlineStr"/>
+      <c r="T205" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="U205" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V205" s="15" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="W205" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z205" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA205" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB205" s="15" t="n">
+        <v>163.09</v>
+      </c>
+      <c r="AC205" s="15" t="n">
+        <v>163.09</v>
+      </c>
+      <c r="AD205" s="15" t="n">
+        <v>161.46</v>
+      </c>
+      <c r="AE205" s="15" t="n">
+        <v>164.72</v>
+      </c>
+      <c r="AF205" s="15" t="n">
+        <v>154.94</v>
+      </c>
+      <c r="AG205" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH205" s="15" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="AI205" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ205" s="15" t="n">
+        <v>187.55</v>
+      </c>
+      <c r="AK205" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL205" s="15" t="n">
+        <v>168.51</v>
+      </c>
+      <c r="AM205" s="15" t="n">
+        <v>-3.22</v>
+      </c>
+      <c r="AN205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP205" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ205" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Earn Days To Next · Fund Earnings Growth · Fund Market Cap Log</t>
+        </is>
+      </c>
+      <c r="AR205" s="15" t="inlineStr"/>
+      <c r="AS205" s="15" t="inlineStr"/>
+      <c r="AT205" s="15" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="AU205" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>AKAM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>AKAM</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr"/>
+      <c r="G206" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H206" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +58.1pp alpha</t>
+        </is>
+      </c>
+      <c r="I206" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K206" s="15" t="inlineStr"/>
+      <c r="L206" s="15" t="inlineStr"/>
+      <c r="M206" s="15" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N206" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O206" s="15" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="P206" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q206" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R206" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #12 · Conf 31% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S206" s="15" t="inlineStr"/>
+      <c r="T206" s="15" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="U206" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V206" s="15" t="n">
+        <v>-25.2</v>
+      </c>
+      <c r="W206" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X206" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z206" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA206" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB206" s="15" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="AC206" s="15" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="AD206" s="15" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="AE206" s="15" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="AF206" s="15" t="n">
+        <v>111.77</v>
+      </c>
+      <c r="AG206" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH206" s="15" t="n">
+        <v>127.06</v>
+      </c>
+      <c r="AI206" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ206" s="15" t="n">
+        <v>135.3</v>
+      </c>
+      <c r="AK206" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL206" s="15" t="n">
+        <v>110.54</v>
+      </c>
+      <c r="AM206" s="15" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AN206" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP206" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ206" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AR206" s="15" t="inlineStr"/>
+      <c r="AS206" s="15" t="inlineStr"/>
+      <c r="AT206" s="15" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="AU206" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>D_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr"/>
+      <c r="G207" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H207" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +58.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K207" s="15" t="inlineStr"/>
+      <c r="L207" s="15" t="inlineStr"/>
+      <c r="M207" s="15" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="N207" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O207" s="15" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="P207" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q207" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R207" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #13 · Conf 33% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S207" s="15" t="inlineStr"/>
+      <c r="T207" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="U207" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V207" s="15" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="W207" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z207" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA207" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB207" s="15" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="AC207" s="15" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="AD207" s="15" t="n">
+        <v>66.48</v>
+      </c>
+      <c r="AE207" s="15" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="AF207" s="15" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="AG207" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH207" s="15" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="AI207" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ207" s="15" t="n">
+        <v>77.22</v>
+      </c>
+      <c r="AK207" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL207" s="15" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="AM207" s="15" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AN207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP207" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ207" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AR207" s="15" t="inlineStr"/>
+      <c r="AS207" s="15" t="inlineStr"/>
+      <c r="AT207" s="15" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="AU207" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>CPT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>CPT</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr"/>
+      <c r="G208" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H208" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +63.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I208" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K208" s="15" t="inlineStr"/>
+      <c r="L208" s="15" t="inlineStr"/>
+      <c r="M208" s="15" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N208" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O208" s="15" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="P208" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q208" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R208" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #14 · Conf 31% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S208" s="15" t="inlineStr"/>
+      <c r="T208" s="15" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="U208" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V208" s="15" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="W208" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X208" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y208" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z208" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA208" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB208" s="15" t="n">
+        <v>109.08</v>
+      </c>
+      <c r="AC208" s="15" t="n">
+        <v>109.08</v>
+      </c>
+      <c r="AD208" s="15" t="n">
+        <v>107.99</v>
+      </c>
+      <c r="AE208" s="15" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="AF208" s="15" t="n">
+        <v>103.63</v>
+      </c>
+      <c r="AG208" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH208" s="15" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="AI208" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ208" s="15" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="AK208" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL208" s="15" t="n">
+        <v>111.93</v>
+      </c>
+      <c r="AM208" s="15" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="AN208" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO208" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP208" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ208" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AR208" s="15" t="inlineStr"/>
+      <c r="AS208" s="15" t="inlineStr"/>
+      <c r="AT208" s="15" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="AU208" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>CARR_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>CARR</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr"/>
+      <c r="G209" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H209" s="15" t="inlineStr">
+        <is>
+          <t>→ PLTR · +64.5pp alpha</t>
+        </is>
+      </c>
+      <c r="I209" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K209" s="15" t="inlineStr"/>
+      <c r="L209" s="15" t="inlineStr"/>
+      <c r="M209" s="15" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N209" s="15" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O209" s="15" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="P209" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q209" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R209" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #15 · Conf 31% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+        </is>
+      </c>
+      <c r="S209" s="15" t="inlineStr"/>
+      <c r="T209" s="15" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="U209" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V209" s="15" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="W209" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X209" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y209" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z209" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA209" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB209" s="15" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="AC209" s="15" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="AD209" s="15" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="AE209" s="15" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="AF209" s="15" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="AG209" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH209" s="15" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="AI209" s="15" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AJ209" s="15" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="AK209" s="15" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AL209" s="15" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="AM209" s="15" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="AN209" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO209" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP209" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ209" s="15" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AR209" s="15" t="inlineStr"/>
+      <c r="AS209" s="15" t="inlineStr"/>
+      <c r="AT209" s="15" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="AU209" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>PLTR_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr"/>
+      <c r="G210" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H210" s="14" t="inlineStr"/>
+      <c r="I210" s="14" t="inlineStr"/>
+      <c r="J210" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="14" t="inlineStr"/>
+      <c r="L210" s="14" t="inlineStr"/>
+      <c r="M210" s="14" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="N210" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O210" s="14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="P210" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q210" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R210" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S210" s="14" t="inlineStr"/>
+      <c r="T210" s="14" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="U210" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V210" s="14" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="W210" s="14" t="inlineStr"/>
+      <c r="X210" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z210" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA210" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB210" s="14" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="AC210" s="14" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="AD210" s="14" t="n">
+        <v>173.48</v>
+      </c>
+      <c r="AE210" s="14" t="n">
+        <v>176.98</v>
+      </c>
+      <c r="AF210" s="14" t="n">
+        <v>166.4685</v>
+      </c>
+      <c r="AG210" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH210" s="14" t="n">
+        <v>196.26</v>
+      </c>
+      <c r="AI210" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ210" s="14" t="n">
+        <v>209.9982</v>
+      </c>
+      <c r="AK210" s="14" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AL210" s="14" t="n">
+        <v>172.01</v>
+      </c>
+      <c r="AM210" s="14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN210" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO210" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP210" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ210" s="14" t="inlineStr"/>
+      <c r="AR210" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS210" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT210" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU210" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>UBER_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr"/>
+      <c r="G211" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H211" s="14" t="inlineStr"/>
+      <c r="I211" s="14" t="inlineStr"/>
+      <c r="J211" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K211" s="14" t="inlineStr"/>
+      <c r="L211" s="14" t="inlineStr"/>
+      <c r="M211" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="N211" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O211" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P211" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q211" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R211" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S211" s="14" t="inlineStr"/>
+      <c r="T211" s="14" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U211" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V211" s="14" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="W211" s="14" t="inlineStr"/>
+      <c r="X211" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z211" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA211" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB211" s="14" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="AC211" s="14" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="AD211" s="14" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="AE211" s="14" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="AF211" s="14" t="n">
+        <v>74.1285</v>
+      </c>
+      <c r="AG211" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH211" s="14" t="n">
+        <v>84.2724</v>
+      </c>
+      <c r="AI211" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ211" s="14" t="n">
+        <v>90.171468</v>
+      </c>
+      <c r="AK211" s="14" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL211" s="14" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="AM211" s="14" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AN211" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO211" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP211" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ211" s="14" t="inlineStr"/>
+      <c r="AR211" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS211" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT211" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU211" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>APA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr"/>
+      <c r="G212" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H212" s="14" t="inlineStr"/>
+      <c r="I212" s="14" t="inlineStr"/>
+      <c r="J212" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K212" s="14" t="inlineStr"/>
+      <c r="L212" s="14" t="inlineStr"/>
+      <c r="M212" s="14" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="N212" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O212" s="14" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="P212" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q212" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R212" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 60% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S212" s="14" t="inlineStr"/>
+      <c r="T212" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="U212" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V212" s="14" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="W212" s="14" t="inlineStr"/>
+      <c r="X212" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y212" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z212" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA212" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB212" s="14" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AC212" s="14" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="AD212" s="14" t="n">
+        <v>40.61</v>
+      </c>
+      <c r="AE212" s="14" t="n">
+        <v>41.43</v>
+      </c>
+      <c r="AF212" s="14" t="n">
+        <v>38.969</v>
+      </c>
+      <c r="AG212" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH212" s="14" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AI212" s="14" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AJ212" s="14" t="n">
+        <v>49.1558</v>
+      </c>
+      <c r="AK212" s="14" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="AL212" s="14" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="AM212" s="14" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="AN212" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO212" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP212" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ212" s="14" t="inlineStr"/>
+      <c r="AR212" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS212" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT212" s="14" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="AU212" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>ADSK_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr"/>
+      <c r="G213" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H213" s="14" t="inlineStr"/>
+      <c r="I213" s="14" t="inlineStr"/>
+      <c r="J213" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K213" s="14" t="inlineStr"/>
+      <c r="L213" s="14" t="inlineStr"/>
+      <c r="M213" s="14" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N213" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O213" s="14" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="P213" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q213" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R213" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S213" s="14" t="inlineStr"/>
+      <c r="T213" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="U213" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V213" s="14" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="W213" s="14" t="inlineStr"/>
+      <c r="X213" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y213" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z213" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA213" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB213" s="14" t="n">
+        <v>256.07</v>
+      </c>
+      <c r="AC213" s="14" t="n">
+        <v>256.07</v>
+      </c>
+      <c r="AD213" s="14" t="n">
+        <v>250.95</v>
+      </c>
+      <c r="AE213" s="14" t="n">
+        <v>261.19</v>
+      </c>
+      <c r="AF213" s="14" t="n">
+        <v>243.2665</v>
+      </c>
+      <c r="AG213" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH213" s="14" t="n">
+        <v>276.5556</v>
+      </c>
+      <c r="AI213" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ213" s="14" t="n">
+        <v>295.9144920000001</v>
+      </c>
+      <c r="AK213" s="14" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL213" s="14" t="n">
+        <v>249.08</v>
+      </c>
+      <c r="AM213" s="14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AN213" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO213" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP213" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ213" s="14" t="inlineStr"/>
+      <c r="AR213" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS213" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT213" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU213" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>ADBE_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="G214" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H214" s="14" t="inlineStr"/>
+      <c r="I214" s="14" t="inlineStr"/>
+      <c r="J214" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K214" s="14" t="inlineStr"/>
+      <c r="L214" s="14" t="inlineStr"/>
+      <c r="M214" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="N214" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O214" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P214" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q214" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R214" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 57% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S214" s="14" t="inlineStr"/>
+      <c r="T214" s="14" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U214" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V214" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="W214" s="14" t="inlineStr"/>
+      <c r="X214" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y214" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z214" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA214" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB214" s="14" t="n">
+        <v>272.96</v>
+      </c>
+      <c r="AC214" s="14" t="n">
+        <v>272.96</v>
+      </c>
+      <c r="AD214" s="14" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="AE214" s="14" t="n">
+        <v>278.42</v>
+      </c>
+      <c r="AF214" s="14" t="n">
+        <v>259.312</v>
+      </c>
+      <c r="AG214" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH214" s="14" t="n">
+        <v>294.7968</v>
+      </c>
+      <c r="AI214" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ214" s="14" t="n">
+        <v>315.432576</v>
+      </c>
+      <c r="AK214" s="14" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL214" s="14" t="n">
+        <v>265.21</v>
+      </c>
+      <c r="AM214" s="14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AN214" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO214" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP214" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ214" s="14" t="inlineStr"/>
+      <c r="AR214" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS214" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT214" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU214" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>IT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr"/>
+      <c r="G215" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H215" s="14" t="inlineStr"/>
+      <c r="I215" s="14" t="inlineStr"/>
+      <c r="J215" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K215" s="14" t="inlineStr"/>
+      <c r="L215" s="14" t="inlineStr"/>
+      <c r="M215" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="N215" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O215" s="14" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="P215" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q215" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R215" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 50% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S215" s="14" t="inlineStr"/>
+      <c r="T215" s="14" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="U215" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V215" s="14" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="W215" s="14" t="inlineStr"/>
+      <c r="X215" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y215" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z215" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA215" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB215" s="14" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="AC215" s="14" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="AD215" s="14" t="n">
+        <v>191.24</v>
+      </c>
+      <c r="AE215" s="14" t="n">
+        <v>195.1</v>
+      </c>
+      <c r="AF215" s="14" t="n">
+        <v>183.5115</v>
+      </c>
+      <c r="AG215" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH215" s="14" t="n">
+        <v>216.35</v>
+      </c>
+      <c r="AI215" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ215" s="14" t="n">
+        <v>231.4945</v>
+      </c>
+      <c r="AK215" s="14" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="AL215" s="14" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="AM215" s="14" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AN215" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO215" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP215" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ215" s="14" t="inlineStr"/>
+      <c r="AR215" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS215" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT215" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU215" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>CF_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr"/>
+      <c r="G216" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H216" s="14" t="inlineStr"/>
+      <c r="I216" s="14" t="inlineStr"/>
+      <c r="J216" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K216" s="14" t="inlineStr"/>
+      <c r="L216" s="14" t="inlineStr"/>
+      <c r="M216" s="14" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N216" s="14" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O216" s="14" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="P216" s="14" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q216" s="14" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R216" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S216" s="14" t="inlineStr"/>
+      <c r="T216" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="U216" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V216" s="14" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="W216" s="14" t="inlineStr"/>
+      <c r="X216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z216" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA216" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB216" s="14" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="AC216" s="14" t="n">
+        <v>121.48</v>
+      </c>
+      <c r="AD216" s="14" t="n">
+        <v>119.05</v>
+      </c>
+      <c r="AE216" s="14" t="n">
+        <v>123.91</v>
+      </c>
+      <c r="AF216" s="14" t="n">
+        <v>115.406</v>
+      </c>
+      <c r="AG216" s="14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH216" s="14" t="n">
+        <v>131.1984</v>
+      </c>
+      <c r="AI216" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ216" s="14" t="n">
+        <v>140.382288</v>
+      </c>
+      <c r="AK216" s="14" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL216" s="14" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="AM216" s="14" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AN216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP216" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ216" s="14" t="inlineStr"/>
+      <c r="AR216" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS216" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT216" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU216" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>ROST_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr"/>
+      <c r="G217" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H217" s="16" t="inlineStr"/>
+      <c r="I217" s="16" t="inlineStr"/>
+      <c r="J217" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K217" s="16" t="inlineStr"/>
+      <c r="L217" s="16" t="inlineStr"/>
+      <c r="M217" s="16" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N217" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O217" s="16" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="P217" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q217" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R217" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S217" s="16" t="inlineStr"/>
+      <c r="T217" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="U217" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V217" s="16" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="W217" s="16" t="inlineStr"/>
+      <c r="X217" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y217" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z217" s="16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA217" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB217" s="16" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="AC217" s="16" t="n">
+        <v>254.82</v>
+      </c>
+      <c r="AD217" s="16" t="n">
+        <v>249.72</v>
+      </c>
+      <c r="AE217" s="16" t="n">
+        <v>259.92</v>
+      </c>
+      <c r="AF217" s="16" t="n">
+        <v>242.079</v>
+      </c>
+      <c r="AG217" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH217" s="16" t="n">
+        <v>275.2056</v>
+      </c>
+      <c r="AI217" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ217" s="16" t="n">
+        <v>294.469992</v>
+      </c>
+      <c r="AK217" s="16" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL217" s="16" t="n">
+        <v>255.23</v>
+      </c>
+      <c r="AM217" s="16" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AN217" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO217" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP217" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ217" s="16" t="inlineStr"/>
+      <c r="AR217" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS217" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT217" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU217" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10 21:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AU196"/>
+  <autoFilter ref="A1:AU217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_history.xlsx
+++ b/reports/telegram/aegis_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AU$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU217"/>
+  <dimension ref="A1:AU259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -32431,8 +32431,6000 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>GNFC_IND_20260806</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>GNFC</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr"/>
+      <c r="G218" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H218" s="13" t="inlineStr"/>
+      <c r="I218" s="13" t="inlineStr"/>
+      <c r="J218" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" s="13" t="inlineStr"/>
+      <c r="L218" s="13" t="inlineStr"/>
+      <c r="M218" s="13" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="N218" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O218" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P218" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q218" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R218" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S218" s="13" t="inlineStr"/>
+      <c r="T218" s="13" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="U218" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V218" s="13" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="W218" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X218" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y218" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z218" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA218" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AB218" s="13" t="n">
+        <v>544.1</v>
+      </c>
+      <c r="AC218" s="13" t="n">
+        <v>553.3</v>
+      </c>
+      <c r="AD218" s="13" t="n">
+        <v>538.66</v>
+      </c>
+      <c r="AE218" s="13" t="n">
+        <v>549.54</v>
+      </c>
+      <c r="AF218" s="13" t="n">
+        <v>511.45</v>
+      </c>
+      <c r="AG218" s="13" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="AH218" s="13" t="n">
+        <v>609.39</v>
+      </c>
+      <c r="AI218" s="13" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AJ218" s="13" t="n">
+        <v>674.6799999999999</v>
+      </c>
+      <c r="AK218" s="13" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="AL218" s="13" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="AM218" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN218" s="13" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AO218" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP218" s="13" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AQ218" s="13" t="inlineStr">
+        <is>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AR218" s="13" t="inlineStr"/>
+      <c r="AS218" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT218" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU218" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>TCS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="G219" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H219" s="13" t="inlineStr"/>
+      <c r="I219" s="13" t="inlineStr"/>
+      <c r="J219" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K219" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L219" s="13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M219" s="13" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="N219" s="13" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O219" s="13" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="P219" s="13" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q219" s="13" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R219" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↑ 9→2 · Conf 39% · band HOLD · 16d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S219" s="13" t="inlineStr"/>
+      <c r="T219" s="13" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U219" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V219" s="13" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="W219" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X219" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y219" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z219" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA219" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB219" s="13" t="n">
+        <v>2425.7</v>
+      </c>
+      <c r="AC219" s="13" t="n">
+        <v>2351.3</v>
+      </c>
+      <c r="AD219" s="13" t="n">
+        <v>2401.44</v>
+      </c>
+      <c r="AE219" s="13" t="n">
+        <v>2449.96</v>
+      </c>
+      <c r="AF219" s="13" t="n">
+        <v>2280.16</v>
+      </c>
+      <c r="AG219" s="13" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="AH219" s="13" t="n">
+        <v>2716.78</v>
+      </c>
+      <c r="AI219" s="13" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AJ219" s="13" t="n">
+        <v>3007.87</v>
+      </c>
+      <c r="AK219" s="13" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AL219" s="13" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="AM219" s="13" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AN219" s="13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AO219" s="13" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AP219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ219" s="13" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Momentum</t>
+        </is>
+      </c>
+      <c r="AR219" s="13" t="inlineStr"/>
+      <c r="AS219" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT219" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>OFSS_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr"/>
+      <c r="G220" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H220" s="16" t="inlineStr"/>
+      <c r="I220" s="16" t="inlineStr"/>
+      <c r="J220" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K220" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L220" s="16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M220" s="16" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="N220" s="16" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O220" s="16" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="P220" s="16" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q220" s="16" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R220" s="16" t="inlineStr">
+        <is>
+          <t>🟡 WAIT (Δ+6.3%) · Rank ↑ 6→3 · Conf 49% · band HOLD · 16d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S220" s="16" t="inlineStr"/>
+      <c r="T220" s="16" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="U220" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V220" s="16" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W220" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X220" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y220" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z220" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA220" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB220" s="16" t="n">
+        <v>11890</v>
+      </c>
+      <c r="AC220" s="16" t="n">
+        <v>11075</v>
+      </c>
+      <c r="AD220" s="16" t="n">
+        <v>10964.25</v>
+      </c>
+      <c r="AE220" s="16" t="n">
+        <v>11185.75</v>
+      </c>
+      <c r="AF220" s="16" t="n">
+        <v>10521.25</v>
+      </c>
+      <c r="AG220" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH220" s="16" t="n">
+        <v>11961</v>
+      </c>
+      <c r="AI220" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ220" s="16" t="n">
+        <v>12736.25</v>
+      </c>
+      <c r="AK220" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL220" s="16" t="n">
+        <v>11805</v>
+      </c>
+      <c r="AM220" s="16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AN220" s="16" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AO220" s="16" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AP220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ220" s="16" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Momentum</t>
+        </is>
+      </c>
+      <c r="AR220" s="16" t="inlineStr"/>
+      <c r="AS220" s="16" t="inlineStr"/>
+      <c r="AT220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR_IND_20260811</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr"/>
+      <c r="G221" s="15" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H221" s="15" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +8.1pp alpha</t>
+        </is>
+      </c>
+      <c r="I221" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K221" s="15" t="inlineStr"/>
+      <c r="L221" s="15" t="inlineStr"/>
+      <c r="M221" s="15" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N221" s="15" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O221" s="15" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="P221" s="15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q221" s="15" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+47 more) → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
+      <c r="R221" s="15" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank #10 · Conf 38% · band HOLD · 90d left · → EXIT (rotate to GNFC.NS)</t>
+        </is>
+      </c>
+      <c r="S221" s="15" t="inlineStr"/>
+      <c r="T221" s="15" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="U221" s="15" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V221" s="15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="W221" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X221" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y221" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z221" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA221" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB221" s="15" t="n">
+        <v>1796.5</v>
+      </c>
+      <c r="AC221" s="15" t="n">
+        <v>1796.5</v>
+      </c>
+      <c r="AD221" s="15" t="n">
+        <v>1778.54</v>
+      </c>
+      <c r="AE221" s="15" t="n">
+        <v>1814.46</v>
+      </c>
+      <c r="AF221" s="15" t="n">
+        <v>1706.67</v>
+      </c>
+      <c r="AG221" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH221" s="15" t="n">
+        <v>1940.22</v>
+      </c>
+      <c r="AI221" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ221" s="15" t="n">
+        <v>2065.97</v>
+      </c>
+      <c r="AK221" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL221" s="15" t="n">
+        <v>1722</v>
+      </c>
+      <c r="AM221" s="15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AN221" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO221" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP221" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ221" s="15" t="inlineStr">
+        <is>
+          <t>Growth · Mean Reversion · Momentum</t>
+        </is>
+      </c>
+      <c r="AR221" s="15" t="inlineStr"/>
+      <c r="AS221" s="15" t="inlineStr"/>
+      <c r="AT221" s="15" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AU221" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G222" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H222" s="13" t="inlineStr"/>
+      <c r="I222" s="13" t="inlineStr"/>
+      <c r="J222" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M222" s="13" t="inlineStr"/>
+      <c r="N222" s="13" t="inlineStr"/>
+      <c r="O222" s="13" t="inlineStr"/>
+      <c r="P222" s="13" t="inlineStr"/>
+      <c r="Q222" s="13" t="inlineStr"/>
+      <c r="R222" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S222" s="13" t="inlineStr"/>
+      <c r="T222" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="U222" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V222" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="W222" s="13" t="inlineStr"/>
+      <c r="X222" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y222" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z222" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA222" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB222" s="13" t="n">
+        <v>1431.8</v>
+      </c>
+      <c r="AC222" s="13" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD222" s="13" t="n">
+        <v>1392</v>
+      </c>
+      <c r="AE222" s="13" t="n">
+        <v>1472</v>
+      </c>
+      <c r="AF222" s="13" t="n">
+        <v>1360.21</v>
+      </c>
+      <c r="AG222" s="13" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="AH222" s="13" t="n">
+        <v>1508</v>
+      </c>
+      <c r="AI222" s="13" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AJ222" s="13" t="n">
+        <v>1613.56</v>
+      </c>
+      <c r="AK222" s="13" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AL222" s="13" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AM222" s="13" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AN222" s="13" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AO222" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP222" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ222" s="13" t="inlineStr"/>
+      <c r="AR222" s="13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS222" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT222" s="13" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AU222" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE_IND_20260811</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr"/>
+      <c r="G223" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H223" s="13" t="inlineStr"/>
+      <c r="I223" s="13" t="inlineStr"/>
+      <c r="J223" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K223" s="13" t="inlineStr"/>
+      <c r="L223" s="13" t="inlineStr"/>
+      <c r="M223" s="13" t="inlineStr"/>
+      <c r="N223" s="13" t="inlineStr"/>
+      <c r="O223" s="13" t="inlineStr"/>
+      <c r="P223" s="13" t="inlineStr"/>
+      <c r="Q223" s="13" t="inlineStr"/>
+      <c r="R223" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank #2 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S223" s="13" t="inlineStr"/>
+      <c r="T223" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="U223" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V223" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="W223" s="13" t="inlineStr"/>
+      <c r="X223" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y223" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z223" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA223" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB223" s="13" t="n">
+        <v>1119</v>
+      </c>
+      <c r="AC223" s="13" t="n">
+        <v>1119</v>
+      </c>
+      <c r="AD223" s="13" t="n">
+        <v>1086</v>
+      </c>
+      <c r="AE223" s="13" t="n">
+        <v>1152</v>
+      </c>
+      <c r="AF223" s="13" t="n">
+        <v>1063.05</v>
+      </c>
+      <c r="AG223" s="13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH223" s="13" t="n">
+        <v>1208.52</v>
+      </c>
+      <c r="AI223" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ223" s="13" t="n">
+        <v>1293.1164</v>
+      </c>
+      <c r="AK223" s="13" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL223" s="13" t="n">
+        <v>1114.2</v>
+      </c>
+      <c r="AM223" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN223" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO223" s="13" t="inlineStr"/>
+      <c r="AP223" s="13" t="inlineStr"/>
+      <c r="AQ223" s="13" t="inlineStr"/>
+      <c r="AR223" s="13" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS223" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT223" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU223" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G224" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H224" s="13" t="inlineStr"/>
+      <c r="I224" s="13" t="inlineStr"/>
+      <c r="J224" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L224" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="13" t="inlineStr"/>
+      <c r="N224" s="13" t="inlineStr"/>
+      <c r="O224" s="13" t="inlineStr"/>
+      <c r="P224" s="13" t="inlineStr"/>
+      <c r="Q224" s="13" t="inlineStr"/>
+      <c r="R224" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 3→3 · Conf 71% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S224" s="13" t="inlineStr"/>
+      <c r="T224" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="U224" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V224" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="W224" s="13" t="inlineStr"/>
+      <c r="X224" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y224" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z224" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA224" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB224" s="13" t="n">
+        <v>2300</v>
+      </c>
+      <c r="AC224" s="13" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD224" s="13" t="n">
+        <v>2240</v>
+      </c>
+      <c r="AE224" s="13" t="n">
+        <v>2360</v>
+      </c>
+      <c r="AF224" s="13" t="n">
+        <v>2185</v>
+      </c>
+      <c r="AG224" s="13" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="AH224" s="13" t="n">
+        <v>2484</v>
+      </c>
+      <c r="AI224" s="13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AJ224" s="13" t="n">
+        <v>2657.88</v>
+      </c>
+      <c r="AK224" s="13" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="AL224" s="13" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM224" s="13" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="AN224" s="13" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="AO224" s="13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP224" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ224" s="13" t="inlineStr"/>
+      <c r="AR224" s="13" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="AS224" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT224" s="13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU224" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G225" s="13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="H225" s="13" t="inlineStr"/>
+      <c r="I225" s="13" t="inlineStr"/>
+      <c r="J225" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K225" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L225" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M225" s="13" t="inlineStr"/>
+      <c r="N225" s="13" t="inlineStr"/>
+      <c r="O225" s="13" t="inlineStr"/>
+      <c r="P225" s="13" t="inlineStr"/>
+      <c r="Q225" s="13" t="inlineStr"/>
+      <c r="R225" s="13" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.8%) · Rank ↑ 5→4 · Conf 72% · momentum → · 61d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="S225" s="13" t="inlineStr"/>
+      <c r="T225" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="U225" s="13" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V225" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="W225" s="13" t="inlineStr"/>
+      <c r="X225" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y225" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z225" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA225" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB225" s="13" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="AC225" s="13" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD225" s="13" t="n">
+        <v>382</v>
+      </c>
+      <c r="AE225" s="13" t="n">
+        <v>405</v>
+      </c>
+      <c r="AF225" s="13" t="n">
+        <v>373.825</v>
+      </c>
+      <c r="AG225" s="13" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="AH225" s="13" t="n">
+        <v>424.98</v>
+      </c>
+      <c r="AI225" s="13" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AJ225" s="13" t="n">
+        <v>454.7286</v>
+      </c>
+      <c r="AK225" s="13" t="n">
+        <v>16.81</v>
+      </c>
+      <c r="AL225" s="13" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AM225" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN225" s="13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO225" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP225" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ225" s="13" t="inlineStr"/>
+      <c r="AR225" s="13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AS225" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT225" s="13" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AU225" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G226" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H226" s="14" t="inlineStr"/>
+      <c r="I226" s="14" t="inlineStr"/>
+      <c r="J226" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K226" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L226" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" s="14" t="inlineStr"/>
+      <c r="N226" s="14" t="inlineStr"/>
+      <c r="O226" s="14" t="inlineStr"/>
+      <c r="P226" s="14" t="inlineStr"/>
+      <c r="Q226" s="14" t="inlineStr"/>
+      <c r="R226" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank ↓ 4→5 · Conf 71% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S226" s="14" t="inlineStr"/>
+      <c r="T226" s="14" t="n">
+        <v>71</v>
+      </c>
+      <c r="U226" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V226" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="W226" s="14" t="inlineStr"/>
+      <c r="X226" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y226" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z226" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA226" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB226" s="14" t="n">
+        <v>340.5</v>
+      </c>
+      <c r="AC226" s="14" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD226" s="14" t="n">
+        <v>332</v>
+      </c>
+      <c r="AE226" s="14" t="n">
+        <v>349</v>
+      </c>
+      <c r="AF226" s="14" t="n">
+        <v>323.475</v>
+      </c>
+      <c r="AG226" s="14" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="AH226" s="14" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="AI226" s="14" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AJ226" s="14" t="n">
+        <v>393.4818</v>
+      </c>
+      <c r="AK226" s="14" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="AL226" s="14" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AM226" s="14" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AN226" s="14" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AO226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP226" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ226" s="14" t="inlineStr"/>
+      <c r="AR226" s="14" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS226" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT226" s="14" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AU226" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G227" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H227" s="14" t="inlineStr"/>
+      <c r="I227" s="14" t="inlineStr"/>
+      <c r="J227" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K227" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L227" s="14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M227" s="14" t="inlineStr"/>
+      <c r="N227" s="14" t="inlineStr"/>
+      <c r="O227" s="14" t="inlineStr"/>
+      <c r="P227" s="14" t="inlineStr"/>
+      <c r="Q227" s="14" t="inlineStr"/>
+      <c r="R227" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→6 · Conf 65% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S227" s="14" t="inlineStr"/>
+      <c r="T227" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="U227" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V227" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="W227" s="14" t="inlineStr"/>
+      <c r="X227" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y227" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z227" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA227" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB227" s="14" t="n">
+        <v>404.4</v>
+      </c>
+      <c r="AC227" s="14" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD227" s="14" t="n">
+        <v>392</v>
+      </c>
+      <c r="AE227" s="14" t="n">
+        <v>417</v>
+      </c>
+      <c r="AF227" s="14" t="n">
+        <v>384.1799999999999</v>
+      </c>
+      <c r="AG227" s="14" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AH227" s="14" t="n">
+        <v>436.752</v>
+      </c>
+      <c r="AI227" s="14" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AJ227" s="14" t="n">
+        <v>467.32464</v>
+      </c>
+      <c r="AK227" s="14" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="AL227" s="14" t="n">
+        <v>401</v>
+      </c>
+      <c r="AM227" s="14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AN227" s="14" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AO227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP227" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ227" s="14" t="inlineStr"/>
+      <c r="AR227" s="14" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="AS227" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT227" s="14" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AU227" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G228" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H228" s="14" t="inlineStr"/>
+      <c r="I228" s="14" t="inlineStr"/>
+      <c r="J228" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K228" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L228" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" s="14" t="inlineStr"/>
+      <c r="N228" s="14" t="inlineStr"/>
+      <c r="O228" s="14" t="inlineStr"/>
+      <c r="P228" s="14" t="inlineStr"/>
+      <c r="Q228" s="14" t="inlineStr"/>
+      <c r="R228" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S228" s="14" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T228" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="U228" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V228" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="W228" s="14" t="inlineStr"/>
+      <c r="X228" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y228" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z228" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA228" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB228" s="14" t="n">
+        <v>270.1</v>
+      </c>
+      <c r="AC228" s="14" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD228" s="14" t="n">
+        <v>263</v>
+      </c>
+      <c r="AE228" s="14" t="n">
+        <v>277</v>
+      </c>
+      <c r="AF228" s="14" t="n">
+        <v>256.595</v>
+      </c>
+      <c r="AG228" s="14" t="n">
+        <v>-10.25</v>
+      </c>
+      <c r="AH228" s="14" t="n">
+        <v>291.708</v>
+      </c>
+      <c r="AI228" s="14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AJ228" s="14" t="n">
+        <v>312.1275600000001</v>
+      </c>
+      <c r="AK228" s="14" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AL228" s="14" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AM228" s="14" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AN228" s="14" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="AO228" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP228" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ228" s="14" t="inlineStr"/>
+      <c r="AR228" s="14" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="AS228" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT228" s="14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AU228" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G229" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H229" s="14" t="inlineStr"/>
+      <c r="I229" s="14" t="inlineStr"/>
+      <c r="J229" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K229" s="14" t="inlineStr"/>
+      <c r="L229" s="14" t="inlineStr"/>
+      <c r="M229" s="14" t="inlineStr"/>
+      <c r="N229" s="14" t="inlineStr"/>
+      <c r="O229" s="14" t="inlineStr"/>
+      <c r="P229" s="14" t="inlineStr"/>
+      <c r="Q229" s="14" t="inlineStr"/>
+      <c r="R229" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank #8 · Conf 72% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S229" s="14" t="inlineStr"/>
+      <c r="T229" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="U229" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V229" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="W229" s="14" t="inlineStr"/>
+      <c r="X229" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y229" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z229" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA229" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB229" s="14" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="AC229" s="14" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD229" s="14" t="n">
+        <v>276</v>
+      </c>
+      <c r="AE229" s="14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF229" s="14" t="n">
+        <v>268.47</v>
+      </c>
+      <c r="AG229" s="14" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AH229" s="14" t="n">
+        <v>283</v>
+      </c>
+      <c r="AI229" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AJ229" s="14" t="n">
+        <v>302.81</v>
+      </c>
+      <c r="AK229" s="14" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="AL229" s="14" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AM229" s="14" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="AN229" s="14" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AO229" s="14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP229" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ229" s="14" t="inlineStr"/>
+      <c r="AR229" s="14" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS229" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT229" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AU229" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G230" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H230" s="16" t="inlineStr"/>
+      <c r="I230" s="16" t="inlineStr"/>
+      <c r="J230" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K230" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L230" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M230" s="16" t="inlineStr"/>
+      <c r="N230" s="16" t="inlineStr"/>
+      <c r="O230" s="16" t="inlineStr"/>
+      <c r="P230" s="16" t="inlineStr"/>
+      <c r="Q230" s="16" t="inlineStr"/>
+      <c r="R230" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S230" s="16" t="inlineStr"/>
+      <c r="T230" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="U230" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V230" s="16" t="n">
+        <v>53</v>
+      </c>
+      <c r="W230" s="16" t="inlineStr"/>
+      <c r="X230" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y230" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z230" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA230" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB230" s="16" t="n">
+        <v>522.2</v>
+      </c>
+      <c r="AC230" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD230" s="16" t="n">
+        <v>506</v>
+      </c>
+      <c r="AE230" s="16" t="n">
+        <v>538</v>
+      </c>
+      <c r="AF230" s="16" t="n">
+        <v>496.09</v>
+      </c>
+      <c r="AG230" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH230" s="16" t="n">
+        <v>563.9760000000001</v>
+      </c>
+      <c r="AI230" s="16" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AJ230" s="16" t="n">
+        <v>603.4543200000002</v>
+      </c>
+      <c r="AK230" s="16" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="AL230" s="16" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AM230" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN230" s="16" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AO230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ230" s="16" t="inlineStr"/>
+      <c r="AR230" s="16" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AS230" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT230" s="16" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AU230" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr"/>
+      <c r="G231" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H231" s="16" t="inlineStr"/>
+      <c r="I231" s="16" t="inlineStr"/>
+      <c r="J231" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K231" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L231" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" s="16" t="inlineStr"/>
+      <c r="N231" s="16" t="inlineStr"/>
+      <c r="O231" s="16" t="inlineStr"/>
+      <c r="P231" s="16" t="inlineStr"/>
+      <c r="Q231" s="16" t="inlineStr"/>
+      <c r="R231" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 9→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S231" s="16" t="inlineStr"/>
+      <c r="T231" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U231" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V231" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="W231" s="16" t="inlineStr"/>
+      <c r="X231" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y231" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z231" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA231" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB231" s="16" t="n">
+        <v>5623.5</v>
+      </c>
+      <c r="AC231" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD231" s="16" t="n">
+        <v>5477</v>
+      </c>
+      <c r="AE231" s="16" t="n">
+        <v>5770</v>
+      </c>
+      <c r="AF231" s="16" t="n">
+        <v>5342.325</v>
+      </c>
+      <c r="AG231" s="16" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AH231" s="16" t="n">
+        <v>6073.38</v>
+      </c>
+      <c r="AI231" s="16" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AJ231" s="16" t="n">
+        <v>6498.516600000001</v>
+      </c>
+      <c r="AK231" s="16" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AL231" s="16" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AM231" s="16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AN231" s="16" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AO231" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP231" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ231" s="16" t="inlineStr"/>
+      <c r="AR231" s="16" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS231" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT231" s="16" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AU231" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G232" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H232" s="14" t="inlineStr"/>
+      <c r="I232" s="14" t="inlineStr"/>
+      <c r="J232" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="K232" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L232" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" s="14" t="inlineStr"/>
+      <c r="N232" s="14" t="inlineStr"/>
+      <c r="O232" s="14" t="inlineStr"/>
+      <c r="P232" s="14" t="inlineStr"/>
+      <c r="Q232" s="14" t="inlineStr"/>
+      <c r="R232" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.8%) · Rank ↓ 10→11 · Conf 66% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S232" s="14" t="inlineStr"/>
+      <c r="T232" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="U232" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V232" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="W232" s="14" t="inlineStr"/>
+      <c r="X232" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y232" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z232" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA232" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB232" s="14" t="n">
+        <v>411</v>
+      </c>
+      <c r="AC232" s="14" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD232" s="14" t="n">
+        <v>399</v>
+      </c>
+      <c r="AE232" s="14" t="n">
+        <v>423</v>
+      </c>
+      <c r="AF232" s="14" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="AG232" s="14" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="AH232" s="14" t="n">
+        <v>443.8800000000001</v>
+      </c>
+      <c r="AI232" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AJ232" s="14" t="n">
+        <v>474.9516000000001</v>
+      </c>
+      <c r="AK232" s="14" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AL232" s="14" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM232" s="14" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AN232" s="14" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AO232" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP232" s="14" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ232" s="14" t="inlineStr"/>
+      <c r="AR232" s="14" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="AS232" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT232" s="14" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AU232" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>ONGC_IND_20260811</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr"/>
+      <c r="G233" s="14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H233" s="14" t="inlineStr"/>
+      <c r="I233" s="14" t="inlineStr"/>
+      <c r="J233" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K233" s="14" t="inlineStr"/>
+      <c r="L233" s="14" t="inlineStr"/>
+      <c r="M233" s="14" t="inlineStr"/>
+      <c r="N233" s="14" t="inlineStr"/>
+      <c r="O233" s="14" t="inlineStr"/>
+      <c r="P233" s="14" t="inlineStr"/>
+      <c r="Q233" s="14" t="inlineStr"/>
+      <c r="R233" s="14" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.3%) · Rank #12 · Conf 66% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S233" s="14" t="inlineStr"/>
+      <c r="T233" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="U233" s="14" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V233" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="W233" s="14" t="inlineStr"/>
+      <c r="X233" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y233" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z233" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA233" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB233" s="14" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="AC233" s="14" t="n">
+        <v>239.8399963378906</v>
+      </c>
+      <c r="AD233" s="14" t="n">
+        <v>232</v>
+      </c>
+      <c r="AE233" s="14" t="n">
+        <v>248</v>
+      </c>
+      <c r="AF233" s="14" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="AG233" s="14" t="n">
+        <v>-5.02</v>
+      </c>
+      <c r="AH233" s="14" t="n">
+        <v>258.984</v>
+      </c>
+      <c r="AI233" s="14" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AJ233" s="14" t="n">
+        <v>277.1128800000001</v>
+      </c>
+      <c r="AK233" s="14" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AL233" s="14" t="n">
+        <v>238.85</v>
+      </c>
+      <c r="AM233" s="14" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN233" s="14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AO233" s="14" t="inlineStr"/>
+      <c r="AP233" s="14" t="inlineStr"/>
+      <c r="AQ233" s="14" t="inlineStr"/>
+      <c r="AR233" s="14" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="AS233" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT233" s="14" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AU233" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G234" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H234" s="16" t="inlineStr"/>
+      <c r="I234" s="16" t="inlineStr"/>
+      <c r="J234" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" s="16" t="inlineStr"/>
+      <c r="N234" s="16" t="inlineStr"/>
+      <c r="O234" s="16" t="inlineStr"/>
+      <c r="P234" s="16" t="inlineStr"/>
+      <c r="Q234" s="16" t="inlineStr"/>
+      <c r="R234" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S234" s="16" t="inlineStr"/>
+      <c r="T234" s="16" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="U234" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V234" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="W234" s="16" t="inlineStr"/>
+      <c r="X234" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y234" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z234" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA234" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB234" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AC234" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD234" s="16" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE234" s="16" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF234" s="16" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG234" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH234" s="16" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI234" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ234" s="16" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK234" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL234" s="16" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM234" s="16" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="AN234" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO234" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP234" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ234" s="16" t="inlineStr"/>
+      <c r="AR234" s="16" t="inlineStr"/>
+      <c r="AS234" s="16" t="inlineStr"/>
+      <c r="AT234" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU234" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
+      <c r="G235" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H235" s="16" t="inlineStr"/>
+      <c r="I235" s="16" t="inlineStr"/>
+      <c r="J235" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K235" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L235" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M235" s="16" t="inlineStr"/>
+      <c r="N235" s="16" t="inlineStr"/>
+      <c r="O235" s="16" t="inlineStr"/>
+      <c r="P235" s="16" t="inlineStr"/>
+      <c r="Q235" s="16" t="inlineStr"/>
+      <c r="R235" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S235" s="16" t="inlineStr"/>
+      <c r="T235" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U235" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V235" s="16" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="W235" s="16" t="inlineStr"/>
+      <c r="X235" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y235" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z235" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA235" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB235" s="16" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="AC235" s="16" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="AD235" s="16" t="n">
+        <v>438.92</v>
+      </c>
+      <c r="AE235" s="16" t="n">
+        <v>447.78</v>
+      </c>
+      <c r="AF235" s="16" t="n">
+        <v>421.1825</v>
+      </c>
+      <c r="AG235" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH235" s="16" t="n">
+        <v>478.818</v>
+      </c>
+      <c r="AI235" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ235" s="16" t="n">
+        <v>509.8525</v>
+      </c>
+      <c r="AK235" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL235" s="16" t="n">
+        <v>450.7</v>
+      </c>
+      <c r="AM235" s="16" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AN235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO235" s="16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AP235" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ235" s="16" t="inlineStr"/>
+      <c r="AR235" s="16" t="inlineStr"/>
+      <c r="AS235" s="16" t="inlineStr"/>
+      <c r="AT235" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU235" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>PNB_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Punjab Natl. Bank</t>
+        </is>
+      </c>
+      <c r="G236" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H236" s="16" t="inlineStr"/>
+      <c r="I236" s="16" t="inlineStr"/>
+      <c r="J236" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K236" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" s="16" t="inlineStr"/>
+      <c r="N236" s="16" t="inlineStr"/>
+      <c r="O236" s="16" t="inlineStr"/>
+      <c r="P236" s="16" t="inlineStr"/>
+      <c r="Q236" s="16" t="inlineStr"/>
+      <c r="R236" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S236" s="16" t="inlineStr"/>
+      <c r="T236" s="16" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="U236" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V236" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W236" s="16" t="inlineStr"/>
+      <c r="X236" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y236" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z236" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA236" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB236" s="16" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="AC236" s="16" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="AD236" s="16" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AE236" s="16" t="n">
+        <v>114.49</v>
+      </c>
+      <c r="AF236" s="16" t="n">
+        <v>107.692</v>
+      </c>
+      <c r="AG236" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH236" s="16" t="n">
+        <v>122.4288</v>
+      </c>
+      <c r="AI236" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ236" s="16" t="n">
+        <v>130.364</v>
+      </c>
+      <c r="AK236" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL236" s="16" t="n">
+        <v>114.81</v>
+      </c>
+      <c r="AM236" s="16" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="AN236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO236" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP236" s="16" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="AQ236" s="16" t="inlineStr"/>
+      <c r="AR236" s="16" t="inlineStr"/>
+      <c r="AS236" s="16" t="inlineStr"/>
+      <c r="AT236" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU236" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G237" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H237" s="16" t="inlineStr"/>
+      <c r="I237" s="16" t="inlineStr"/>
+      <c r="J237" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K237" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L237" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" s="16" t="inlineStr"/>
+      <c r="N237" s="16" t="inlineStr"/>
+      <c r="O237" s="16" t="inlineStr"/>
+      <c r="P237" s="16" t="inlineStr"/>
+      <c r="Q237" s="16" t="inlineStr"/>
+      <c r="R237" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S237" s="16" t="inlineStr"/>
+      <c r="T237" s="16" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U237" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V237" s="16" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W237" s="16" t="inlineStr"/>
+      <c r="X237" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y237" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z237" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA237" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB237" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AC237" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD237" s="16" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE237" s="16" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF237" s="16" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG237" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH237" s="16" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI237" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ237" s="16" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK237" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL237" s="16" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM237" s="16" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AN237" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO237" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP237" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ237" s="16" t="inlineStr"/>
+      <c r="AR237" s="16" t="inlineStr"/>
+      <c r="AS237" s="16" t="inlineStr"/>
+      <c r="AT237" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU237" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G238" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H238" s="16" t="inlineStr"/>
+      <c r="I238" s="16" t="inlineStr"/>
+      <c r="J238" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K238" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L238" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M238" s="16" t="inlineStr"/>
+      <c r="N238" s="16" t="inlineStr"/>
+      <c r="O238" s="16" t="inlineStr"/>
+      <c r="P238" s="16" t="inlineStr"/>
+      <c r="Q238" s="16" t="inlineStr"/>
+      <c r="R238" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S238" s="16" t="inlineStr"/>
+      <c r="T238" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U238" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V238" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W238" s="16" t="inlineStr"/>
+      <c r="X238" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y238" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z238" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA238" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB238" s="16" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AC238" s="16" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD238" s="16" t="n">
+        <v>280.07</v>
+      </c>
+      <c r="AE238" s="16" t="n">
+        <v>285.73</v>
+      </c>
+      <c r="AF238" s="16" t="n">
+        <v>268.7549999999999</v>
+      </c>
+      <c r="AG238" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH238" s="16" t="n">
+        <v>305.532</v>
+      </c>
+      <c r="AI238" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ238" s="16" t="n">
+        <v>325.3349999999999</v>
+      </c>
+      <c r="AK238" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL238" s="16" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="AM238" s="16" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="AN238" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO238" s="16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP238" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ238" s="16" t="inlineStr"/>
+      <c r="AR238" s="16" t="inlineStr"/>
+      <c r="AS238" s="16" t="inlineStr"/>
+      <c r="AT238" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU238" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc</t>
+        </is>
+      </c>
+      <c r="G239" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H239" s="16" t="inlineStr"/>
+      <c r="I239" s="16" t="inlineStr"/>
+      <c r="J239" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K239" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L239" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="16" t="inlineStr"/>
+      <c r="N239" s="16" t="inlineStr"/>
+      <c r="O239" s="16" t="inlineStr"/>
+      <c r="P239" s="16" t="inlineStr"/>
+      <c r="Q239" s="16" t="inlineStr"/>
+      <c r="R239" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S239" s="16" t="inlineStr"/>
+      <c r="T239" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U239" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V239" s="16" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="W239" s="16" t="inlineStr"/>
+      <c r="X239" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y239" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z239" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA239" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB239" s="16" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="AC239" s="16" t="n">
+        <v>552.4</v>
+      </c>
+      <c r="AD239" s="16" t="n">
+        <v>546.88</v>
+      </c>
+      <c r="AE239" s="16" t="n">
+        <v>557.92</v>
+      </c>
+      <c r="AF239" s="16" t="n">
+        <v>524.78</v>
+      </c>
+      <c r="AG239" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH239" s="16" t="n">
+        <v>596.592</v>
+      </c>
+      <c r="AI239" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ239" s="16" t="n">
+        <v>635.2599999999999</v>
+      </c>
+      <c r="AK239" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL239" s="16" t="n">
+        <v>603</v>
+      </c>
+      <c r="AM239" s="16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AN239" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO239" s="16" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="AP239" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ239" s="16" t="inlineStr"/>
+      <c r="AR239" s="16" t="inlineStr"/>
+      <c r="AS239" s="16" t="inlineStr"/>
+      <c r="AT239" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU239" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>BATAINDIA_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
+      <c r="G240" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H240" s="16" t="inlineStr"/>
+      <c r="I240" s="16" t="inlineStr"/>
+      <c r="J240" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K240" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L240" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" s="16" t="inlineStr"/>
+      <c r="N240" s="16" t="inlineStr"/>
+      <c r="O240" s="16" t="inlineStr"/>
+      <c r="P240" s="16" t="inlineStr"/>
+      <c r="Q240" s="16" t="inlineStr"/>
+      <c r="R240" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S240" s="16" t="inlineStr"/>
+      <c r="T240" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U240" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V240" s="16" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="W240" s="16" t="inlineStr"/>
+      <c r="X240" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y240" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z240" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA240" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB240" s="16" t="n">
+        <v>709</v>
+      </c>
+      <c r="AC240" s="16" t="n">
+        <v>709</v>
+      </c>
+      <c r="AD240" s="16" t="n">
+        <v>701.91</v>
+      </c>
+      <c r="AE240" s="16" t="n">
+        <v>716.09</v>
+      </c>
+      <c r="AF240" s="16" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="AG240" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH240" s="16" t="n">
+        <v>765.72</v>
+      </c>
+      <c r="AI240" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ240" s="16" t="n">
+        <v>815.3499999999999</v>
+      </c>
+      <c r="AK240" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL240" s="16" t="n">
+        <v>720.5</v>
+      </c>
+      <c r="AM240" s="16" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AN240" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO240" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP240" s="16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AQ240" s="16" t="inlineStr"/>
+      <c r="AR240" s="16" t="inlineStr"/>
+      <c r="AS240" s="16" t="inlineStr"/>
+      <c r="AT240" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU240" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>IEX_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr"/>
+      <c r="G241" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H241" s="16" t="inlineStr"/>
+      <c r="I241" s="16" t="inlineStr"/>
+      <c r="J241" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K241" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L241" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" s="16" t="inlineStr"/>
+      <c r="N241" s="16" t="inlineStr"/>
+      <c r="O241" s="16" t="inlineStr"/>
+      <c r="P241" s="16" t="inlineStr"/>
+      <c r="Q241" s="16" t="inlineStr"/>
+      <c r="R241" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 39% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S241" s="16" t="inlineStr"/>
+      <c r="T241" s="16" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U241" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V241" s="16" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="W241" s="16" t="inlineStr"/>
+      <c r="X241" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y241" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z241" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA241" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB241" s="16" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AC241" s="16" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="AD241" s="16" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="AE241" s="16" t="n">
+        <v>134.43</v>
+      </c>
+      <c r="AF241" s="16" t="n">
+        <v>126.445</v>
+      </c>
+      <c r="AG241" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH241" s="16" t="n">
+        <v>143.748</v>
+      </c>
+      <c r="AI241" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ241" s="16" t="n">
+        <v>153.065</v>
+      </c>
+      <c r="AK241" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL241" s="16" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="AM241" s="16" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AN241" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO241" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP241" s="16" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="AQ241" s="16" t="inlineStr"/>
+      <c r="AR241" s="16" t="inlineStr"/>
+      <c r="AS241" s="16" t="inlineStr"/>
+      <c r="AT241" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU241" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr"/>
+      <c r="G242" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H242" s="16" t="inlineStr"/>
+      <c r="I242" s="16" t="inlineStr"/>
+      <c r="J242" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K242" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L242" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" s="16" t="inlineStr"/>
+      <c r="N242" s="16" t="inlineStr"/>
+      <c r="O242" s="16" t="inlineStr"/>
+      <c r="P242" s="16" t="inlineStr"/>
+      <c r="Q242" s="16" t="inlineStr"/>
+      <c r="R242" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S242" s="16" t="inlineStr"/>
+      <c r="T242" s="16" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="U242" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V242" s="16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="W242" s="16" t="inlineStr"/>
+      <c r="X242" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y242" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z242" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA242" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB242" s="16" t="n">
+        <v>5322.4</v>
+      </c>
+      <c r="AC242" s="16" t="n">
+        <v>5322.4</v>
+      </c>
+      <c r="AD242" s="16" t="n">
+        <v>5269.18</v>
+      </c>
+      <c r="AE242" s="16" t="n">
+        <v>5375.62</v>
+      </c>
+      <c r="AF242" s="16" t="n">
+        <v>5056.28</v>
+      </c>
+      <c r="AG242" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH242" s="16" t="n">
+        <v>5748.192</v>
+      </c>
+      <c r="AI242" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ242" s="16" t="n">
+        <v>6120.759999999999</v>
+      </c>
+      <c r="AK242" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL242" s="16" t="n">
+        <v>5475</v>
+      </c>
+      <c r="AM242" s="16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AN242" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO242" s="16" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AP242" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ242" s="16" t="inlineStr"/>
+      <c r="AR242" s="16" t="inlineStr"/>
+      <c r="AS242" s="16" t="inlineStr"/>
+      <c r="AT242" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU242" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr"/>
+      <c r="G243" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H243" s="16" t="inlineStr"/>
+      <c r="I243" s="16" t="inlineStr"/>
+      <c r="J243" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K243" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L243" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" s="16" t="inlineStr"/>
+      <c r="N243" s="16" t="inlineStr"/>
+      <c r="O243" s="16" t="inlineStr"/>
+      <c r="P243" s="16" t="inlineStr"/>
+      <c r="Q243" s="16" t="inlineStr"/>
+      <c r="R243" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S243" s="16" t="inlineStr"/>
+      <c r="T243" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="U243" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V243" s="16" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W243" s="16" t="inlineStr"/>
+      <c r="X243" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y243" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z243" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA243" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB243" s="16" t="n">
+        <v>11127</v>
+      </c>
+      <c r="AC243" s="16" t="n">
+        <v>11127</v>
+      </c>
+      <c r="AD243" s="16" t="n">
+        <v>11015.73</v>
+      </c>
+      <c r="AE243" s="16" t="n">
+        <v>11238.27</v>
+      </c>
+      <c r="AF243" s="16" t="n">
+        <v>10570.65</v>
+      </c>
+      <c r="AG243" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH243" s="16" t="n">
+        <v>12017.16</v>
+      </c>
+      <c r="AI243" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ243" s="16" t="n">
+        <v>12796.05</v>
+      </c>
+      <c r="AK243" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL243" s="16" t="n">
+        <v>11456</v>
+      </c>
+      <c r="AM243" s="16" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AN243" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO243" s="16" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AP243" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ243" s="16" t="inlineStr"/>
+      <c r="AR243" s="16" t="inlineStr"/>
+      <c r="AS243" s="16" t="inlineStr"/>
+      <c r="AT243" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU243" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr"/>
+      <c r="G244" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H244" s="16" t="inlineStr"/>
+      <c r="I244" s="16" t="inlineStr"/>
+      <c r="J244" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K244" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L244" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" s="16" t="inlineStr"/>
+      <c r="N244" s="16" t="inlineStr"/>
+      <c r="O244" s="16" t="inlineStr"/>
+      <c r="P244" s="16" t="inlineStr"/>
+      <c r="Q244" s="16" t="inlineStr"/>
+      <c r="R244" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S244" s="16" t="inlineStr"/>
+      <c r="T244" s="16" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U244" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V244" s="16" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="W244" s="16" t="inlineStr"/>
+      <c r="X244" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y244" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z244" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA244" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB244" s="16" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="AC244" s="16" t="n">
+        <v>1360.5</v>
+      </c>
+      <c r="AD244" s="16" t="n">
+        <v>1346.89</v>
+      </c>
+      <c r="AE244" s="16" t="n">
+        <v>1374.11</v>
+      </c>
+      <c r="AF244" s="16" t="n">
+        <v>1292.475</v>
+      </c>
+      <c r="AG244" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH244" s="16" t="n">
+        <v>1469.34</v>
+      </c>
+      <c r="AI244" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ244" s="16" t="n">
+        <v>1564.575</v>
+      </c>
+      <c r="AK244" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL244" s="16" t="n">
+        <v>1372.4</v>
+      </c>
+      <c r="AM244" s="16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AN244" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO244" s="16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AP244" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ244" s="16" t="inlineStr"/>
+      <c r="AR244" s="16" t="inlineStr"/>
+      <c r="AS244" s="16" t="inlineStr"/>
+      <c r="AT244" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU244" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr"/>
+      <c r="G245" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H245" s="16" t="inlineStr"/>
+      <c r="I245" s="16" t="inlineStr"/>
+      <c r="J245" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K245" s="16" t="inlineStr"/>
+      <c r="L245" s="16" t="inlineStr"/>
+      <c r="M245" s="16" t="inlineStr"/>
+      <c r="N245" s="16" t="inlineStr"/>
+      <c r="O245" s="16" t="inlineStr"/>
+      <c r="P245" s="16" t="inlineStr"/>
+      <c r="Q245" s="16" t="inlineStr"/>
+      <c r="R245" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 41% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S245" s="16" t="inlineStr"/>
+      <c r="T245" s="16" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="U245" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V245" s="16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W245" s="16" t="inlineStr"/>
+      <c r="X245" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y245" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z245" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA245" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB245" s="16" t="n">
+        <v>377</v>
+      </c>
+      <c r="AC245" s="16" t="n">
+        <v>377</v>
+      </c>
+      <c r="AD245" s="16" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="AE245" s="16" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="AF245" s="16" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="AG245" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH245" s="16" t="n">
+        <v>407.16</v>
+      </c>
+      <c r="AI245" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ245" s="16" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="AK245" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL245" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="AM245" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN245" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO245" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP245" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ245" s="16" t="inlineStr"/>
+      <c r="AR245" s="16" t="inlineStr"/>
+      <c r="AS245" s="16" t="inlineStr"/>
+      <c r="AT245" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU245" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>LICI_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr"/>
+      <c r="G246" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H246" s="16" t="inlineStr"/>
+      <c r="I246" s="16" t="inlineStr"/>
+      <c r="J246" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K246" s="16" t="inlineStr"/>
+      <c r="L246" s="16" t="inlineStr"/>
+      <c r="M246" s="16" t="inlineStr"/>
+      <c r="N246" s="16" t="inlineStr"/>
+      <c r="O246" s="16" t="inlineStr"/>
+      <c r="P246" s="16" t="inlineStr"/>
+      <c r="Q246" s="16" t="inlineStr"/>
+      <c r="R246" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S246" s="16" t="inlineStr"/>
+      <c r="T246" s="16" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="U246" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V246" s="16" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W246" s="16" t="inlineStr"/>
+      <c r="X246" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y246" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z246" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA246" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB246" s="16" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AC246" s="16" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="AD246" s="16" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="AE246" s="16" t="n">
+        <v>395.21</v>
+      </c>
+      <c r="AF246" s="16" t="n">
+        <v>371.735</v>
+      </c>
+      <c r="AG246" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH246" s="16" t="n">
+        <v>422.604</v>
+      </c>
+      <c r="AI246" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ246" s="16" t="n">
+        <v>449.995</v>
+      </c>
+      <c r="AK246" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL246" s="16" t="n">
+        <v>394</v>
+      </c>
+      <c r="AM246" s="16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AN246" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO246" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP246" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ246" s="16" t="inlineStr"/>
+      <c r="AR246" s="16" t="inlineStr"/>
+      <c r="AS246" s="16" t="inlineStr"/>
+      <c r="AT246" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU246" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>TIINDIA_IND_20260805</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr"/>
+      <c r="G247" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H247" s="16" t="inlineStr"/>
+      <c r="I247" s="16" t="inlineStr"/>
+      <c r="J247" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K247" s="16" t="inlineStr"/>
+      <c r="L247" s="16" t="inlineStr"/>
+      <c r="M247" s="16" t="inlineStr"/>
+      <c r="N247" s="16" t="inlineStr"/>
+      <c r="O247" s="16" t="inlineStr"/>
+      <c r="P247" s="16" t="inlineStr"/>
+      <c r="Q247" s="16" t="inlineStr"/>
+      <c r="R247" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S247" s="16" t="inlineStr"/>
+      <c r="T247" s="16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U247" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V247" s="16" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="W247" s="16" t="inlineStr"/>
+      <c r="X247" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y247" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z247" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA247" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB247" s="16" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AC247" s="16" t="n">
+        <v>2744.3</v>
+      </c>
+      <c r="AD247" s="16" t="n">
+        <v>2716.86</v>
+      </c>
+      <c r="AE247" s="16" t="n">
+        <v>2771.74</v>
+      </c>
+      <c r="AF247" s="16" t="n">
+        <v>2607.085</v>
+      </c>
+      <c r="AG247" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH247" s="16" t="n">
+        <v>2963.844000000001</v>
+      </c>
+      <c r="AI247" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ247" s="16" t="n">
+        <v>3155.945</v>
+      </c>
+      <c r="AK247" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL247" s="16" t="n">
+        <v>2772</v>
+      </c>
+      <c r="AM247" s="16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN247" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO247" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP247" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ247" s="16" t="inlineStr"/>
+      <c r="AR247" s="16" t="inlineStr"/>
+      <c r="AS247" s="16" t="inlineStr"/>
+      <c r="AT247" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU247" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
+      <c r="G248" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H248" s="16" t="inlineStr"/>
+      <c r="I248" s="16" t="inlineStr"/>
+      <c r="J248" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K248" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L248" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" s="16" t="inlineStr"/>
+      <c r="N248" s="16" t="inlineStr"/>
+      <c r="O248" s="16" t="inlineStr"/>
+      <c r="P248" s="16" t="inlineStr"/>
+      <c r="Q248" s="16" t="inlineStr"/>
+      <c r="R248" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 2→2 · Conf 83% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S248" s="16" t="inlineStr"/>
+      <c r="T248" s="16" t="n">
+        <v>83</v>
+      </c>
+      <c r="U248" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V248" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="W248" s="16" t="inlineStr"/>
+      <c r="X248" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y248" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z248" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA248" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB248" s="16" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AC248" s="16" t="n">
+        <v>1438.5</v>
+      </c>
+      <c r="AD248" s="16" t="n">
+        <v>1424.12</v>
+      </c>
+      <c r="AE248" s="16" t="n">
+        <v>1452.88</v>
+      </c>
+      <c r="AF248" s="16" t="n">
+        <v>1366.575</v>
+      </c>
+      <c r="AG248" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH248" s="16" t="n">
+        <v>1553.58</v>
+      </c>
+      <c r="AI248" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ248" s="16" t="n">
+        <v>1654.275</v>
+      </c>
+      <c r="AK248" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL248" s="16" t="n">
+        <v>1421</v>
+      </c>
+      <c r="AM248" s="16" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AN248" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO248" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP248" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ248" s="16" t="inlineStr"/>
+      <c r="AR248" s="16" t="inlineStr"/>
+      <c r="AS248" s="16" t="inlineStr"/>
+      <c r="AT248" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU248" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Sun Pharma</t>
+        </is>
+      </c>
+      <c r="G249" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H249" s="16" t="inlineStr"/>
+      <c r="I249" s="16" t="inlineStr"/>
+      <c r="J249" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K249" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M249" s="16" t="inlineStr"/>
+      <c r="N249" s="16" t="inlineStr"/>
+      <c r="O249" s="16" t="inlineStr"/>
+      <c r="P249" s="16" t="inlineStr"/>
+      <c r="Q249" s="16" t="inlineStr"/>
+      <c r="R249" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 90% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S249" s="16" t="inlineStr"/>
+      <c r="T249" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="U249" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V249" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="W249" s="16" t="inlineStr"/>
+      <c r="X249" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y249" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z249" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA249" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB249" s="16" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AC249" s="16" t="n">
+        <v>2014.8</v>
+      </c>
+      <c r="AD249" s="16" t="n">
+        <v>1994.65</v>
+      </c>
+      <c r="AE249" s="16" t="n">
+        <v>2034.95</v>
+      </c>
+      <c r="AF249" s="16" t="n">
+        <v>1914.06</v>
+      </c>
+      <c r="AG249" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH249" s="16" t="n">
+        <v>2175.984</v>
+      </c>
+      <c r="AI249" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ249" s="16" t="n">
+        <v>2317.02</v>
+      </c>
+      <c r="AK249" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL249" s="16" t="n">
+        <v>1949</v>
+      </c>
+      <c r="AM249" s="16" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AN249" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO249" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP249" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ249" s="16" t="inlineStr"/>
+      <c r="AR249" s="16" t="inlineStr"/>
+      <c r="AS249" s="16" t="inlineStr"/>
+      <c r="AT249" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU249" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
+      <c r="G250" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H250" s="16" t="inlineStr"/>
+      <c r="I250" s="16" t="inlineStr"/>
+      <c r="J250" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K250" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L250" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="16" t="inlineStr"/>
+      <c r="N250" s="16" t="inlineStr"/>
+      <c r="O250" s="16" t="inlineStr"/>
+      <c r="P250" s="16" t="inlineStr"/>
+      <c r="Q250" s="16" t="inlineStr"/>
+      <c r="R250" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S250" s="16" t="inlineStr"/>
+      <c r="T250" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="U250" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V250" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="W250" s="16" t="inlineStr"/>
+      <c r="X250" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y250" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z250" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA250" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB250" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AC250" s="16" t="n">
+        <v>2417</v>
+      </c>
+      <c r="AD250" s="16" t="n">
+        <v>2392.83</v>
+      </c>
+      <c r="AE250" s="16" t="n">
+        <v>2441.17</v>
+      </c>
+      <c r="AF250" s="16" t="n">
+        <v>2296.15</v>
+      </c>
+      <c r="AG250" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH250" s="16" t="n">
+        <v>2610.36</v>
+      </c>
+      <c r="AI250" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ250" s="16" t="n">
+        <v>2779.55</v>
+      </c>
+      <c r="AK250" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL250" s="16" t="n">
+        <v>2363.5</v>
+      </c>
+      <c r="AM250" s="16" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="AN250" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO250" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AP250" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ250" s="16" t="inlineStr"/>
+      <c r="AR250" s="16" t="inlineStr"/>
+      <c r="AS250" s="16" t="inlineStr"/>
+      <c r="AT250" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU250" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Pidilite</t>
+        </is>
+      </c>
+      <c r="G251" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H251" s="16" t="inlineStr"/>
+      <c r="I251" s="16" t="inlineStr"/>
+      <c r="J251" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K251" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L251" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" s="16" t="inlineStr"/>
+      <c r="N251" s="16" t="inlineStr"/>
+      <c r="O251" s="16" t="inlineStr"/>
+      <c r="P251" s="16" t="inlineStr"/>
+      <c r="Q251" s="16" t="inlineStr"/>
+      <c r="R251" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S251" s="16" t="inlineStr"/>
+      <c r="T251" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="U251" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V251" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="W251" s="16" t="inlineStr"/>
+      <c r="X251" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y251" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z251" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA251" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB251" s="16" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AC251" s="16" t="n">
+        <v>1625.5</v>
+      </c>
+      <c r="AD251" s="16" t="n">
+        <v>1609.24</v>
+      </c>
+      <c r="AE251" s="16" t="n">
+        <v>1641.76</v>
+      </c>
+      <c r="AF251" s="16" t="n">
+        <v>1544.225</v>
+      </c>
+      <c r="AG251" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH251" s="16" t="n">
+        <v>1755.54</v>
+      </c>
+      <c r="AI251" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ251" s="16" t="n">
+        <v>1869.325</v>
+      </c>
+      <c r="AK251" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL251" s="16" t="n">
+        <v>1657</v>
+      </c>
+      <c r="AM251" s="16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN251" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO251" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP251" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ251" s="16" t="inlineStr"/>
+      <c r="AR251" s="16" t="inlineStr"/>
+      <c r="AS251" s="16" t="inlineStr"/>
+      <c r="AT251" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU251" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>NTPC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="G252" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H252" s="16" t="inlineStr"/>
+      <c r="I252" s="16" t="inlineStr"/>
+      <c r="J252" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K252" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L252" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" s="16" t="inlineStr"/>
+      <c r="N252" s="16" t="inlineStr"/>
+      <c r="O252" s="16" t="inlineStr"/>
+      <c r="P252" s="16" t="inlineStr"/>
+      <c r="Q252" s="16" t="inlineStr"/>
+      <c r="R252" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 72% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S252" s="16" t="inlineStr"/>
+      <c r="T252" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="U252" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V252" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="W252" s="16" t="inlineStr"/>
+      <c r="X252" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y252" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z252" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA252" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB252" s="16" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AC252" s="16" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="AD252" s="16" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="AE252" s="16" t="n">
+        <v>349.21</v>
+      </c>
+      <c r="AF252" s="16" t="n">
+        <v>328.4625</v>
+      </c>
+      <c r="AG252" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH252" s="16" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="AI252" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ252" s="16" t="n">
+        <v>397.6125</v>
+      </c>
+      <c r="AK252" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL252" s="16" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="AM252" s="16" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AN252" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO252" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP252" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ252" s="16" t="inlineStr"/>
+      <c r="AR252" s="16" t="inlineStr"/>
+      <c r="AS252" s="16" t="inlineStr"/>
+      <c r="AT252" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU252" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
+      <c r="G253" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H253" s="16" t="inlineStr"/>
+      <c r="I253" s="16" t="inlineStr"/>
+      <c r="J253" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K253" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L253" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" s="16" t="inlineStr"/>
+      <c r="N253" s="16" t="inlineStr"/>
+      <c r="O253" s="16" t="inlineStr"/>
+      <c r="P253" s="16" t="inlineStr"/>
+      <c r="Q253" s="16" t="inlineStr"/>
+      <c r="R253" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S253" s="16" t="inlineStr"/>
+      <c r="T253" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="U253" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V253" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="W253" s="16" t="inlineStr"/>
+      <c r="X253" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y253" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z253" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA253" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB253" s="16" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AC253" s="16" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="AD253" s="16" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="AE253" s="16" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="AF253" s="16" t="n">
+        <v>369.835</v>
+      </c>
+      <c r="AG253" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH253" s="16" t="n">
+        <v>420.444</v>
+      </c>
+      <c r="AI253" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ253" s="16" t="n">
+        <v>447.695</v>
+      </c>
+      <c r="AK253" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL253" s="16" t="n">
+        <v>390.75</v>
+      </c>
+      <c r="AM253" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN253" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO253" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP253" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ253" s="16" t="inlineStr"/>
+      <c r="AR253" s="16" t="inlineStr"/>
+      <c r="AS253" s="16" t="inlineStr"/>
+      <c r="AT253" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU253" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Power Grid</t>
+        </is>
+      </c>
+      <c r="G254" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H254" s="16" t="inlineStr"/>
+      <c r="I254" s="16" t="inlineStr"/>
+      <c r="J254" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K254" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L254" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="16" t="inlineStr"/>
+      <c r="N254" s="16" t="inlineStr"/>
+      <c r="O254" s="16" t="inlineStr"/>
+      <c r="P254" s="16" t="inlineStr"/>
+      <c r="Q254" s="16" t="inlineStr"/>
+      <c r="R254" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 69% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S254" s="16" t="inlineStr"/>
+      <c r="T254" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="U254" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V254" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="W254" s="16" t="inlineStr"/>
+      <c r="X254" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y254" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z254" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA254" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB254" s="16" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AC254" s="16" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AD254" s="16" t="n">
+        <v>283.04</v>
+      </c>
+      <c r="AE254" s="16" t="n">
+        <v>288.76</v>
+      </c>
+      <c r="AF254" s="16" t="n">
+        <v>271.605</v>
+      </c>
+      <c r="AG254" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH254" s="16" t="n">
+        <v>308.772</v>
+      </c>
+      <c r="AI254" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ254" s="16" t="n">
+        <v>328.785</v>
+      </c>
+      <c r="AK254" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL254" s="16" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="AM254" s="16" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AN254" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO254" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP254" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ254" s="16" t="inlineStr"/>
+      <c r="AR254" s="16" t="inlineStr"/>
+      <c r="AS254" s="16" t="inlineStr"/>
+      <c r="AT254" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU254" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G255" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H255" s="16" t="inlineStr"/>
+      <c r="I255" s="16" t="inlineStr"/>
+      <c r="J255" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K255" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L255" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" s="16" t="inlineStr"/>
+      <c r="N255" s="16" t="inlineStr"/>
+      <c r="O255" s="16" t="inlineStr"/>
+      <c r="P255" s="16" t="inlineStr"/>
+      <c r="Q255" s="16" t="inlineStr"/>
+      <c r="R255" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S255" s="16" t="inlineStr"/>
+      <c r="T255" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="U255" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V255" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="W255" s="16" t="inlineStr"/>
+      <c r="X255" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y255" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z255" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA255" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB255" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AC255" s="16" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD255" s="16" t="n">
+        <v>489.41</v>
+      </c>
+      <c r="AE255" s="16" t="n">
+        <v>499.29</v>
+      </c>
+      <c r="AF255" s="16" t="n">
+        <v>469.6325</v>
+      </c>
+      <c r="AG255" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH255" s="16" t="n">
+        <v>533.898</v>
+      </c>
+      <c r="AI255" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ255" s="16" t="n">
+        <v>568.5024999999999</v>
+      </c>
+      <c r="AK255" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL255" s="16" t="n">
+        <v>519.95</v>
+      </c>
+      <c r="AM255" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN255" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO255" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP255" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ255" s="16" t="inlineStr"/>
+      <c r="AR255" s="16" t="inlineStr"/>
+      <c r="AS255" s="16" t="inlineStr"/>
+      <c r="AT255" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU255" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>BEL_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
+      <c r="G256" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H256" s="16" t="inlineStr"/>
+      <c r="I256" s="16" t="inlineStr"/>
+      <c r="J256" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K256" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L256" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="16" t="inlineStr"/>
+      <c r="N256" s="16" t="inlineStr"/>
+      <c r="O256" s="16" t="inlineStr"/>
+      <c r="P256" s="16" t="inlineStr"/>
+      <c r="Q256" s="16" t="inlineStr"/>
+      <c r="R256" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 8→8 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S256" s="16" t="inlineStr"/>
+      <c r="T256" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="U256" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V256" s="16" t="n">
+        <v>53</v>
+      </c>
+      <c r="W256" s="16" t="inlineStr"/>
+      <c r="X256" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y256" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z256" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA256" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB256" s="16" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AC256" s="16" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD256" s="16" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="AE256" s="16" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="AF256" s="16" t="n">
+        <v>369.265</v>
+      </c>
+      <c r="AG256" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH256" s="16" t="n">
+        <v>419.796</v>
+      </c>
+      <c r="AI256" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ256" s="16" t="n">
+        <v>447.0049999999999</v>
+      </c>
+      <c r="AK256" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL256" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="AM256" s="16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AN256" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO256" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP256" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ256" s="16" t="inlineStr"/>
+      <c r="AR256" s="16" t="inlineStr"/>
+      <c r="AS256" s="16" t="inlineStr"/>
+      <c r="AT256" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU256" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
+      <c r="G257" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H257" s="16" t="inlineStr"/>
+      <c r="I257" s="16" t="inlineStr"/>
+      <c r="J257" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K257" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L257" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" s="16" t="inlineStr"/>
+      <c r="N257" s="16" t="inlineStr"/>
+      <c r="O257" s="16" t="inlineStr"/>
+      <c r="P257" s="16" t="inlineStr"/>
+      <c r="Q257" s="16" t="inlineStr"/>
+      <c r="R257" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S257" s="16" t="inlineStr"/>
+      <c r="T257" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U257" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V257" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="W257" s="16" t="inlineStr"/>
+      <c r="X257" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y257" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z257" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA257" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB257" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AC257" s="16" t="n">
+        <v>411.3</v>
+      </c>
+      <c r="AD257" s="16" t="n">
+        <v>407.19</v>
+      </c>
+      <c r="AE257" s="16" t="n">
+        <v>415.41</v>
+      </c>
+      <c r="AF257" s="16" t="n">
+        <v>390.735</v>
+      </c>
+      <c r="AG257" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH257" s="16" t="n">
+        <v>444.2040000000001</v>
+      </c>
+      <c r="AI257" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ257" s="16" t="n">
+        <v>472.995</v>
+      </c>
+      <c r="AK257" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL257" s="16" t="n">
+        <v>415.25</v>
+      </c>
+      <c r="AM257" s="16" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AN257" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO257" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP257" s="16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AQ257" s="16" t="inlineStr"/>
+      <c r="AR257" s="16" t="inlineStr"/>
+      <c r="AS257" s="16" t="inlineStr"/>
+      <c r="AT257" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU257" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260801</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr"/>
+      <c r="G258" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H258" s="16" t="inlineStr"/>
+      <c r="I258" s="16" t="inlineStr"/>
+      <c r="J258" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="K258" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" s="16" t="inlineStr"/>
+      <c r="N258" s="16" t="inlineStr"/>
+      <c r="O258" s="16" t="inlineStr"/>
+      <c r="P258" s="16" t="inlineStr"/>
+      <c r="Q258" s="16" t="inlineStr"/>
+      <c r="R258" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S258" s="16" t="inlineStr"/>
+      <c r="T258" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="U258" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V258" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="W258" s="16" t="inlineStr"/>
+      <c r="X258" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y258" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z258" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA258" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AB258" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AC258" s="16" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD258" s="16" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="AE258" s="16" t="n">
+        <v>5460.06</v>
+      </c>
+      <c r="AF258" s="16" t="n">
+        <v>5135.7</v>
+      </c>
+      <c r="AG258" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH258" s="16" t="n">
+        <v>5838.48</v>
+      </c>
+      <c r="AI258" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ258" s="16" t="n">
+        <v>6216.9</v>
+      </c>
+      <c r="AK258" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL258" s="16" t="n">
+        <v>5510</v>
+      </c>
+      <c r="AM258" s="16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AN258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP258" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ258" s="16" t="inlineStr"/>
+      <c r="AR258" s="16" t="inlineStr"/>
+      <c r="AS258" s="16" t="inlineStr"/>
+      <c r="AT258" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU258" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260804</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="G259" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H259" s="16" t="inlineStr"/>
+      <c r="I259" s="16" t="inlineStr"/>
+      <c r="J259" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K259" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L259" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" s="16" t="inlineStr"/>
+      <c r="N259" s="16" t="inlineStr"/>
+      <c r="O259" s="16" t="inlineStr"/>
+      <c r="P259" s="16" t="inlineStr"/>
+      <c r="Q259" s="16" t="inlineStr"/>
+      <c r="R259" s="16" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S259" s="16" t="inlineStr"/>
+      <c r="T259" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="U259" s="16" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V259" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="W259" s="16" t="inlineStr"/>
+      <c r="X259" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y259" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z259" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA259" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB259" s="16" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AC259" s="16" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AD259" s="16" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="AE259" s="16" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="AF259" s="16" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG259" s="16" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH259" s="16" t="n">
+        <v>412.128</v>
+      </c>
+      <c r="AI259" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ259" s="16" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="AK259" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL259" s="16" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="AM259" s="16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN259" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO259" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP259" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ259" s="16" t="inlineStr"/>
+      <c r="AR259" s="16" t="inlineStr"/>
+      <c r="AS259" s="16" t="inlineStr"/>
+      <c r="AT259" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU259" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AU217"/>
+  <autoFilter ref="A1:AU259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>